--- a/VALORIZADO FALTANTES.xlsx
+++ b/VALORIZADO FALTANTES.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1483" uniqueCount="486">
   <si>
     <t>Categoría</t>
   </si>
@@ -139,6 +139,9 @@
     <t>104677-1</t>
   </si>
   <si>
+    <t>1090-09000-01</t>
+  </si>
+  <si>
     <t>110-30-5-7300CM</t>
   </si>
   <si>
@@ -154,6 +157,9 @@
     <t>161-1039SBI/8929105</t>
   </si>
   <si>
+    <t>16-17769-000</t>
+  </si>
+  <si>
     <t>1673785C92/2001470/360002</t>
   </si>
   <si>
@@ -244,9 +250,6 @@
     <t>3892T4934/S5947/58400</t>
   </si>
   <si>
-    <t>4302265/4306650</t>
-  </si>
-  <si>
     <t>4302384/2385</t>
   </si>
   <si>
@@ -358,6 +361,9 @@
     <t>K1699</t>
   </si>
   <si>
+    <t>K1935</t>
+  </si>
+  <si>
     <t>K3366</t>
   </si>
   <si>
@@ -418,6 +424,9 @@
     <t>SPL250X-3X/DANA</t>
   </si>
   <si>
+    <t>U8877691</t>
+  </si>
+  <si>
     <t>VAD306.01.0047</t>
   </si>
   <si>
@@ -445,6 +454,9 @@
     <t>4301795</t>
   </si>
   <si>
+    <t>1229G4661/009013</t>
+  </si>
+  <si>
     <t>125437 ILLINOIS</t>
   </si>
   <si>
@@ -517,6 +529,9 @@
     <t>13653</t>
   </si>
   <si>
+    <t>328349</t>
+  </si>
+  <si>
     <t>4303603</t>
   </si>
   <si>
@@ -661,6 +676,9 @@
     <t>LF3620</t>
   </si>
   <si>
+    <t>4302092WAP</t>
+  </si>
+  <si>
     <t>2234H1438NAL</t>
   </si>
   <si>
@@ -697,6 +715,9 @@
     <t>ACE</t>
   </si>
   <si>
+    <t>FREIGHTLINER</t>
+  </si>
+  <si>
     <t>BEDIA</t>
   </si>
   <si>
@@ -871,6 +892,9 @@
     <t>KIT EMBRAGUE SIN BAL FORD AGRALE/CARGO</t>
   </si>
   <si>
+    <t>FAN CLUTCH  ENTRADA DE AIRE DEL</t>
+  </si>
+  <si>
     <t>TUBO CARDAN170 PARA ARME POR (CENTIMETR)</t>
   </si>
   <si>
@@ -886,6 +910,9 @@
     <t>RODAJA DT60</t>
   </si>
   <si>
+    <t>BUJE MUELLE DELANTERO HUECO M2 106 SYD</t>
+  </si>
+  <si>
     <t>PERA/SENSOR NIVEL REFRIG. EAGLE Y KW</t>
   </si>
   <si>
@@ -976,9 +1003,6 @@
     <t>PIÑON PIÑA 46160</t>
   </si>
   <si>
-    <t>PIÑA EJE CDIZO FR/FRO - TODAS</t>
-  </si>
-  <si>
     <t>PIÑON 3RA CDIZO 8709/8908 SELLADO</t>
   </si>
   <si>
@@ -1087,6 +1111,9 @@
     <t>KIT EMPAQUES VALVULA LATERAL 12515/608</t>
   </si>
   <si>
+    <t>KIT REPAR VÁLVULA LATERAL 14715/915/918"USA ORING NEGRO"</t>
+  </si>
+  <si>
     <t>TAPA CARCAZA BAJO CAJA 16E-318</t>
   </si>
   <si>
@@ -1147,6 +1174,9 @@
     <t>CRUCETA 6,417 (6"13/32 APROX)DADO 2362"</t>
   </si>
   <si>
+    <t>HINO KIT ESPACIADORES EJE DE TOMA</t>
+  </si>
+  <si>
     <t>CILINDRO AUXI CLUTCH M2106-112/CASCADIA</t>
   </si>
   <si>
@@ -1171,6 +1201,9 @@
     <t>PIÑÓN MONO TODAS 18 CAMBIOS</t>
   </si>
   <si>
+    <t>ARANDELA PLANETARIO RS 21-230/  15-180</t>
+  </si>
+  <si>
     <t>BALINERA CLUTCH DOBLE GRASERA</t>
   </si>
   <si>
@@ -1243,6 +1276,9 @@
     <t>ORING TUBO LUBRIC CACH A7471 K3331 K3341</t>
   </si>
   <si>
+    <t>SPLINDER 14600 LB BUJE PLAS 9,06" x 1,87</t>
+  </si>
+  <si>
     <t>ARANDELA EST.INT CDIZO  14/16918</t>
   </si>
   <si>
@@ -1381,6 +1417,9 @@
     <t>FILTRO DE ACEITE PARA FREIGHTLINER Y CASCADIA</t>
   </si>
   <si>
+    <t>PIÑON DEL MONO RTX 16710</t>
+  </si>
+  <si>
     <t>PLANETARIO ESCUALIZACION 46160</t>
   </si>
   <si>
@@ -1426,13 +1465,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 30/09/2025 09:57:11</t>
+    <t>Período: 31/10/2025 09:15:37</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 08/09/2025 09:57:30</t>
+    <t>Fecha y hora de generación: 21/10/2025 09:15:59</t>
   </si>
 </sst>
 </file>
@@ -1846,28 +1885,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L212"/>
+  <dimension ref="A1:L218"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1883,7 +1922,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1899,12 +1938,12 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="I7" s="5" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -1956,19 +1995,19 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D10" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="E10" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="F10" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="I10" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J10">
         <v>3</v>
@@ -1988,19 +2027,19 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D11" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="E11" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F11" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I11" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -2020,19 +2059,19 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D12" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="E12" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F12" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I12" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -2052,19 +2091,19 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D13" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="E13" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="F13" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="I13" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -2084,19 +2123,19 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D14" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="E14" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F14" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I14" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -2116,19 +2155,19 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D15" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E15" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F15" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I15" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -2148,19 +2187,19 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D16" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E16" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="F16" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="I16" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J16">
         <v>2</v>
@@ -2180,19 +2219,19 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D17" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E17" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="F17" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="I17" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2212,19 +2251,19 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D18" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E18" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F18" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I18" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2244,19 +2283,19 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D19" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="E19" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F19" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I19" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -2276,19 +2315,19 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D20" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="E20" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F20" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I20" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2308,19 +2347,19 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D21" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="E21" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F21" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I21" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2340,19 +2379,19 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D22" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="E22" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F22" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I22" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J22">
         <v>3</v>
@@ -2372,19 +2411,19 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D23" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="E23" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F23" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I23" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J23">
         <v>2</v>
@@ -2404,19 +2443,19 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D24" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="E24" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F24" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I24" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -2436,19 +2475,19 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D25" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="E25" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F25" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I25" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J25">
         <v>2</v>
@@ -2468,19 +2507,19 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D26" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="E26" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F26" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I26" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -2500,19 +2539,19 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D27" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="E27" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F27" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I27" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J27">
         <v>3</v>
@@ -2532,19 +2571,19 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D28" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="E28" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F28" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I28" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2564,19 +2603,19 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D29" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="E29" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F29" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I29" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2596,19 +2635,19 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D30" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E30" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F30" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I30" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J30">
         <v>2</v>
@@ -2628,19 +2667,19 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D31" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E31" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F31" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I31" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J31">
         <v>2</v>
@@ -2660,19 +2699,19 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D32" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="E32" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="F32" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="I32" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J32">
         <v>12</v>
@@ -2692,19 +2731,19 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D33" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="E33" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="F33" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="I33" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J33">
         <v>6</v>
@@ -2724,19 +2763,19 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D34" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="E34" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="F34" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="I34" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J34">
         <v>6</v>
@@ -2756,19 +2795,19 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D35" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="E35" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="F35" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="I35" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2788,19 +2827,19 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D36" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="E36" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F36" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I36" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2814,66 +2853,66 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D37" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="E37" t="s">
-        <v>458</v>
+        <v>229</v>
       </c>
       <c r="F37" t="s">
-        <v>458</v>
+        <v>229</v>
       </c>
       <c r="I37" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J37">
-        <v>123</v>
+        <v>1</v>
       </c>
       <c r="K37">
-        <v>1578.02</v>
+        <v>1585579.04</v>
       </c>
       <c r="L37">
-        <v>194096.46</v>
+        <v>1585579.04</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B38" t="s">
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D38" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="E38" t="s">
-        <v>225</v>
+        <v>471</v>
       </c>
       <c r="F38" t="s">
-        <v>225</v>
+        <v>471</v>
       </c>
       <c r="I38" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J38">
-        <v>4</v>
+        <v>123</v>
       </c>
       <c r="K38">
-        <v>16186.82</v>
+        <v>1578.02</v>
       </c>
       <c r="L38">
-        <v>64747.28</v>
+        <v>194096.46</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2884,28 +2923,28 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D39" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="E39" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F39" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="I39" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K39">
-        <v>151783.14</v>
+        <v>16186.82</v>
       </c>
       <c r="L39">
-        <v>151783.14</v>
+        <v>64747.28</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2916,65 +2955,65 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D40" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="E40" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="F40" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="I40" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J40">
         <v>1</v>
       </c>
       <c r="K40">
-        <v>133605.86</v>
+        <v>151783.14</v>
       </c>
       <c r="L40">
-        <v>133605.86</v>
+        <v>151783.14</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B41" t="s">
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="D41" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="E41" t="s">
-        <v>457</v>
+        <v>232</v>
       </c>
       <c r="F41" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="I41" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J41">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K41">
-        <v>10090.39</v>
+        <v>133605.86</v>
       </c>
       <c r="L41">
-        <v>121084.68</v>
+        <v>133605.86</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
@@ -2983,25 +3022,25 @@
         <v>227</v>
       </c>
       <c r="D42" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="E42" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="F42" t="s">
-        <v>459</v>
+        <v>227</v>
       </c>
       <c r="I42" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K42">
-        <v>294840.16</v>
+        <v>10090.39</v>
       </c>
       <c r="L42">
-        <v>294840.16</v>
+        <v>121084.68</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -3012,28 +3051,28 @@
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D43" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="E43" t="s">
-        <v>459</v>
+        <v>237</v>
       </c>
       <c r="F43" t="s">
-        <v>459</v>
+        <v>237</v>
       </c>
       <c r="I43" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J43">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K43">
-        <v>22300.22</v>
+        <v>55214.31</v>
       </c>
       <c r="L43">
-        <v>267602.64</v>
+        <v>55214.31</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -3044,28 +3083,28 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D44" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="E44" t="s">
-        <v>228</v>
+        <v>472</v>
       </c>
       <c r="F44" t="s">
-        <v>228</v>
+        <v>472</v>
       </c>
       <c r="I44" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K44">
-        <v>69469.2</v>
+        <v>273006.7</v>
       </c>
       <c r="L44">
-        <v>69469.2</v>
+        <v>546013.4</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -3076,28 +3115,28 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D45" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="E45" t="s">
-        <v>229</v>
+        <v>472</v>
       </c>
       <c r="F45" t="s">
-        <v>229</v>
+        <v>472</v>
       </c>
       <c r="I45" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J45">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K45">
-        <v>38542.45</v>
+        <v>22300.22</v>
       </c>
       <c r="L45">
-        <v>77084.89999999999</v>
+        <v>267602.64</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -3108,28 +3147,28 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="D46" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="E46" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F46" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I46" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K46">
-        <v>73169.58</v>
+        <v>69469.2</v>
       </c>
       <c r="L46">
-        <v>292678.32</v>
+        <v>69469.2</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -3140,28 +3179,28 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D47" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="E47" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F47" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="I47" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K47">
-        <v>57029.66</v>
+        <v>38542.45</v>
       </c>
       <c r="L47">
-        <v>57029.66</v>
+        <v>77084.89999999999</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -3172,28 +3211,28 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D48" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E48" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="F48" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="I48" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K48">
-        <v>124113.03</v>
+        <v>73169.58</v>
       </c>
       <c r="L48">
-        <v>620565.15</v>
+        <v>292678.32</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -3204,60 +3243,60 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D49" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="E49" t="s">
-        <v>459</v>
+        <v>235</v>
       </c>
       <c r="F49" t="s">
-        <v>459</v>
+        <v>235</v>
       </c>
       <c r="I49" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J49">
         <v>1</v>
       </c>
       <c r="K49">
-        <v>143954.72</v>
+        <v>57029.66</v>
       </c>
       <c r="L49">
-        <v>143954.72</v>
+        <v>57029.66</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D50" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="E50" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F50" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="I50" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K50">
-        <v>374186</v>
+        <v>124113.03</v>
       </c>
       <c r="L50">
-        <v>1122558</v>
+        <v>620565.15</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -3268,60 +3307,60 @@
         <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D51" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E51" t="s">
-        <v>232</v>
+        <v>472</v>
       </c>
       <c r="F51" t="s">
-        <v>232</v>
+        <v>472</v>
       </c>
       <c r="I51" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K51">
-        <v>451755.47</v>
+        <v>143954.72</v>
       </c>
       <c r="L51">
-        <v>903510.9399999999</v>
+        <v>143954.72</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B52" t="s">
         <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="D52" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="E52" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="F52" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="I52" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K52">
-        <v>297477.98</v>
+        <v>374186</v>
       </c>
       <c r="L52">
-        <v>297477.98</v>
+        <v>1122558</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -3332,28 +3371,28 @@
         <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="D53" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="E53" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="F53" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="I53" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K53">
-        <v>116675.06</v>
+        <v>451755.47</v>
       </c>
       <c r="L53">
-        <v>350025.18</v>
+        <v>903510.9399999999</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -3364,28 +3403,28 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D54" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="E54" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F54" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I54" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J54">
         <v>1</v>
       </c>
       <c r="K54">
-        <v>241521.59</v>
+        <v>297477.98</v>
       </c>
       <c r="L54">
-        <v>241521.59</v>
+        <v>297477.98</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3396,28 +3435,28 @@
         <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="D55" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="E55" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="F55" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="I55" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K55">
-        <v>123123.72</v>
+        <v>116675.06</v>
       </c>
       <c r="L55">
-        <v>246247.44</v>
+        <v>350025.18</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -3428,28 +3467,28 @@
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D56" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="E56" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F56" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I56" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K56">
-        <v>277740.62</v>
+        <v>241521.59</v>
       </c>
       <c r="L56">
-        <v>555481.24</v>
+        <v>241521.59</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -3460,28 +3499,28 @@
         <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D57" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="E57" t="s">
-        <v>457</v>
+        <v>224</v>
       </c>
       <c r="F57" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I57" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J57">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="K57">
-        <v>9923</v>
+        <v>123123.72</v>
       </c>
       <c r="L57">
-        <v>902993</v>
+        <v>246247.44</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3492,60 +3531,60 @@
         <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D58" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="E58" t="s">
-        <v>457</v>
+        <v>224</v>
       </c>
       <c r="F58" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I58" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J58">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="K58">
-        <v>5328.05</v>
+        <v>277740.62</v>
       </c>
       <c r="L58">
-        <v>149185.4</v>
+        <v>555481.24</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
         <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D59" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E59" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="F59" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="I59" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J59">
-        <v>6</v>
+        <v>91</v>
       </c>
       <c r="K59">
-        <v>12871.55</v>
+        <v>9923</v>
       </c>
       <c r="L59">
-        <v>77229.3</v>
+        <v>902993</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3556,92 +3595,92 @@
         <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D60" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="E60" t="s">
-        <v>237</v>
+        <v>470</v>
       </c>
       <c r="F60" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="I60" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J60">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="K60">
-        <v>11227.66</v>
+        <v>5328.05</v>
       </c>
       <c r="L60">
-        <v>718570.24</v>
+        <v>149185.4</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B61" t="s">
         <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D61" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="E61" t="s">
-        <v>237</v>
+        <v>470</v>
       </c>
       <c r="F61" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="I61" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J61">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K61">
-        <v>74410.03</v>
+        <v>12871.55</v>
       </c>
       <c r="L61">
-        <v>223230.09</v>
+        <v>77229.3</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
         <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="D62" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="E62" t="s">
-        <v>458</v>
+        <v>244</v>
       </c>
       <c r="F62" t="s">
-        <v>458</v>
+        <v>240</v>
       </c>
       <c r="I62" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J62">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="K62">
-        <v>52014.93</v>
+        <v>11227.66</v>
       </c>
       <c r="L62">
-        <v>104029.86</v>
+        <v>718570.24</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3652,60 +3691,60 @@
         <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="D63" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E63" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="F63" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="I63" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J63">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="K63">
-        <v>94380.39999999999</v>
+        <v>74410.03</v>
       </c>
       <c r="L63">
-        <v>1887608</v>
+        <v>223230.09</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B64" t="s">
         <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D64" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="E64" t="s">
-        <v>234</v>
+        <v>471</v>
       </c>
       <c r="F64" t="s">
-        <v>234</v>
+        <v>471</v>
       </c>
       <c r="I64" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J64">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K64">
-        <v>1157466.59</v>
+        <v>52014.93</v>
       </c>
       <c r="L64">
-        <v>5787332.95</v>
+        <v>104029.86</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3716,28 +3755,28 @@
         <v>69</v>
       </c>
       <c r="C65" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D65" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="E65" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F65" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I65" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J65">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K65">
-        <v>553925.89</v>
+        <v>94380.39999999999</v>
       </c>
       <c r="L65">
-        <v>553925.89</v>
+        <v>1887608</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3748,28 +3787,28 @@
         <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="D66" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="E66" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="F66" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="I66" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J66">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K66">
-        <v>456192.75</v>
+        <v>1157466.59</v>
       </c>
       <c r="L66">
-        <v>456192.75</v>
+        <v>5787332.95</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3780,60 +3819,60 @@
         <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="D67" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="E67" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="F67" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="I67" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J67">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K67">
-        <v>459216.59</v>
+        <v>553925.89</v>
       </c>
       <c r="L67">
-        <v>2296082.95</v>
+        <v>553925.89</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
         <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D68" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="E68" t="s">
-        <v>460</v>
+        <v>231</v>
       </c>
       <c r="F68" t="s">
-        <v>460</v>
+        <v>231</v>
       </c>
       <c r="I68" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K68">
-        <v>107611.43</v>
+        <v>456192.75</v>
       </c>
       <c r="L68">
-        <v>215222.86</v>
+        <v>456192.75</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3844,60 +3883,60 @@
         <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D69" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="E69" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F69" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="I69" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K69">
-        <v>162784.49</v>
+        <v>459216.59</v>
       </c>
       <c r="L69">
-        <v>651137.96</v>
+        <v>2296082.95</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B70" t="s">
         <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D70" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="E70" t="s">
-        <v>237</v>
+        <v>473</v>
       </c>
       <c r="F70" t="s">
-        <v>237</v>
+        <v>473</v>
       </c>
       <c r="I70" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K70">
-        <v>64596.41</v>
+        <v>107611.43</v>
       </c>
       <c r="L70">
-        <v>193789.23</v>
+        <v>215222.86</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3908,28 +3947,28 @@
         <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="D71" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E71" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="F71" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="I71" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J71">
         <v>4</v>
       </c>
       <c r="K71">
-        <v>520965.57</v>
+        <v>162784.49</v>
       </c>
       <c r="L71">
-        <v>2083862.28</v>
+        <v>651137.96</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3940,28 +3979,28 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="D72" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="E72" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="F72" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="I72" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J72">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K72">
-        <v>63606.11</v>
+        <v>64596.41</v>
       </c>
       <c r="L72">
-        <v>1017697.76</v>
+        <v>193789.23</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3972,28 +4011,28 @@
         <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D73" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E73" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="F73" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="I73" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J73">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K73">
-        <v>234957.18</v>
+        <v>520965.57</v>
       </c>
       <c r="L73">
-        <v>234957.18</v>
+        <v>2083862.28</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -4004,60 +4043,60 @@
         <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D74" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="E74" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F74" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I74" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J74">
         <v>1</v>
       </c>
       <c r="K74">
-        <v>561136.28</v>
+        <v>234957.18</v>
       </c>
       <c r="L74">
-        <v>561136.28</v>
+        <v>234957.18</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B75" t="s">
         <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D75" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="E75" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F75" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I75" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J75">
         <v>1</v>
       </c>
       <c r="K75">
-        <v>548933.98</v>
+        <v>561136.28</v>
       </c>
       <c r="L75">
-        <v>548933.98</v>
+        <v>561136.28</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -4068,28 +4107,28 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D76" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="E76" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F76" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I76" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K76">
-        <v>348438.94</v>
+        <v>548933.98</v>
       </c>
       <c r="L76">
-        <v>696877.88</v>
+        <v>548933.98</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -4100,28 +4139,28 @@
         <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D77" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="E77" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F77" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I77" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K77">
-        <v>176616.64</v>
+        <v>348438.94</v>
       </c>
       <c r="L77">
-        <v>176616.64</v>
+        <v>696877.88</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -4132,60 +4171,60 @@
         <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D78" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="E78" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F78" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I78" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K78">
-        <v>54474.6</v>
+        <v>176616.64</v>
       </c>
       <c r="L78">
-        <v>163423.8</v>
+        <v>176616.64</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B79" t="s">
         <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D79" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="E79" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F79" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I79" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K79">
-        <v>289538.6</v>
+        <v>54474.6</v>
       </c>
       <c r="L79">
-        <v>289538.6</v>
+        <v>163423.8</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -4196,28 +4235,28 @@
         <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D80" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="E80" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="F80" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="I80" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J80">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K80">
-        <v>106058.91</v>
+        <v>289538.6</v>
       </c>
       <c r="L80">
-        <v>530294.55</v>
+        <v>289538.6</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -4228,92 +4267,92 @@
         <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D81" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="E81" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="F81" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="I81" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J81">
         <v>5</v>
       </c>
       <c r="K81">
-        <v>24077.89</v>
+        <v>106058.91</v>
       </c>
       <c r="L81">
-        <v>120389.45</v>
+        <v>530294.55</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B82" t="s">
         <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D82" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="E82" t="s">
-        <v>458</v>
+        <v>236</v>
       </c>
       <c r="F82" t="s">
-        <v>458</v>
+        <v>236</v>
       </c>
       <c r="I82" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J82">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="K82">
-        <v>13504.82</v>
+        <v>24077.89</v>
       </c>
       <c r="L82">
-        <v>283601.22</v>
+        <v>120389.45</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B83" t="s">
         <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="D83" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E83" t="s">
-        <v>235</v>
+        <v>471</v>
       </c>
       <c r="F83" t="s">
-        <v>235</v>
+        <v>471</v>
       </c>
       <c r="I83" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J83">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K83">
-        <v>244653.18</v>
+        <v>13504.82</v>
       </c>
       <c r="L83">
-        <v>244653.18</v>
+        <v>283601.22</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -4324,60 +4363,60 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D84" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="E84" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F84" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="I84" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J84">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K84">
-        <v>116579.52</v>
+        <v>244653.18</v>
       </c>
       <c r="L84">
-        <v>466318.08</v>
+        <v>244653.18</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B85" t="s">
         <v>89</v>
       </c>
       <c r="C85" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="D85" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="E85" t="s">
-        <v>460</v>
+        <v>246</v>
       </c>
       <c r="F85" t="s">
-        <v>460</v>
+        <v>246</v>
       </c>
       <c r="I85" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J85">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K85">
-        <v>132950.29</v>
+        <v>116579.52</v>
       </c>
       <c r="L85">
-        <v>265900.58</v>
+        <v>466318.08</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4388,124 +4427,124 @@
         <v>90</v>
       </c>
       <c r="C86" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D86" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="E86" t="s">
-        <v>237</v>
+        <v>473</v>
       </c>
       <c r="F86" t="s">
-        <v>233</v>
+        <v>473</v>
       </c>
       <c r="I86" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J86">
         <v>2</v>
       </c>
       <c r="K86">
-        <v>130565.76</v>
+        <v>132950.29</v>
       </c>
       <c r="L86">
-        <v>261131.52</v>
+        <v>265900.58</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B87" t="s">
         <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="D87" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="E87" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="F87" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="I87" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J87">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K87">
-        <v>32532.84</v>
+        <v>130565.76</v>
       </c>
       <c r="L87">
-        <v>325328.4</v>
+        <v>261131.52</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
         <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="D88" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="E88" t="s">
-        <v>457</v>
+        <v>236</v>
       </c>
       <c r="F88" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="I88" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J88">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K88">
-        <v>36184.1</v>
+        <v>32532.84</v>
       </c>
       <c r="L88">
-        <v>289472.8</v>
+        <v>325328.4</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B89" t="s">
         <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="D89" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="E89" t="s">
-        <v>240</v>
+        <v>470</v>
       </c>
       <c r="F89" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="I89" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J89">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K89">
-        <v>202984.86</v>
+        <v>36184.1</v>
       </c>
       <c r="L89">
-        <v>202984.86</v>
+        <v>289472.8</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4516,60 +4555,60 @@
         <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D90" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="E90" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="F90" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="I90" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K90">
-        <v>98967.53</v>
+        <v>202984.86</v>
       </c>
       <c r="L90">
-        <v>197935.06</v>
+        <v>202984.86</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B91" t="s">
         <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D91" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="E91" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="F91" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="I91" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J91">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K91">
-        <v>140000</v>
+        <v>98967.53</v>
       </c>
       <c r="L91">
-        <v>560000</v>
+        <v>197935.06</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4580,28 +4619,28 @@
         <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="D92" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="E92" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F92" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="I92" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J92">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K92">
-        <v>60000</v>
+        <v>140000</v>
       </c>
       <c r="L92">
-        <v>480000</v>
+        <v>560000</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4612,60 +4651,60 @@
         <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="D93" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E93" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="F93" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="I93" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J93">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K93">
-        <v>183395.81</v>
+        <v>60000</v>
       </c>
       <c r="L93">
-        <v>366791.62</v>
+        <v>480000</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B94" t="s">
         <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="D94" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="E94" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="F94" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="I94" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K94">
-        <v>561283.11</v>
+        <v>183395.81</v>
       </c>
       <c r="L94">
-        <v>561283.11</v>
+        <v>366791.62</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4676,28 +4715,28 @@
         <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D95" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="E95" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F95" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="I95" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K95">
-        <v>400703.47</v>
+        <v>561283.11</v>
       </c>
       <c r="L95">
-        <v>801406.9399999999</v>
+        <v>561283.11</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4708,28 +4747,28 @@
         <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D96" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="E96" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F96" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I96" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J96">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="K96">
-        <v>62347.32</v>
+        <v>400703.47</v>
       </c>
       <c r="L96">
-        <v>1309293.72</v>
+        <v>801406.9399999999</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4740,28 +4779,28 @@
         <v>101</v>
       </c>
       <c r="C97" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D97" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="E97" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="F97" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="I97" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J97">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K97">
-        <v>339984.3</v>
+        <v>62347.32</v>
       </c>
       <c r="L97">
-        <v>339984.3</v>
+        <v>1309293.72</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4772,124 +4811,124 @@
         <v>102</v>
       </c>
       <c r="C98" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D98" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="E98" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F98" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I98" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K98">
-        <v>212047.99</v>
+        <v>339984.3</v>
       </c>
       <c r="L98">
-        <v>636143.97</v>
+        <v>339984.3</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B99" t="s">
         <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D99" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="E99" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F99" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I99" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K99">
-        <v>116716.34</v>
+        <v>212047.99</v>
       </c>
       <c r="L99">
-        <v>116716.34</v>
+        <v>636143.97</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B100" t="s">
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="D100" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="E100" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="F100" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="I100" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J100">
         <v>1</v>
       </c>
       <c r="K100">
-        <v>147576.31</v>
+        <v>116716.34</v>
       </c>
       <c r="L100">
-        <v>147576.31</v>
+        <v>116716.34</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B101" t="s">
         <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="D101" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="E101" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="F101" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="I101" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K101">
-        <v>25956.31</v>
+        <v>147576.31</v>
       </c>
       <c r="L101">
-        <v>51912.62</v>
+        <v>147576.31</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -4900,92 +4939,92 @@
         <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="D102" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="E102" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="F102" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="I102" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J102">
         <v>2</v>
       </c>
       <c r="K102">
-        <v>207223.89</v>
+        <v>25956.31</v>
       </c>
       <c r="L102">
-        <v>414447.78</v>
+        <v>51912.62</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B103" t="s">
         <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D103" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="E103" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="F103" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="I103" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J103">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K103">
-        <v>52993.42</v>
+        <v>207223.89</v>
       </c>
       <c r="L103">
-        <v>688914.46</v>
+        <v>414447.78</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B104" t="s">
         <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="D104" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="E104" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F104" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="I104" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J104">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K104">
-        <v>365807.37</v>
+        <v>52993.42</v>
       </c>
       <c r="L104">
-        <v>1097422.11</v>
+        <v>688914.46</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -4996,60 +5035,60 @@
         <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="D105" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="E105" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F105" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="I105" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J105">
-        <v>276</v>
+        <v>3</v>
       </c>
       <c r="K105">
-        <v>910.4400000000001</v>
+        <v>365807.37</v>
       </c>
       <c r="L105">
-        <v>251281.44</v>
+        <v>1097422.11</v>
       </c>
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B106" t="s">
         <v>110</v>
       </c>
       <c r="C106" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="D106" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="E106" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="F106" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="I106" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J106">
-        <v>1</v>
+        <v>276</v>
       </c>
       <c r="K106">
-        <v>61252.9</v>
+        <v>910.4400000000001</v>
       </c>
       <c r="L106">
-        <v>61252.9</v>
+        <v>251281.44</v>
       </c>
     </row>
     <row r="107" spans="1:12">
@@ -5060,28 +5099,28 @@
         <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D107" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="E107" t="s">
-        <v>457</v>
+        <v>250</v>
       </c>
       <c r="F107" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="I107" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J107">
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="K107">
-        <v>12408.84</v>
+        <v>61252.9</v>
       </c>
       <c r="L107">
-        <v>1786872.96</v>
+        <v>61252.9</v>
       </c>
     </row>
     <row r="108" spans="1:12">
@@ -5092,28 +5131,28 @@
         <v>112</v>
       </c>
       <c r="C108" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D108" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="E108" t="s">
-        <v>237</v>
+        <v>470</v>
       </c>
       <c r="F108" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="I108" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J108">
-        <v>10</v>
+        <v>144</v>
       </c>
       <c r="K108">
-        <v>82259.44</v>
+        <v>12408.84</v>
       </c>
       <c r="L108">
-        <v>822594.4</v>
+        <v>1786872.96</v>
       </c>
     </row>
     <row r="109" spans="1:12">
@@ -5124,28 +5163,28 @@
         <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="D109" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E109" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="F109" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="I109" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J109">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K109">
-        <v>43930.6</v>
+        <v>82259.44</v>
       </c>
       <c r="L109">
-        <v>219653</v>
+        <v>822594.4</v>
       </c>
     </row>
     <row r="110" spans="1:12">
@@ -5156,156 +5195,156 @@
         <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D110" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E110" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F110" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I110" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J110">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K110">
-        <v>253717.21</v>
+        <v>43930.6</v>
       </c>
       <c r="L110">
-        <v>507434.42</v>
+        <v>219653</v>
       </c>
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B111" t="s">
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="D111" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="E111" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="F111" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="I111" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J111">
         <v>1</v>
       </c>
       <c r="K111">
-        <v>462132.13</v>
+        <v>78505.56</v>
       </c>
       <c r="L111">
-        <v>462132.13</v>
+        <v>78505.56</v>
       </c>
     </row>
     <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B112" t="s">
         <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="D112" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="E112" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="F112" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="I112" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K112">
-        <v>294400</v>
+        <v>253717.21</v>
       </c>
       <c r="L112">
-        <v>294400</v>
+        <v>507434.42</v>
       </c>
     </row>
     <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B113" t="s">
         <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="D113" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="E113" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="F113" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="I113" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K113">
-        <v>308720.23</v>
+        <v>462132.13</v>
       </c>
       <c r="L113">
-        <v>617440.46</v>
+        <v>462132.13</v>
       </c>
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B114" t="s">
         <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="D114" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="E114" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="F114" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="I114" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J114">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K114">
-        <v>130424.26</v>
+        <v>294400</v>
       </c>
       <c r="L114">
-        <v>521697.04</v>
+        <v>294400</v>
       </c>
     </row>
     <row r="115" spans="1:12">
@@ -5316,28 +5355,28 @@
         <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D115" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="E115" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="F115" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="I115" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K115">
-        <v>142359.27</v>
+        <v>308720.23</v>
       </c>
       <c r="L115">
-        <v>142359.27</v>
+        <v>617440.46</v>
       </c>
     </row>
     <row r="116" spans="1:12">
@@ -5348,28 +5387,28 @@
         <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="D116" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="E116" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="F116" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="I116" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J116">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K116">
-        <v>2373776.35</v>
+        <v>130424.26</v>
       </c>
       <c r="L116">
-        <v>2373776.35</v>
+        <v>521697.04</v>
       </c>
     </row>
     <row r="117" spans="1:12">
@@ -5380,60 +5419,60 @@
         <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D117" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="E117" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="F117" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="I117" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J117">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K117">
-        <v>153331.85</v>
+        <v>142359.27</v>
       </c>
       <c r="L117">
-        <v>459995.55</v>
+        <v>142359.27</v>
       </c>
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B118" t="s">
         <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D118" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="E118" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="F118" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="I118" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J118">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K118">
-        <v>151827.5</v>
+        <v>2373776.35</v>
       </c>
       <c r="L118">
-        <v>759137.5</v>
+        <v>2373776.35</v>
       </c>
     </row>
     <row r="119" spans="1:12">
@@ -5444,60 +5483,60 @@
         <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D119" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="E119" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="F119" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="I119" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J119">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K119">
-        <v>126875.69</v>
+        <v>153331.85</v>
       </c>
       <c r="L119">
-        <v>126875.69</v>
+        <v>459995.55</v>
       </c>
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B120" t="s">
         <v>124</v>
       </c>
       <c r="C120" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D120" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="E120" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="F120" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="I120" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J120">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K120">
-        <v>418397.52</v>
+        <v>151827.5</v>
       </c>
       <c r="L120">
-        <v>418397.52</v>
+        <v>759137.5</v>
       </c>
     </row>
     <row r="121" spans="1:12">
@@ -5508,28 +5547,28 @@
         <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="D121" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="E121" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F121" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="I121" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J121">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K121">
-        <v>60881.05</v>
+        <v>126875.69</v>
       </c>
       <c r="L121">
-        <v>730572.6</v>
+        <v>126875.69</v>
       </c>
     </row>
     <row r="122" spans="1:12">
@@ -5540,28 +5579,28 @@
         <v>126</v>
       </c>
       <c r="C122" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="D122" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="E122" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F122" t="s">
-        <v>461</v>
+        <v>236</v>
       </c>
       <c r="I122" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J122">
         <v>1</v>
       </c>
       <c r="K122">
-        <v>53403.02</v>
+        <v>418397.52</v>
       </c>
       <c r="L122">
-        <v>53403.02</v>
+        <v>418397.52</v>
       </c>
     </row>
     <row r="123" spans="1:12">
@@ -5572,28 +5611,28 @@
         <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D123" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="E123" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F123" t="s">
-        <v>461</v>
+        <v>231</v>
       </c>
       <c r="I123" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J123">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K123">
-        <v>80962.22</v>
+        <v>60881.05</v>
       </c>
       <c r="L123">
-        <v>404811.1</v>
+        <v>730572.6</v>
       </c>
     </row>
     <row r="124" spans="1:12">
@@ -5604,28 +5643,28 @@
         <v>128</v>
       </c>
       <c r="C124" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D124" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="E124" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F124" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="I124" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J124">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K124">
-        <v>30016.79</v>
+        <v>53403.02</v>
       </c>
       <c r="L124">
-        <v>90050.37</v>
+        <v>53403.02</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -5636,28 +5675,28 @@
         <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D125" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="E125" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F125" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="I125" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J125">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K125">
-        <v>55960.12</v>
+        <v>80962.22</v>
       </c>
       <c r="L125">
-        <v>111920.24</v>
+        <v>404811.1</v>
       </c>
     </row>
     <row r="126" spans="1:12">
@@ -5668,28 +5707,28 @@
         <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D126" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="E126" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F126" t="s">
-        <v>225</v>
+        <v>474</v>
       </c>
       <c r="I126" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J126">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K126">
-        <v>57770.2</v>
+        <v>30016.79</v>
       </c>
       <c r="L126">
-        <v>57770.2</v>
+        <v>90050.37</v>
       </c>
     </row>
     <row r="127" spans="1:12">
@@ -5700,188 +5739,188 @@
         <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D127" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E127" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F127" t="s">
-        <v>225</v>
+        <v>474</v>
       </c>
       <c r="I127" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J127">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K127">
-        <v>122224.03</v>
+        <v>55960.12</v>
       </c>
       <c r="L127">
-        <v>488896.12</v>
+        <v>111920.24</v>
       </c>
     </row>
     <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B128" t="s">
         <v>132</v>
       </c>
       <c r="C128" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="D128" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="E128" t="s">
-        <v>458</v>
+        <v>231</v>
       </c>
       <c r="F128" t="s">
-        <v>458</v>
+        <v>231</v>
       </c>
       <c r="I128" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K128">
-        <v>345599.99</v>
+        <v>57770.2</v>
       </c>
       <c r="L128">
-        <v>691199.98</v>
+        <v>57770.2</v>
       </c>
     </row>
     <row r="129" spans="1:12">
       <c r="A129" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B129" t="s">
         <v>133</v>
       </c>
       <c r="C129" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="D129" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="E129" t="s">
-        <v>458</v>
+        <v>231</v>
       </c>
       <c r="F129" t="s">
-        <v>458</v>
+        <v>231</v>
       </c>
       <c r="I129" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J129">
         <v>4</v>
       </c>
       <c r="K129">
-        <v>406977.4</v>
+        <v>122224.03</v>
       </c>
       <c r="L129">
-        <v>1627909.6</v>
+        <v>488896.12</v>
       </c>
     </row>
     <row r="130" spans="1:12">
       <c r="A130" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B130" t="s">
         <v>134</v>
       </c>
       <c r="C130" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="D130" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="E130" t="s">
-        <v>246</v>
+        <v>471</v>
       </c>
       <c r="F130" t="s">
-        <v>246</v>
+        <v>471</v>
       </c>
       <c r="I130" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K130">
-        <v>155407.11</v>
+        <v>345599.99</v>
       </c>
       <c r="L130">
-        <v>155407.11</v>
+        <v>691199.98</v>
       </c>
     </row>
     <row r="131" spans="1:12">
       <c r="A131" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B131" t="s">
         <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="D131" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="E131" t="s">
-        <v>247</v>
+        <v>471</v>
       </c>
       <c r="F131" t="s">
-        <v>247</v>
+        <v>471</v>
       </c>
       <c r="I131" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J131">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K131">
-        <v>302306.98</v>
+        <v>406977.4</v>
       </c>
       <c r="L131">
-        <v>604613.96</v>
+        <v>1627909.6</v>
       </c>
     </row>
     <row r="132" spans="1:12">
       <c r="A132" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B132" t="s">
         <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="D132" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="E132" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="F132" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="I132" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J132">
         <v>1</v>
       </c>
       <c r="K132">
-        <v>462946.56</v>
+        <v>108921.66</v>
       </c>
       <c r="L132">
-        <v>462946.56</v>
+        <v>108921.66</v>
       </c>
     </row>
     <row r="133" spans="1:12">
@@ -5892,28 +5931,28 @@
         <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="D133" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="E133" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="F133" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="I133" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J133">
         <v>1</v>
       </c>
       <c r="K133">
-        <v>622170.75</v>
+        <v>155407.11</v>
       </c>
       <c r="L133">
-        <v>622170.75</v>
+        <v>155407.11</v>
       </c>
     </row>
     <row r="134" spans="1:12">
@@ -5924,28 +5963,28 @@
         <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="D134" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="E134" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="F134" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="I134" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J134">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K134">
-        <v>7246.46</v>
+        <v>302306.98</v>
       </c>
       <c r="L134">
-        <v>65218.14</v>
+        <v>604613.96</v>
       </c>
     </row>
     <row r="135" spans="1:12">
@@ -5956,60 +5995,60 @@
         <v>139</v>
       </c>
       <c r="C135" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="D135" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="E135" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="F135" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="I135" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J135">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K135">
-        <v>9200.629999999999</v>
+        <v>462946.56</v>
       </c>
       <c r="L135">
-        <v>202413.86</v>
+        <v>462946.56</v>
       </c>
     </row>
     <row r="136" spans="1:12">
       <c r="A136" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B136" t="s">
         <v>140</v>
       </c>
       <c r="C136" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="D136" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="E136" t="s">
-        <v>458</v>
+        <v>254</v>
       </c>
       <c r="F136" t="s">
-        <v>458</v>
+        <v>254</v>
       </c>
       <c r="I136" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J136">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K136">
-        <v>13906.96</v>
+        <v>622170.75</v>
       </c>
       <c r="L136">
-        <v>83441.75999999999</v>
+        <v>622170.75</v>
       </c>
     </row>
     <row r="137" spans="1:12">
@@ -6020,28 +6059,28 @@
         <v>141</v>
       </c>
       <c r="C137" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="D137" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="E137" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F137" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="I137" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J137">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K137">
-        <v>67728.10000000001</v>
+        <v>7246.46</v>
       </c>
       <c r="L137">
-        <v>677281</v>
+        <v>65218.14</v>
       </c>
     </row>
     <row r="138" spans="1:12">
@@ -6052,28 +6091,28 @@
         <v>142</v>
       </c>
       <c r="C138" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D138" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="E138" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F138" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I138" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J138">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="K138">
-        <v>541166.88</v>
+        <v>9200.629999999999</v>
       </c>
       <c r="L138">
-        <v>2164667.52</v>
+        <v>202413.86</v>
       </c>
     </row>
     <row r="139" spans="1:12">
@@ -6084,28 +6123,28 @@
         <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="D139" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="E139" t="s">
-        <v>256</v>
+        <v>471</v>
       </c>
       <c r="F139" t="s">
-        <v>256</v>
+        <v>471</v>
       </c>
       <c r="I139" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J139">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K139">
-        <v>107104.68</v>
+        <v>13906.96</v>
       </c>
       <c r="L139">
-        <v>214209.36</v>
+        <v>83441.75999999999</v>
       </c>
     </row>
     <row r="140" spans="1:12">
@@ -6116,28 +6155,28 @@
         <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="D140" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="E140" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F140" t="s">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="I140" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J140">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K140">
-        <v>221067.08</v>
+        <v>67728.10000000001</v>
       </c>
       <c r="L140">
-        <v>221067.08</v>
+        <v>677281</v>
       </c>
     </row>
     <row r="141" spans="1:12">
@@ -6148,92 +6187,92 @@
         <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D141" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="E141" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F141" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I141" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J141">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K141">
-        <v>204405.71</v>
+        <v>541166.88</v>
       </c>
       <c r="L141">
-        <v>204405.71</v>
+        <v>2164667.52</v>
       </c>
     </row>
     <row r="142" spans="1:12">
       <c r="A142" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B142" t="s">
         <v>146</v>
       </c>
       <c r="C142" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="D142" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="E142" t="s">
-        <v>458</v>
+        <v>231</v>
       </c>
       <c r="F142" t="s">
-        <v>458</v>
+        <v>231</v>
       </c>
       <c r="I142" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K142">
-        <v>151612.17</v>
+        <v>31630.01</v>
       </c>
       <c r="L142">
-        <v>151612.17</v>
+        <v>63260.02</v>
       </c>
     </row>
     <row r="143" spans="1:12">
       <c r="A143" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B143" t="s">
         <v>147</v>
       </c>
       <c r="C143" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="D143" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="E143" t="s">
-        <v>218</v>
+        <v>263</v>
       </c>
       <c r="F143" t="s">
-        <v>218</v>
+        <v>263</v>
       </c>
       <c r="I143" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J143">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K143">
-        <v>152565.53</v>
+        <v>107104.68</v>
       </c>
       <c r="L143">
-        <v>762827.65</v>
+        <v>214209.36</v>
       </c>
     </row>
     <row r="144" spans="1:12">
@@ -6244,28 +6283,28 @@
         <v>148</v>
       </c>
       <c r="C144" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D144" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="E144" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F144" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I144" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J144">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K144">
-        <v>648344.71</v>
+        <v>221067.08</v>
       </c>
       <c r="L144">
-        <v>1945034.13</v>
+        <v>221067.08</v>
       </c>
     </row>
     <row r="145" spans="1:12">
@@ -6276,92 +6315,92 @@
         <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D145" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="E145" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F145" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I145" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J145">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K145">
-        <v>61274.69</v>
+        <v>204405.71</v>
       </c>
       <c r="L145">
-        <v>245098.76</v>
+        <v>204405.71</v>
       </c>
     </row>
     <row r="146" spans="1:12">
       <c r="A146" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B146" t="s">
         <v>150</v>
       </c>
       <c r="C146" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D146" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="E146" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="F146" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="I146" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J146">
         <v>1</v>
       </c>
       <c r="K146">
-        <v>134461.16</v>
+        <v>151612.17</v>
       </c>
       <c r="L146">
-        <v>134461.16</v>
+        <v>151612.17</v>
       </c>
     </row>
     <row r="147" spans="1:12">
       <c r="A147" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B147" t="s">
         <v>151</v>
       </c>
       <c r="C147" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D147" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="E147" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F147" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I147" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J147">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K147">
-        <v>150000</v>
+        <v>152565.53</v>
       </c>
       <c r="L147">
-        <v>150000</v>
+        <v>762827.65</v>
       </c>
     </row>
     <row r="148" spans="1:12">
@@ -6372,28 +6411,28 @@
         <v>152</v>
       </c>
       <c r="C148" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D148" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="E148" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F148" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I148" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J148">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K148">
-        <v>437278.29</v>
+        <v>648344.71</v>
       </c>
       <c r="L148">
-        <v>437278.29</v>
+        <v>1945034.13</v>
       </c>
     </row>
     <row r="149" spans="1:12">
@@ -6404,28 +6443,28 @@
         <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D149" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="E149" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="F149" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="I149" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J149">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K149">
-        <v>68988.75999999999</v>
+        <v>61274.69</v>
       </c>
       <c r="L149">
-        <v>689887.6</v>
+        <v>245098.76</v>
       </c>
     </row>
     <row r="150" spans="1:12">
@@ -6436,28 +6475,28 @@
         <v>154</v>
       </c>
       <c r="C150" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="D150" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="E150" t="s">
-        <v>218</v>
+        <v>472</v>
       </c>
       <c r="F150" t="s">
-        <v>218</v>
+        <v>472</v>
       </c>
       <c r="I150" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K150">
-        <v>321061.61</v>
+        <v>134461.16</v>
       </c>
       <c r="L150">
-        <v>642123.22</v>
+        <v>134461.16</v>
       </c>
     </row>
     <row r="151" spans="1:12">
@@ -6468,33 +6507,33 @@
         <v>155</v>
       </c>
       <c r="C151" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D151" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="E151" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F151" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I151" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J151">
         <v>1</v>
       </c>
       <c r="K151">
-        <v>86292.41</v>
+        <v>150000</v>
       </c>
       <c r="L151">
-        <v>86292.41</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="152" spans="1:12">
       <c r="A152" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B152" t="s">
         <v>156</v>
@@ -6503,25 +6542,25 @@
         <v>224</v>
       </c>
       <c r="D152" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="E152" t="s">
-        <v>458</v>
+        <v>224</v>
       </c>
       <c r="F152" t="s">
-        <v>458</v>
+        <v>224</v>
       </c>
       <c r="I152" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J152">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K152">
-        <v>275914.15</v>
+        <v>437278.29</v>
       </c>
       <c r="L152">
-        <v>827742.45</v>
+        <v>437278.29</v>
       </c>
     </row>
     <row r="153" spans="1:12">
@@ -6532,28 +6571,28 @@
         <v>157</v>
       </c>
       <c r="C153" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="D153" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="E153" t="s">
-        <v>460</v>
+        <v>224</v>
       </c>
       <c r="F153" t="s">
-        <v>460</v>
+        <v>224</v>
       </c>
       <c r="I153" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J153">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K153">
-        <v>145438.64</v>
+        <v>68988.75999999999</v>
       </c>
       <c r="L153">
-        <v>145438.64</v>
+        <v>689887.6</v>
       </c>
     </row>
     <row r="154" spans="1:12">
@@ -6564,28 +6603,28 @@
         <v>158</v>
       </c>
       <c r="C154" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D154" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="E154" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F154" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I154" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J154">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K154">
-        <v>124259.74</v>
+        <v>321061.61</v>
       </c>
       <c r="L154">
-        <v>1988155.84</v>
+        <v>642123.22</v>
       </c>
     </row>
     <row r="155" spans="1:12">
@@ -6596,92 +6635,92 @@
         <v>159</v>
       </c>
       <c r="C155" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D155" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="E155" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="F155" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="I155" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J155">
         <v>1</v>
       </c>
       <c r="K155">
-        <v>127385.01</v>
+        <v>86292.41</v>
       </c>
       <c r="L155">
-        <v>127385.01</v>
+        <v>86292.41</v>
       </c>
     </row>
     <row r="156" spans="1:12">
       <c r="A156" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B156" t="s">
         <v>160</v>
       </c>
       <c r="C156" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="D156" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="E156" t="s">
-        <v>218</v>
+        <v>471</v>
       </c>
       <c r="F156" t="s">
-        <v>218</v>
+        <v>471</v>
       </c>
       <c r="I156" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J156">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K156">
-        <v>409485.91</v>
+        <v>275914.15</v>
       </c>
       <c r="L156">
-        <v>818971.8199999999</v>
+        <v>827742.45</v>
       </c>
     </row>
     <row r="157" spans="1:12">
       <c r="A157" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B157" t="s">
         <v>161</v>
       </c>
       <c r="C157" t="s">
-        <v>218</v>
+        <v>257</v>
       </c>
       <c r="D157" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="E157" t="s">
-        <v>218</v>
+        <v>473</v>
       </c>
       <c r="F157" t="s">
-        <v>218</v>
+        <v>473</v>
       </c>
       <c r="I157" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J157">
         <v>1</v>
       </c>
       <c r="K157">
-        <v>411573.74</v>
+        <v>145438.64</v>
       </c>
       <c r="L157">
-        <v>411573.74</v>
+        <v>145438.64</v>
       </c>
     </row>
     <row r="158" spans="1:12">
@@ -6692,60 +6731,60 @@
         <v>162</v>
       </c>
       <c r="C158" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D158" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="E158" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F158" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I158" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J158">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K158">
-        <v>177929.28</v>
+        <v>124259.74</v>
       </c>
       <c r="L158">
-        <v>355858.56</v>
+        <v>1988155.84</v>
       </c>
     </row>
     <row r="159" spans="1:12">
       <c r="A159" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B159" t="s">
         <v>163</v>
       </c>
       <c r="C159" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="D159" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="E159" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="F159" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="I159" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J159">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K159">
-        <v>386975.07</v>
+        <v>127385.01</v>
       </c>
       <c r="L159">
-        <v>773950.14</v>
+        <v>127385.01</v>
       </c>
     </row>
     <row r="160" spans="1:12">
@@ -6756,92 +6795,92 @@
         <v>164</v>
       </c>
       <c r="C160" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D160" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="E160" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F160" t="s">
-        <v>461</v>
+        <v>224</v>
       </c>
       <c r="I160" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J160">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K160">
-        <v>66983.8</v>
+        <v>409485.91</v>
       </c>
       <c r="L160">
-        <v>267935.2</v>
+        <v>818971.8199999999</v>
       </c>
     </row>
     <row r="161" spans="1:12">
       <c r="A161" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B161" t="s">
         <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="D161" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="E161" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="F161" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="I161" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J161">
         <v>1</v>
       </c>
       <c r="K161">
-        <v>159709.51</v>
+        <v>411573.74</v>
       </c>
       <c r="L161">
-        <v>159709.51</v>
+        <v>411573.74</v>
       </c>
     </row>
     <row r="162" spans="1:12">
       <c r="A162" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B162" t="s">
         <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="D162" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="E162" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="F162" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="I162" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J162">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="K162">
-        <v>2473.41</v>
+        <v>177929.28</v>
       </c>
       <c r="L162">
-        <v>93989.58</v>
+        <v>355858.56</v>
       </c>
     </row>
     <row r="163" spans="1:12">
@@ -6852,28 +6891,28 @@
         <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="D163" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="E163" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="F163" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="I163" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J163">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K163">
-        <v>27987.95</v>
+        <v>386975.07</v>
       </c>
       <c r="L163">
-        <v>83963.85000000001</v>
+        <v>773950.14</v>
       </c>
     </row>
     <row r="164" spans="1:12">
@@ -6884,60 +6923,60 @@
         <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="D164" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="E164" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="F164" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="I164" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J164">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K164">
-        <v>274730.29</v>
+        <v>66983.8</v>
       </c>
       <c r="L164">
-        <v>2747302.9</v>
+        <v>267935.2</v>
       </c>
     </row>
     <row r="165" spans="1:12">
       <c r="A165" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B165" t="s">
         <v>169</v>
       </c>
       <c r="C165" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="D165" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="E165" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="F165" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="I165" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J165">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K165">
-        <v>5073.44</v>
+        <v>159709.51</v>
       </c>
       <c r="L165">
-        <v>50734.4</v>
+        <v>159709.51</v>
       </c>
     </row>
     <row r="166" spans="1:12">
@@ -6948,60 +6987,60 @@
         <v>170</v>
       </c>
       <c r="C166" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D166" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="E166" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F166" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I166" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J166">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="K166">
-        <v>271098.72</v>
+        <v>2473.41</v>
       </c>
       <c r="L166">
-        <v>1626592.32</v>
+        <v>93989.58</v>
       </c>
     </row>
     <row r="167" spans="1:12">
       <c r="A167" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B167" t="s">
         <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D167" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="E167" t="s">
-        <v>225</v>
+        <v>471</v>
       </c>
       <c r="F167" t="s">
-        <v>225</v>
+        <v>471</v>
       </c>
       <c r="I167" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J167">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K167">
-        <v>21390.12</v>
+        <v>636180.6800000001</v>
       </c>
       <c r="L167">
-        <v>171120.96</v>
+        <v>636180.6800000001</v>
       </c>
     </row>
     <row r="168" spans="1:12">
@@ -7012,28 +7051,28 @@
         <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="D168" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="E168" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F168" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="I168" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J168">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K168">
-        <v>325882.63</v>
+        <v>27987.95</v>
       </c>
       <c r="L168">
-        <v>325882.63</v>
+        <v>83963.85000000001</v>
       </c>
     </row>
     <row r="169" spans="1:12">
@@ -7044,92 +7083,92 @@
         <v>173</v>
       </c>
       <c r="C169" t="s">
-        <v>218</v>
+        <v>258</v>
       </c>
       <c r="D169" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="E169" t="s">
-        <v>218</v>
+        <v>259</v>
       </c>
       <c r="F169" t="s">
-        <v>218</v>
+        <v>475</v>
       </c>
       <c r="I169" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J169">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K169">
-        <v>66789.11</v>
+        <v>274730.29</v>
       </c>
       <c r="L169">
-        <v>133578.22</v>
+        <v>2747302.9</v>
       </c>
     </row>
     <row r="170" spans="1:12">
       <c r="A170" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B170" t="s">
         <v>174</v>
       </c>
       <c r="C170" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D170" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="E170" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F170" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I170" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J170">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K170">
-        <v>78468.91</v>
+        <v>5073.44</v>
       </c>
       <c r="L170">
-        <v>235406.73</v>
+        <v>50734.4</v>
       </c>
     </row>
     <row r="171" spans="1:12">
       <c r="A171" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B171" t="s">
         <v>175</v>
       </c>
       <c r="C171" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="D171" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="E171" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="F171" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="I171" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J171">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K171">
-        <v>263646.09</v>
+        <v>271098.72</v>
       </c>
       <c r="L171">
-        <v>790938.27</v>
+        <v>1626592.32</v>
       </c>
     </row>
     <row r="172" spans="1:12">
@@ -7140,28 +7179,28 @@
         <v>176</v>
       </c>
       <c r="C172" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D172" t="s">
-        <v>325</v>
+        <v>425</v>
       </c>
       <c r="E172" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="F172" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="I172" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J172">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K172">
-        <v>271387.84</v>
+        <v>21390.12</v>
       </c>
       <c r="L172">
-        <v>542775.6800000001</v>
+        <v>171120.96</v>
       </c>
     </row>
     <row r="173" spans="1:12">
@@ -7172,60 +7211,60 @@
         <v>177</v>
       </c>
       <c r="C173" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="D173" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="E173" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F173" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="I173" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J173">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K173">
-        <v>73037.78999999999</v>
+        <v>325882.63</v>
       </c>
       <c r="L173">
-        <v>219113.37</v>
+        <v>325882.63</v>
       </c>
     </row>
     <row r="174" spans="1:12">
       <c r="A174" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B174" t="s">
         <v>178</v>
       </c>
       <c r="C174" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D174" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="E174" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F174" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I174" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J174">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K174">
-        <v>7049.74</v>
+        <v>66789.11</v>
       </c>
       <c r="L174">
-        <v>98696.36</v>
+        <v>133578.22</v>
       </c>
     </row>
     <row r="175" spans="1:12">
@@ -7236,28 +7275,28 @@
         <v>179</v>
       </c>
       <c r="C175" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D175" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="E175" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F175" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I175" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J175">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K175">
-        <v>73190.35000000001</v>
+        <v>78468.91</v>
       </c>
       <c r="L175">
-        <v>805093.85</v>
+        <v>235406.73</v>
       </c>
     </row>
     <row r="176" spans="1:12">
@@ -7268,28 +7307,28 @@
         <v>180</v>
       </c>
       <c r="C176" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="D176" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="E176" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="F176" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="I176" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J176">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K176">
-        <v>128859.45</v>
+        <v>263646.09</v>
       </c>
       <c r="L176">
-        <v>257718.9</v>
+        <v>790938.27</v>
       </c>
     </row>
     <row r="177" spans="1:12">
@@ -7300,28 +7339,28 @@
         <v>181</v>
       </c>
       <c r="C177" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="D177" t="s">
-        <v>422</v>
+        <v>333</v>
       </c>
       <c r="E177" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="F177" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="I177" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K177">
-        <v>451021.21</v>
+        <v>271387.84</v>
       </c>
       <c r="L177">
-        <v>451021.21</v>
+        <v>542775.6800000001</v>
       </c>
     </row>
     <row r="178" spans="1:12">
@@ -7332,60 +7371,60 @@
         <v>182</v>
       </c>
       <c r="C178" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D178" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="E178" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F178" t="s">
-        <v>461</v>
+        <v>231</v>
       </c>
       <c r="I178" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J178">
         <v>3</v>
       </c>
       <c r="K178">
-        <v>76547.52</v>
+        <v>73037.78999999999</v>
       </c>
       <c r="L178">
-        <v>229642.56</v>
+        <v>219113.37</v>
       </c>
     </row>
     <row r="179" spans="1:12">
       <c r="A179" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B179" t="s">
         <v>183</v>
       </c>
       <c r="C179" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D179" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="E179" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="F179" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="I179" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J179">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K179">
-        <v>116937.56</v>
+        <v>7049.74</v>
       </c>
       <c r="L179">
-        <v>116937.56</v>
+        <v>98696.36</v>
       </c>
     </row>
     <row r="180" spans="1:12">
@@ -7396,60 +7435,60 @@
         <v>184</v>
       </c>
       <c r="C180" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D180" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="E180" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F180" t="s">
-        <v>461</v>
+        <v>231</v>
       </c>
       <c r="I180" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J180">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K180">
-        <v>98083.52</v>
+        <v>73190.35000000001</v>
       </c>
       <c r="L180">
-        <v>686584.64</v>
+        <v>805093.85</v>
       </c>
     </row>
     <row r="181" spans="1:12">
       <c r="A181" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B181" t="s">
         <v>185</v>
       </c>
       <c r="C181" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D181" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="E181" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F181" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="I181" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J181">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K181">
-        <v>167744.87</v>
+        <v>128859.45</v>
       </c>
       <c r="L181">
-        <v>167744.87</v>
+        <v>257718.9</v>
       </c>
     </row>
     <row r="182" spans="1:12">
@@ -7460,28 +7499,28 @@
         <v>186</v>
       </c>
       <c r="C182" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D182" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="E182" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="F182" t="s">
-        <v>463</v>
+        <v>240</v>
       </c>
       <c r="I182" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J182">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K182">
-        <v>23661.7</v>
+        <v>451021.21</v>
       </c>
       <c r="L182">
-        <v>141970.2</v>
+        <v>451021.21</v>
       </c>
     </row>
     <row r="183" spans="1:12">
@@ -7492,28 +7531,28 @@
         <v>187</v>
       </c>
       <c r="C183" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D183" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="E183" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="F183" t="s">
-        <v>218</v>
+        <v>474</v>
       </c>
       <c r="I183" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J183">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K183">
-        <v>20116.83</v>
+        <v>76547.52</v>
       </c>
       <c r="L183">
-        <v>120700.98</v>
+        <v>229642.56</v>
       </c>
     </row>
     <row r="184" spans="1:12">
@@ -7524,28 +7563,28 @@
         <v>188</v>
       </c>
       <c r="C184" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D184" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="E184" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F184" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I184" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J184">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K184">
-        <v>60010.35</v>
+        <v>116937.56</v>
       </c>
       <c r="L184">
-        <v>240041.4</v>
+        <v>116937.56</v>
       </c>
     </row>
     <row r="185" spans="1:12">
@@ -7556,60 +7595,60 @@
         <v>189</v>
       </c>
       <c r="C185" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D185" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="E185" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F185" t="s">
-        <v>225</v>
+        <v>474</v>
       </c>
       <c r="I185" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J185">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K185">
-        <v>100496.28</v>
+        <v>98083.52</v>
       </c>
       <c r="L185">
-        <v>200992.56</v>
+        <v>686584.64</v>
       </c>
     </row>
     <row r="186" spans="1:12">
       <c r="A186" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B186" t="s">
         <v>190</v>
       </c>
       <c r="C186" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="D186" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="E186" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="F186" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="I186" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J186">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="K186">
-        <v>10684.18</v>
+        <v>167744.87</v>
       </c>
       <c r="L186">
-        <v>427367.2</v>
+        <v>167744.87</v>
       </c>
     </row>
     <row r="187" spans="1:12">
@@ -7620,28 +7659,28 @@
         <v>191</v>
       </c>
       <c r="C187" t="s">
-        <v>225</v>
+        <v>259</v>
       </c>
       <c r="D187" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="E187" t="s">
-        <v>225</v>
+        <v>259</v>
       </c>
       <c r="F187" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="I187" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J187">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K187">
-        <v>128320.65</v>
+        <v>23661.7</v>
       </c>
       <c r="L187">
-        <v>128320.65</v>
+        <v>141970.2</v>
       </c>
     </row>
     <row r="188" spans="1:12">
@@ -7652,28 +7691,28 @@
         <v>192</v>
       </c>
       <c r="C188" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D188" t="s">
-        <v>340</v>
+        <v>440</v>
       </c>
       <c r="E188" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F188" t="s">
-        <v>461</v>
+        <v>224</v>
       </c>
       <c r="I188" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J188">
         <v>6</v>
       </c>
       <c r="K188">
-        <v>156649.71</v>
+        <v>20116.83</v>
       </c>
       <c r="L188">
-        <v>939898.26</v>
+        <v>120700.98</v>
       </c>
     </row>
     <row r="189" spans="1:12">
@@ -7684,28 +7723,28 @@
         <v>193</v>
       </c>
       <c r="C189" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D189" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="E189" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F189" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I189" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J189">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K189">
-        <v>92193.81</v>
+        <v>60010.35</v>
       </c>
       <c r="L189">
-        <v>184387.62</v>
+        <v>240041.4</v>
       </c>
     </row>
     <row r="190" spans="1:12">
@@ -7716,60 +7755,60 @@
         <v>194</v>
       </c>
       <c r="C190" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D190" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="E190" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="F190" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="I190" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J190">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K190">
-        <v>99834.53</v>
+        <v>100496.28</v>
       </c>
       <c r="L190">
-        <v>1098179.83</v>
+        <v>200992.56</v>
       </c>
     </row>
     <row r="191" spans="1:12">
       <c r="A191" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B191" t="s">
         <v>195</v>
       </c>
       <c r="C191" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D191" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="E191" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F191" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="I191" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J191">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="K191">
-        <v>24129.88</v>
+        <v>10684.18</v>
       </c>
       <c r="L191">
-        <v>144779.28</v>
+        <v>427367.2</v>
       </c>
     </row>
     <row r="192" spans="1:12">
@@ -7780,60 +7819,60 @@
         <v>196</v>
       </c>
       <c r="C192" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D192" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="E192" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F192" t="s">
-        <v>225</v>
+        <v>474</v>
       </c>
       <c r="I192" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J192">
         <v>1</v>
       </c>
       <c r="K192">
-        <v>477767.5</v>
+        <v>128320.65</v>
       </c>
       <c r="L192">
-        <v>477767.5</v>
+        <v>128320.65</v>
       </c>
     </row>
     <row r="193" spans="1:12">
       <c r="A193" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B193" t="s">
         <v>197</v>
       </c>
       <c r="C193" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="D193" t="s">
-        <v>437</v>
+        <v>348</v>
       </c>
       <c r="E193" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="F193" t="s">
-        <v>256</v>
+        <v>474</v>
       </c>
       <c r="I193" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J193">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K193">
-        <v>119118.65</v>
+        <v>156649.71</v>
       </c>
       <c r="L193">
-        <v>476474.6</v>
+        <v>939898.26</v>
       </c>
     </row>
     <row r="194" spans="1:12">
@@ -7844,92 +7883,92 @@
         <v>198</v>
       </c>
       <c r="C194" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D194" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="E194" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="F194" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="I194" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J194">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K194">
-        <v>12254.05</v>
+        <v>92193.81</v>
       </c>
       <c r="L194">
-        <v>134794.55</v>
+        <v>184387.62</v>
       </c>
     </row>
     <row r="195" spans="1:12">
       <c r="A195" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B195" t="s">
         <v>199</v>
       </c>
       <c r="C195" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D195" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="E195" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F195" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I195" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J195">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="K195">
-        <v>2043.59</v>
+        <v>99834.53</v>
       </c>
       <c r="L195">
-        <v>198228.23</v>
+        <v>1098179.83</v>
       </c>
     </row>
     <row r="196" spans="1:12">
       <c r="A196" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B196" t="s">
         <v>200</v>
       </c>
       <c r="C196" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="D196" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="E196" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="F196" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="I196" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J196">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K196">
-        <v>57019.29</v>
+        <v>24129.88</v>
       </c>
       <c r="L196">
-        <v>114038.58</v>
+        <v>144779.28</v>
       </c>
     </row>
     <row r="197" spans="1:12">
@@ -7940,65 +7979,65 @@
         <v>201</v>
       </c>
       <c r="C197" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D197" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="E197" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="F197" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="I197" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J197">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K197">
-        <v>54790.74</v>
+        <v>477767.5</v>
       </c>
       <c r="L197">
-        <v>219162.96</v>
+        <v>477767.5</v>
       </c>
     </row>
     <row r="198" spans="1:12">
       <c r="A198" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B198" t="s">
         <v>202</v>
       </c>
       <c r="C198" t="s">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="D198" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="E198" t="s">
-        <v>225</v>
+        <v>263</v>
       </c>
       <c r="F198" t="s">
-        <v>225</v>
+        <v>263</v>
       </c>
       <c r="I198" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J198">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K198">
-        <v>276872.24</v>
+        <v>119118.65</v>
       </c>
       <c r="L198">
-        <v>276872.24</v>
+        <v>476474.6</v>
       </c>
     </row>
     <row r="199" spans="1:12">
       <c r="A199" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B199" t="s">
         <v>203</v>
@@ -8007,25 +8046,25 @@
         <v>224</v>
       </c>
       <c r="D199" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="E199" t="s">
-        <v>458</v>
+        <v>224</v>
       </c>
       <c r="F199" t="s">
-        <v>458</v>
+        <v>224</v>
       </c>
       <c r="I199" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J199">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K199">
-        <v>228580.22</v>
+        <v>12254.05</v>
       </c>
       <c r="L199">
-        <v>228580.22</v>
+        <v>134794.55</v>
       </c>
     </row>
     <row r="200" spans="1:12">
@@ -8036,28 +8075,28 @@
         <v>204</v>
       </c>
       <c r="C200" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D200" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="E200" t="s">
-        <v>458</v>
+        <v>229</v>
       </c>
       <c r="F200" t="s">
-        <v>458</v>
+        <v>229</v>
       </c>
       <c r="I200" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J200">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="K200">
-        <v>588448.45</v>
+        <v>2043.59</v>
       </c>
       <c r="L200">
-        <v>588448.45</v>
+        <v>198228.23</v>
       </c>
     </row>
     <row r="201" spans="1:12">
@@ -8068,60 +8107,60 @@
         <v>205</v>
       </c>
       <c r="C201" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D201" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="E201" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="F201" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="I201" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J201">
         <v>2</v>
       </c>
       <c r="K201">
-        <v>171904.24</v>
+        <v>57019.29</v>
       </c>
       <c r="L201">
-        <v>343808.48</v>
+        <v>114038.58</v>
       </c>
     </row>
     <row r="202" spans="1:12">
       <c r="A202" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B202" t="s">
         <v>206</v>
       </c>
       <c r="C202" t="s">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="D202" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="E202" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="F202" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="I202" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J202">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K202">
-        <v>52120.37</v>
+        <v>54790.74</v>
       </c>
       <c r="L202">
-        <v>52120.37</v>
+        <v>219162.96</v>
       </c>
     </row>
     <row r="203" spans="1:12">
@@ -8132,28 +8171,28 @@
         <v>207</v>
       </c>
       <c r="C203" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D203" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="E203" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="F203" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="I203" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J203">
         <v>1</v>
       </c>
       <c r="K203">
-        <v>907492.78</v>
+        <v>276872.24</v>
       </c>
       <c r="L203">
-        <v>907492.78</v>
+        <v>276872.24</v>
       </c>
     </row>
     <row r="204" spans="1:12">
@@ -8164,28 +8203,28 @@
         <v>208</v>
       </c>
       <c r="C204" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="D204" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="E204" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="F204" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="I204" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J204">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K204">
-        <v>118001.73</v>
+        <v>228580.22</v>
       </c>
       <c r="L204">
-        <v>236003.46</v>
+        <v>228580.22</v>
       </c>
     </row>
     <row r="205" spans="1:12">
@@ -8196,28 +8235,28 @@
         <v>209</v>
       </c>
       <c r="C205" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="D205" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="E205" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="F205" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="I205" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J205">
         <v>1</v>
       </c>
       <c r="K205">
-        <v>56470.99</v>
+        <v>588448.45</v>
       </c>
       <c r="L205">
-        <v>56470.99</v>
+        <v>588448.45</v>
       </c>
     </row>
     <row r="206" spans="1:12">
@@ -8228,60 +8267,60 @@
         <v>210</v>
       </c>
       <c r="C206" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D206" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="E206" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F206" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I206" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J206">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K206">
-        <v>20316.27</v>
+        <v>171904.24</v>
       </c>
       <c r="L206">
-        <v>121897.62</v>
+        <v>343808.48</v>
       </c>
     </row>
     <row r="207" spans="1:12">
       <c r="A207" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B207" t="s">
         <v>211</v>
       </c>
       <c r="C207" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D207" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="E207" t="s">
-        <v>218</v>
+        <v>263</v>
       </c>
       <c r="F207" t="s">
-        <v>218</v>
+        <v>263</v>
       </c>
       <c r="I207" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J207">
         <v>1</v>
       </c>
       <c r="K207">
-        <v>64719.29</v>
+        <v>52120.37</v>
       </c>
       <c r="L207">
-        <v>64719.29</v>
+        <v>52120.37</v>
       </c>
     </row>
     <row r="208" spans="1:12">
@@ -8292,155 +8331,347 @@
         <v>212</v>
       </c>
       <c r="C208" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D208" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="E208" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F208" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I208" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J208">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K208">
-        <v>15431.69</v>
+        <v>907492.78</v>
       </c>
       <c r="L208">
-        <v>77158.45</v>
+        <v>907492.78</v>
       </c>
     </row>
     <row r="209" spans="1:12">
       <c r="A209" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B209" t="s">
         <v>213</v>
       </c>
       <c r="C209" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="D209" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="E209" t="s">
-        <v>218</v>
+        <v>471</v>
       </c>
       <c r="F209" t="s">
-        <v>218</v>
+        <v>471</v>
       </c>
       <c r="I209" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J209">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="K209">
-        <v>2999.26</v>
+        <v>118001.73</v>
       </c>
       <c r="L209">
-        <v>68982.98</v>
+        <v>236003.46</v>
       </c>
     </row>
     <row r="210" spans="1:12">
       <c r="A210" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B210" t="s">
         <v>214</v>
       </c>
       <c r="C210" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D210" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="E210" t="s">
-        <v>255</v>
+        <v>471</v>
       </c>
       <c r="F210" t="s">
-        <v>255</v>
+        <v>471</v>
       </c>
       <c r="I210" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J210">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K210">
-        <v>40143.73</v>
+        <v>56470.99</v>
       </c>
       <c r="L210">
-        <v>160574.92</v>
+        <v>56470.99</v>
       </c>
     </row>
     <row r="211" spans="1:12">
       <c r="A211" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B211" t="s">
         <v>215</v>
       </c>
       <c r="C211" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="D211" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="E211" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="F211" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="I211" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J211">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K211">
-        <v>112000</v>
+        <v>20316.27</v>
       </c>
       <c r="L211">
-        <v>224000</v>
+        <v>121897.62</v>
       </c>
     </row>
     <row r="212" spans="1:12">
       <c r="A212" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B212" t="s">
         <v>216</v>
       </c>
       <c r="C212" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="E212" t="s">
-        <v>257</v>
+        <v>224</v>
       </c>
       <c r="F212" t="s">
-        <v>257</v>
+        <v>224</v>
       </c>
       <c r="I212" t="s">
+        <v>477</v>
+      </c>
+      <c r="J212">
+        <v>1</v>
+      </c>
+      <c r="K212">
+        <v>64719.29</v>
+      </c>
+      <c r="L212">
+        <v>64719.29</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12">
+      <c r="A213" t="s">
+        <v>12</v>
+      </c>
+      <c r="B213" t="s">
+        <v>217</v>
+      </c>
+      <c r="C213" t="s">
+        <v>224</v>
+      </c>
+      <c r="D213" t="s">
         <v>464</v>
       </c>
-      <c r="J212">
+      <c r="E213" t="s">
+        <v>224</v>
+      </c>
+      <c r="F213" t="s">
+        <v>224</v>
+      </c>
+      <c r="I213" t="s">
+        <v>477</v>
+      </c>
+      <c r="J213">
+        <v>5</v>
+      </c>
+      <c r="K213">
+        <v>15431.69</v>
+      </c>
+      <c r="L213">
+        <v>77158.45</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12">
+      <c r="A214" t="s">
+        <v>12</v>
+      </c>
+      <c r="B214" t="s">
+        <v>218</v>
+      </c>
+      <c r="C214" t="s">
+        <v>224</v>
+      </c>
+      <c r="D214" t="s">
+        <v>465</v>
+      </c>
+      <c r="E214" t="s">
+        <v>224</v>
+      </c>
+      <c r="F214" t="s">
+        <v>224</v>
+      </c>
+      <c r="I214" t="s">
+        <v>477</v>
+      </c>
+      <c r="J214">
+        <v>23</v>
+      </c>
+      <c r="K214">
+        <v>2999.26</v>
+      </c>
+      <c r="L214">
+        <v>68982.98</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12">
+      <c r="A215" t="s">
+        <v>12</v>
+      </c>
+      <c r="B215" t="s">
+        <v>219</v>
+      </c>
+      <c r="C215" t="s">
+        <v>262</v>
+      </c>
+      <c r="D215" t="s">
+        <v>466</v>
+      </c>
+      <c r="E215" t="s">
+        <v>262</v>
+      </c>
+      <c r="F215" t="s">
+        <v>262</v>
+      </c>
+      <c r="I215" t="s">
+        <v>477</v>
+      </c>
+      <c r="J215">
+        <v>4</v>
+      </c>
+      <c r="K215">
+        <v>40143.73</v>
+      </c>
+      <c r="L215">
+        <v>160574.92</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12">
+      <c r="A216" t="s">
+        <v>13</v>
+      </c>
+      <c r="B216" t="s">
+        <v>220</v>
+      </c>
+      <c r="C216" t="s">
+        <v>259</v>
+      </c>
+      <c r="D216" t="s">
+        <v>467</v>
+      </c>
+      <c r="E216" t="s">
+        <v>259</v>
+      </c>
+      <c r="F216" t="s">
+        <v>475</v>
+      </c>
+      <c r="I216" t="s">
+        <v>477</v>
+      </c>
+      <c r="J216">
+        <v>1</v>
+      </c>
+      <c r="K216">
+        <v>259475.34</v>
+      </c>
+      <c r="L216">
+        <v>259475.34</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12">
+      <c r="A217" t="s">
+        <v>13</v>
+      </c>
+      <c r="B217" t="s">
+        <v>221</v>
+      </c>
+      <c r="C217" t="s">
+        <v>263</v>
+      </c>
+      <c r="D217" t="s">
+        <v>468</v>
+      </c>
+      <c r="E217" t="s">
+        <v>263</v>
+      </c>
+      <c r="F217" t="s">
+        <v>263</v>
+      </c>
+      <c r="I217" t="s">
+        <v>477</v>
+      </c>
+      <c r="J217">
+        <v>2</v>
+      </c>
+      <c r="K217">
+        <v>112000</v>
+      </c>
+      <c r="L217">
+        <v>224000</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12">
+      <c r="A218" t="s">
+        <v>13</v>
+      </c>
+      <c r="B218" t="s">
+        <v>222</v>
+      </c>
+      <c r="C218" t="s">
+        <v>264</v>
+      </c>
+      <c r="D218" t="s">
+        <v>469</v>
+      </c>
+      <c r="E218" t="s">
+        <v>264</v>
+      </c>
+      <c r="F218" t="s">
+        <v>264</v>
+      </c>
+      <c r="I218" t="s">
+        <v>477</v>
+      </c>
+      <c r="J218">
         <v>6</v>
       </c>
-      <c r="K212">
+      <c r="K218">
         <v>128205</v>
       </c>
-      <c r="L212">
+      <c r="L218">
         <v>769230</v>
       </c>
     </row>

--- a/VALORIZADO FALTANTES.xlsx
+++ b/VALORIZADO FALTANTES.xlsx
@@ -1471,13 +1471,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/10/2025 09:44:16</t>
+    <t>Período: 31/10/2025 12:37:31</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 23/10/2025 09:52:30</t>
+    <t>Fecha y hora de generación: 27/10/2025 12:37:50</t>
   </si>
 </sst>
 </file>

--- a/VALORIZADO FALTANTES.xlsx
+++ b/VALORIZADO FALTANTES.xlsx
@@ -1471,13 +1471,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/10/2025 12:37:31</t>
+    <t>Período: 31/10/2025 08:45:56</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 27/10/2025 12:37:50</t>
+    <t>Fecha y hora de generación: 30/10/2025 08:46:48</t>
   </si>
 </sst>
 </file>

--- a/VALORIZADO FALTANTES.xlsx
+++ b/VALORIZADO FALTANTES.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jlopez\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{337E83A5-A696-4C48-907A-C0260E1F5203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Valorizado" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="452">
   <si>
     <t>Categoría</t>
   </si>
@@ -58,69 +77,6 @@
     <t>Categoría producto</t>
   </si>
   <si>
-    <t>9373</t>
-  </si>
-  <si>
-    <t>16866</t>
-  </si>
-  <si>
-    <t>21360</t>
-  </si>
-  <si>
-    <t>131973</t>
-  </si>
-  <si>
-    <t>691445</t>
-  </si>
-  <si>
-    <t>691934</t>
-  </si>
-  <si>
-    <t>994349</t>
-  </si>
-  <si>
-    <t>994370</t>
-  </si>
-  <si>
-    <t>3344768</t>
-  </si>
-  <si>
-    <t>3344862</t>
-  </si>
-  <si>
-    <t>4301467</t>
-  </si>
-  <si>
-    <t>4301762</t>
-  </si>
-  <si>
-    <t>4302411</t>
-  </si>
-  <si>
-    <t>4302484</t>
-  </si>
-  <si>
-    <t>4302506</t>
-  </si>
-  <si>
-    <t>4303357</t>
-  </si>
-  <si>
-    <t>4303428</t>
-  </si>
-  <si>
-    <t>4303476</t>
-  </si>
-  <si>
-    <t>4303825</t>
-  </si>
-  <si>
-    <t>4304499</t>
-  </si>
-  <si>
-    <t>4304641</t>
-  </si>
-  <si>
     <t>K3454/7349</t>
   </si>
   <si>
@@ -442,21 +398,6 @@
     <t>WAB9111549202</t>
   </si>
   <si>
-    <t>8968</t>
-  </si>
-  <si>
-    <t>15980</t>
-  </si>
-  <si>
-    <t>83726</t>
-  </si>
-  <si>
-    <t>127760</t>
-  </si>
-  <si>
-    <t>4301795</t>
-  </si>
-  <si>
     <t>1229G4661/009013</t>
   </si>
   <si>
@@ -529,21 +470,6 @@
     <t>WAB4324102442</t>
   </si>
   <si>
-    <t>13653</t>
-  </si>
-  <si>
-    <t>328349</t>
-  </si>
-  <si>
-    <t>4303603</t>
-  </si>
-  <si>
-    <t>5566510</t>
-  </si>
-  <si>
-    <t>5568529</t>
-  </si>
-  <si>
     <t>1033-40600-02</t>
   </si>
   <si>
@@ -595,9 +521,6 @@
     <t>131095KWAP</t>
   </si>
   <si>
-    <t>4300119</t>
-  </si>
-  <si>
     <t>2233J1024/092061</t>
   </si>
   <si>
@@ -628,12 +551,6 @@
     <t>SET410KOYO</t>
   </si>
   <si>
-    <t>85003</t>
-  </si>
-  <si>
-    <t>10021566</t>
-  </si>
-  <si>
     <t>1228F552/P2252</t>
   </si>
   <si>
@@ -670,12 +587,6 @@
     <t>4301417FULLER</t>
   </si>
   <si>
-    <t>4303424</t>
-  </si>
-  <si>
-    <t>16980</t>
-  </si>
-  <si>
     <t>LF3620</t>
   </si>
   <si>
@@ -1471,20 +1382,20 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/10/2025 08:45:56</t>
+    <t>Período: 30/11/2025 12:29:18</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 30/10/2025 08:46:48</t>
+    <t>Fecha y hora de generación: 01/11/2025 12:29:46</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1577,10 +1488,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1588,28 +1505,31 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1647,7 +1567,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1681,6 +1601,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1715,9 +1636,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1890,130 +1812,130 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L219"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>480</v>
+        <v>444</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>482</v>
+        <v>446</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="4" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="I7" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="6" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="21" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+    </row>
+    <row r="5" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I7" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s">
-        <v>14</v>
+      <c r="B10" s="7">
+        <v>9373</v>
       </c>
       <c r="C10" t="s">
-        <v>224</v>
+        <v>188</v>
       </c>
       <c r="D10" t="s">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="E10" t="s">
-        <v>224</v>
+        <v>188</v>
       </c>
       <c r="F10" t="s">
-        <v>224</v>
+        <v>188</v>
       </c>
       <c r="I10" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J10">
         <v>3</v>
@@ -2025,27 +1947,27 @@
         <v>1012839.99</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="B11" t="s">
-        <v>15</v>
+      <c r="B11" s="7">
+        <v>16866</v>
       </c>
       <c r="C11" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D11" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="E11" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F11" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I11" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -2057,27 +1979,27 @@
         <v>20451.8</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" t="s">
-        <v>16</v>
+      <c r="B12" s="7">
+        <v>21360</v>
       </c>
       <c r="C12" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="E12" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F12" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I12" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -2089,27 +2011,27 @@
         <v>85144.72</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>17</v>
+      <c r="B13" s="7">
+        <v>131973</v>
       </c>
       <c r="C13" t="s">
-        <v>226</v>
+        <v>190</v>
       </c>
       <c r="D13" t="s">
-        <v>269</v>
+        <v>233</v>
       </c>
       <c r="E13" t="s">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="F13" t="s">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="I13" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -2121,27 +2043,27 @@
         <v>400839.72</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>18</v>
+      <c r="B14" s="7">
+        <v>691445</v>
       </c>
       <c r="C14" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D14" t="s">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="E14" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F14" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I14" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -2153,27 +2075,27 @@
         <v>274251.7</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>12</v>
       </c>
-      <c r="B15" t="s">
-        <v>19</v>
+      <c r="B15" s="7">
+        <v>691934</v>
       </c>
       <c r="C15" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D15" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="E15" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F15" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I15" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -2185,27 +2107,27 @@
         <v>103305.02</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>12</v>
       </c>
-      <c r="B16" t="s">
-        <v>20</v>
+      <c r="B16" s="7">
+        <v>994349</v>
       </c>
       <c r="C16" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="D16" t="s">
-        <v>272</v>
+        <v>236</v>
       </c>
       <c r="E16" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="F16" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="I16" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J16">
         <v>2</v>
@@ -2217,27 +2139,27 @@
         <v>586270.9</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>12</v>
       </c>
-      <c r="B17" t="s">
-        <v>21</v>
+      <c r="B17" s="7">
+        <v>994370</v>
       </c>
       <c r="C17" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="D17" t="s">
-        <v>273</v>
+        <v>237</v>
       </c>
       <c r="E17" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="F17" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="I17" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2249,27 +2171,27 @@
         <v>239445.31</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
-      <c r="B18" t="s">
-        <v>22</v>
+      <c r="B18" s="7">
+        <v>3344768</v>
       </c>
       <c r="C18" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D18" t="s">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="E18" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F18" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I18" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2281,27 +2203,27 @@
         <v>107249.13</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>12</v>
       </c>
-      <c r="B19" t="s">
-        <v>23</v>
+      <c r="B19" s="7">
+        <v>3344862</v>
       </c>
       <c r="C19" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D19" t="s">
-        <v>275</v>
+        <v>239</v>
       </c>
       <c r="E19" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F19" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I19" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -2313,59 +2235,59 @@
         <v>221724.9</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
-      <c r="B20" t="s">
-        <v>24</v>
+      <c r="B20" s="7">
+        <v>4301467</v>
       </c>
       <c r="C20" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D20" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
       <c r="E20" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F20" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I20" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J20">
         <v>1</v>
       </c>
       <c r="K20">
-        <v>72202.42999999999</v>
+        <v>72202.429999999993</v>
       </c>
       <c r="L20">
-        <v>72202.42999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+        <v>72202.429999999993</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
-      <c r="B21" t="s">
-        <v>25</v>
+      <c r="B21" s="7">
+        <v>4301762</v>
       </c>
       <c r="C21" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D21" t="s">
-        <v>277</v>
+        <v>241</v>
       </c>
       <c r="E21" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F21" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I21" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2377,59 +2299,59 @@
         <v>344188.26</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
-      <c r="B22" t="s">
-        <v>26</v>
+      <c r="B22" s="7">
+        <v>4302411</v>
       </c>
       <c r="C22" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D22" t="s">
-        <v>278</v>
+        <v>242</v>
       </c>
       <c r="E22" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F22" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I22" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J22">
         <v>3</v>
       </c>
       <c r="K22">
-        <v>286220.53</v>
+        <v>286220.53000000003</v>
       </c>
       <c r="L22">
         <v>858661.59</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
-      <c r="B23" t="s">
-        <v>27</v>
+      <c r="B23" s="7">
+        <v>4302484</v>
       </c>
       <c r="C23" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D23" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F23" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I23" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J23">
         <v>2</v>
@@ -2441,27 +2363,27 @@
         <v>710132.86</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
-      <c r="B24" t="s">
-        <v>28</v>
+      <c r="B24" s="7">
+        <v>4302506</v>
       </c>
       <c r="C24" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D24" t="s">
-        <v>280</v>
+        <v>244</v>
       </c>
       <c r="E24" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F24" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I24" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -2473,27 +2395,27 @@
         <v>618795.86</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
-      <c r="B25" t="s">
-        <v>29</v>
+      <c r="B25" s="7">
+        <v>4303357</v>
       </c>
       <c r="C25" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D25" t="s">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="E25" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F25" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I25" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J25">
         <v>2</v>
@@ -2505,27 +2427,27 @@
         <v>907043.74</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
-      <c r="B26" t="s">
-        <v>30</v>
+      <c r="B26" s="7">
+        <v>4303428</v>
       </c>
       <c r="C26" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D26" t="s">
-        <v>282</v>
+        <v>246</v>
       </c>
       <c r="E26" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F26" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I26" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -2537,27 +2459,27 @@
         <v>528176.74</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>12</v>
       </c>
-      <c r="B27" t="s">
-        <v>31</v>
+      <c r="B27" s="7">
+        <v>4303476</v>
       </c>
       <c r="C27" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D27" t="s">
-        <v>283</v>
+        <v>247</v>
       </c>
       <c r="E27" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F27" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I27" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J27">
         <v>3</v>
@@ -2569,27 +2491,27 @@
         <v>884427.72</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>13</v>
       </c>
-      <c r="B28" t="s">
-        <v>32</v>
+      <c r="B28" s="7">
+        <v>4303825</v>
       </c>
       <c r="C28" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D28" t="s">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="E28" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F28" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I28" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2601,27 +2523,27 @@
         <v>324848.81</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>12</v>
       </c>
-      <c r="B29" t="s">
-        <v>33</v>
+      <c r="B29" s="7">
+        <v>4304499</v>
       </c>
       <c r="C29" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D29" t="s">
-        <v>285</v>
+        <v>249</v>
       </c>
       <c r="E29" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F29" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I29" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2633,27 +2555,27 @@
         <v>119219.24</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>12</v>
       </c>
-      <c r="B30" t="s">
-        <v>34</v>
+      <c r="B30" s="7">
+        <v>4304641</v>
       </c>
       <c r="C30" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D30" t="s">
-        <v>286</v>
+        <v>250</v>
       </c>
       <c r="E30" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F30" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I30" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J30">
         <v>2</v>
@@ -2662,62 +2584,62 @@
         <v>456594.41</v>
       </c>
       <c r="L30">
-        <v>913188.8199999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
+        <v>913188.82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D31" t="s">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="E31" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F31" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I31" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J31">
         <v>2</v>
       </c>
       <c r="K31">
-        <v>84932.64999999999</v>
+        <v>84932.65</v>
       </c>
       <c r="L31">
         <v>169865.3</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>228</v>
+        <v>192</v>
       </c>
       <c r="D32" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="E32" t="s">
-        <v>472</v>
+        <v>436</v>
       </c>
       <c r="F32" t="s">
-        <v>228</v>
+        <v>192</v>
       </c>
       <c r="I32" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J32">
         <v>12</v>
@@ -2729,27 +2651,27 @@
         <v>366964.32</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>228</v>
+        <v>192</v>
       </c>
       <c r="D33" t="s">
-        <v>289</v>
+        <v>253</v>
       </c>
       <c r="E33" t="s">
-        <v>472</v>
+        <v>436</v>
       </c>
       <c r="F33" t="s">
-        <v>228</v>
+        <v>192</v>
       </c>
       <c r="I33" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J33">
         <v>6</v>
@@ -2761,59 +2683,59 @@
         <v>200111.34</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="D34" t="s">
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="E34" t="s">
-        <v>472</v>
+        <v>436</v>
       </c>
       <c r="F34" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="I34" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J34">
         <v>6</v>
       </c>
       <c r="K34">
-        <v>26185.2</v>
+        <v>26185.200000000001</v>
       </c>
       <c r="L34">
-        <v>157111.2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12">
+        <v>157111.20000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="D35" t="s">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="E35" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="F35" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="I35" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2825,27 +2747,27 @@
         <v>132383.57</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C36" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D36" t="s">
-        <v>292</v>
+        <v>256</v>
       </c>
       <c r="E36" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F36" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I36" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2857,27 +2779,27 @@
         <v>1666305.17</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="D37" t="s">
-        <v>293</v>
+        <v>257</v>
       </c>
       <c r="E37" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="F37" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="I37" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J37">
         <v>3</v>
@@ -2889,27 +2811,27 @@
         <v>3585224.85</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="C38" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="D38" t="s">
-        <v>294</v>
+        <v>258</v>
       </c>
       <c r="E38" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="F38" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="I38" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J38">
         <v>123</v>
@@ -2921,27 +2843,27 @@
         <v>194096.46</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D39" t="s">
-        <v>295</v>
+        <v>259</v>
       </c>
       <c r="E39" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F39" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I39" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J39">
         <v>4</v>
@@ -2953,91 +2875,91 @@
         <v>64747.28</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C40" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="D40" t="s">
-        <v>296</v>
+        <v>260</v>
       </c>
       <c r="E40" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="F40" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="I40" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J40">
         <v>1</v>
       </c>
       <c r="K40">
-        <v>151783.14</v>
+        <v>151783.14000000001</v>
       </c>
       <c r="L40">
-        <v>151783.14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12">
+        <v>151783.14000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C41" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="D41" t="s">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="E41" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="F41" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="I41" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J41">
         <v>1</v>
       </c>
       <c r="K41">
-        <v>133605.86</v>
+        <v>133605.85999999999</v>
       </c>
       <c r="L41">
-        <v>133605.86</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12">
+        <v>133605.85999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>13</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="C42" t="s">
-        <v>228</v>
+        <v>192</v>
       </c>
       <c r="D42" t="s">
-        <v>298</v>
+        <v>262</v>
       </c>
       <c r="E42" t="s">
-        <v>472</v>
+        <v>436</v>
       </c>
       <c r="F42" t="s">
-        <v>228</v>
+        <v>192</v>
       </c>
       <c r="I42" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J42">
         <v>12</v>
@@ -3049,27 +2971,27 @@
         <v>121084.68</v>
       </c>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="C43" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D43" t="s">
-        <v>299</v>
+        <v>263</v>
       </c>
       <c r="E43" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="F43" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="I43" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -3081,27 +3003,27 @@
         <v>55214.31</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D44" t="s">
-        <v>300</v>
+        <v>264</v>
       </c>
       <c r="E44" t="s">
-        <v>474</v>
+        <v>438</v>
       </c>
       <c r="F44" t="s">
-        <v>474</v>
+        <v>438</v>
       </c>
       <c r="I44" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J44">
         <v>2</v>
@@ -3113,27 +3035,27 @@
         <v>546013.4</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="C45" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="D45" t="s">
-        <v>301</v>
+        <v>265</v>
       </c>
       <c r="E45" t="s">
-        <v>474</v>
+        <v>438</v>
       </c>
       <c r="F45" t="s">
-        <v>474</v>
+        <v>438</v>
       </c>
       <c r="I45" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J45">
         <v>12</v>
@@ -3145,27 +3067,27 @@
         <v>267602.64</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C46" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="D46" t="s">
-        <v>302</v>
+        <v>266</v>
       </c>
       <c r="E46" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="F46" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="I46" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -3177,59 +3099,59 @@
         <v>69469.2</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="C47" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="D47" t="s">
-        <v>303</v>
+        <v>267</v>
       </c>
       <c r="E47" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="F47" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="I47" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J47">
         <v>2</v>
       </c>
       <c r="K47">
-        <v>38542.45</v>
+        <v>38542.449999999997</v>
       </c>
       <c r="L47">
-        <v>77084.89999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12">
+        <v>77084.899999999994</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C48" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="D48" t="s">
-        <v>304</v>
+        <v>268</v>
       </c>
       <c r="E48" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="F48" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="I48" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J48">
         <v>4</v>
@@ -3241,27 +3163,27 @@
         <v>292678.32</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C49" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="D49" t="s">
-        <v>305</v>
+        <v>269</v>
       </c>
       <c r="E49" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="F49" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="I49" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -3273,27 +3195,27 @@
         <v>57029.66</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="C50" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="D50" t="s">
-        <v>306</v>
+        <v>270</v>
       </c>
       <c r="E50" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="F50" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="I50" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J50">
         <v>5</v>
@@ -3305,27 +3227,27 @@
         <v>620565.15</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C51" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
       <c r="D51" t="s">
-        <v>307</v>
+        <v>271</v>
       </c>
       <c r="E51" t="s">
-        <v>474</v>
+        <v>438</v>
       </c>
       <c r="F51" t="s">
-        <v>474</v>
+        <v>438</v>
       </c>
       <c r="I51" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -3337,27 +3259,27 @@
         <v>143954.72</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>13</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="C52" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="D52" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="E52" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="F52" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="I52" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J52">
         <v>3</v>
@@ -3369,27 +3291,27 @@
         <v>1122558</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="C53" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="D53" t="s">
-        <v>309</v>
+        <v>273</v>
       </c>
       <c r="E53" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="F53" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="I53" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J53">
         <v>2</v>
@@ -3398,30 +3320,30 @@
         <v>451755.47</v>
       </c>
       <c r="L53">
-        <v>903510.9399999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12">
+        <v>903510.94</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="C54" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D54" t="s">
-        <v>310</v>
+        <v>274</v>
       </c>
       <c r="E54" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F54" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I54" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -3433,27 +3355,27 @@
         <v>297477.98</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C55" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="D55" t="s">
-        <v>311</v>
+        <v>275</v>
       </c>
       <c r="E55" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="F55" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="I55" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J55">
         <v>3</v>
@@ -3465,27 +3387,27 @@
         <v>350025.18</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="C56" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D56" t="s">
-        <v>312</v>
+        <v>276</v>
       </c>
       <c r="E56" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F56" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I56" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -3497,27 +3419,27 @@
         <v>241521.59</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="C57" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D57" t="s">
-        <v>313</v>
+        <v>277</v>
       </c>
       <c r="E57" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F57" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I57" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J57">
         <v>2</v>
@@ -3529,27 +3451,27 @@
         <v>246247.44</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="C58" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D58" t="s">
-        <v>314</v>
+        <v>278</v>
       </c>
       <c r="E58" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F58" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I58" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J58">
         <v>2</v>
@@ -3561,27 +3483,27 @@
         <v>555481.24</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="C59" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="D59" t="s">
-        <v>315</v>
+        <v>279</v>
       </c>
       <c r="E59" t="s">
-        <v>472</v>
+        <v>436</v>
       </c>
       <c r="F59" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="I59" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J59">
         <v>91</v>
@@ -3593,27 +3515,27 @@
         <v>902993</v>
       </c>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="C60" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="D60" t="s">
-        <v>316</v>
+        <v>280</v>
       </c>
       <c r="E60" t="s">
-        <v>472</v>
+        <v>436</v>
       </c>
       <c r="F60" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="I60" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J60">
         <v>28</v>
@@ -3625,27 +3547,27 @@
         <v>149185.4</v>
       </c>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>13</v>
       </c>
       <c r="B61" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C61" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="D61" t="s">
-        <v>317</v>
+        <v>281</v>
       </c>
       <c r="E61" t="s">
-        <v>472</v>
+        <v>436</v>
       </c>
       <c r="F61" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="I61" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J61">
         <v>6</v>
@@ -3657,27 +3579,27 @@
         <v>77229.3</v>
       </c>
     </row>
-    <row r="62" spans="1:12">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C62" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="D62" t="s">
-        <v>318</v>
+        <v>282</v>
       </c>
       <c r="E62" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="F62" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="I62" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J62">
         <v>64</v>
@@ -3689,27 +3611,27 @@
         <v>718570.24</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="C63" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="D63" t="s">
-        <v>319</v>
+        <v>283</v>
       </c>
       <c r="E63" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="F63" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="I63" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J63">
         <v>3</v>
@@ -3721,27 +3643,27 @@
         <v>223230.09</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>13</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="C64" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="D64" t="s">
-        <v>320</v>
+        <v>284</v>
       </c>
       <c r="E64" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="F64" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="I64" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J64">
         <v>2</v>
@@ -3753,91 +3675,91 @@
         <v>104029.86</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="C65" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="D65" t="s">
-        <v>321</v>
+        <v>285</v>
       </c>
       <c r="E65" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="F65" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="I65" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J65">
         <v>20</v>
       </c>
       <c r="K65">
-        <v>94380.39999999999</v>
+        <v>94380.4</v>
       </c>
       <c r="L65">
         <v>1887608</v>
       </c>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="C66" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
       <c r="D66" t="s">
-        <v>322</v>
+        <v>286</v>
       </c>
       <c r="E66" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
       <c r="F66" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
       <c r="I66" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J66">
         <v>5</v>
       </c>
       <c r="K66">
-        <v>1157466.59</v>
+        <v>1157466.5900000001</v>
       </c>
       <c r="L66">
-        <v>5787332.95</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12">
+        <v>5787332.9500000002</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="C67" t="s">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="D67" t="s">
-        <v>323</v>
+        <v>287</v>
       </c>
       <c r="E67" t="s">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="F67" t="s">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="I67" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3849,27 +3771,27 @@
         <v>553925.89</v>
       </c>
     </row>
-    <row r="68" spans="1:12">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C68" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D68" t="s">
-        <v>324</v>
+        <v>288</v>
       </c>
       <c r="E68" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F68" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I68" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3881,27 +3803,27 @@
         <v>456192.75</v>
       </c>
     </row>
-    <row r="69" spans="1:12">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="C69" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D69" t="s">
-        <v>325</v>
+        <v>289</v>
       </c>
       <c r="E69" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F69" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I69" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J69">
         <v>5</v>
@@ -3910,30 +3832,30 @@
         <v>459216.59</v>
       </c>
       <c r="L69">
-        <v>2296082.95</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12">
+        <v>2296082.9500000002</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>13</v>
       </c>
       <c r="B70" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C70" t="s">
-        <v>244</v>
+        <v>208</v>
       </c>
       <c r="D70" t="s">
-        <v>326</v>
+        <v>290</v>
       </c>
       <c r="E70" t="s">
-        <v>475</v>
+        <v>439</v>
       </c>
       <c r="F70" t="s">
-        <v>475</v>
+        <v>439</v>
       </c>
       <c r="I70" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J70">
         <v>2</v>
@@ -3945,27 +3867,27 @@
         <v>215222.86</v>
       </c>
     </row>
-    <row r="71" spans="1:12">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="C71" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="D71" t="s">
-        <v>327</v>
+        <v>291</v>
       </c>
       <c r="E71" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="F71" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="I71" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J71">
         <v>4</v>
@@ -3977,27 +3899,27 @@
         <v>651137.96</v>
       </c>
     </row>
-    <row r="72" spans="1:12">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="C72" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="D72" t="s">
-        <v>328</v>
+        <v>292</v>
       </c>
       <c r="E72" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="F72" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="I72" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J72">
         <v>3</v>
@@ -4009,27 +3931,27 @@
         <v>193789.23</v>
       </c>
     </row>
-    <row r="73" spans="1:12">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="C73" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D73" t="s">
-        <v>329</v>
+        <v>293</v>
       </c>
       <c r="E73" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F73" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I73" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J73">
         <v>4</v>
@@ -4041,27 +3963,27 @@
         <v>2083862.28</v>
       </c>
     </row>
-    <row r="74" spans="1:12">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="C74" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D74" t="s">
-        <v>330</v>
+        <v>294</v>
       </c>
       <c r="E74" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F74" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I74" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -4073,27 +3995,27 @@
         <v>234957.18</v>
       </c>
     </row>
-    <row r="75" spans="1:12">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="C75" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D75" t="s">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="E75" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F75" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I75" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J75">
         <v>1</v>
@@ -4105,27 +4027,27 @@
         <v>561136.28</v>
       </c>
     </row>
-    <row r="76" spans="1:12">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>13</v>
       </c>
       <c r="B76" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="C76" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D76" t="s">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="E76" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F76" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I76" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J76">
         <v>1</v>
@@ -4137,27 +4059,27 @@
         <v>548933.98</v>
       </c>
     </row>
-    <row r="77" spans="1:12">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="C77" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D77" t="s">
-        <v>332</v>
+        <v>296</v>
       </c>
       <c r="E77" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F77" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I77" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J77">
         <v>2</v>
@@ -4169,27 +4091,27 @@
         <v>696877.88</v>
       </c>
     </row>
-    <row r="78" spans="1:12">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>13</v>
       </c>
       <c r="B78" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="C78" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D78" t="s">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="E78" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F78" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I78" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J78">
         <v>1</v>
@@ -4201,27 +4123,27 @@
         <v>176616.64</v>
       </c>
     </row>
-    <row r="79" spans="1:12">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="C79" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D79" t="s">
-        <v>334</v>
+        <v>298</v>
       </c>
       <c r="E79" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F79" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I79" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J79">
         <v>3</v>
@@ -4230,62 +4152,62 @@
         <v>54474.6</v>
       </c>
       <c r="L79">
-        <v>163423.8</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12">
+        <v>163423.79999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C80" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D80" t="s">
-        <v>335</v>
+        <v>299</v>
       </c>
       <c r="E80" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F80" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I80" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J80">
         <v>1</v>
       </c>
       <c r="K80">
-        <v>289538.6</v>
+        <v>289538.59999999998</v>
       </c>
       <c r="L80">
-        <v>289538.6</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12">
+        <v>289538.59999999998</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C81" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
       <c r="D81" t="s">
-        <v>336</v>
+        <v>300</v>
       </c>
       <c r="E81" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
       <c r="F81" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
       <c r="I81" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J81">
         <v>2</v>
@@ -4297,27 +4219,27 @@
         <v>120382.36</v>
       </c>
     </row>
-    <row r="82" spans="1:12">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="C82" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="D82" t="s">
-        <v>337</v>
+        <v>301</v>
       </c>
       <c r="E82" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="F82" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="I82" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J82">
         <v>5</v>
@@ -4326,30 +4248,30 @@
         <v>106058.91</v>
       </c>
       <c r="L82">
-        <v>530294.55</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12">
+        <v>530294.55000000005</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="C83" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="D83" t="s">
-        <v>338</v>
+        <v>302</v>
       </c>
       <c r="E83" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="F83" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="I83" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J83">
         <v>5</v>
@@ -4361,27 +4283,27 @@
         <v>120389.45</v>
       </c>
     </row>
-    <row r="84" spans="1:12">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="C84" t="s">
-        <v>246</v>
+        <v>210</v>
       </c>
       <c r="D84" t="s">
-        <v>339</v>
+        <v>303</v>
       </c>
       <c r="E84" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="F84" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="I84" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J84">
         <v>21</v>
@@ -4390,30 +4312,30 @@
         <v>13504.82</v>
       </c>
       <c r="L84">
-        <v>283601.22</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12">
+        <v>283601.21999999997</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="C85" t="s">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="D85" t="s">
-        <v>340</v>
+        <v>304</v>
       </c>
       <c r="E85" t="s">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="F85" t="s">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="I85" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J85">
         <v>1</v>
@@ -4425,27 +4347,27 @@
         <v>244653.18</v>
       </c>
     </row>
-    <row r="86" spans="1:12">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C86" t="s">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="D86" t="s">
-        <v>341</v>
+        <v>305</v>
       </c>
       <c r="E86" t="s">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="F86" t="s">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="I86" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J86">
         <v>4</v>
@@ -4454,30 +4376,30 @@
         <v>116579.52</v>
       </c>
       <c r="L86">
-        <v>466318.08</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12">
+        <v>466318.08000000002</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="C87" t="s">
-        <v>244</v>
+        <v>208</v>
       </c>
       <c r="D87" t="s">
-        <v>342</v>
+        <v>306</v>
       </c>
       <c r="E87" t="s">
-        <v>475</v>
+        <v>439</v>
       </c>
       <c r="F87" t="s">
-        <v>475</v>
+        <v>439</v>
       </c>
       <c r="I87" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J87">
         <v>2</v>
@@ -4489,59 +4411,59 @@
         <v>265900.58</v>
       </c>
     </row>
-    <row r="88" spans="1:12">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="C88" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="D88" t="s">
-        <v>343</v>
+        <v>307</v>
       </c>
       <c r="E88" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="F88" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="I88" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J88">
         <v>2</v>
       </c>
       <c r="K88">
-        <v>130565.76</v>
+        <v>130565.75999999999</v>
       </c>
       <c r="L88">
-        <v>261131.52</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12">
+        <v>261131.51999999999</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="C89" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="D89" t="s">
-        <v>344</v>
+        <v>308</v>
       </c>
       <c r="E89" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="F89" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="I89" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J89">
         <v>10</v>
@@ -4550,30 +4472,30 @@
         <v>32532.84</v>
       </c>
       <c r="L89">
-        <v>325328.4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12">
+        <v>325328.40000000002</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="C90" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="D90" t="s">
-        <v>345</v>
+        <v>309</v>
       </c>
       <c r="E90" t="s">
-        <v>472</v>
+        <v>436</v>
       </c>
       <c r="F90" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="I90" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J90">
         <v>8</v>
@@ -4585,27 +4507,27 @@
         <v>289472.8</v>
       </c>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="C91" t="s">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="D91" t="s">
-        <v>346</v>
+        <v>310</v>
       </c>
       <c r="E91" t="s">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="F91" t="s">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="I91" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J91">
         <v>1</v>
@@ -4617,27 +4539,27 @@
         <v>202984.86</v>
       </c>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C92" t="s">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="D92" t="s">
-        <v>347</v>
+        <v>311</v>
       </c>
       <c r="E92" t="s">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="F92" t="s">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="I92" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J92">
         <v>2</v>
@@ -4649,27 +4571,27 @@
         <v>197935.06</v>
       </c>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="C93" t="s">
-        <v>249</v>
+        <v>213</v>
       </c>
       <c r="D93" t="s">
-        <v>348</v>
+        <v>312</v>
       </c>
       <c r="E93" t="s">
-        <v>249</v>
+        <v>213</v>
       </c>
       <c r="F93" t="s">
-        <v>249</v>
+        <v>213</v>
       </c>
       <c r="I93" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J93">
         <v>4</v>
@@ -4681,27 +4603,27 @@
         <v>560000</v>
       </c>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="C94" t="s">
-        <v>249</v>
+        <v>213</v>
       </c>
       <c r="D94" t="s">
-        <v>349</v>
+        <v>313</v>
       </c>
       <c r="E94" t="s">
-        <v>249</v>
+        <v>213</v>
       </c>
       <c r="F94" t="s">
-        <v>249</v>
+        <v>213</v>
       </c>
       <c r="I94" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J94">
         <v>8</v>
@@ -4713,27 +4635,27 @@
         <v>480000</v>
       </c>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C95" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D95" t="s">
-        <v>350</v>
+        <v>314</v>
       </c>
       <c r="E95" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F95" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I95" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J95">
         <v>2</v>
@@ -4745,27 +4667,27 @@
         <v>366791.62</v>
       </c>
     </row>
-    <row r="96" spans="1:12">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="C96" t="s">
-        <v>224</v>
+        <v>188</v>
       </c>
       <c r="D96" t="s">
-        <v>351</v>
+        <v>315</v>
       </c>
       <c r="E96" t="s">
-        <v>224</v>
+        <v>188</v>
       </c>
       <c r="F96" t="s">
-        <v>224</v>
+        <v>188</v>
       </c>
       <c r="I96" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J96">
         <v>1</v>
@@ -4777,27 +4699,27 @@
         <v>561283.11</v>
       </c>
     </row>
-    <row r="97" spans="1:12">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="C97" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="D97" t="s">
-        <v>352</v>
+        <v>316</v>
       </c>
       <c r="E97" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="F97" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="I97" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J97">
         <v>2</v>
@@ -4806,30 +4728,30 @@
         <v>400703.47</v>
       </c>
       <c r="L97">
-        <v>801406.9399999999</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12">
+        <v>801406.94</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="C98" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D98" t="s">
-        <v>353</v>
+        <v>317</v>
       </c>
       <c r="E98" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F98" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I98" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J98">
         <v>21</v>
@@ -4841,27 +4763,27 @@
         <v>1309293.72</v>
       </c>
     </row>
-    <row r="99" spans="1:12">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="C99" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D99" t="s">
-        <v>354</v>
+        <v>318</v>
       </c>
       <c r="E99" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F99" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I99" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J99">
         <v>1</v>
@@ -4873,27 +4795,27 @@
         <v>339984.3</v>
       </c>
     </row>
-    <row r="100" spans="1:12">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D100" t="s">
-        <v>355</v>
+        <v>319</v>
       </c>
       <c r="E100" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F100" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I100" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J100">
         <v>3</v>
@@ -4905,27 +4827,27 @@
         <v>636143.97</v>
       </c>
     </row>
-    <row r="101" spans="1:12">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="C101" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D101" t="s">
-        <v>356</v>
+        <v>320</v>
       </c>
       <c r="E101" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F101" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I101" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J101">
         <v>1</v>
@@ -4937,27 +4859,27 @@
         <v>116716.34</v>
       </c>
     </row>
-    <row r="102" spans="1:12">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="C102" t="s">
-        <v>250</v>
+        <v>214</v>
       </c>
       <c r="D102" t="s">
-        <v>357</v>
+        <v>321</v>
       </c>
       <c r="E102" t="s">
-        <v>250</v>
+        <v>214</v>
       </c>
       <c r="F102" t="s">
-        <v>250</v>
+        <v>214</v>
       </c>
       <c r="I102" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J102">
         <v>1</v>
@@ -4969,27 +4891,27 @@
         <v>147576.31</v>
       </c>
     </row>
-    <row r="103" spans="1:12">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>13</v>
       </c>
       <c r="B103" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="C103" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="D103" t="s">
-        <v>358</v>
+        <v>322</v>
       </c>
       <c r="E103" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="F103" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="I103" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J103">
         <v>2</v>
@@ -5001,27 +4923,27 @@
         <v>51912.62</v>
       </c>
     </row>
-    <row r="104" spans="1:12">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>13</v>
       </c>
       <c r="B104" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="C104" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="D104" t="s">
-        <v>359</v>
+        <v>323</v>
       </c>
       <c r="E104" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="F104" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="I104" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J104">
         <v>2</v>
@@ -5033,27 +4955,27 @@
         <v>414447.78</v>
       </c>
     </row>
-    <row r="105" spans="1:12">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="C105" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="D105" t="s">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="E105" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="F105" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="I105" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J105">
         <v>13</v>
@@ -5065,27 +4987,27 @@
         <v>688914.46</v>
       </c>
     </row>
-    <row r="106" spans="1:12">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>13</v>
       </c>
       <c r="B106" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="C106" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D106" t="s">
-        <v>361</v>
+        <v>325</v>
       </c>
       <c r="E106" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F106" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I106" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J106">
         <v>3</v>
@@ -5094,62 +5016,62 @@
         <v>365807.37</v>
       </c>
       <c r="L106">
-        <v>1097422.11</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12">
+        <v>1097422.1100000001</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>13</v>
       </c>
       <c r="B107" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="C107" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="D107" t="s">
-        <v>362</v>
+        <v>326</v>
       </c>
       <c r="E107" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="F107" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="I107" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J107">
         <v>276</v>
       </c>
       <c r="K107">
-        <v>910.4400000000001</v>
+        <v>910.44</v>
       </c>
       <c r="L107">
         <v>251281.44</v>
       </c>
     </row>
-    <row r="108" spans="1:12">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C108" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="D108" t="s">
-        <v>363</v>
+        <v>327</v>
       </c>
       <c r="E108" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="F108" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="I108" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J108">
         <v>1</v>
@@ -5161,27 +5083,27 @@
         <v>61252.9</v>
       </c>
     </row>
-    <row r="109" spans="1:12">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="C109" t="s">
-        <v>252</v>
+        <v>216</v>
       </c>
       <c r="D109" t="s">
-        <v>364</v>
+        <v>328</v>
       </c>
       <c r="E109" t="s">
-        <v>472</v>
+        <v>436</v>
       </c>
       <c r="F109" t="s">
-        <v>252</v>
+        <v>216</v>
       </c>
       <c r="I109" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J109">
         <v>144</v>
@@ -5193,27 +5115,27 @@
         <v>1786872.96</v>
       </c>
     </row>
-    <row r="110" spans="1:12">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="C110" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="D110" t="s">
-        <v>365</v>
+        <v>329</v>
       </c>
       <c r="E110" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="F110" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="I110" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J110">
         <v>10</v>
@@ -5225,27 +5147,27 @@
         <v>822594.4</v>
       </c>
     </row>
-    <row r="111" spans="1:12">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="C111" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D111" t="s">
-        <v>366</v>
+        <v>330</v>
       </c>
       <c r="E111" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F111" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I111" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J111">
         <v>5</v>
@@ -5257,27 +5179,27 @@
         <v>219653</v>
       </c>
     </row>
-    <row r="112" spans="1:12">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="C112" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D112" t="s">
-        <v>367</v>
+        <v>331</v>
       </c>
       <c r="E112" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F112" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I112" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J112">
         <v>1</v>
@@ -5289,27 +5211,27 @@
         <v>78505.56</v>
       </c>
     </row>
-    <row r="113" spans="1:12">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="C113" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D113" t="s">
-        <v>368</v>
+        <v>332</v>
       </c>
       <c r="E113" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F113" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I113" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J113">
         <v>2</v>
@@ -5321,27 +5243,27 @@
         <v>507434.42</v>
       </c>
     </row>
-    <row r="114" spans="1:12">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>13</v>
       </c>
       <c r="B114" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="C114" t="s">
-        <v>252</v>
+        <v>216</v>
       </c>
       <c r="D114" t="s">
-        <v>369</v>
+        <v>333</v>
       </c>
       <c r="E114" t="s">
-        <v>252</v>
+        <v>216</v>
       </c>
       <c r="F114" t="s">
-        <v>252</v>
+        <v>216</v>
       </c>
       <c r="I114" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J114">
         <v>1</v>
@@ -5353,27 +5275,27 @@
         <v>462132.13</v>
       </c>
     </row>
-    <row r="115" spans="1:12">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>13</v>
       </c>
       <c r="B115" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="C115" t="s">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="D115" t="s">
-        <v>370</v>
+        <v>334</v>
       </c>
       <c r="E115" t="s">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="F115" t="s">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="I115" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J115">
         <v>1</v>
@@ -5385,27 +5307,27 @@
         <v>294400</v>
       </c>
     </row>
-    <row r="116" spans="1:12">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="C116" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="D116" t="s">
-        <v>371</v>
+        <v>335</v>
       </c>
       <c r="E116" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="F116" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="I116" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J116">
         <v>2</v>
@@ -5417,27 +5339,27 @@
         <v>617440.46</v>
       </c>
     </row>
-    <row r="117" spans="1:12">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="C117" t="s">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="D117" t="s">
-        <v>372</v>
+        <v>336</v>
       </c>
       <c r="E117" t="s">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="F117" t="s">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="I117" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J117">
         <v>4</v>
@@ -5449,59 +5371,59 @@
         <v>521697.04</v>
       </c>
     </row>
-    <row r="118" spans="1:12">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="C118" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="D118" t="s">
-        <v>373</v>
+        <v>337</v>
       </c>
       <c r="E118" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="F118" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="I118" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J118">
         <v>1</v>
       </c>
       <c r="K118">
-        <v>142359.27</v>
+        <v>142359.26999999999</v>
       </c>
       <c r="L118">
-        <v>142359.27</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12">
+        <v>142359.26999999999</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="C119" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="D119" t="s">
-        <v>374</v>
+        <v>338</v>
       </c>
       <c r="E119" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="F119" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="I119" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J119">
         <v>1</v>
@@ -5513,27 +5435,27 @@
         <v>2373776.35</v>
       </c>
     </row>
-    <row r="120" spans="1:12">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="C120" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="D120" t="s">
-        <v>375</v>
+        <v>339</v>
       </c>
       <c r="E120" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="F120" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="I120" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J120">
         <v>3</v>
@@ -5545,27 +5467,27 @@
         <v>459995.55</v>
       </c>
     </row>
-    <row r="121" spans="1:12">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>13</v>
       </c>
       <c r="B121" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="C121" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="D121" t="s">
-        <v>376</v>
+        <v>340</v>
       </c>
       <c r="E121" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="F121" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="I121" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J121">
         <v>5</v>
@@ -5577,27 +5499,27 @@
         <v>759137.5</v>
       </c>
     </row>
-    <row r="122" spans="1:12">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="C122" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="D122" t="s">
-        <v>377</v>
+        <v>341</v>
       </c>
       <c r="E122" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="F122" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="I122" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J122">
         <v>1</v>
@@ -5609,27 +5531,27 @@
         <v>126875.69</v>
       </c>
     </row>
-    <row r="123" spans="1:12">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>12</v>
       </c>
       <c r="B123" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="C123" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="D123" t="s">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="E123" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="F123" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="I123" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J123">
         <v>1</v>
@@ -5641,27 +5563,27 @@
         <v>418397.52</v>
       </c>
     </row>
-    <row r="124" spans="1:12">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="C124" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D124" t="s">
-        <v>379</v>
+        <v>343</v>
       </c>
       <c r="E124" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F124" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I124" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J124">
         <v>12</v>
@@ -5673,27 +5595,27 @@
         <v>730572.6</v>
       </c>
     </row>
-    <row r="125" spans="1:12">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="C125" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D125" t="s">
-        <v>380</v>
+        <v>344</v>
       </c>
       <c r="E125" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F125" t="s">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="I125" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J125">
         <v>1</v>
@@ -5705,27 +5627,27 @@
         <v>53403.02</v>
       </c>
     </row>
-    <row r="126" spans="1:12">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="C126" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D126" t="s">
-        <v>381</v>
+        <v>345</v>
       </c>
       <c r="E126" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F126" t="s">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="I126" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J126">
         <v>5</v>
@@ -5737,27 +5659,27 @@
         <v>404811.1</v>
       </c>
     </row>
-    <row r="127" spans="1:12">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>12</v>
       </c>
       <c r="B127" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="C127" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D127" t="s">
-        <v>382</v>
+        <v>346</v>
       </c>
       <c r="E127" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F127" t="s">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="I127" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J127">
         <v>3</v>
@@ -5769,27 +5691,27 @@
         <v>90050.37</v>
       </c>
     </row>
-    <row r="128" spans="1:12">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>12</v>
       </c>
       <c r="B128" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="C128" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D128" t="s">
-        <v>383</v>
+        <v>347</v>
       </c>
       <c r="E128" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F128" t="s">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="I128" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J128">
         <v>2</v>
@@ -5801,27 +5723,27 @@
         <v>111920.24</v>
       </c>
     </row>
-    <row r="129" spans="1:12">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>12</v>
       </c>
       <c r="B129" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="C129" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D129" t="s">
-        <v>384</v>
+        <v>348</v>
       </c>
       <c r="E129" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F129" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I129" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J129">
         <v>1</v>
@@ -5833,27 +5755,27 @@
         <v>57770.2</v>
       </c>
     </row>
-    <row r="130" spans="1:12">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>12</v>
       </c>
       <c r="B130" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="C130" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D130" t="s">
-        <v>385</v>
+        <v>349</v>
       </c>
       <c r="E130" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F130" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I130" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J130">
         <v>4</v>
@@ -5865,27 +5787,27 @@
         <v>488896.12</v>
       </c>
     </row>
-    <row r="131" spans="1:12">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>13</v>
       </c>
       <c r="B131" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="C131" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="D131" t="s">
-        <v>386</v>
+        <v>350</v>
       </c>
       <c r="E131" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="F131" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="I131" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J131">
         <v>2</v>
@@ -5897,27 +5819,27 @@
         <v>691199.98</v>
       </c>
     </row>
-    <row r="132" spans="1:12">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>13</v>
       </c>
       <c r="B132" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="C132" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="D132" t="s">
-        <v>387</v>
+        <v>351</v>
       </c>
       <c r="E132" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="F132" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="I132" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J132">
         <v>4</v>
@@ -5929,27 +5851,27 @@
         <v>1627909.6</v>
       </c>
     </row>
-    <row r="133" spans="1:12">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>13</v>
       </c>
       <c r="B133" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="C133" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D133" t="s">
-        <v>388</v>
+        <v>352</v>
       </c>
       <c r="E133" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F133" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I133" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J133">
         <v>1</v>
@@ -5961,59 +5883,59 @@
         <v>108921.66</v>
       </c>
     </row>
-    <row r="134" spans="1:12">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>12</v>
       </c>
       <c r="B134" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="C134" t="s">
-        <v>254</v>
+        <v>218</v>
       </c>
       <c r="D134" t="s">
-        <v>389</v>
+        <v>353</v>
       </c>
       <c r="E134" t="s">
-        <v>254</v>
+        <v>218</v>
       </c>
       <c r="F134" t="s">
-        <v>254</v>
+        <v>218</v>
       </c>
       <c r="I134" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J134">
         <v>1</v>
       </c>
       <c r="K134">
-        <v>155407.11</v>
+        <v>155407.10999999999</v>
       </c>
       <c r="L134">
-        <v>155407.11</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12">
+        <v>155407.10999999999</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>12</v>
       </c>
       <c r="B135" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="C135" t="s">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="D135" t="s">
-        <v>389</v>
+        <v>353</v>
       </c>
       <c r="E135" t="s">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="F135" t="s">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="I135" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J135">
         <v>2</v>
@@ -6025,27 +5947,27 @@
         <v>604613.96</v>
       </c>
     </row>
-    <row r="136" spans="1:12">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>12</v>
       </c>
       <c r="B136" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="C136" t="s">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="D136" t="s">
-        <v>390</v>
+        <v>354</v>
       </c>
       <c r="E136" t="s">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="F136" t="s">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="I136" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J136">
         <v>1</v>
@@ -6057,27 +5979,27 @@
         <v>462946.56</v>
       </c>
     </row>
-    <row r="137" spans="1:12">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>12</v>
       </c>
       <c r="B137" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="C137" t="s">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="D137" t="s">
-        <v>391</v>
+        <v>355</v>
       </c>
       <c r="E137" t="s">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="F137" t="s">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="I137" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J137">
         <v>1</v>
@@ -6089,27 +6011,27 @@
         <v>622170.75</v>
       </c>
     </row>
-    <row r="138" spans="1:12">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>12</v>
       </c>
-      <c r="B138" t="s">
-        <v>142</v>
+      <c r="B138" s="7">
+        <v>8968</v>
       </c>
       <c r="C138" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D138" t="s">
-        <v>392</v>
+        <v>356</v>
       </c>
       <c r="E138" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F138" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I138" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J138">
         <v>9</v>
@@ -6121,59 +6043,59 @@
         <v>65218.14</v>
       </c>
     </row>
-    <row r="139" spans="1:12">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>12</v>
       </c>
-      <c r="B139" t="s">
-        <v>143</v>
+      <c r="B139" s="7">
+        <v>15980</v>
       </c>
       <c r="C139" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D139" t="s">
-        <v>393</v>
+        <v>357</v>
       </c>
       <c r="E139" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F139" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I139" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J139">
         <v>22</v>
       </c>
       <c r="K139">
-        <v>9200.629999999999</v>
+        <v>9200.6299999999992</v>
       </c>
       <c r="L139">
         <v>202413.86</v>
       </c>
     </row>
-    <row r="140" spans="1:12">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>13</v>
       </c>
-      <c r="B140" t="s">
-        <v>144</v>
+      <c r="B140" s="7">
+        <v>83726</v>
       </c>
       <c r="C140" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="D140" t="s">
-        <v>394</v>
+        <v>358</v>
       </c>
       <c r="E140" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="F140" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="I140" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J140">
         <v>6</v>
@@ -6182,62 +6104,62 @@
         <v>13906.96</v>
       </c>
       <c r="L140">
-        <v>83441.75999999999</v>
-      </c>
-    </row>
-    <row r="141" spans="1:12">
+        <v>83441.759999999995</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>12</v>
       </c>
-      <c r="B141" t="s">
-        <v>145</v>
+      <c r="B141" s="7">
+        <v>127760</v>
       </c>
       <c r="C141" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D141" t="s">
-        <v>395</v>
+        <v>359</v>
       </c>
       <c r="E141" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F141" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="I141" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J141">
         <v>10</v>
       </c>
       <c r="K141">
-        <v>67728.10000000001</v>
+        <v>67728.100000000006</v>
       </c>
       <c r="L141">
         <v>677281</v>
       </c>
     </row>
-    <row r="142" spans="1:12">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>12</v>
       </c>
-      <c r="B142" t="s">
-        <v>146</v>
+      <c r="B142" s="7">
+        <v>4301795</v>
       </c>
       <c r="C142" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D142" t="s">
-        <v>396</v>
+        <v>360</v>
       </c>
       <c r="E142" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F142" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I142" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J142">
         <v>4</v>
@@ -6249,27 +6171,27 @@
         <v>2164667.52</v>
       </c>
     </row>
-    <row r="143" spans="1:12">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="C143" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D143" t="s">
-        <v>397</v>
+        <v>361</v>
       </c>
       <c r="E143" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F143" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I143" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J143">
         <v>2</v>
@@ -6281,27 +6203,27 @@
         <v>63260.02</v>
       </c>
     </row>
-    <row r="144" spans="1:12">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>13</v>
       </c>
       <c r="B144" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="C144" t="s">
-        <v>257</v>
+        <v>221</v>
       </c>
       <c r="D144" t="s">
-        <v>398</v>
+        <v>362</v>
       </c>
       <c r="E144" t="s">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="F144" t="s">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="I144" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J144">
         <v>2</v>
@@ -6313,27 +6235,27 @@
         <v>214209.36</v>
       </c>
     </row>
-    <row r="145" spans="1:12">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="C145" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D145" t="s">
-        <v>399</v>
+        <v>363</v>
       </c>
       <c r="E145" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F145" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I145" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J145">
         <v>1</v>
@@ -6345,27 +6267,27 @@
         <v>221067.08</v>
       </c>
     </row>
-    <row r="146" spans="1:12">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>12</v>
       </c>
       <c r="B146" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="C146" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D146" t="s">
-        <v>400</v>
+        <v>364</v>
       </c>
       <c r="E146" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F146" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I146" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J146">
         <v>1</v>
@@ -6377,59 +6299,59 @@
         <v>204405.71</v>
       </c>
     </row>
-    <row r="147" spans="1:12">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>13</v>
       </c>
       <c r="B147" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="C147" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="D147" t="s">
-        <v>401</v>
+        <v>365</v>
       </c>
       <c r="E147" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="F147" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="I147" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J147">
         <v>1</v>
       </c>
       <c r="K147">
-        <v>151612.17</v>
+        <v>151612.17000000001</v>
       </c>
       <c r="L147">
-        <v>151612.17</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12">
+        <v>151612.17000000001</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="C148" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D148" t="s">
-        <v>402</v>
+        <v>366</v>
       </c>
       <c r="E148" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F148" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I148" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J148">
         <v>5</v>
@@ -6441,27 +6363,27 @@
         <v>762827.65</v>
       </c>
     </row>
-    <row r="149" spans="1:12">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="C149" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D149" t="s">
-        <v>403</v>
+        <v>367</v>
       </c>
       <c r="E149" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F149" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I149" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J149">
         <v>3</v>
@@ -6473,27 +6395,27 @@
         <v>1945034.13</v>
       </c>
     </row>
-    <row r="150" spans="1:12">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="C150" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D150" t="s">
-        <v>404</v>
+        <v>368</v>
       </c>
       <c r="E150" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F150" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I150" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J150">
         <v>4</v>
@@ -6505,27 +6427,27 @@
         <v>245098.76</v>
       </c>
     </row>
-    <row r="151" spans="1:12">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="C151" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="D151" t="s">
-        <v>405</v>
+        <v>369</v>
       </c>
       <c r="E151" t="s">
-        <v>474</v>
+        <v>438</v>
       </c>
       <c r="F151" t="s">
-        <v>474</v>
+        <v>438</v>
       </c>
       <c r="I151" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J151">
         <v>1</v>
@@ -6537,27 +6459,27 @@
         <v>134461.16</v>
       </c>
     </row>
-    <row r="152" spans="1:12">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>13</v>
       </c>
       <c r="B152" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="C152" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D152" t="s">
-        <v>406</v>
+        <v>370</v>
       </c>
       <c r="E152" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F152" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I152" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J152">
         <v>1</v>
@@ -6569,27 +6491,27 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="153" spans="1:12">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="C153" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D153" t="s">
-        <v>407</v>
+        <v>371</v>
       </c>
       <c r="E153" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F153" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I153" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J153">
         <v>1</v>
@@ -6601,59 +6523,59 @@
         <v>437278.29</v>
       </c>
     </row>
-    <row r="154" spans="1:12">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="C154" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D154" t="s">
-        <v>408</v>
+        <v>372</v>
       </c>
       <c r="E154" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F154" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I154" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J154">
         <v>10</v>
       </c>
       <c r="K154">
-        <v>68988.75999999999</v>
+        <v>68988.759999999995</v>
       </c>
       <c r="L154">
         <v>689887.6</v>
       </c>
     </row>
-    <row r="155" spans="1:12">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="C155" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D155" t="s">
-        <v>409</v>
+        <v>373</v>
       </c>
       <c r="E155" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F155" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I155" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J155">
         <v>2</v>
@@ -6665,27 +6587,27 @@
         <v>642123.22</v>
       </c>
     </row>
-    <row r="156" spans="1:12">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>13</v>
       </c>
       <c r="B156" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="C156" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D156" t="s">
-        <v>410</v>
+        <v>374</v>
       </c>
       <c r="E156" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F156" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I156" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J156">
         <v>1</v>
@@ -6697,91 +6619,91 @@
         <v>86292.41</v>
       </c>
     </row>
-    <row r="157" spans="1:12">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>13</v>
       </c>
       <c r="B157" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="C157" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="D157" t="s">
-        <v>411</v>
+        <v>375</v>
       </c>
       <c r="E157" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="F157" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="I157" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J157">
         <v>3</v>
       </c>
       <c r="K157">
-        <v>275914.15</v>
+        <v>275914.15000000002</v>
       </c>
       <c r="L157">
         <v>827742.45</v>
       </c>
     </row>
-    <row r="158" spans="1:12">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="C158" t="s">
-        <v>258</v>
+        <v>222</v>
       </c>
       <c r="D158" t="s">
-        <v>412</v>
+        <v>376</v>
       </c>
       <c r="E158" t="s">
-        <v>475</v>
+        <v>439</v>
       </c>
       <c r="F158" t="s">
-        <v>475</v>
+        <v>439</v>
       </c>
       <c r="I158" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J158">
         <v>1</v>
       </c>
       <c r="K158">
-        <v>145438.64</v>
+        <v>145438.64000000001</v>
       </c>
       <c r="L158">
-        <v>145438.64</v>
-      </c>
-    </row>
-    <row r="159" spans="1:12">
+        <v>145438.64000000001</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="C159" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D159" t="s">
-        <v>413</v>
+        <v>377</v>
       </c>
       <c r="E159" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F159" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I159" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J159">
         <v>16</v>
@@ -6793,27 +6715,27 @@
         <v>1988155.84</v>
       </c>
     </row>
-    <row r="160" spans="1:12">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>13</v>
       </c>
       <c r="B160" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="C160" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="D160" t="s">
-        <v>414</v>
+        <v>378</v>
       </c>
       <c r="E160" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="F160" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="I160" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J160">
         <v>1</v>
@@ -6825,27 +6747,27 @@
         <v>127385.01</v>
       </c>
     </row>
-    <row r="161" spans="1:12">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="C161" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D161" t="s">
-        <v>415</v>
+        <v>379</v>
       </c>
       <c r="E161" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F161" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I161" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J161">
         <v>2</v>
@@ -6854,30 +6776,30 @@
         <v>409485.91</v>
       </c>
       <c r="L161">
-        <v>818971.8199999999</v>
-      </c>
-    </row>
-    <row r="162" spans="1:12">
+        <v>818971.82</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>13</v>
       </c>
       <c r="B162" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="C162" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D162" t="s">
-        <v>416</v>
+        <v>380</v>
       </c>
       <c r="E162" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F162" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I162" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J162">
         <v>1</v>
@@ -6889,27 +6811,27 @@
         <v>411573.74</v>
       </c>
     </row>
-    <row r="163" spans="1:12">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="C163" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="D163" t="s">
-        <v>417</v>
+        <v>381</v>
       </c>
       <c r="E163" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="F163" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="I163" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J163">
         <v>2</v>
@@ -6921,27 +6843,27 @@
         <v>355858.56</v>
       </c>
     </row>
-    <row r="164" spans="1:12">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="C164" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
       <c r="D164" t="s">
-        <v>418</v>
+        <v>382</v>
       </c>
       <c r="E164" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
       <c r="F164" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
       <c r="I164" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J164">
         <v>2</v>
@@ -6953,27 +6875,27 @@
         <v>773950.14</v>
       </c>
     </row>
-    <row r="165" spans="1:12">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="C165" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D165" t="s">
-        <v>419</v>
+        <v>383</v>
       </c>
       <c r="E165" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F165" t="s">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="I165" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J165">
         <v>4</v>
@@ -6985,27 +6907,27 @@
         <v>267935.2</v>
       </c>
     </row>
-    <row r="166" spans="1:12">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="C166" t="s">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="D166" t="s">
-        <v>420</v>
+        <v>384</v>
       </c>
       <c r="E166" t="s">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="F166" t="s">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="I166" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J166">
         <v>1</v>
@@ -7017,27 +6939,27 @@
         <v>159709.51</v>
       </c>
     </row>
-    <row r="167" spans="1:12">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>13</v>
       </c>
-      <c r="B167" t="s">
-        <v>171</v>
+      <c r="B167" s="7">
+        <v>13653</v>
       </c>
       <c r="C167" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D167" t="s">
-        <v>421</v>
+        <v>385</v>
       </c>
       <c r="E167" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F167" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I167" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J167">
         <v>38</v>
@@ -7049,59 +6971,59 @@
         <v>93989.58</v>
       </c>
     </row>
-    <row r="168" spans="1:12">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>13</v>
       </c>
-      <c r="B168" t="s">
-        <v>172</v>
+      <c r="B168" s="7">
+        <v>328349</v>
       </c>
       <c r="C168" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="D168" t="s">
-        <v>422</v>
+        <v>386</v>
       </c>
       <c r="E168" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="F168" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="I168" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J168">
         <v>1</v>
       </c>
       <c r="K168">
-        <v>636180.6800000001</v>
+        <v>636180.68000000005</v>
       </c>
       <c r="L168">
-        <v>636180.6800000001</v>
-      </c>
-    </row>
-    <row r="169" spans="1:12">
+        <v>636180.68000000005</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>12</v>
       </c>
-      <c r="B169" t="s">
-        <v>173</v>
+      <c r="B169" s="7">
+        <v>4303603</v>
       </c>
       <c r="C169" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D169" t="s">
-        <v>423</v>
+        <v>387</v>
       </c>
       <c r="E169" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F169" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I169" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J169">
         <v>3</v>
@@ -7110,126 +7032,126 @@
         <v>27987.95</v>
       </c>
       <c r="L169">
-        <v>83963.85000000001</v>
-      </c>
-    </row>
-    <row r="170" spans="1:12">
+        <v>83963.85</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>12</v>
       </c>
-      <c r="B170" t="s">
-        <v>174</v>
+      <c r="B170" s="7">
+        <v>5566510</v>
       </c>
       <c r="C170" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="D170" t="s">
-        <v>424</v>
+        <v>388</v>
       </c>
       <c r="E170" t="s">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="F170" t="s">
-        <v>477</v>
+        <v>441</v>
       </c>
       <c r="I170" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J170">
         <v>10</v>
       </c>
       <c r="K170">
-        <v>274730.29</v>
+        <v>274730.28999999998</v>
       </c>
       <c r="L170">
         <v>2747302.9</v>
       </c>
     </row>
-    <row r="171" spans="1:12">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>13</v>
       </c>
-      <c r="B171" t="s">
-        <v>175</v>
+      <c r="B171" s="7">
+        <v>5568529</v>
       </c>
       <c r="C171" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D171" t="s">
-        <v>425</v>
+        <v>389</v>
       </c>
       <c r="E171" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F171" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I171" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J171">
         <v>10</v>
       </c>
       <c r="K171">
-        <v>5073.44</v>
+        <v>5073.4399999999996</v>
       </c>
       <c r="L171">
-        <v>50734.4</v>
-      </c>
-    </row>
-    <row r="172" spans="1:12">
+        <v>50734.400000000001</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>13</v>
       </c>
       <c r="B172" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="C172" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="D172" t="s">
-        <v>426</v>
+        <v>390</v>
       </c>
       <c r="E172" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="F172" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="I172" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J172">
         <v>6</v>
       </c>
       <c r="K172">
-        <v>271098.72</v>
+        <v>271098.71999999997</v>
       </c>
       <c r="L172">
         <v>1626592.32</v>
       </c>
     </row>
-    <row r="173" spans="1:12">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>12</v>
       </c>
       <c r="B173" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="C173" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D173" t="s">
-        <v>427</v>
+        <v>391</v>
       </c>
       <c r="E173" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F173" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I173" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J173">
         <v>8</v>
@@ -7241,27 +7163,27 @@
         <v>171120.96</v>
       </c>
     </row>
-    <row r="174" spans="1:12">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="C174" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="D174" t="s">
-        <v>428</v>
+        <v>392</v>
       </c>
       <c r="E174" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F174" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="I174" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J174">
         <v>1</v>
@@ -7273,27 +7195,27 @@
         <v>325882.63</v>
       </c>
     </row>
-    <row r="175" spans="1:12">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="C175" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D175" t="s">
-        <v>429</v>
+        <v>393</v>
       </c>
       <c r="E175" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F175" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I175" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J175">
         <v>2</v>
@@ -7305,27 +7227,27 @@
         <v>133578.22</v>
       </c>
     </row>
-    <row r="176" spans="1:12">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="C176" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D176" t="s">
-        <v>430</v>
+        <v>394</v>
       </c>
       <c r="E176" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F176" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I176" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J176">
         <v>3</v>
@@ -7337,123 +7259,123 @@
         <v>235406.73</v>
       </c>
     </row>
-    <row r="177" spans="1:12">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>12</v>
       </c>
       <c r="B177" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="C177" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D177" t="s">
-        <v>431</v>
+        <v>395</v>
       </c>
       <c r="E177" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F177" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I177" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J177">
         <v>3</v>
       </c>
       <c r="K177">
-        <v>263646.09</v>
+        <v>263646.09000000003</v>
       </c>
       <c r="L177">
         <v>790938.27</v>
       </c>
     </row>
-    <row r="178" spans="1:12">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>12</v>
       </c>
       <c r="B178" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="C178" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D178" t="s">
-        <v>334</v>
+        <v>298</v>
       </c>
       <c r="E178" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F178" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I178" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J178">
         <v>2</v>
       </c>
       <c r="K178">
-        <v>271387.84</v>
+        <v>271387.84000000003</v>
       </c>
       <c r="L178">
-        <v>542775.6800000001</v>
-      </c>
-    </row>
-    <row r="179" spans="1:12">
+        <v>542775.68000000005</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>12</v>
       </c>
       <c r="B179" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="C179" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D179" t="s">
-        <v>432</v>
+        <v>396</v>
       </c>
       <c r="E179" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F179" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I179" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J179">
         <v>3</v>
       </c>
       <c r="K179">
-        <v>73037.78999999999</v>
+        <v>73037.789999999994</v>
       </c>
       <c r="L179">
         <v>219113.37</v>
       </c>
     </row>
-    <row r="180" spans="1:12">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>13</v>
       </c>
       <c r="B180" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="C180" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D180" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="E180" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F180" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I180" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J180">
         <v>14</v>
@@ -7465,59 +7387,59 @@
         <v>98696.36</v>
       </c>
     </row>
-    <row r="181" spans="1:12">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>12</v>
       </c>
       <c r="B181" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="C181" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D181" t="s">
-        <v>434</v>
+        <v>398</v>
       </c>
       <c r="E181" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F181" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I181" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J181">
         <v>11</v>
       </c>
       <c r="K181">
-        <v>73190.35000000001</v>
+        <v>73190.350000000006</v>
       </c>
       <c r="L181">
         <v>805093.85</v>
       </c>
     </row>
-    <row r="182" spans="1:12">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>12</v>
       </c>
       <c r="B182" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="C182" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="D182" t="s">
-        <v>435</v>
+        <v>399</v>
       </c>
       <c r="E182" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="F182" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="I182" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J182">
         <v>2</v>
@@ -7529,27 +7451,27 @@
         <v>257718.9</v>
       </c>
     </row>
-    <row r="183" spans="1:12">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>12</v>
       </c>
       <c r="B183" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="C183" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="D183" t="s">
-        <v>436</v>
+        <v>400</v>
       </c>
       <c r="E183" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="F183" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="I183" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J183">
         <v>1</v>
@@ -7561,59 +7483,59 @@
         <v>451021.21</v>
       </c>
     </row>
-    <row r="184" spans="1:12">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="C184" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D184" t="s">
-        <v>437</v>
+        <v>401</v>
       </c>
       <c r="E184" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F184" t="s">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="I184" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J184">
         <v>3</v>
       </c>
       <c r="K184">
-        <v>76547.52</v>
+        <v>76547.520000000004</v>
       </c>
       <c r="L184">
         <v>229642.56</v>
       </c>
     </row>
-    <row r="185" spans="1:12">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>12</v>
       </c>
       <c r="B185" t="s">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="C185" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D185" t="s">
-        <v>438</v>
+        <v>402</v>
       </c>
       <c r="E185" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F185" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I185" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J185">
         <v>1</v>
@@ -7625,59 +7547,59 @@
         <v>116937.56</v>
       </c>
     </row>
-    <row r="186" spans="1:12">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>12</v>
       </c>
       <c r="B186" t="s">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="C186" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D186" t="s">
-        <v>439</v>
+        <v>403</v>
       </c>
       <c r="E186" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F186" t="s">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="I186" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J186">
         <v>7</v>
       </c>
       <c r="K186">
-        <v>98083.52</v>
+        <v>98083.520000000004</v>
       </c>
       <c r="L186">
         <v>686584.64</v>
       </c>
     </row>
-    <row r="187" spans="1:12">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>13</v>
       </c>
       <c r="B187" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="C187" t="s">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="D187" t="s">
-        <v>440</v>
+        <v>404</v>
       </c>
       <c r="E187" t="s">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="F187" t="s">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="I187" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J187">
         <v>1</v>
@@ -7689,27 +7611,27 @@
         <v>167744.87</v>
       </c>
     </row>
-    <row r="188" spans="1:12">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>12</v>
       </c>
       <c r="B188" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="C188" t="s">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="D188" t="s">
-        <v>441</v>
+        <v>405</v>
       </c>
       <c r="E188" t="s">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="F188" t="s">
-        <v>478</v>
+        <v>442</v>
       </c>
       <c r="I188" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J188">
         <v>6</v>
@@ -7718,62 +7640,62 @@
         <v>23661.7</v>
       </c>
       <c r="L188">
-        <v>141970.2</v>
-      </c>
-    </row>
-    <row r="189" spans="1:12">
+        <v>141970.20000000001</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>12</v>
       </c>
-      <c r="B189" t="s">
-        <v>193</v>
+      <c r="B189" s="7">
+        <v>4300119</v>
       </c>
       <c r="C189" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D189" t="s">
-        <v>442</v>
+        <v>406</v>
       </c>
       <c r="E189" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F189" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I189" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J189">
         <v>6</v>
       </c>
       <c r="K189">
-        <v>20116.83</v>
+        <v>20116.830000000002</v>
       </c>
       <c r="L189">
         <v>120700.98</v>
       </c>
     </row>
-    <row r="190" spans="1:12">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>12</v>
       </c>
       <c r="B190" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="C190" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D190" t="s">
-        <v>443</v>
+        <v>407</v>
       </c>
       <c r="E190" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F190" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I190" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J190">
         <v>4</v>
@@ -7785,27 +7707,27 @@
         <v>240041.4</v>
       </c>
     </row>
-    <row r="191" spans="1:12">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>12</v>
       </c>
       <c r="B191" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="C191" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D191" t="s">
-        <v>444</v>
+        <v>408</v>
       </c>
       <c r="E191" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F191" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I191" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J191">
         <v>2</v>
@@ -7817,27 +7739,27 @@
         <v>200992.56</v>
       </c>
     </row>
-    <row r="192" spans="1:12">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>12</v>
       </c>
       <c r="B192" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="C192" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D192" t="s">
-        <v>445</v>
+        <v>409</v>
       </c>
       <c r="E192" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F192" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I192" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J192">
         <v>40</v>
@@ -7849,27 +7771,27 @@
         <v>427367.2</v>
       </c>
     </row>
-    <row r="193" spans="1:12">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>12</v>
       </c>
       <c r="B193" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="C193" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D193" t="s">
-        <v>446</v>
+        <v>410</v>
       </c>
       <c r="E193" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F193" t="s">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="I193" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J193">
         <v>1</v>
@@ -7881,27 +7803,27 @@
         <v>128320.65</v>
       </c>
     </row>
-    <row r="194" spans="1:12">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>12</v>
       </c>
       <c r="B194" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="C194" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D194" t="s">
-        <v>350</v>
+        <v>314</v>
       </c>
       <c r="E194" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F194" t="s">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="I194" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J194">
         <v>6</v>
@@ -7913,27 +7835,27 @@
         <v>939898.26</v>
       </c>
     </row>
-    <row r="195" spans="1:12">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>12</v>
       </c>
       <c r="B195" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="C195" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D195" t="s">
-        <v>447</v>
+        <v>411</v>
       </c>
       <c r="E195" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F195" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I195" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J195">
         <v>2</v>
@@ -7945,27 +7867,27 @@
         <v>184387.62</v>
       </c>
     </row>
-    <row r="196" spans="1:12">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>12</v>
       </c>
       <c r="B196" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="C196" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D196" t="s">
-        <v>448</v>
+        <v>412</v>
       </c>
       <c r="E196" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F196" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I196" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J196">
         <v>11</v>
@@ -7977,27 +7899,27 @@
         <v>1098179.83</v>
       </c>
     </row>
-    <row r="197" spans="1:12">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>13</v>
       </c>
       <c r="B197" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="C197" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="D197" t="s">
-        <v>449</v>
+        <v>413</v>
       </c>
       <c r="E197" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="F197" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="I197" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J197">
         <v>6</v>
@@ -8009,27 +7931,27 @@
         <v>144779.28</v>
       </c>
     </row>
-    <row r="198" spans="1:12">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>12</v>
       </c>
       <c r="B198" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C198" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D198" t="s">
-        <v>450</v>
+        <v>414</v>
       </c>
       <c r="E198" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F198" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I198" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J198">
         <v>1</v>
@@ -8041,27 +7963,27 @@
         <v>477767.5</v>
       </c>
     </row>
-    <row r="199" spans="1:12">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>13</v>
       </c>
       <c r="B199" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="D199" t="s">
-        <v>451</v>
+        <v>415</v>
       </c>
       <c r="E199" t="s">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="F199" t="s">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="I199" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J199">
         <v>4</v>
@@ -8073,27 +7995,27 @@
         <v>476474.6</v>
       </c>
     </row>
-    <row r="200" spans="1:12">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>12</v>
       </c>
-      <c r="B200" t="s">
-        <v>204</v>
+      <c r="B200" s="7">
+        <v>85003</v>
       </c>
       <c r="C200" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D200" t="s">
-        <v>452</v>
+        <v>416</v>
       </c>
       <c r="E200" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F200" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I200" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J200">
         <v>11</v>
@@ -8102,30 +8024,30 @@
         <v>12254.05</v>
       </c>
       <c r="L200">
-        <v>134794.55</v>
-      </c>
-    </row>
-    <row r="201" spans="1:12">
+        <v>134794.54999999999</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>13</v>
       </c>
-      <c r="B201" t="s">
-        <v>205</v>
+      <c r="B201" s="7">
+        <v>10021566</v>
       </c>
       <c r="C201" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="D201" t="s">
-        <v>453</v>
+        <v>417</v>
       </c>
       <c r="E201" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="F201" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
       <c r="I201" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J201">
         <v>97</v>
@@ -8137,27 +8059,27 @@
         <v>198228.23</v>
       </c>
     </row>
-    <row r="202" spans="1:12">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>12</v>
       </c>
       <c r="B202" t="s">
-        <v>206</v>
+        <v>172</v>
       </c>
       <c r="C202" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D202" t="s">
-        <v>454</v>
+        <v>418</v>
       </c>
       <c r="E202" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F202" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I202" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J202">
         <v>2</v>
@@ -8169,27 +8091,27 @@
         <v>114038.58</v>
       </c>
     </row>
-    <row r="203" spans="1:12">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>12</v>
       </c>
       <c r="B203" t="s">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="C203" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D203" t="s">
-        <v>455</v>
+        <v>419</v>
       </c>
       <c r="E203" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F203" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I203" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J203">
         <v>4</v>
@@ -8201,27 +8123,27 @@
         <v>219162.96</v>
       </c>
     </row>
-    <row r="204" spans="1:12">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>12</v>
       </c>
       <c r="B204" t="s">
-        <v>208</v>
+        <v>174</v>
       </c>
       <c r="C204" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D204" t="s">
-        <v>456</v>
+        <v>420</v>
       </c>
       <c r="E204" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F204" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I204" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J204">
         <v>1</v>
@@ -8233,27 +8155,27 @@
         <v>276872.24</v>
       </c>
     </row>
-    <row r="205" spans="1:12">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>13</v>
       </c>
       <c r="B205" t="s">
-        <v>209</v>
+        <v>175</v>
       </c>
       <c r="C205" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="D205" t="s">
-        <v>457</v>
+        <v>421</v>
       </c>
       <c r="E205" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="F205" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="I205" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J205">
         <v>1</v>
@@ -8265,59 +8187,59 @@
         <v>228580.22</v>
       </c>
     </row>
-    <row r="206" spans="1:12">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>13</v>
       </c>
       <c r="B206" t="s">
-        <v>210</v>
+        <v>176</v>
       </c>
       <c r="C206" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="D206" t="s">
-        <v>458</v>
+        <v>422</v>
       </c>
       <c r="E206" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="F206" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="I206" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J206">
         <v>1</v>
       </c>
       <c r="K206">
-        <v>588448.45</v>
+        <v>588448.44999999995</v>
       </c>
       <c r="L206">
-        <v>588448.45</v>
-      </c>
-    </row>
-    <row r="207" spans="1:12">
+        <v>588448.44999999995</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>12</v>
       </c>
       <c r="B207" t="s">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="C207" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D207" t="s">
-        <v>459</v>
+        <v>423</v>
       </c>
       <c r="E207" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F207" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I207" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J207">
         <v>2</v>
@@ -8329,27 +8251,27 @@
         <v>343808.48</v>
       </c>
     </row>
-    <row r="208" spans="1:12">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>13</v>
       </c>
       <c r="B208" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="D208" t="s">
-        <v>460</v>
+        <v>424</v>
       </c>
       <c r="E208" t="s">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="F208" t="s">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="I208" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J208">
         <v>1</v>
@@ -8361,27 +8283,27 @@
         <v>52120.37</v>
       </c>
     </row>
-    <row r="209" spans="1:12">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>12</v>
       </c>
       <c r="B209" t="s">
-        <v>213</v>
+        <v>179</v>
       </c>
       <c r="C209" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D209" t="s">
-        <v>461</v>
+        <v>425</v>
       </c>
       <c r="E209" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F209" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I209" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J209">
         <v>1</v>
@@ -8393,27 +8315,27 @@
         <v>907492.78</v>
       </c>
     </row>
-    <row r="210" spans="1:12">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>13</v>
       </c>
       <c r="B210" t="s">
-        <v>214</v>
+        <v>180</v>
       </c>
       <c r="C210" t="s">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="D210" t="s">
-        <v>462</v>
+        <v>426</v>
       </c>
       <c r="E210" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="F210" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="I210" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J210">
         <v>2</v>
@@ -8425,27 +8347,27 @@
         <v>236003.46</v>
       </c>
     </row>
-    <row r="211" spans="1:12">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>13</v>
       </c>
       <c r="B211" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="C211" t="s">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="D211" t="s">
-        <v>463</v>
+        <v>427</v>
       </c>
       <c r="E211" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="F211" t="s">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="I211" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J211">
         <v>1</v>
@@ -8457,27 +8379,27 @@
         <v>56470.99</v>
       </c>
     </row>
-    <row r="212" spans="1:12">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="C212" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="D212" t="s">
-        <v>464</v>
+        <v>428</v>
       </c>
       <c r="E212" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="F212" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I212" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J212">
         <v>6</v>
@@ -8489,27 +8411,27 @@
         <v>121897.62</v>
       </c>
     </row>
-    <row r="213" spans="1:12">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>217</v>
+        <v>183</v>
       </c>
       <c r="C213" t="s">
-        <v>262</v>
+        <v>226</v>
       </c>
       <c r="D213" t="s">
-        <v>465</v>
+        <v>429</v>
       </c>
       <c r="E213" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F213" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I213" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J213">
         <v>1</v>
@@ -8521,27 +8443,27 @@
         <v>64719.29</v>
       </c>
     </row>
-    <row r="214" spans="1:12">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>12</v>
       </c>
-      <c r="B214" t="s">
-        <v>218</v>
+      <c r="B214" s="7">
+        <v>4303424</v>
       </c>
       <c r="C214" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D214" t="s">
-        <v>466</v>
+        <v>430</v>
       </c>
       <c r="E214" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F214" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I214" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J214">
         <v>5</v>
@@ -8553,27 +8475,27 @@
         <v>77158.45</v>
       </c>
     </row>
-    <row r="215" spans="1:12">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>12</v>
       </c>
-      <c r="B215" t="s">
-        <v>219</v>
+      <c r="B215" s="7">
+        <v>16980</v>
       </c>
       <c r="C215" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D215" t="s">
-        <v>467</v>
+        <v>431</v>
       </c>
       <c r="E215" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="F215" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I215" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J215">
         <v>23</v>
@@ -8585,59 +8507,59 @@
         <v>68982.98</v>
       </c>
     </row>
-    <row r="216" spans="1:12">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="C216" t="s">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="D216" t="s">
-        <v>468</v>
+        <v>432</v>
       </c>
       <c r="E216" t="s">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="F216" t="s">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="I216" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J216">
         <v>4</v>
       </c>
       <c r="K216">
-        <v>40143.73</v>
+        <v>40143.730000000003</v>
       </c>
       <c r="L216">
-        <v>160574.92</v>
-      </c>
-    </row>
-    <row r="217" spans="1:12">
+        <v>160574.92000000001</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>13</v>
       </c>
       <c r="B217" t="s">
-        <v>221</v>
+        <v>185</v>
       </c>
       <c r="C217" t="s">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="D217" t="s">
-        <v>469</v>
+        <v>433</v>
       </c>
       <c r="E217" t="s">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="F217" t="s">
-        <v>477</v>
+        <v>441</v>
       </c>
       <c r="I217" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J217">
         <v>1</v>
@@ -8649,27 +8571,27 @@
         <v>259475.34</v>
       </c>
     </row>
-    <row r="218" spans="1:12">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>13</v>
       </c>
       <c r="B218" t="s">
-        <v>222</v>
+        <v>186</v>
       </c>
       <c r="C218" t="s">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="D218" t="s">
-        <v>470</v>
+        <v>434</v>
       </c>
       <c r="E218" t="s">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="F218" t="s">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="I218" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J218">
         <v>2</v>
@@ -8681,27 +8603,27 @@
         <v>224000</v>
       </c>
     </row>
-    <row r="219" spans="1:12">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>13</v>
       </c>
       <c r="B219" t="s">
-        <v>223</v>
+        <v>187</v>
       </c>
       <c r="C219" t="s">
-        <v>265</v>
+        <v>229</v>
       </c>
       <c r="D219" t="s">
-        <v>471</v>
+        <v>435</v>
       </c>
       <c r="E219" t="s">
-        <v>265</v>
+        <v>229</v>
       </c>
       <c r="F219" t="s">
-        <v>265</v>
+        <v>229</v>
       </c>
       <c r="I219" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="J219">
         <v>6</v>

--- a/VALORIZADO FALTANTES.xlsx
+++ b/VALORIZADO FALTANTES.xlsx
@@ -1,39 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jlopez\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{337E83A5-A696-4C48-907A-C0260E1F5203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Valorizado" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="488">
   <si>
     <t>Categoría</t>
   </si>
@@ -77,6 +58,69 @@
     <t>Categoría producto</t>
   </si>
   <si>
+    <t>9373</t>
+  </si>
+  <si>
+    <t>16866</t>
+  </si>
+  <si>
+    <t>21360</t>
+  </si>
+  <si>
+    <t>131973</t>
+  </si>
+  <si>
+    <t>691445</t>
+  </si>
+  <si>
+    <t>691934</t>
+  </si>
+  <si>
+    <t>994349</t>
+  </si>
+  <si>
+    <t>994370</t>
+  </si>
+  <si>
+    <t>3344768</t>
+  </si>
+  <si>
+    <t>3344862</t>
+  </si>
+  <si>
+    <t>4301467</t>
+  </si>
+  <si>
+    <t>4301762</t>
+  </si>
+  <si>
+    <t>4302411</t>
+  </si>
+  <si>
+    <t>4302484</t>
+  </si>
+  <si>
+    <t>4302506</t>
+  </si>
+  <si>
+    <t>4303357</t>
+  </si>
+  <si>
+    <t>4303428</t>
+  </si>
+  <si>
+    <t>4303476</t>
+  </si>
+  <si>
+    <t>4303825</t>
+  </si>
+  <si>
+    <t>4304499</t>
+  </si>
+  <si>
+    <t>4304641</t>
+  </si>
+  <si>
     <t>K3454/7349</t>
   </si>
   <si>
@@ -398,6 +442,21 @@
     <t>WAB9111549202</t>
   </si>
   <si>
+    <t>8968</t>
+  </si>
+  <si>
+    <t>15980</t>
+  </si>
+  <si>
+    <t>83726</t>
+  </si>
+  <si>
+    <t>127760</t>
+  </si>
+  <si>
+    <t>4301795</t>
+  </si>
+  <si>
     <t>1229G4661/009013</t>
   </si>
   <si>
@@ -470,6 +529,21 @@
     <t>WAB4324102442</t>
   </si>
   <si>
+    <t>13653</t>
+  </si>
+  <si>
+    <t>328349</t>
+  </si>
+  <si>
+    <t>4303603</t>
+  </si>
+  <si>
+    <t>5566510</t>
+  </si>
+  <si>
+    <t>5568529</t>
+  </si>
+  <si>
     <t>1033-40600-02</t>
   </si>
   <si>
@@ -521,6 +595,9 @@
     <t>131095KWAP</t>
   </si>
   <si>
+    <t>4300119</t>
+  </si>
+  <si>
     <t>2233J1024/092061</t>
   </si>
   <si>
@@ -551,6 +628,12 @@
     <t>SET410KOYO</t>
   </si>
   <si>
+    <t>85003</t>
+  </si>
+  <si>
+    <t>10021566</t>
+  </si>
+  <si>
     <t>1228F552/P2252</t>
   </si>
   <si>
@@ -587,6 +670,12 @@
     <t>4301417FULLER</t>
   </si>
   <si>
+    <t>4303424</t>
+  </si>
+  <si>
+    <t>16980</t>
+  </si>
+  <si>
     <t>LF3620</t>
   </si>
   <si>
@@ -1382,20 +1471,20 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 30/11/2025 12:29:18</t>
+    <t>Período: 29/11/2025 22:19:30</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 01/11/2025 12:29:46</t>
+    <t>Fecha y hora de generación: 04/11/2025 22:19:57</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1488,16 +1577,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1505,31 +1588,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1567,7 +1647,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1601,7 +1681,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1636,10 +1715,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1812,130 +1890,130 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L219"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>444</v>
+        <v>480</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>446</v>
+        <v>482</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-    </row>
-    <row r="5" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-    </row>
-    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="I7" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="4" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="I7" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="L9" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="7">
-        <v>9373</v>
+      <c r="B10" t="s">
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="D10" t="s">
-        <v>230</v>
+        <v>266</v>
       </c>
       <c r="E10" t="s">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="F10" t="s">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="I10" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J10">
         <v>3</v>
@@ -1947,27 +2025,27 @@
         <v>1012839.99</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="7">
-        <v>16866</v>
+      <c r="B11" t="s">
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D11" t="s">
-        <v>231</v>
+        <v>267</v>
       </c>
       <c r="E11" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F11" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I11" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1979,27 +2057,27 @@
         <v>20451.8</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="7">
-        <v>21360</v>
+      <c r="B12" t="s">
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D12" t="s">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="E12" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F12" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I12" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -2011,27 +2089,27 @@
         <v>85144.72</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7">
-        <v>131973</v>
+      <c r="B13" t="s">
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>190</v>
+        <v>226</v>
       </c>
       <c r="D13" t="s">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="E13" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="F13" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="I13" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -2043,27 +2121,27 @@
         <v>400839.72</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="7">
-        <v>691445</v>
+      <c r="B14" t="s">
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D14" t="s">
-        <v>234</v>
+        <v>270</v>
       </c>
       <c r="E14" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F14" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I14" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -2075,27 +2153,27 @@
         <v>274251.7</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="7">
-        <v>691934</v>
+      <c r="B15" t="s">
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D15" t="s">
-        <v>235</v>
+        <v>271</v>
       </c>
       <c r="E15" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F15" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I15" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -2107,27 +2185,27 @@
         <v>103305.02</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="7">
-        <v>994349</v>
+      <c r="B16" t="s">
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="D16" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="E16" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="F16" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="I16" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J16">
         <v>2</v>
@@ -2139,27 +2217,27 @@
         <v>586270.9</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="7">
-        <v>994370</v>
+      <c r="B17" t="s">
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="D17" t="s">
-        <v>237</v>
+        <v>273</v>
       </c>
       <c r="E17" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="F17" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="I17" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2171,27 +2249,27 @@
         <v>239445.31</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="7">
-        <v>3344768</v>
+      <c r="B18" t="s">
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D18" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="E18" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F18" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I18" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2203,27 +2281,27 @@
         <v>107249.13</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="7">
-        <v>3344862</v>
+      <c r="B19" t="s">
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D19" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="E19" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F19" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I19" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -2235,59 +2313,59 @@
         <v>221724.9</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="7">
-        <v>4301467</v>
+      <c r="B20" t="s">
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D20" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="E20" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F20" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I20" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J20">
         <v>1</v>
       </c>
       <c r="K20">
-        <v>72202.429999999993</v>
+        <v>72202.42999999999</v>
       </c>
       <c r="L20">
-        <v>72202.429999999993</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+        <v>72202.42999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="7">
-        <v>4301762</v>
+      <c r="B21" t="s">
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D21" t="s">
-        <v>241</v>
+        <v>277</v>
       </c>
       <c r="E21" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F21" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I21" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2299,59 +2377,59 @@
         <v>344188.26</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="7">
-        <v>4302411</v>
+      <c r="B22" t="s">
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D22" t="s">
-        <v>242</v>
+        <v>278</v>
       </c>
       <c r="E22" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F22" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I22" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J22">
         <v>3</v>
       </c>
       <c r="K22">
-        <v>286220.53000000003</v>
+        <v>286220.53</v>
       </c>
       <c r="L22">
         <v>858661.59</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="7">
-        <v>4302484</v>
+      <c r="B23" t="s">
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D23" t="s">
-        <v>243</v>
+        <v>279</v>
       </c>
       <c r="E23" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F23" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I23" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J23">
         <v>2</v>
@@ -2363,27 +2441,27 @@
         <v>710132.86</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12">
       <c r="A24" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="7">
-        <v>4302506</v>
+      <c r="B24" t="s">
+        <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D24" t="s">
-        <v>244</v>
+        <v>280</v>
       </c>
       <c r="E24" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F24" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I24" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -2395,27 +2473,27 @@
         <v>618795.86</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12">
       <c r="A25" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="7">
-        <v>4303357</v>
+      <c r="B25" t="s">
+        <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D25" t="s">
-        <v>245</v>
+        <v>281</v>
       </c>
       <c r="E25" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F25" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I25" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J25">
         <v>2</v>
@@ -2427,27 +2505,27 @@
         <v>907043.74</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12">
       <c r="A26" t="s">
         <v>12</v>
       </c>
-      <c r="B26" s="7">
-        <v>4303428</v>
+      <c r="B26" t="s">
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D26" t="s">
-        <v>246</v>
+        <v>282</v>
       </c>
       <c r="E26" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F26" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I26" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -2459,27 +2537,27 @@
         <v>528176.74</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12">
       <c r="A27" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="7">
-        <v>4303476</v>
+      <c r="B27" t="s">
+        <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D27" t="s">
-        <v>247</v>
+        <v>283</v>
       </c>
       <c r="E27" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F27" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I27" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J27">
         <v>3</v>
@@ -2491,27 +2569,27 @@
         <v>884427.72</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12">
       <c r="A28" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="7">
-        <v>4303825</v>
+      <c r="B28" t="s">
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D28" t="s">
-        <v>248</v>
+        <v>284</v>
       </c>
       <c r="E28" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F28" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I28" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2523,27 +2601,27 @@
         <v>324848.81</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12">
       <c r="A29" t="s">
         <v>12</v>
       </c>
-      <c r="B29" s="7">
-        <v>4304499</v>
+      <c r="B29" t="s">
+        <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D29" t="s">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="E29" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F29" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I29" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2555,27 +2633,27 @@
         <v>119219.24</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12">
       <c r="A30" t="s">
         <v>12</v>
       </c>
-      <c r="B30" s="7">
-        <v>4304641</v>
+      <c r="B30" t="s">
+        <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D30" t="s">
-        <v>250</v>
+        <v>286</v>
       </c>
       <c r="E30" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F30" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I30" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J30">
         <v>2</v>
@@ -2584,62 +2662,62 @@
         <v>456594.41</v>
       </c>
       <c r="L30">
-        <v>913188.82</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+        <v>913188.8199999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" t="s">
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D31" t="s">
-        <v>251</v>
+        <v>287</v>
       </c>
       <c r="E31" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F31" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I31" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J31">
         <v>2</v>
       </c>
       <c r="K31">
-        <v>84932.65</v>
+        <v>84932.64999999999</v>
       </c>
       <c r="L31">
         <v>169865.3</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12">
       <c r="A32" t="s">
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="D32" t="s">
-        <v>252</v>
+        <v>288</v>
       </c>
       <c r="E32" t="s">
-        <v>436</v>
+        <v>472</v>
       </c>
       <c r="F32" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="I32" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J32">
         <v>12</v>
@@ -2651,27 +2729,27 @@
         <v>366964.32</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12">
       <c r="A33" t="s">
         <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="D33" t="s">
-        <v>253</v>
+        <v>289</v>
       </c>
       <c r="E33" t="s">
-        <v>436</v>
+        <v>472</v>
       </c>
       <c r="F33" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="I33" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J33">
         <v>6</v>
@@ -2683,59 +2761,59 @@
         <v>200111.34</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12">
       <c r="A34" t="s">
         <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="D34" t="s">
-        <v>254</v>
+        <v>290</v>
       </c>
       <c r="E34" t="s">
-        <v>436</v>
+        <v>472</v>
       </c>
       <c r="F34" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="I34" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J34">
         <v>6</v>
       </c>
       <c r="K34">
-        <v>26185.200000000001</v>
+        <v>26185.2</v>
       </c>
       <c r="L34">
-        <v>157111.20000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+        <v>157111.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35" t="s">
         <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="D35" t="s">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="E35" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="F35" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="I35" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2747,27 +2825,27 @@
         <v>132383.57</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12">
       <c r="A36" t="s">
         <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D36" t="s">
-        <v>256</v>
+        <v>292</v>
       </c>
       <c r="E36" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F36" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I36" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2779,27 +2857,27 @@
         <v>1666305.17</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12">
       <c r="A37" t="s">
         <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="D37" t="s">
-        <v>257</v>
+        <v>293</v>
       </c>
       <c r="E37" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="F37" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="I37" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J37">
         <v>3</v>
@@ -2811,27 +2889,27 @@
         <v>3585224.85</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12">
       <c r="A38" t="s">
         <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="D38" t="s">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="E38" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="F38" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="I38" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J38">
         <v>123</v>
@@ -2843,27 +2921,27 @@
         <v>194096.46</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12">
       <c r="A39" t="s">
         <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D39" t="s">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="E39" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F39" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I39" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J39">
         <v>4</v>
@@ -2875,91 +2953,91 @@
         <v>64747.28</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12">
       <c r="A40" t="s">
         <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="D40" t="s">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="E40" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="F40" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="I40" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J40">
         <v>1</v>
       </c>
       <c r="K40">
-        <v>151783.14000000001</v>
+        <v>151783.14</v>
       </c>
       <c r="L40">
-        <v>151783.14000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+        <v>151783.14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41" t="s">
         <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="D41" t="s">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="E41" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="F41" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="I41" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J41">
         <v>1</v>
       </c>
       <c r="K41">
-        <v>133605.85999999999</v>
+        <v>133605.86</v>
       </c>
       <c r="L41">
-        <v>133605.85999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+        <v>133605.86</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
       <c r="A42" t="s">
         <v>13</v>
       </c>
       <c r="B42" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="D42" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="E42" t="s">
-        <v>436</v>
+        <v>472</v>
       </c>
       <c r="F42" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="I42" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J42">
         <v>12</v>
@@ -2971,27 +3049,27 @@
         <v>121084.68</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12">
       <c r="A43" t="s">
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>198</v>
+        <v>234</v>
       </c>
       <c r="D43" t="s">
-        <v>263</v>
+        <v>299</v>
       </c>
       <c r="E43" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="F43" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="I43" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -3003,27 +3081,27 @@
         <v>55214.31</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12">
       <c r="A44" t="s">
         <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="D44" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="E44" t="s">
-        <v>438</v>
+        <v>474</v>
       </c>
       <c r="F44" t="s">
-        <v>438</v>
+        <v>474</v>
       </c>
       <c r="I44" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J44">
         <v>2</v>
@@ -3035,27 +3113,27 @@
         <v>546013.4</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12">
       <c r="A45" t="s">
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="D45" t="s">
-        <v>265</v>
+        <v>301</v>
       </c>
       <c r="E45" t="s">
-        <v>438</v>
+        <v>474</v>
       </c>
       <c r="F45" t="s">
-        <v>438</v>
+        <v>474</v>
       </c>
       <c r="I45" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J45">
         <v>12</v>
@@ -3067,27 +3145,27 @@
         <v>267602.64</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12">
       <c r="A46" t="s">
         <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="D46" t="s">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="E46" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="F46" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="I46" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -3099,59 +3177,59 @@
         <v>69469.2</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12">
       <c r="A47" t="s">
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="D47" t="s">
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="E47" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="F47" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="I47" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J47">
         <v>2</v>
       </c>
       <c r="K47">
-        <v>38542.449999999997</v>
+        <v>38542.45</v>
       </c>
       <c r="L47">
-        <v>77084.899999999994</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+        <v>77084.89999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
       <c r="A48" t="s">
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="D48" t="s">
-        <v>268</v>
+        <v>304</v>
       </c>
       <c r="E48" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="F48" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="I48" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J48">
         <v>4</v>
@@ -3163,27 +3241,27 @@
         <v>292678.32</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12">
       <c r="A49" t="s">
         <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="D49" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="E49" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="F49" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="I49" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -3195,27 +3273,27 @@
         <v>57029.66</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12">
       <c r="A50" t="s">
         <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="D50" t="s">
-        <v>270</v>
+        <v>306</v>
       </c>
       <c r="E50" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="F50" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="I50" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J50">
         <v>5</v>
@@ -3227,27 +3305,27 @@
         <v>620565.15</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12">
       <c r="A51" t="s">
         <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="D51" t="s">
-        <v>271</v>
+        <v>307</v>
       </c>
       <c r="E51" t="s">
-        <v>438</v>
+        <v>474</v>
       </c>
       <c r="F51" t="s">
-        <v>438</v>
+        <v>474</v>
       </c>
       <c r="I51" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -3259,27 +3337,27 @@
         <v>143954.72</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12">
       <c r="A52" t="s">
         <v>13</v>
       </c>
       <c r="B52" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="D52" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="E52" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="F52" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="I52" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J52">
         <v>3</v>
@@ -3291,27 +3369,27 @@
         <v>1122558</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12">
       <c r="A53" t="s">
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="D53" t="s">
-        <v>273</v>
+        <v>309</v>
       </c>
       <c r="E53" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="F53" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="I53" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J53">
         <v>2</v>
@@ -3320,30 +3398,30 @@
         <v>451755.47</v>
       </c>
       <c r="L53">
-        <v>903510.94</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+        <v>903510.9399999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
       <c r="A54" t="s">
         <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D54" t="s">
-        <v>274</v>
+        <v>310</v>
       </c>
       <c r="E54" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F54" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I54" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -3355,27 +3433,27 @@
         <v>297477.98</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12">
       <c r="A55" t="s">
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="D55" t="s">
-        <v>275</v>
+        <v>311</v>
       </c>
       <c r="E55" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="F55" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="I55" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J55">
         <v>3</v>
@@ -3387,27 +3465,27 @@
         <v>350025.18</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12">
       <c r="A56" t="s">
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D56" t="s">
-        <v>276</v>
+        <v>312</v>
       </c>
       <c r="E56" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F56" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I56" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -3419,27 +3497,27 @@
         <v>241521.59</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12">
       <c r="A57" t="s">
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D57" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
       <c r="E57" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F57" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I57" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J57">
         <v>2</v>
@@ -3451,27 +3529,27 @@
         <v>246247.44</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12">
       <c r="A58" t="s">
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D58" t="s">
-        <v>278</v>
+        <v>314</v>
       </c>
       <c r="E58" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F58" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I58" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J58">
         <v>2</v>
@@ -3483,27 +3561,27 @@
         <v>555481.24</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12">
       <c r="A59" t="s">
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="D59" t="s">
-        <v>279</v>
+        <v>315</v>
       </c>
       <c r="E59" t="s">
-        <v>436</v>
+        <v>472</v>
       </c>
       <c r="F59" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="I59" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J59">
         <v>91</v>
@@ -3515,27 +3593,27 @@
         <v>902993</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12">
       <c r="A60" t="s">
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="D60" t="s">
-        <v>280</v>
+        <v>316</v>
       </c>
       <c r="E60" t="s">
-        <v>436</v>
+        <v>472</v>
       </c>
       <c r="F60" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="I60" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J60">
         <v>28</v>
@@ -3547,27 +3625,27 @@
         <v>149185.4</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12">
       <c r="A61" t="s">
         <v>13</v>
       </c>
       <c r="B61" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="D61" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="E61" t="s">
-        <v>436</v>
+        <v>472</v>
       </c>
       <c r="F61" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="I61" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J61">
         <v>6</v>
@@ -3579,27 +3657,27 @@
         <v>77229.3</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12">
       <c r="A62" t="s">
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="D62" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="E62" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="F62" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="I62" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J62">
         <v>64</v>
@@ -3611,27 +3689,27 @@
         <v>718570.24</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12">
       <c r="A63" t="s">
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="D63" t="s">
-        <v>283</v>
+        <v>319</v>
       </c>
       <c r="E63" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="F63" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="I63" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J63">
         <v>3</v>
@@ -3643,27 +3721,27 @@
         <v>223230.09</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12">
       <c r="A64" t="s">
         <v>13</v>
       </c>
       <c r="B64" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="D64" t="s">
-        <v>284</v>
+        <v>320</v>
       </c>
       <c r="E64" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="F64" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="I64" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J64">
         <v>2</v>
@@ -3675,91 +3753,91 @@
         <v>104029.86</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12">
       <c r="A65" t="s">
         <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C65" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="D65" t="s">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="E65" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="F65" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="I65" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J65">
         <v>20</v>
       </c>
       <c r="K65">
-        <v>94380.4</v>
+        <v>94380.39999999999</v>
       </c>
       <c r="L65">
         <v>1887608</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12">
       <c r="A66" t="s">
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="D66" t="s">
-        <v>286</v>
+        <v>322</v>
       </c>
       <c r="E66" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="F66" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="I66" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J66">
         <v>5</v>
       </c>
       <c r="K66">
-        <v>1157466.5900000001</v>
+        <v>1157466.59</v>
       </c>
       <c r="L66">
-        <v>5787332.9500000002</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+        <v>5787332.95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
       <c r="A67" t="s">
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="D67" t="s">
-        <v>287</v>
+        <v>323</v>
       </c>
       <c r="E67" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="F67" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="I67" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3771,27 +3849,27 @@
         <v>553925.89</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12">
       <c r="A68" t="s">
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D68" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
       <c r="E68" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F68" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I68" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3803,27 +3881,27 @@
         <v>456192.75</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12">
       <c r="A69" t="s">
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D69" t="s">
-        <v>289</v>
+        <v>325</v>
       </c>
       <c r="E69" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F69" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I69" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J69">
         <v>5</v>
@@ -3832,30 +3910,30 @@
         <v>459216.59</v>
       </c>
       <c r="L69">
-        <v>2296082.9500000002</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+        <v>2296082.95</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
       <c r="A70" t="s">
         <v>13</v>
       </c>
       <c r="B70" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>208</v>
+        <v>244</v>
       </c>
       <c r="D70" t="s">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="E70" t="s">
-        <v>439</v>
+        <v>475</v>
       </c>
       <c r="F70" t="s">
-        <v>439</v>
+        <v>475</v>
       </c>
       <c r="I70" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J70">
         <v>2</v>
@@ -3867,27 +3945,27 @@
         <v>215222.86</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12">
       <c r="A71" t="s">
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="D71" t="s">
-        <v>291</v>
+        <v>327</v>
       </c>
       <c r="E71" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="F71" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="I71" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J71">
         <v>4</v>
@@ -3899,27 +3977,27 @@
         <v>651137.96</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12">
       <c r="A72" t="s">
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="D72" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="E72" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="F72" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="I72" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J72">
         <v>3</v>
@@ -3931,27 +4009,27 @@
         <v>193789.23</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12">
       <c r="A73" t="s">
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D73" t="s">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="E73" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F73" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I73" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J73">
         <v>4</v>
@@ -3963,27 +4041,27 @@
         <v>2083862.28</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12">
       <c r="A74" t="s">
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D74" t="s">
-        <v>294</v>
+        <v>330</v>
       </c>
       <c r="E74" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F74" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I74" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -3995,27 +4073,27 @@
         <v>234957.18</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12">
       <c r="A75" t="s">
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D75" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="E75" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F75" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I75" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J75">
         <v>1</v>
@@ -4027,27 +4105,27 @@
         <v>561136.28</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12">
       <c r="A76" t="s">
         <v>13</v>
       </c>
       <c r="B76" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D76" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="E76" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F76" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I76" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J76">
         <v>1</v>
@@ -4059,27 +4137,27 @@
         <v>548933.98</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12">
       <c r="A77" t="s">
         <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D77" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="E77" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F77" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I77" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J77">
         <v>2</v>
@@ -4091,27 +4169,27 @@
         <v>696877.88</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12">
       <c r="A78" t="s">
         <v>13</v>
       </c>
       <c r="B78" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D78" t="s">
-        <v>297</v>
+        <v>333</v>
       </c>
       <c r="E78" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F78" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I78" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J78">
         <v>1</v>
@@ -4123,27 +4201,27 @@
         <v>176616.64</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12">
       <c r="A79" t="s">
         <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D79" t="s">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="E79" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F79" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I79" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J79">
         <v>3</v>
@@ -4152,62 +4230,62 @@
         <v>54474.6</v>
       </c>
       <c r="L79">
-        <v>163423.79999999999</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+        <v>163423.8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
       <c r="A80" t="s">
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D80" t="s">
-        <v>299</v>
+        <v>335</v>
       </c>
       <c r="E80" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F80" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I80" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J80">
         <v>1</v>
       </c>
       <c r="K80">
-        <v>289538.59999999998</v>
+        <v>289538.6</v>
       </c>
       <c r="L80">
-        <v>289538.59999999998</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+        <v>289538.6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
       <c r="A81" t="s">
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="D81" t="s">
-        <v>300</v>
+        <v>336</v>
       </c>
       <c r="E81" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="F81" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="I81" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J81">
         <v>2</v>
@@ -4219,27 +4297,27 @@
         <v>120382.36</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12">
       <c r="A82" t="s">
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="D82" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="E82" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="F82" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="I82" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J82">
         <v>5</v>
@@ -4248,30 +4326,30 @@
         <v>106058.91</v>
       </c>
       <c r="L82">
-        <v>530294.55000000005</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+        <v>530294.55</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
       <c r="A83" t="s">
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="D83" t="s">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="E83" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="F83" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="I83" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J83">
         <v>5</v>
@@ -4283,27 +4361,27 @@
         <v>120389.45</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12">
       <c r="A84" t="s">
         <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>210</v>
+        <v>246</v>
       </c>
       <c r="D84" t="s">
-        <v>303</v>
+        <v>339</v>
       </c>
       <c r="E84" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="F84" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="I84" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J84">
         <v>21</v>
@@ -4312,30 +4390,30 @@
         <v>13504.82</v>
       </c>
       <c r="L84">
-        <v>283601.21999999997</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+        <v>283601.22</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
       <c r="A85" t="s">
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="C85" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="D85" t="s">
-        <v>304</v>
+        <v>340</v>
       </c>
       <c r="E85" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="F85" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="I85" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J85">
         <v>1</v>
@@ -4347,27 +4425,27 @@
         <v>244653.18</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12">
       <c r="A86" t="s">
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="C86" t="s">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="D86" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="E86" t="s">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="F86" t="s">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="I86" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J86">
         <v>4</v>
@@ -4376,30 +4454,30 @@
         <v>116579.52</v>
       </c>
       <c r="L86">
-        <v>466318.08000000002</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+        <v>466318.08</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
       <c r="A87" t="s">
         <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>208</v>
+        <v>244</v>
       </c>
       <c r="D87" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="E87" t="s">
-        <v>439</v>
+        <v>475</v>
       </c>
       <c r="F87" t="s">
-        <v>439</v>
+        <v>475</v>
       </c>
       <c r="I87" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J87">
         <v>2</v>
@@ -4411,59 +4489,59 @@
         <v>265900.58</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12">
       <c r="A88" t="s">
         <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="D88" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
       <c r="E88" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="F88" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="I88" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J88">
         <v>2</v>
       </c>
       <c r="K88">
-        <v>130565.75999999999</v>
+        <v>130565.76</v>
       </c>
       <c r="L88">
-        <v>261131.51999999999</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+        <v>261131.52</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
       <c r="A89" t="s">
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="D89" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="E89" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="F89" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="I89" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J89">
         <v>10</v>
@@ -4472,30 +4550,30 @@
         <v>32532.84</v>
       </c>
       <c r="L89">
-        <v>325328.40000000002</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+        <v>325328.4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
       <c r="A90" t="s">
         <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="D90" t="s">
-        <v>309</v>
+        <v>345</v>
       </c>
       <c r="E90" t="s">
-        <v>436</v>
+        <v>472</v>
       </c>
       <c r="F90" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="I90" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J90">
         <v>8</v>
@@ -4507,27 +4585,27 @@
         <v>289472.8</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12">
       <c r="A91" t="s">
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="D91" t="s">
-        <v>310</v>
+        <v>346</v>
       </c>
       <c r="E91" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="F91" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="I91" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J91">
         <v>1</v>
@@ -4539,27 +4617,27 @@
         <v>202984.86</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12">
       <c r="A92" t="s">
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="D92" t="s">
-        <v>311</v>
+        <v>347</v>
       </c>
       <c r="E92" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="F92" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="I92" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J92">
         <v>2</v>
@@ -4571,27 +4649,27 @@
         <v>197935.06</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12">
       <c r="A93" t="s">
         <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="D93" t="s">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="E93" t="s">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="F93" t="s">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="I93" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J93">
         <v>4</v>
@@ -4603,27 +4681,27 @@
         <v>560000</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12">
       <c r="A94" t="s">
         <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="D94" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="E94" t="s">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="F94" t="s">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="I94" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J94">
         <v>8</v>
@@ -4635,27 +4713,27 @@
         <v>480000</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12">
       <c r="A95" t="s">
         <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D95" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="E95" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F95" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I95" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J95">
         <v>2</v>
@@ -4667,27 +4745,27 @@
         <v>366791.62</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12">
       <c r="A96" t="s">
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="D96" t="s">
-        <v>315</v>
+        <v>351</v>
       </c>
       <c r="E96" t="s">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="F96" t="s">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="I96" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J96">
         <v>1</v>
@@ -4699,27 +4777,27 @@
         <v>561283.11</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12">
       <c r="A97" t="s">
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C97" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="D97" t="s">
-        <v>316</v>
+        <v>352</v>
       </c>
       <c r="E97" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="F97" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="I97" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J97">
         <v>2</v>
@@ -4728,30 +4806,30 @@
         <v>400703.47</v>
       </c>
       <c r="L97">
-        <v>801406.94</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+        <v>801406.9399999999</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12">
       <c r="A98" t="s">
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C98" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D98" t="s">
-        <v>317</v>
+        <v>353</v>
       </c>
       <c r="E98" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F98" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I98" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J98">
         <v>21</v>
@@ -4763,27 +4841,27 @@
         <v>1309293.72</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12">
       <c r="A99" t="s">
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D99" t="s">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="E99" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F99" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I99" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J99">
         <v>1</v>
@@ -4795,27 +4873,27 @@
         <v>339984.3</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12">
       <c r="A100" t="s">
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D100" t="s">
-        <v>319</v>
+        <v>355</v>
       </c>
       <c r="E100" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I100" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J100">
         <v>3</v>
@@ -4827,27 +4905,27 @@
         <v>636143.97</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12">
       <c r="A101" t="s">
         <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D101" t="s">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="E101" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F101" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I101" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J101">
         <v>1</v>
@@ -4859,27 +4937,27 @@
         <v>116716.34</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12">
       <c r="A102" t="s">
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>214</v>
+        <v>250</v>
       </c>
       <c r="D102" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="E102" t="s">
-        <v>214</v>
+        <v>250</v>
       </c>
       <c r="F102" t="s">
-        <v>214</v>
+        <v>250</v>
       </c>
       <c r="I102" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J102">
         <v>1</v>
@@ -4891,27 +4969,27 @@
         <v>147576.31</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12">
       <c r="A103" t="s">
         <v>13</v>
       </c>
       <c r="B103" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="D103" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="E103" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="F103" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="I103" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J103">
         <v>2</v>
@@ -4923,27 +5001,27 @@
         <v>51912.62</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12">
       <c r="A104" t="s">
         <v>13</v>
       </c>
       <c r="B104" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="D104" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
       <c r="E104" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="F104" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="I104" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J104">
         <v>2</v>
@@ -4955,27 +5033,27 @@
         <v>414447.78</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12">
       <c r="A105" t="s">
         <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="D105" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="E105" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="F105" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="I105" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J105">
         <v>13</v>
@@ -4987,27 +5065,27 @@
         <v>688914.46</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12">
       <c r="A106" t="s">
         <v>13</v>
       </c>
       <c r="B106" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="C106" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D106" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="E106" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F106" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I106" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J106">
         <v>3</v>
@@ -5016,62 +5094,62 @@
         <v>365807.37</v>
       </c>
       <c r="L106">
-        <v>1097422.1100000001</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1097422.11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12">
       <c r="A107" t="s">
         <v>13</v>
       </c>
       <c r="B107" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="D107" t="s">
-        <v>326</v>
+        <v>362</v>
       </c>
       <c r="E107" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="F107" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="I107" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J107">
         <v>276</v>
       </c>
       <c r="K107">
-        <v>910.44</v>
+        <v>910.4400000000001</v>
       </c>
       <c r="L107">
         <v>251281.44</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12">
       <c r="A108" t="s">
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="C108" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="D108" t="s">
-        <v>327</v>
+        <v>363</v>
       </c>
       <c r="E108" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="F108" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="I108" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J108">
         <v>1</v>
@@ -5083,27 +5161,27 @@
         <v>61252.9</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12">
       <c r="A109" t="s">
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="D109" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="E109" t="s">
-        <v>436</v>
+        <v>472</v>
       </c>
       <c r="F109" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="I109" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J109">
         <v>144</v>
@@ -5115,27 +5193,27 @@
         <v>1786872.96</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12">
       <c r="A110" t="s">
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="D110" t="s">
-        <v>329</v>
+        <v>365</v>
       </c>
       <c r="E110" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="F110" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="I110" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J110">
         <v>10</v>
@@ -5147,27 +5225,27 @@
         <v>822594.4</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12">
       <c r="A111" t="s">
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D111" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="E111" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F111" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I111" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J111">
         <v>5</v>
@@ -5179,27 +5257,27 @@
         <v>219653</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12">
       <c r="A112" t="s">
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D112" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="E112" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I112" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J112">
         <v>1</v>
@@ -5211,27 +5289,27 @@
         <v>78505.56</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12">
       <c r="A113" t="s">
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D113" t="s">
-        <v>332</v>
+        <v>368</v>
       </c>
       <c r="E113" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F113" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I113" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J113">
         <v>2</v>
@@ -5243,27 +5321,27 @@
         <v>507434.42</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12">
       <c r="A114" t="s">
         <v>13</v>
       </c>
       <c r="B114" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="D114" t="s">
-        <v>333</v>
+        <v>369</v>
       </c>
       <c r="E114" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="F114" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="I114" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J114">
         <v>1</v>
@@ -5275,27 +5353,27 @@
         <v>462132.13</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12">
       <c r="A115" t="s">
         <v>13</v>
       </c>
       <c r="B115" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="D115" t="s">
-        <v>334</v>
+        <v>370</v>
       </c>
       <c r="E115" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="F115" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="I115" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J115">
         <v>1</v>
@@ -5307,27 +5385,27 @@
         <v>294400</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12">
       <c r="A116" t="s">
         <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="D116" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
       <c r="E116" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="F116" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="I116" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J116">
         <v>2</v>
@@ -5339,27 +5417,27 @@
         <v>617440.46</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12">
       <c r="A117" t="s">
         <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="D117" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="E117" t="s">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="F117" t="s">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="I117" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J117">
         <v>4</v>
@@ -5371,59 +5449,59 @@
         <v>521697.04</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12">
       <c r="A118" t="s">
         <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="D118" t="s">
-        <v>337</v>
+        <v>373</v>
       </c>
       <c r="E118" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="F118" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="I118" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J118">
         <v>1</v>
       </c>
       <c r="K118">
-        <v>142359.26999999999</v>
+        <v>142359.27</v>
       </c>
       <c r="L118">
-        <v>142359.26999999999</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+        <v>142359.27</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12">
       <c r="A119" t="s">
         <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="D119" t="s">
-        <v>338</v>
+        <v>374</v>
       </c>
       <c r="E119" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="F119" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="I119" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J119">
         <v>1</v>
@@ -5435,27 +5513,27 @@
         <v>2373776.35</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12">
       <c r="A120" t="s">
         <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="C120" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="D120" t="s">
-        <v>339</v>
+        <v>375</v>
       </c>
       <c r="E120" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="F120" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="I120" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J120">
         <v>3</v>
@@ -5467,27 +5545,27 @@
         <v>459995.55</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12">
       <c r="A121" t="s">
         <v>13</v>
       </c>
       <c r="B121" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="D121" t="s">
-        <v>340</v>
+        <v>376</v>
       </c>
       <c r="E121" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="F121" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="I121" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J121">
         <v>5</v>
@@ -5499,27 +5577,27 @@
         <v>759137.5</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12">
       <c r="A122" t="s">
         <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="C122" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="D122" t="s">
-        <v>341</v>
+        <v>377</v>
       </c>
       <c r="E122" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="F122" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="I122" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J122">
         <v>1</v>
@@ -5531,27 +5609,27 @@
         <v>126875.69</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12">
       <c r="A123" t="s">
         <v>12</v>
       </c>
       <c r="B123" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="D123" t="s">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="E123" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="F123" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="I123" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J123">
         <v>1</v>
@@ -5563,27 +5641,27 @@
         <v>418397.52</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12">
       <c r="A124" t="s">
         <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="C124" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D124" t="s">
-        <v>343</v>
+        <v>379</v>
       </c>
       <c r="E124" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F124" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I124" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J124">
         <v>12</v>
@@ -5595,27 +5673,27 @@
         <v>730572.6</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12">
       <c r="A125" t="s">
         <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D125" t="s">
-        <v>344</v>
+        <v>380</v>
       </c>
       <c r="E125" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F125" t="s">
-        <v>440</v>
+        <v>476</v>
       </c>
       <c r="I125" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J125">
         <v>1</v>
@@ -5627,27 +5705,27 @@
         <v>53403.02</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12">
       <c r="A126" t="s">
         <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D126" t="s">
-        <v>345</v>
+        <v>381</v>
       </c>
       <c r="E126" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F126" t="s">
-        <v>440</v>
+        <v>476</v>
       </c>
       <c r="I126" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J126">
         <v>5</v>
@@ -5659,27 +5737,27 @@
         <v>404811.1</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12">
       <c r="A127" t="s">
         <v>12</v>
       </c>
       <c r="B127" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D127" t="s">
-        <v>346</v>
+        <v>382</v>
       </c>
       <c r="E127" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F127" t="s">
-        <v>440</v>
+        <v>476</v>
       </c>
       <c r="I127" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J127">
         <v>3</v>
@@ -5691,27 +5769,27 @@
         <v>90050.37</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12">
       <c r="A128" t="s">
         <v>12</v>
       </c>
       <c r="B128" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="C128" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D128" t="s">
-        <v>347</v>
+        <v>383</v>
       </c>
       <c r="E128" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F128" t="s">
-        <v>440</v>
+        <v>476</v>
       </c>
       <c r="I128" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J128">
         <v>2</v>
@@ -5723,27 +5801,27 @@
         <v>111920.24</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12">
       <c r="A129" t="s">
         <v>12</v>
       </c>
       <c r="B129" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="C129" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D129" t="s">
-        <v>348</v>
+        <v>384</v>
       </c>
       <c r="E129" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F129" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I129" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J129">
         <v>1</v>
@@ -5755,27 +5833,27 @@
         <v>57770.2</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12">
       <c r="A130" t="s">
         <v>12</v>
       </c>
       <c r="B130" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="C130" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D130" t="s">
-        <v>349</v>
+        <v>385</v>
       </c>
       <c r="E130" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F130" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I130" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J130">
         <v>4</v>
@@ -5787,27 +5865,27 @@
         <v>488896.12</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12">
       <c r="A131" t="s">
         <v>13</v>
       </c>
       <c r="B131" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="D131" t="s">
-        <v>350</v>
+        <v>386</v>
       </c>
       <c r="E131" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="F131" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="I131" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J131">
         <v>2</v>
@@ -5819,27 +5897,27 @@
         <v>691199.98</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12">
       <c r="A132" t="s">
         <v>13</v>
       </c>
       <c r="B132" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="D132" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="E132" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="F132" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="I132" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J132">
         <v>4</v>
@@ -5851,27 +5929,27 @@
         <v>1627909.6</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12">
       <c r="A133" t="s">
         <v>13</v>
       </c>
       <c r="B133" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D133" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="E133" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F133" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I133" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J133">
         <v>1</v>
@@ -5883,59 +5961,59 @@
         <v>108921.66</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12">
       <c r="A134" t="s">
         <v>12</v>
       </c>
       <c r="B134" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="D134" t="s">
-        <v>353</v>
+        <v>389</v>
       </c>
       <c r="E134" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="F134" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="I134" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J134">
         <v>1</v>
       </c>
       <c r="K134">
-        <v>155407.10999999999</v>
+        <v>155407.11</v>
       </c>
       <c r="L134">
-        <v>155407.10999999999</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+        <v>155407.11</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12">
       <c r="A135" t="s">
         <v>12</v>
       </c>
       <c r="B135" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="C135" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="D135" t="s">
-        <v>353</v>
+        <v>389</v>
       </c>
       <c r="E135" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="F135" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="I135" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J135">
         <v>2</v>
@@ -5947,27 +6025,27 @@
         <v>604613.96</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12">
       <c r="A136" t="s">
         <v>12</v>
       </c>
       <c r="B136" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="C136" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="D136" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E136" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="F136" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="I136" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J136">
         <v>1</v>
@@ -5979,27 +6057,27 @@
         <v>462946.56</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12">
       <c r="A137" t="s">
         <v>12</v>
       </c>
       <c r="B137" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="C137" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="D137" t="s">
-        <v>355</v>
+        <v>391</v>
       </c>
       <c r="E137" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="F137" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="I137" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J137">
         <v>1</v>
@@ -6011,27 +6089,27 @@
         <v>622170.75</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12">
       <c r="A138" t="s">
         <v>12</v>
       </c>
-      <c r="B138" s="7">
-        <v>8968</v>
+      <c r="B138" t="s">
+        <v>142</v>
       </c>
       <c r="C138" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D138" t="s">
-        <v>356</v>
+        <v>392</v>
       </c>
       <c r="E138" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F138" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I138" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J138">
         <v>9</v>
@@ -6043,59 +6121,59 @@
         <v>65218.14</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12">
       <c r="A139" t="s">
         <v>12</v>
       </c>
-      <c r="B139" s="7">
-        <v>15980</v>
+      <c r="B139" t="s">
+        <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D139" t="s">
-        <v>357</v>
+        <v>393</v>
       </c>
       <c r="E139" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F139" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I139" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J139">
         <v>22</v>
       </c>
       <c r="K139">
-        <v>9200.6299999999992</v>
+        <v>9200.629999999999</v>
       </c>
       <c r="L139">
         <v>202413.86</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12">
       <c r="A140" t="s">
         <v>13</v>
       </c>
-      <c r="B140" s="7">
-        <v>83726</v>
+      <c r="B140" t="s">
+        <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="D140" t="s">
-        <v>358</v>
+        <v>394</v>
       </c>
       <c r="E140" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="F140" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="I140" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J140">
         <v>6</v>
@@ -6104,62 +6182,62 @@
         <v>13906.96</v>
       </c>
       <c r="L140">
-        <v>83441.759999999995</v>
-      </c>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+        <v>83441.75999999999</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12">
       <c r="A141" t="s">
         <v>12</v>
       </c>
-      <c r="B141" s="7">
-        <v>127760</v>
+      <c r="B141" t="s">
+        <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>220</v>
+        <v>256</v>
       </c>
       <c r="D141" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="E141" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F141" t="s">
-        <v>220</v>
+        <v>256</v>
       </c>
       <c r="I141" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J141">
         <v>10</v>
       </c>
       <c r="K141">
-        <v>67728.100000000006</v>
+        <v>67728.10000000001</v>
       </c>
       <c r="L141">
         <v>677281</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12">
       <c r="A142" t="s">
         <v>12</v>
       </c>
-      <c r="B142" s="7">
-        <v>4301795</v>
+      <c r="B142" t="s">
+        <v>146</v>
       </c>
       <c r="C142" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D142" t="s">
-        <v>360</v>
+        <v>396</v>
       </c>
       <c r="E142" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F142" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I142" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J142">
         <v>4</v>
@@ -6171,27 +6249,27 @@
         <v>2164667.52</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12">
       <c r="A143" t="s">
         <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="C143" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D143" t="s">
-        <v>361</v>
+        <v>397</v>
       </c>
       <c r="E143" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F143" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I143" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J143">
         <v>2</v>
@@ -6203,27 +6281,27 @@
         <v>63260.02</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12">
       <c r="A144" t="s">
         <v>13</v>
       </c>
       <c r="B144" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="C144" t="s">
-        <v>221</v>
+        <v>257</v>
       </c>
       <c r="D144" t="s">
-        <v>362</v>
+        <v>398</v>
       </c>
       <c r="E144" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="F144" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="I144" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J144">
         <v>2</v>
@@ -6235,27 +6313,27 @@
         <v>214209.36</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12">
       <c r="A145" t="s">
         <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D145" t="s">
-        <v>363</v>
+        <v>399</v>
       </c>
       <c r="E145" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F145" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I145" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J145">
         <v>1</v>
@@ -6267,27 +6345,27 @@
         <v>221067.08</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12">
       <c r="A146" t="s">
         <v>12</v>
       </c>
       <c r="B146" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="C146" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D146" t="s">
-        <v>364</v>
+        <v>400</v>
       </c>
       <c r="E146" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F146" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I146" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J146">
         <v>1</v>
@@ -6299,59 +6377,59 @@
         <v>204405.71</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12">
       <c r="A147" t="s">
         <v>13</v>
       </c>
       <c r="B147" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="C147" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="D147" t="s">
-        <v>365</v>
+        <v>401</v>
       </c>
       <c r="E147" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="F147" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="I147" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J147">
         <v>1</v>
       </c>
       <c r="K147">
-        <v>151612.17000000001</v>
+        <v>151612.17</v>
       </c>
       <c r="L147">
-        <v>151612.17000000001</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+        <v>151612.17</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12">
       <c r="A148" t="s">
         <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="C148" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D148" t="s">
-        <v>366</v>
+        <v>402</v>
       </c>
       <c r="E148" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F148" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I148" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J148">
         <v>5</v>
@@ -6363,27 +6441,27 @@
         <v>762827.65</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12">
       <c r="A149" t="s">
         <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D149" t="s">
-        <v>367</v>
+        <v>403</v>
       </c>
       <c r="E149" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F149" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I149" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J149">
         <v>3</v>
@@ -6395,27 +6473,27 @@
         <v>1945034.13</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12">
       <c r="A150" t="s">
         <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="C150" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D150" t="s">
-        <v>368</v>
+        <v>404</v>
       </c>
       <c r="E150" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F150" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I150" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J150">
         <v>4</v>
@@ -6427,27 +6505,27 @@
         <v>245098.76</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12">
       <c r="A151" t="s">
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="C151" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="D151" t="s">
-        <v>369</v>
+        <v>405</v>
       </c>
       <c r="E151" t="s">
-        <v>438</v>
+        <v>474</v>
       </c>
       <c r="F151" t="s">
-        <v>438</v>
+        <v>474</v>
       </c>
       <c r="I151" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J151">
         <v>1</v>
@@ -6459,27 +6537,27 @@
         <v>134461.16</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12">
       <c r="A152" t="s">
         <v>13</v>
       </c>
       <c r="B152" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="C152" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D152" t="s">
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="E152" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F152" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I152" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J152">
         <v>1</v>
@@ -6491,27 +6569,27 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12">
       <c r="A153" t="s">
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="C153" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D153" t="s">
-        <v>371</v>
+        <v>407</v>
       </c>
       <c r="E153" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F153" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I153" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J153">
         <v>1</v>
@@ -6523,59 +6601,59 @@
         <v>437278.29</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12">
       <c r="A154" t="s">
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="C154" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D154" t="s">
-        <v>372</v>
+        <v>408</v>
       </c>
       <c r="E154" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F154" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I154" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J154">
         <v>10</v>
       </c>
       <c r="K154">
-        <v>68988.759999999995</v>
+        <v>68988.75999999999</v>
       </c>
       <c r="L154">
         <v>689887.6</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12">
       <c r="A155" t="s">
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="C155" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D155" t="s">
-        <v>373</v>
+        <v>409</v>
       </c>
       <c r="E155" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F155" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I155" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J155">
         <v>2</v>
@@ -6587,27 +6665,27 @@
         <v>642123.22</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12">
       <c r="A156" t="s">
         <v>13</v>
       </c>
       <c r="B156" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="C156" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D156" t="s">
-        <v>374</v>
+        <v>410</v>
       </c>
       <c r="E156" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F156" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I156" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J156">
         <v>1</v>
@@ -6619,91 +6697,91 @@
         <v>86292.41</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12">
       <c r="A157" t="s">
         <v>13</v>
       </c>
       <c r="B157" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="C157" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="D157" t="s">
-        <v>375</v>
+        <v>411</v>
       </c>
       <c r="E157" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="F157" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="I157" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J157">
         <v>3</v>
       </c>
       <c r="K157">
-        <v>275914.15000000002</v>
+        <v>275914.15</v>
       </c>
       <c r="L157">
         <v>827742.45</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12">
       <c r="A158" t="s">
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="C158" t="s">
-        <v>222</v>
+        <v>258</v>
       </c>
       <c r="D158" t="s">
-        <v>376</v>
+        <v>412</v>
       </c>
       <c r="E158" t="s">
-        <v>439</v>
+        <v>475</v>
       </c>
       <c r="F158" t="s">
-        <v>439</v>
+        <v>475</v>
       </c>
       <c r="I158" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J158">
         <v>1</v>
       </c>
       <c r="K158">
-        <v>145438.64000000001</v>
+        <v>145438.64</v>
       </c>
       <c r="L158">
-        <v>145438.64000000001</v>
-      </c>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+        <v>145438.64</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12">
       <c r="A159" t="s">
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="C159" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D159" t="s">
-        <v>377</v>
+        <v>413</v>
       </c>
       <c r="E159" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F159" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I159" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J159">
         <v>16</v>
@@ -6715,27 +6793,27 @@
         <v>1988155.84</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12">
       <c r="A160" t="s">
         <v>13</v>
       </c>
       <c r="B160" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="C160" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="D160" t="s">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="E160" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="F160" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="I160" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J160">
         <v>1</v>
@@ -6747,27 +6825,27 @@
         <v>127385.01</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12">
       <c r="A161" t="s">
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D161" t="s">
-        <v>379</v>
+        <v>415</v>
       </c>
       <c r="E161" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F161" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I161" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J161">
         <v>2</v>
@@ -6776,30 +6854,30 @@
         <v>409485.91</v>
       </c>
       <c r="L161">
-        <v>818971.82</v>
-      </c>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+        <v>818971.8199999999</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12">
       <c r="A162" t="s">
         <v>13</v>
       </c>
       <c r="B162" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D162" t="s">
-        <v>380</v>
+        <v>416</v>
       </c>
       <c r="E162" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F162" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I162" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J162">
         <v>1</v>
@@ -6811,27 +6889,27 @@
         <v>411573.74</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12">
       <c r="A163" t="s">
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="D163" t="s">
-        <v>381</v>
+        <v>417</v>
       </c>
       <c r="E163" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="F163" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="I163" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J163">
         <v>2</v>
@@ -6843,27 +6921,27 @@
         <v>355858.56</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12">
       <c r="A164" t="s">
         <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="D164" t="s">
-        <v>382</v>
+        <v>418</v>
       </c>
       <c r="E164" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="F164" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="I164" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J164">
         <v>2</v>
@@ -6875,27 +6953,27 @@
         <v>773950.14</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12">
       <c r="A165" t="s">
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="C165" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D165" t="s">
-        <v>383</v>
+        <v>419</v>
       </c>
       <c r="E165" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F165" t="s">
-        <v>440</v>
+        <v>476</v>
       </c>
       <c r="I165" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J165">
         <v>4</v>
@@ -6907,27 +6985,27 @@
         <v>267935.2</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12">
       <c r="A166" t="s">
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="C166" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="D166" t="s">
-        <v>384</v>
+        <v>420</v>
       </c>
       <c r="E166" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="F166" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="I166" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J166">
         <v>1</v>
@@ -6939,27 +7017,27 @@
         <v>159709.51</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12">
       <c r="A167" t="s">
         <v>13</v>
       </c>
-      <c r="B167" s="7">
-        <v>13653</v>
+      <c r="B167" t="s">
+        <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D167" t="s">
-        <v>385</v>
+        <v>421</v>
       </c>
       <c r="E167" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F167" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I167" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J167">
         <v>38</v>
@@ -6971,59 +7049,59 @@
         <v>93989.58</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12">
       <c r="A168" t="s">
         <v>13</v>
       </c>
-      <c r="B168" s="7">
-        <v>328349</v>
+      <c r="B168" t="s">
+        <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="D168" t="s">
-        <v>386</v>
+        <v>422</v>
       </c>
       <c r="E168" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="F168" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="I168" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J168">
         <v>1</v>
       </c>
       <c r="K168">
-        <v>636180.68000000005</v>
+        <v>636180.6800000001</v>
       </c>
       <c r="L168">
-        <v>636180.68000000005</v>
-      </c>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+        <v>636180.6800000001</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12">
       <c r="A169" t="s">
         <v>12</v>
       </c>
-      <c r="B169" s="7">
-        <v>4303603</v>
+      <c r="B169" t="s">
+        <v>173</v>
       </c>
       <c r="C169" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D169" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="E169" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F169" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I169" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J169">
         <v>3</v>
@@ -7032,126 +7110,126 @@
         <v>27987.95</v>
       </c>
       <c r="L169">
-        <v>83963.85</v>
-      </c>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+        <v>83963.85000000001</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12">
       <c r="A170" t="s">
         <v>12</v>
       </c>
-      <c r="B170" s="7">
-        <v>5566510</v>
+      <c r="B170" t="s">
+        <v>174</v>
       </c>
       <c r="C170" t="s">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="E170" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="F170" t="s">
-        <v>441</v>
+        <v>477</v>
       </c>
       <c r="I170" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J170">
         <v>10</v>
       </c>
       <c r="K170">
-        <v>274730.28999999998</v>
+        <v>274730.29</v>
       </c>
       <c r="L170">
         <v>2747302.9</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12">
       <c r="A171" t="s">
         <v>13</v>
       </c>
-      <c r="B171" s="7">
-        <v>5568529</v>
+      <c r="B171" t="s">
+        <v>175</v>
       </c>
       <c r="C171" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D171" t="s">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="E171" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F171" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I171" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J171">
         <v>10</v>
       </c>
       <c r="K171">
-        <v>5073.4399999999996</v>
+        <v>5073.44</v>
       </c>
       <c r="L171">
-        <v>50734.400000000001</v>
-      </c>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+        <v>50734.4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12">
       <c r="A172" t="s">
         <v>13</v>
       </c>
       <c r="B172" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="C172" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="D172" t="s">
-        <v>390</v>
+        <v>426</v>
       </c>
       <c r="E172" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="F172" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="I172" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J172">
         <v>6</v>
       </c>
       <c r="K172">
-        <v>271098.71999999997</v>
+        <v>271098.72</v>
       </c>
       <c r="L172">
         <v>1626592.32</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12">
       <c r="A173" t="s">
         <v>12</v>
       </c>
       <c r="B173" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="C173" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D173" t="s">
-        <v>391</v>
+        <v>427</v>
       </c>
       <c r="E173" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F173" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I173" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J173">
         <v>8</v>
@@ -7163,27 +7241,27 @@
         <v>171120.96</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12">
       <c r="A174" t="s">
         <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="C174" t="s">
-        <v>220</v>
+        <v>256</v>
       </c>
       <c r="D174" t="s">
-        <v>392</v>
+        <v>428</v>
       </c>
       <c r="E174" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F174" t="s">
-        <v>220</v>
+        <v>256</v>
       </c>
       <c r="I174" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J174">
         <v>1</v>
@@ -7195,27 +7273,27 @@
         <v>325882.63</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12">
       <c r="A175" t="s">
         <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="C175" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D175" t="s">
-        <v>393</v>
+        <v>429</v>
       </c>
       <c r="E175" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F175" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I175" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J175">
         <v>2</v>
@@ -7227,27 +7305,27 @@
         <v>133578.22</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12">
       <c r="A176" t="s">
         <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="C176" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D176" t="s">
-        <v>394</v>
+        <v>430</v>
       </c>
       <c r="E176" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F176" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I176" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J176">
         <v>3</v>
@@ -7259,123 +7337,123 @@
         <v>235406.73</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12">
       <c r="A177" t="s">
         <v>12</v>
       </c>
       <c r="B177" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="C177" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D177" t="s">
-        <v>395</v>
+        <v>431</v>
       </c>
       <c r="E177" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F177" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I177" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J177">
         <v>3</v>
       </c>
       <c r="K177">
-        <v>263646.09000000003</v>
+        <v>263646.09</v>
       </c>
       <c r="L177">
         <v>790938.27</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12">
       <c r="A178" t="s">
         <v>12</v>
       </c>
       <c r="B178" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="C178" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D178" t="s">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="E178" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F178" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I178" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J178">
         <v>2</v>
       </c>
       <c r="K178">
-        <v>271387.84000000003</v>
+        <v>271387.84</v>
       </c>
       <c r="L178">
-        <v>542775.68000000005</v>
-      </c>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+        <v>542775.6800000001</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12">
       <c r="A179" t="s">
         <v>12</v>
       </c>
       <c r="B179" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C179" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D179" t="s">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="E179" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F179" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I179" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J179">
         <v>3</v>
       </c>
       <c r="K179">
-        <v>73037.789999999994</v>
+        <v>73037.78999999999</v>
       </c>
       <c r="L179">
         <v>219113.37</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12">
       <c r="A180" t="s">
         <v>13</v>
       </c>
       <c r="B180" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="C180" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D180" t="s">
-        <v>397</v>
+        <v>433</v>
       </c>
       <c r="E180" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F180" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I180" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J180">
         <v>14</v>
@@ -7387,59 +7465,59 @@
         <v>98696.36</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12">
       <c r="A181" t="s">
         <v>12</v>
       </c>
       <c r="B181" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="C181" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D181" t="s">
-        <v>398</v>
+        <v>434</v>
       </c>
       <c r="E181" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F181" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I181" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J181">
         <v>11</v>
       </c>
       <c r="K181">
-        <v>73190.350000000006</v>
+        <v>73190.35000000001</v>
       </c>
       <c r="L181">
         <v>805093.85</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12">
       <c r="A182" t="s">
         <v>12</v>
       </c>
       <c r="B182" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="C182" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="D182" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="E182" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="F182" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="I182" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J182">
         <v>2</v>
@@ -7451,27 +7529,27 @@
         <v>257718.9</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12">
       <c r="A183" t="s">
         <v>12</v>
       </c>
       <c r="B183" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="C183" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="D183" t="s">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="E183" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="F183" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="I183" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J183">
         <v>1</v>
@@ -7483,59 +7561,59 @@
         <v>451021.21</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12">
       <c r="A184" t="s">
         <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="C184" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D184" t="s">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="E184" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F184" t="s">
-        <v>440</v>
+        <v>476</v>
       </c>
       <c r="I184" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J184">
         <v>3</v>
       </c>
       <c r="K184">
-        <v>76547.520000000004</v>
+        <v>76547.52</v>
       </c>
       <c r="L184">
         <v>229642.56</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12">
       <c r="A185" t="s">
         <v>12</v>
       </c>
       <c r="B185" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="C185" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D185" t="s">
-        <v>402</v>
+        <v>438</v>
       </c>
       <c r="E185" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F185" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I185" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J185">
         <v>1</v>
@@ -7547,59 +7625,59 @@
         <v>116937.56</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12">
       <c r="A186" t="s">
         <v>12</v>
       </c>
       <c r="B186" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="C186" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D186" t="s">
-        <v>403</v>
+        <v>439</v>
       </c>
       <c r="E186" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F186" t="s">
-        <v>440</v>
+        <v>476</v>
       </c>
       <c r="I186" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J186">
         <v>7</v>
       </c>
       <c r="K186">
-        <v>98083.520000000004</v>
+        <v>98083.52</v>
       </c>
       <c r="L186">
         <v>686584.64</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12">
       <c r="A187" t="s">
         <v>13</v>
       </c>
       <c r="B187" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="C187" t="s">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="D187" t="s">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="E187" t="s">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="F187" t="s">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="I187" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J187">
         <v>1</v>
@@ -7611,27 +7689,27 @@
         <v>167744.87</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12">
       <c r="A188" t="s">
         <v>12</v>
       </c>
       <c r="B188" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="C188" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="D188" t="s">
-        <v>405</v>
+        <v>441</v>
       </c>
       <c r="E188" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="F188" t="s">
-        <v>442</v>
+        <v>478</v>
       </c>
       <c r="I188" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J188">
         <v>6</v>
@@ -7640,62 +7718,62 @@
         <v>23661.7</v>
       </c>
       <c r="L188">
-        <v>141970.20000000001</v>
-      </c>
-    </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+        <v>141970.2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12">
       <c r="A189" t="s">
         <v>12</v>
       </c>
-      <c r="B189" s="7">
-        <v>4300119</v>
+      <c r="B189" t="s">
+        <v>193</v>
       </c>
       <c r="C189" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D189" t="s">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="E189" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F189" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I189" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J189">
         <v>6</v>
       </c>
       <c r="K189">
-        <v>20116.830000000002</v>
+        <v>20116.83</v>
       </c>
       <c r="L189">
         <v>120700.98</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12">
       <c r="A190" t="s">
         <v>12</v>
       </c>
       <c r="B190" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="C190" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D190" t="s">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="E190" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F190" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I190" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J190">
         <v>4</v>
@@ -7707,27 +7785,27 @@
         <v>240041.4</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12">
       <c r="A191" t="s">
         <v>12</v>
       </c>
       <c r="B191" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="C191" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D191" t="s">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="E191" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F191" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I191" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J191">
         <v>2</v>
@@ -7739,27 +7817,27 @@
         <v>200992.56</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12">
       <c r="A192" t="s">
         <v>12</v>
       </c>
       <c r="B192" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="C192" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D192" t="s">
-        <v>409</v>
+        <v>445</v>
       </c>
       <c r="E192" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F192" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I192" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J192">
         <v>40</v>
@@ -7771,27 +7849,27 @@
         <v>427367.2</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12">
       <c r="A193" t="s">
         <v>12</v>
       </c>
       <c r="B193" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="C193" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D193" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
       <c r="E193" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F193" t="s">
-        <v>440</v>
+        <v>476</v>
       </c>
       <c r="I193" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J193">
         <v>1</v>
@@ -7803,27 +7881,27 @@
         <v>128320.65</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12">
       <c r="A194" t="s">
         <v>12</v>
       </c>
       <c r="B194" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="C194" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D194" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="E194" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F194" t="s">
-        <v>440</v>
+        <v>476</v>
       </c>
       <c r="I194" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J194">
         <v>6</v>
@@ -7835,27 +7913,27 @@
         <v>939898.26</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12">
       <c r="A195" t="s">
         <v>12</v>
       </c>
       <c r="B195" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="C195" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D195" t="s">
-        <v>411</v>
+        <v>447</v>
       </c>
       <c r="E195" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F195" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I195" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J195">
         <v>2</v>
@@ -7867,27 +7945,27 @@
         <v>184387.62</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12">
       <c r="A196" t="s">
         <v>12</v>
       </c>
       <c r="B196" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="C196" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D196" t="s">
-        <v>412</v>
+        <v>448</v>
       </c>
       <c r="E196" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F196" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I196" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J196">
         <v>11</v>
@@ -7899,27 +7977,27 @@
         <v>1098179.83</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12">
       <c r="A197" t="s">
         <v>13</v>
       </c>
       <c r="B197" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="C197" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="D197" t="s">
-        <v>413</v>
+        <v>449</v>
       </c>
       <c r="E197" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="F197" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="I197" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J197">
         <v>6</v>
@@ -7931,27 +8009,27 @@
         <v>144779.28</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12">
       <c r="A198" t="s">
         <v>12</v>
       </c>
       <c r="B198" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="C198" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D198" t="s">
-        <v>414</v>
+        <v>450</v>
       </c>
       <c r="E198" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F198" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I198" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J198">
         <v>1</v>
@@ -7963,27 +8041,27 @@
         <v>477767.5</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12">
       <c r="A199" t="s">
         <v>13</v>
       </c>
       <c r="B199" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="C199" t="s">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>415</v>
+        <v>451</v>
       </c>
       <c r="E199" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="F199" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="I199" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J199">
         <v>4</v>
@@ -7995,27 +8073,27 @@
         <v>476474.6</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12">
       <c r="A200" t="s">
         <v>12</v>
       </c>
-      <c r="B200" s="7">
-        <v>85003</v>
+      <c r="B200" t="s">
+        <v>204</v>
       </c>
       <c r="C200" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D200" t="s">
-        <v>416</v>
+        <v>452</v>
       </c>
       <c r="E200" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F200" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I200" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J200">
         <v>11</v>
@@ -8024,30 +8102,30 @@
         <v>12254.05</v>
       </c>
       <c r="L200">
-        <v>134794.54999999999</v>
-      </c>
-    </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+        <v>134794.55</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12">
       <c r="A201" t="s">
         <v>13</v>
       </c>
-      <c r="B201" s="7">
-        <v>10021566</v>
+      <c r="B201" t="s">
+        <v>205</v>
       </c>
       <c r="C201" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="D201" t="s">
-        <v>417</v>
+        <v>453</v>
       </c>
       <c r="E201" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="F201" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="I201" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J201">
         <v>97</v>
@@ -8059,27 +8137,27 @@
         <v>198228.23</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12">
       <c r="A202" t="s">
         <v>12</v>
       </c>
       <c r="B202" t="s">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="C202" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D202" t="s">
-        <v>418</v>
+        <v>454</v>
       </c>
       <c r="E202" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F202" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I202" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J202">
         <v>2</v>
@@ -8091,27 +8169,27 @@
         <v>114038.58</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12">
       <c r="A203" t="s">
         <v>12</v>
       </c>
       <c r="B203" t="s">
-        <v>173</v>
+        <v>207</v>
       </c>
       <c r="C203" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D203" t="s">
-        <v>419</v>
+        <v>455</v>
       </c>
       <c r="E203" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F203" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I203" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J203">
         <v>4</v>
@@ -8123,27 +8201,27 @@
         <v>219162.96</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12">
       <c r="A204" t="s">
         <v>12</v>
       </c>
       <c r="B204" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="C204" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D204" t="s">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="E204" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F204" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I204" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J204">
         <v>1</v>
@@ -8155,27 +8233,27 @@
         <v>276872.24</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12">
       <c r="A205" t="s">
         <v>13</v>
       </c>
       <c r="B205" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="C205" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="D205" t="s">
-        <v>421</v>
+        <v>457</v>
       </c>
       <c r="E205" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="F205" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="I205" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J205">
         <v>1</v>
@@ -8187,59 +8265,59 @@
         <v>228580.22</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12">
       <c r="A206" t="s">
         <v>13</v>
       </c>
       <c r="B206" t="s">
-        <v>176</v>
+        <v>210</v>
       </c>
       <c r="C206" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="D206" t="s">
-        <v>422</v>
+        <v>458</v>
       </c>
       <c r="E206" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="F206" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="I206" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J206">
         <v>1</v>
       </c>
       <c r="K206">
-        <v>588448.44999999995</v>
+        <v>588448.45</v>
       </c>
       <c r="L206">
-        <v>588448.44999999995</v>
-      </c>
-    </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+        <v>588448.45</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12">
       <c r="A207" t="s">
         <v>12</v>
       </c>
       <c r="B207" t="s">
-        <v>177</v>
+        <v>211</v>
       </c>
       <c r="C207" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D207" t="s">
-        <v>423</v>
+        <v>459</v>
       </c>
       <c r="E207" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F207" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I207" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J207">
         <v>2</v>
@@ -8251,27 +8329,27 @@
         <v>343808.48</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12">
       <c r="A208" t="s">
         <v>13</v>
       </c>
       <c r="B208" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="C208" t="s">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="D208" t="s">
-        <v>424</v>
+        <v>460</v>
       </c>
       <c r="E208" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="F208" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="I208" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J208">
         <v>1</v>
@@ -8283,27 +8361,27 @@
         <v>52120.37</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12">
       <c r="A209" t="s">
         <v>12</v>
       </c>
       <c r="B209" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="C209" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D209" t="s">
-        <v>425</v>
+        <v>461</v>
       </c>
       <c r="E209" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F209" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I209" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J209">
         <v>1</v>
@@ -8315,27 +8393,27 @@
         <v>907492.78</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12">
       <c r="A210" t="s">
         <v>13</v>
       </c>
       <c r="B210" t="s">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="C210" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>426</v>
+        <v>462</v>
       </c>
       <c r="E210" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="F210" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="I210" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J210">
         <v>2</v>
@@ -8347,27 +8425,27 @@
         <v>236003.46</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12">
       <c r="A211" t="s">
         <v>13</v>
       </c>
       <c r="B211" t="s">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="C211" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>427</v>
+        <v>463</v>
       </c>
       <c r="E211" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="F211" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="I211" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J211">
         <v>1</v>
@@ -8379,27 +8457,27 @@
         <v>56470.99</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12">
       <c r="A212" t="s">
         <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>182</v>
+        <v>216</v>
       </c>
       <c r="C212" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="D212" t="s">
-        <v>428</v>
+        <v>464</v>
       </c>
       <c r="E212" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="F212" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="I212" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J212">
         <v>6</v>
@@ -8411,27 +8489,27 @@
         <v>121897.62</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12">
       <c r="A213" t="s">
         <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="C213" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="D213" t="s">
-        <v>429</v>
+        <v>465</v>
       </c>
       <c r="E213" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F213" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I213" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J213">
         <v>1</v>
@@ -8443,27 +8521,27 @@
         <v>64719.29</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12">
       <c r="A214" t="s">
         <v>12</v>
       </c>
-      <c r="B214" s="7">
-        <v>4303424</v>
+      <c r="B214" t="s">
+        <v>218</v>
       </c>
       <c r="C214" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D214" t="s">
-        <v>430</v>
+        <v>466</v>
       </c>
       <c r="E214" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F214" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I214" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J214">
         <v>5</v>
@@ -8475,27 +8553,27 @@
         <v>77158.45</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12">
       <c r="A215" t="s">
         <v>12</v>
       </c>
-      <c r="B215" s="7">
-        <v>16980</v>
+      <c r="B215" t="s">
+        <v>219</v>
       </c>
       <c r="C215" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="D215" t="s">
-        <v>431</v>
+        <v>467</v>
       </c>
       <c r="E215" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="F215" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="I215" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J215">
         <v>23</v>
@@ -8507,59 +8585,59 @@
         <v>68982.98</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12">
       <c r="A216" t="s">
         <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>184</v>
+        <v>220</v>
       </c>
       <c r="C216" t="s">
-        <v>227</v>
+        <v>263</v>
       </c>
       <c r="D216" t="s">
-        <v>432</v>
+        <v>468</v>
       </c>
       <c r="E216" t="s">
-        <v>227</v>
+        <v>263</v>
       </c>
       <c r="F216" t="s">
-        <v>227</v>
+        <v>263</v>
       </c>
       <c r="I216" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J216">
         <v>4</v>
       </c>
       <c r="K216">
-        <v>40143.730000000003</v>
+        <v>40143.73</v>
       </c>
       <c r="L216">
-        <v>160574.92000000001</v>
-      </c>
-    </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+        <v>160574.92</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12">
       <c r="A217" t="s">
         <v>13</v>
       </c>
       <c r="B217" t="s">
-        <v>185</v>
+        <v>221</v>
       </c>
       <c r="C217" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="D217" t="s">
-        <v>433</v>
+        <v>469</v>
       </c>
       <c r="E217" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="F217" t="s">
-        <v>441</v>
+        <v>477</v>
       </c>
       <c r="I217" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J217">
         <v>1</v>
@@ -8571,27 +8649,27 @@
         <v>259475.34</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12">
       <c r="A218" t="s">
         <v>13</v>
       </c>
       <c r="B218" t="s">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="C218" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>434</v>
+        <v>470</v>
       </c>
       <c r="E218" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="F218" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="I218" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J218">
         <v>2</v>
@@ -8603,27 +8681,27 @@
         <v>224000</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12">
       <c r="A219" t="s">
         <v>13</v>
       </c>
       <c r="B219" t="s">
-        <v>187</v>
+        <v>223</v>
       </c>
       <c r="C219" t="s">
-        <v>229</v>
+        <v>265</v>
       </c>
       <c r="D219" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="E219" t="s">
-        <v>229</v>
+        <v>265</v>
       </c>
       <c r="F219" t="s">
-        <v>229</v>
+        <v>265</v>
       </c>
       <c r="I219" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="J219">
         <v>6</v>

--- a/VALORIZADO FALTANTES.xlsx
+++ b/VALORIZADO FALTANTES.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1483" uniqueCount="486">
   <si>
     <t>Categoría</t>
   </si>
@@ -385,9 +385,6 @@
     <t>PAI0514</t>
   </si>
   <si>
-    <t>PAI360-104-501</t>
-  </si>
-  <si>
     <t>PAI8280-004</t>
   </si>
   <si>
@@ -1138,9 +1135,6 @@
     <t>RELOJ TEMPERATURA AGUA CUMMINS 72 INC</t>
   </si>
   <si>
-    <t>OVERHAUL DT360 PISTON 410010 "1817178C2"</t>
-  </si>
-  <si>
     <t>CAMISA MOTOR-004 MACK 315-E6</t>
   </si>
   <si>
@@ -1432,15 +1426,15 @@
     <t>BUJES EJE DE LEVAS CUMMINS L10 - ISM (JUEGO X 7UND)</t>
   </si>
   <si>
+    <t>MT-OTROS</t>
+  </si>
+  <si>
     <t>REPARACION CULATA</t>
   </si>
   <si>
     <t>DANA</t>
   </si>
   <si>
-    <t>MT-OTROS</t>
-  </si>
-  <si>
     <t>AMORTIGUADORES</t>
   </si>
   <si>
@@ -1471,13 +1465,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/10/2025 08:45:56</t>
+    <t>Período: 30/11/2025 08:47:22</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 30/10/2025 08:46:48</t>
+    <t>Fecha y hora de generación: 26/11/2025 08:48:22</t>
   </si>
 </sst>
 </file>
@@ -1891,28 +1885,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L219"/>
+  <dimension ref="A1:L218"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1928,7 +1922,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1944,12 +1938,12 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="I7" s="5" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -2001,19 +1995,19 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I10" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J10">
         <v>3</v>
@@ -2033,19 +2027,19 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I11" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -2065,19 +2059,19 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I12" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -2097,19 +2091,19 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E13" t="s">
-        <v>264</v>
+        <v>470</v>
       </c>
       <c r="F13" t="s">
-        <v>264</v>
+        <v>470</v>
       </c>
       <c r="I13" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -2129,19 +2123,19 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I14" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -2161,19 +2155,19 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I15" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -2193,19 +2187,19 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I16" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J16">
         <v>2</v>
@@ -2225,19 +2219,19 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D17" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E17" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F17" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I17" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2257,19 +2251,19 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D18" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E18" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F18" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I18" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2289,19 +2283,19 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I19" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -2321,19 +2315,19 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D20" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I20" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2353,19 +2347,19 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I21" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2385,19 +2379,19 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D22" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I22" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J22">
         <v>3</v>
@@ -2417,19 +2411,19 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D23" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I23" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J23">
         <v>2</v>
@@ -2449,19 +2443,19 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D24" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E24" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F24" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I24" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -2481,19 +2475,19 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D25" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E25" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F25" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I25" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J25">
         <v>2</v>
@@ -2513,19 +2507,19 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D26" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I26" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -2545,19 +2539,19 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E27" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F27" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I27" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J27">
         <v>3</v>
@@ -2577,19 +2571,19 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D28" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E28" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F28" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I28" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2609,19 +2603,19 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I29" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2641,19 +2635,19 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D30" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E30" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F30" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I30" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J30">
         <v>2</v>
@@ -2673,19 +2667,19 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D31" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I31" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J31">
         <v>2</v>
@@ -2705,19 +2699,19 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D32" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E32" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I32" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J32">
         <v>12</v>
@@ -2737,19 +2731,19 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D33" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E33" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F33" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I33" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J33">
         <v>6</v>
@@ -2769,19 +2763,19 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D34" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E34" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F34" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I34" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J34">
         <v>6</v>
@@ -2801,19 +2795,19 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D35" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E35" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F35" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I35" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2833,19 +2827,19 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D36" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E36" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F36" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I36" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2865,19 +2859,19 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D37" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E37" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F37" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I37" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J37">
         <v>3</v>
@@ -2897,19 +2891,19 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D38" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E38" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F38" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I38" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J38">
         <v>123</v>
@@ -2929,19 +2923,19 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D39" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E39" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F39" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I39" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J39">
         <v>4</v>
@@ -2961,19 +2955,19 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D40" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E40" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F40" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I40" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -2993,19 +2987,19 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D41" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I41" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -3025,19 +3019,19 @@
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D42" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E42" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F42" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I42" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J42">
         <v>12</v>
@@ -3057,19 +3051,19 @@
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D43" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E43" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F43" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I43" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -3089,19 +3083,19 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D44" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E44" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="F44" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="I44" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J44">
         <v>2</v>
@@ -3121,19 +3115,19 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D45" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E45" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="F45" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="I45" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J45">
         <v>12</v>
@@ -3153,19 +3147,19 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D46" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E46" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F46" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I46" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -3185,19 +3179,19 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D47" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I47" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J47">
         <v>2</v>
@@ -3217,19 +3211,19 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D48" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E48" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F48" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I48" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J48">
         <v>4</v>
@@ -3249,19 +3243,19 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D49" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E49" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F49" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I49" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -3281,19 +3275,19 @@
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D50" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E50" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F50" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I50" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J50">
         <v>5</v>
@@ -3313,19 +3307,19 @@
         <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D51" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E51" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="F51" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="I51" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -3345,19 +3339,19 @@
         <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D52" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E52" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F52" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I52" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J52">
         <v>3</v>
@@ -3377,19 +3371,19 @@
         <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D53" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I53" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J53">
         <v>2</v>
@@ -3409,19 +3403,19 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D54" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E54" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F54" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I54" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -3441,19 +3435,19 @@
         <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D55" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E55" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F55" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I55" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J55">
         <v>3</v>
@@ -3473,19 +3467,19 @@
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D56" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E56" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F56" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I56" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -3505,19 +3499,19 @@
         <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D57" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E57" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F57" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I57" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J57">
         <v>2</v>
@@ -3537,19 +3531,19 @@
         <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D58" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E58" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F58" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I58" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J58">
         <v>2</v>
@@ -3569,28 +3563,28 @@
         <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D59" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E59" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F59" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I59" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J59">
-        <v>91</v>
+        <v>206</v>
       </c>
       <c r="K59">
-        <v>9923</v>
+        <v>10428.31</v>
       </c>
       <c r="L59">
-        <v>902993</v>
+        <v>2148231.86</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3601,28 +3595,28 @@
         <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D60" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E60" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F60" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I60" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J60">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="K60">
-        <v>5328.05</v>
+        <v>5719.65</v>
       </c>
       <c r="L60">
-        <v>149185.4</v>
+        <v>263103.9</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3633,19 +3627,19 @@
         <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D61" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E61" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F61" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I61" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J61">
         <v>6</v>
@@ -3665,19 +3659,19 @@
         <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D62" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E62" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F62" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I62" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J62">
         <v>64</v>
@@ -3697,19 +3691,19 @@
         <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D63" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E63" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F63" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I63" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J63">
         <v>3</v>
@@ -3729,19 +3723,19 @@
         <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D64" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E64" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F64" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I64" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J64">
         <v>2</v>
@@ -3761,19 +3755,19 @@
         <v>69</v>
       </c>
       <c r="C65" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D65" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E65" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F65" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I65" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J65">
         <v>20</v>
@@ -3793,19 +3787,19 @@
         <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D66" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E66" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F66" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I66" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J66">
         <v>5</v>
@@ -3825,19 +3819,19 @@
         <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D67" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E67" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F67" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I67" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3857,19 +3851,19 @@
         <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D68" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E68" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F68" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I68" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3889,19 +3883,19 @@
         <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D69" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E69" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F69" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I69" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J69">
         <v>5</v>
@@ -3921,19 +3915,19 @@
         <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D70" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E70" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F70" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="I70" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J70">
         <v>2</v>
@@ -3953,19 +3947,19 @@
         <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D71" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E71" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F71" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I71" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J71">
         <v>4</v>
@@ -3985,19 +3979,19 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D72" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E72" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F72" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I72" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J72">
         <v>3</v>
@@ -4017,19 +4011,19 @@
         <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D73" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E73" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F73" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I73" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J73">
         <v>4</v>
@@ -4049,19 +4043,19 @@
         <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D74" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E74" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F74" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I74" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -4081,19 +4075,19 @@
         <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D75" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E75" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F75" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I75" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J75">
         <v>1</v>
@@ -4113,19 +4107,19 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D76" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E76" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F76" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I76" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J76">
         <v>1</v>
@@ -4145,19 +4139,19 @@
         <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D77" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E77" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F77" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I77" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J77">
         <v>2</v>
@@ -4177,19 +4171,19 @@
         <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D78" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E78" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F78" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I78" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J78">
         <v>1</v>
@@ -4209,19 +4203,19 @@
         <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D79" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E79" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F79" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I79" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J79">
         <v>3</v>
@@ -4241,19 +4235,19 @@
         <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D80" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E80" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F80" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I80" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J80">
         <v>1</v>
@@ -4273,19 +4267,19 @@
         <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D81" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E81" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F81" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I81" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J81">
         <v>2</v>
@@ -4305,19 +4299,19 @@
         <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D82" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E82" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F82" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I82" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J82">
         <v>5</v>
@@ -4337,19 +4331,19 @@
         <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D83" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E83" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F83" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I83" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J83">
         <v>5</v>
@@ -4369,19 +4363,19 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D84" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E84" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F84" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I84" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J84">
         <v>21</v>
@@ -4401,19 +4395,19 @@
         <v>89</v>
       </c>
       <c r="C85" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D85" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E85" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F85" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I85" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J85">
         <v>1</v>
@@ -4433,19 +4427,19 @@
         <v>90</v>
       </c>
       <c r="C86" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D86" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E86" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F86" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I86" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J86">
         <v>4</v>
@@ -4465,19 +4459,19 @@
         <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D87" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E87" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F87" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="I87" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J87">
         <v>2</v>
@@ -4497,19 +4491,19 @@
         <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D88" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E88" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F88" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I88" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J88">
         <v>2</v>
@@ -4529,19 +4523,19 @@
         <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D89" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E89" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F89" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I89" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J89">
         <v>10</v>
@@ -4561,19 +4555,19 @@
         <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D90" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E90" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F90" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I90" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J90">
         <v>8</v>
@@ -4593,19 +4587,19 @@
         <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D91" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E91" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F91" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I91" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J91">
         <v>1</v>
@@ -4625,19 +4619,19 @@
         <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D92" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E92" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F92" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I92" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J92">
         <v>2</v>
@@ -4657,19 +4651,19 @@
         <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D93" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E93" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F93" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I93" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J93">
         <v>4</v>
@@ -4689,19 +4683,19 @@
         <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D94" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E94" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F94" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I94" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J94">
         <v>8</v>
@@ -4721,19 +4715,19 @@
         <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D95" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E95" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F95" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I95" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J95">
         <v>2</v>
@@ -4753,19 +4747,19 @@
         <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D96" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E96" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F96" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I96" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J96">
         <v>1</v>
@@ -4785,19 +4779,19 @@
         <v>101</v>
       </c>
       <c r="C97" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D97" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E97" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F97" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I97" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J97">
         <v>2</v>
@@ -4817,19 +4811,19 @@
         <v>102</v>
       </c>
       <c r="C98" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D98" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E98" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F98" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I98" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J98">
         <v>21</v>
@@ -4849,19 +4843,19 @@
         <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D99" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E99" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F99" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I99" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J99">
         <v>1</v>
@@ -4881,19 +4875,19 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D100" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E100" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F100" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I100" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J100">
         <v>3</v>
@@ -4913,19 +4907,19 @@
         <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D101" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E101" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F101" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I101" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J101">
         <v>1</v>
@@ -4945,19 +4939,19 @@
         <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D102" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E102" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F102" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I102" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J102">
         <v>1</v>
@@ -4977,19 +4971,19 @@
         <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D103" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E103" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F103" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I103" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J103">
         <v>2</v>
@@ -5009,19 +5003,19 @@
         <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D104" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E104" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F104" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I104" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J104">
         <v>2</v>
@@ -5041,19 +5035,19 @@
         <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D105" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E105" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F105" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I105" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J105">
         <v>13</v>
@@ -5073,19 +5067,19 @@
         <v>110</v>
       </c>
       <c r="C106" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D106" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E106" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F106" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I106" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J106">
         <v>3</v>
@@ -5105,19 +5099,19 @@
         <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D107" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E107" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F107" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I107" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J107">
         <v>276</v>
@@ -5137,19 +5131,19 @@
         <v>112</v>
       </c>
       <c r="C108" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D108" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E108" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F108" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I108" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J108">
         <v>1</v>
@@ -5169,19 +5163,19 @@
         <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D109" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E109" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F109" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I109" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J109">
         <v>144</v>
@@ -5201,19 +5195,19 @@
         <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D110" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E110" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F110" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I110" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J110">
         <v>10</v>
@@ -5233,19 +5227,19 @@
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D111" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E111" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F111" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I111" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J111">
         <v>5</v>
@@ -5265,19 +5259,19 @@
         <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D112" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E112" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F112" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I112" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J112">
         <v>1</v>
@@ -5297,19 +5291,19 @@
         <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D113" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E113" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F113" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I113" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J113">
         <v>2</v>
@@ -5329,19 +5323,19 @@
         <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D114" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E114" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F114" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I114" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J114">
         <v>1</v>
@@ -5361,19 +5355,19 @@
         <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D115" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E115" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F115" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I115" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J115">
         <v>1</v>
@@ -5393,19 +5387,19 @@
         <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D116" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E116" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F116" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I116" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J116">
         <v>2</v>
@@ -5425,19 +5419,19 @@
         <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D117" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E117" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F117" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I117" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J117">
         <v>4</v>
@@ -5457,19 +5451,19 @@
         <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D118" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E118" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F118" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I118" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J118">
         <v>1</v>
@@ -5489,92 +5483,92 @@
         <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D119" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E119" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F119" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I119" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J119">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K119">
-        <v>2373776.35</v>
+        <v>153331.85</v>
       </c>
       <c r="L119">
-        <v>2373776.35</v>
+        <v>459995.55</v>
       </c>
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B120" t="s">
         <v>124</v>
       </c>
       <c r="C120" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D120" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E120" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F120" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I120" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J120">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K120">
-        <v>153331.85</v>
+        <v>151827.5</v>
       </c>
       <c r="L120">
-        <v>459995.55</v>
+        <v>759137.5</v>
       </c>
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B121" t="s">
         <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D121" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E121" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F121" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I121" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J121">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K121">
-        <v>151827.5</v>
+        <v>126875.69</v>
       </c>
       <c r="L121">
-        <v>759137.5</v>
+        <v>126875.69</v>
       </c>
     </row>
     <row r="122" spans="1:12">
@@ -5585,28 +5579,28 @@
         <v>126</v>
       </c>
       <c r="C122" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D122" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E122" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F122" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I122" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J122">
         <v>1</v>
       </c>
       <c r="K122">
-        <v>126875.69</v>
+        <v>418397.52</v>
       </c>
       <c r="L122">
-        <v>126875.69</v>
+        <v>418397.52</v>
       </c>
     </row>
     <row r="123" spans="1:12">
@@ -5617,28 +5611,28 @@
         <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D123" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E123" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="F123" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="I123" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J123">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K123">
-        <v>418397.52</v>
+        <v>60881.05</v>
       </c>
       <c r="L123">
-        <v>418397.52</v>
+        <v>730572.6</v>
       </c>
     </row>
     <row r="124" spans="1:12">
@@ -5649,28 +5643,28 @@
         <v>128</v>
       </c>
       <c r="C124" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D124" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E124" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F124" t="s">
-        <v>232</v>
+        <v>474</v>
       </c>
       <c r="I124" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J124">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K124">
-        <v>60881.05</v>
+        <v>53403.02</v>
       </c>
       <c r="L124">
-        <v>730572.6</v>
+        <v>53403.02</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -5681,28 +5675,28 @@
         <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D125" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E125" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F125" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I125" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J125">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K125">
-        <v>53403.02</v>
+        <v>80962.22</v>
       </c>
       <c r="L125">
-        <v>53403.02</v>
+        <v>404811.1</v>
       </c>
     </row>
     <row r="126" spans="1:12">
@@ -5713,28 +5707,28 @@
         <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D126" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E126" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F126" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I126" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J126">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K126">
-        <v>80962.22</v>
+        <v>30016.79</v>
       </c>
       <c r="L126">
-        <v>404811.1</v>
+        <v>90050.37</v>
       </c>
     </row>
     <row r="127" spans="1:12">
@@ -5745,28 +5739,28 @@
         <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D127" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E127" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F127" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I127" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J127">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K127">
-        <v>30016.79</v>
+        <v>55960.12</v>
       </c>
       <c r="L127">
-        <v>90050.37</v>
+        <v>111920.24</v>
       </c>
     </row>
     <row r="128" spans="1:12">
@@ -5777,28 +5771,28 @@
         <v>132</v>
       </c>
       <c r="C128" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D128" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E128" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F128" t="s">
-        <v>476</v>
+        <v>231</v>
       </c>
       <c r="I128" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K128">
-        <v>55960.12</v>
+        <v>57770.2</v>
       </c>
       <c r="L128">
-        <v>111920.24</v>
+        <v>57770.2</v>
       </c>
     </row>
     <row r="129" spans="1:12">
@@ -5809,60 +5803,60 @@
         <v>133</v>
       </c>
       <c r="C129" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D129" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E129" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F129" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I129" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J129">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K129">
-        <v>57770.2</v>
+        <v>122224.03</v>
       </c>
       <c r="L129">
-        <v>57770.2</v>
+        <v>488896.12</v>
       </c>
     </row>
     <row r="130" spans="1:12">
       <c r="A130" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B130" t="s">
         <v>134</v>
       </c>
       <c r="C130" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D130" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E130" t="s">
-        <v>232</v>
+        <v>472</v>
       </c>
       <c r="F130" t="s">
-        <v>232</v>
+        <v>472</v>
       </c>
       <c r="I130" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J130">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K130">
-        <v>122224.03</v>
+        <v>345599.99</v>
       </c>
       <c r="L130">
-        <v>488896.12</v>
+        <v>691199.98</v>
       </c>
     </row>
     <row r="131" spans="1:12">
@@ -5873,28 +5867,28 @@
         <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D131" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E131" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F131" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I131" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J131">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K131">
-        <v>345599.99</v>
+        <v>406977.4</v>
       </c>
       <c r="L131">
-        <v>691199.98</v>
+        <v>1627909.6</v>
       </c>
     </row>
     <row r="132" spans="1:12">
@@ -5905,60 +5899,60 @@
         <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D132" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E132" t="s">
-        <v>473</v>
+        <v>224</v>
       </c>
       <c r="F132" t="s">
-        <v>473</v>
+        <v>224</v>
       </c>
       <c r="I132" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J132">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K132">
-        <v>406977.4</v>
+        <v>108921.66</v>
       </c>
       <c r="L132">
-        <v>1627909.6</v>
+        <v>108921.66</v>
       </c>
     </row>
     <row r="133" spans="1:12">
       <c r="A133" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B133" t="s">
         <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="D133" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E133" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="F133" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="I133" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J133">
         <v>1</v>
       </c>
       <c r="K133">
-        <v>108921.66</v>
+        <v>155407.11</v>
       </c>
       <c r="L133">
-        <v>108921.66</v>
+        <v>155407.11</v>
       </c>
     </row>
     <row r="134" spans="1:12">
@@ -5972,7 +5966,7 @@
         <v>254</v>
       </c>
       <c r="D134" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E134" t="s">
         <v>254</v>
@@ -5981,16 +5975,16 @@
         <v>254</v>
       </c>
       <c r="I134" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K134">
-        <v>155407.11</v>
+        <v>302306.98</v>
       </c>
       <c r="L134">
-        <v>155407.11</v>
+        <v>604613.96</v>
       </c>
     </row>
     <row r="135" spans="1:12">
@@ -6001,28 +5995,28 @@
         <v>139</v>
       </c>
       <c r="C135" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D135" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E135" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F135" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I135" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K135">
-        <v>302306.98</v>
+        <v>462946.56</v>
       </c>
       <c r="L135">
-        <v>604613.96</v>
+        <v>462946.56</v>
       </c>
     </row>
     <row r="136" spans="1:12">
@@ -6033,28 +6027,28 @@
         <v>140</v>
       </c>
       <c r="C136" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D136" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E136" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F136" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I136" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J136">
         <v>1</v>
       </c>
       <c r="K136">
-        <v>462946.56</v>
+        <v>622170.75</v>
       </c>
       <c r="L136">
-        <v>462946.56</v>
+        <v>622170.75</v>
       </c>
     </row>
     <row r="137" spans="1:12">
@@ -6065,28 +6059,28 @@
         <v>141</v>
       </c>
       <c r="C137" t="s">
-        <v>255</v>
+        <v>224</v>
       </c>
       <c r="D137" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E137" t="s">
-        <v>255</v>
+        <v>224</v>
       </c>
       <c r="F137" t="s">
-        <v>255</v>
+        <v>224</v>
       </c>
       <c r="I137" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J137">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K137">
-        <v>622170.75</v>
+        <v>7246.46</v>
       </c>
       <c r="L137">
-        <v>622170.75</v>
+        <v>65218.14</v>
       </c>
     </row>
     <row r="138" spans="1:12">
@@ -6097,92 +6091,92 @@
         <v>142</v>
       </c>
       <c r="C138" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D138" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E138" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F138" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I138" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J138">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="K138">
-        <v>7246.46</v>
+        <v>9200.629999999999</v>
       </c>
       <c r="L138">
-        <v>65218.14</v>
+        <v>202413.86</v>
       </c>
     </row>
     <row r="139" spans="1:12">
       <c r="A139" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B139" t="s">
         <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D139" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E139" t="s">
-        <v>225</v>
+        <v>472</v>
       </c>
       <c r="F139" t="s">
-        <v>225</v>
+        <v>472</v>
       </c>
       <c r="I139" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J139">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="K139">
-        <v>9200.629999999999</v>
+        <v>13906.96</v>
       </c>
       <c r="L139">
-        <v>202413.86</v>
+        <v>83441.75999999999</v>
       </c>
     </row>
     <row r="140" spans="1:12">
       <c r="A140" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B140" t="s">
         <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="D140" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E140" t="s">
-        <v>473</v>
+        <v>224</v>
       </c>
       <c r="F140" t="s">
-        <v>473</v>
+        <v>255</v>
       </c>
       <c r="I140" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J140">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K140">
-        <v>13906.96</v>
+        <v>67728.10000000001</v>
       </c>
       <c r="L140">
-        <v>83441.75999999999</v>
+        <v>677281</v>
       </c>
     </row>
     <row r="141" spans="1:12">
@@ -6193,28 +6187,28 @@
         <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="D141" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E141" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F141" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="I141" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J141">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K141">
-        <v>67728.10000000001</v>
+        <v>541166.88</v>
       </c>
       <c r="L141">
-        <v>677281</v>
+        <v>2164667.52</v>
       </c>
     </row>
     <row r="142" spans="1:12">
@@ -6225,92 +6219,92 @@
         <v>146</v>
       </c>
       <c r="C142" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D142" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E142" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F142" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I142" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J142">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K142">
-        <v>541166.88</v>
+        <v>31630.01</v>
       </c>
       <c r="L142">
-        <v>2164667.52</v>
+        <v>63260.02</v>
       </c>
     </row>
     <row r="143" spans="1:12">
       <c r="A143" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B143" t="s">
         <v>147</v>
       </c>
       <c r="C143" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="D143" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E143" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="F143" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="I143" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J143">
         <v>2</v>
       </c>
       <c r="K143">
-        <v>31630.01</v>
+        <v>107104.68</v>
       </c>
       <c r="L143">
-        <v>63260.02</v>
+        <v>214209.36</v>
       </c>
     </row>
     <row r="144" spans="1:12">
       <c r="A144" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B144" t="s">
         <v>148</v>
       </c>
       <c r="C144" t="s">
-        <v>257</v>
+        <v>224</v>
       </c>
       <c r="D144" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E144" t="s">
-        <v>264</v>
+        <v>224</v>
       </c>
       <c r="F144" t="s">
-        <v>264</v>
+        <v>224</v>
       </c>
       <c r="I144" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J144">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K144">
-        <v>107104.68</v>
+        <v>221067.08</v>
       </c>
       <c r="L144">
-        <v>214209.36</v>
+        <v>221067.08</v>
       </c>
     </row>
     <row r="145" spans="1:12">
@@ -6321,92 +6315,92 @@
         <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D145" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E145" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F145" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I145" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J145">
         <v>1</v>
       </c>
       <c r="K145">
-        <v>221067.08</v>
+        <v>204405.71</v>
       </c>
       <c r="L145">
-        <v>221067.08</v>
+        <v>204405.71</v>
       </c>
     </row>
     <row r="146" spans="1:12">
       <c r="A146" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B146" t="s">
         <v>150</v>
       </c>
       <c r="C146" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D146" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E146" t="s">
-        <v>225</v>
+        <v>472</v>
       </c>
       <c r="F146" t="s">
-        <v>225</v>
+        <v>472</v>
       </c>
       <c r="I146" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J146">
         <v>1</v>
       </c>
       <c r="K146">
-        <v>204405.71</v>
+        <v>151612.17</v>
       </c>
       <c r="L146">
-        <v>204405.71</v>
+        <v>151612.17</v>
       </c>
     </row>
     <row r="147" spans="1:12">
       <c r="A147" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B147" t="s">
         <v>151</v>
       </c>
       <c r="C147" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D147" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E147" t="s">
-        <v>473</v>
+        <v>224</v>
       </c>
       <c r="F147" t="s">
-        <v>473</v>
+        <v>224</v>
       </c>
       <c r="I147" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J147">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K147">
-        <v>151612.17</v>
+        <v>152565.53</v>
       </c>
       <c r="L147">
-        <v>151612.17</v>
+        <v>762827.65</v>
       </c>
     </row>
     <row r="148" spans="1:12">
@@ -6417,28 +6411,28 @@
         <v>152</v>
       </c>
       <c r="C148" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D148" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E148" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F148" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I148" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J148">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K148">
-        <v>152565.53</v>
+        <v>648344.71</v>
       </c>
       <c r="L148">
-        <v>762827.65</v>
+        <v>1945034.13</v>
       </c>
     </row>
     <row r="149" spans="1:12">
@@ -6449,28 +6443,28 @@
         <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D149" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E149" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F149" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I149" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J149">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K149">
-        <v>648344.71</v>
+        <v>61274.69</v>
       </c>
       <c r="L149">
-        <v>1945034.13</v>
+        <v>245098.76</v>
       </c>
     </row>
     <row r="150" spans="1:12">
@@ -6481,92 +6475,92 @@
         <v>154</v>
       </c>
       <c r="C150" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D150" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E150" t="s">
-        <v>232</v>
+        <v>470</v>
       </c>
       <c r="F150" t="s">
-        <v>232</v>
+        <v>470</v>
       </c>
       <c r="I150" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J150">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K150">
-        <v>61274.69</v>
+        <v>134461.16</v>
       </c>
       <c r="L150">
-        <v>245098.76</v>
+        <v>134461.16</v>
       </c>
     </row>
     <row r="151" spans="1:12">
       <c r="A151" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B151" t="s">
         <v>155</v>
       </c>
       <c r="C151" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D151" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E151" t="s">
-        <v>474</v>
+        <v>231</v>
       </c>
       <c r="F151" t="s">
-        <v>474</v>
+        <v>231</v>
       </c>
       <c r="I151" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J151">
         <v>1</v>
       </c>
       <c r="K151">
-        <v>134461.16</v>
+        <v>150000</v>
       </c>
       <c r="L151">
-        <v>134461.16</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="152" spans="1:12">
       <c r="A152" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B152" t="s">
         <v>156</v>
       </c>
       <c r="C152" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D152" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E152" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="F152" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="I152" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J152">
         <v>1</v>
       </c>
       <c r="K152">
-        <v>150000</v>
+        <v>437278.29</v>
       </c>
       <c r="L152">
-        <v>150000</v>
+        <v>437278.29</v>
       </c>
     </row>
     <row r="153" spans="1:12">
@@ -6577,28 +6571,28 @@
         <v>157</v>
       </c>
       <c r="C153" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D153" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E153" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F153" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I153" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J153">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K153">
-        <v>437278.29</v>
+        <v>68988.75999999999</v>
       </c>
       <c r="L153">
-        <v>437278.29</v>
+        <v>689887.6</v>
       </c>
     </row>
     <row r="154" spans="1:12">
@@ -6609,60 +6603,60 @@
         <v>158</v>
       </c>
       <c r="C154" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D154" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E154" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F154" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I154" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J154">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K154">
-        <v>68988.75999999999</v>
+        <v>321061.61</v>
       </c>
       <c r="L154">
-        <v>689887.6</v>
+        <v>642123.22</v>
       </c>
     </row>
     <row r="155" spans="1:12">
       <c r="A155" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B155" t="s">
         <v>159</v>
       </c>
       <c r="C155" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D155" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E155" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F155" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I155" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J155">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K155">
-        <v>321061.61</v>
+        <v>86292.41</v>
       </c>
       <c r="L155">
-        <v>642123.22</v>
+        <v>86292.41</v>
       </c>
     </row>
     <row r="156" spans="1:12">
@@ -6673,42 +6667,42 @@
         <v>160</v>
       </c>
       <c r="C156" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D156" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E156" t="s">
-        <v>232</v>
+        <v>472</v>
       </c>
       <c r="F156" t="s">
-        <v>232</v>
+        <v>472</v>
       </c>
       <c r="I156" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J156">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K156">
-        <v>86292.41</v>
+        <v>275914.15</v>
       </c>
       <c r="L156">
-        <v>86292.41</v>
+        <v>827742.45</v>
       </c>
     </row>
     <row r="157" spans="1:12">
       <c r="A157" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B157" t="s">
         <v>161</v>
       </c>
       <c r="C157" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="D157" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E157" t="s">
         <v>473</v>
@@ -6717,16 +6711,16 @@
         <v>473</v>
       </c>
       <c r="I157" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J157">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K157">
-        <v>275914.15</v>
+        <v>145438.64</v>
       </c>
       <c r="L157">
-        <v>827742.45</v>
+        <v>145438.64</v>
       </c>
     </row>
     <row r="158" spans="1:12">
@@ -6737,156 +6731,156 @@
         <v>162</v>
       </c>
       <c r="C158" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="D158" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E158" t="s">
-        <v>475</v>
+        <v>231</v>
       </c>
       <c r="F158" t="s">
-        <v>475</v>
+        <v>231</v>
       </c>
       <c r="I158" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J158">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="K158">
-        <v>145438.64</v>
+        <v>124259.74</v>
       </c>
       <c r="L158">
-        <v>145438.64</v>
+        <v>1988155.84</v>
       </c>
     </row>
     <row r="159" spans="1:12">
       <c r="A159" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B159" t="s">
         <v>163</v>
       </c>
       <c r="C159" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="D159" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E159" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="F159" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="I159" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J159">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K159">
-        <v>124259.74</v>
+        <v>127385.01</v>
       </c>
       <c r="L159">
-        <v>1988155.84</v>
+        <v>127385.01</v>
       </c>
     </row>
     <row r="160" spans="1:12">
       <c r="A160" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B160" t="s">
         <v>164</v>
       </c>
       <c r="C160" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="D160" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E160" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="F160" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="I160" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J160">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K160">
-        <v>127385.01</v>
+        <v>409485.91</v>
       </c>
       <c r="L160">
-        <v>127385.01</v>
+        <v>818971.8199999999</v>
       </c>
     </row>
     <row r="161" spans="1:12">
       <c r="A161" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B161" t="s">
         <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D161" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E161" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F161" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I161" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J161">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K161">
-        <v>409485.91</v>
+        <v>411573.74</v>
       </c>
       <c r="L161">
-        <v>818971.8199999999</v>
+        <v>411573.74</v>
       </c>
     </row>
     <row r="162" spans="1:12">
       <c r="A162" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B162" t="s">
         <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="D162" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E162" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F162" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="I162" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J162">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K162">
-        <v>411573.74</v>
+        <v>177929.28</v>
       </c>
       <c r="L162">
-        <v>411573.74</v>
+        <v>355858.56</v>
       </c>
     </row>
     <row r="163" spans="1:12">
@@ -6897,28 +6891,28 @@
         <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D163" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E163" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F163" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="I163" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J163">
         <v>2</v>
       </c>
       <c r="K163">
-        <v>177929.28</v>
+        <v>386975.07</v>
       </c>
       <c r="L163">
-        <v>355858.56</v>
+        <v>773950.14</v>
       </c>
     </row>
     <row r="164" spans="1:12">
@@ -6929,28 +6923,28 @@
         <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="D164" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E164" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="F164" t="s">
-        <v>242</v>
+        <v>474</v>
       </c>
       <c r="I164" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J164">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K164">
-        <v>386975.07</v>
+        <v>66983.8</v>
       </c>
       <c r="L164">
-        <v>773950.14</v>
+        <v>267935.2</v>
       </c>
     </row>
     <row r="165" spans="1:12">
@@ -6961,60 +6955,60 @@
         <v>169</v>
       </c>
       <c r="C165" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="D165" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E165" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="F165" t="s">
-        <v>476</v>
+        <v>254</v>
       </c>
       <c r="I165" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J165">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K165">
-        <v>66983.8</v>
+        <v>159709.51</v>
       </c>
       <c r="L165">
-        <v>267935.2</v>
+        <v>159709.51</v>
       </c>
     </row>
     <row r="166" spans="1:12">
       <c r="A166" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B166" t="s">
         <v>170</v>
       </c>
       <c r="C166" t="s">
-        <v>255</v>
+        <v>224</v>
       </c>
       <c r="D166" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E166" t="s">
-        <v>255</v>
+        <v>224</v>
       </c>
       <c r="F166" t="s">
-        <v>255</v>
+        <v>224</v>
       </c>
       <c r="I166" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J166">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="K166">
-        <v>159709.51</v>
+        <v>2473.41</v>
       </c>
       <c r="L166">
-        <v>159709.51</v>
+        <v>93989.58</v>
       </c>
     </row>
     <row r="167" spans="1:12">
@@ -7025,60 +7019,60 @@
         <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D167" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E167" t="s">
-        <v>225</v>
+        <v>472</v>
       </c>
       <c r="F167" t="s">
-        <v>225</v>
+        <v>472</v>
       </c>
       <c r="I167" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J167">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="K167">
-        <v>2473.41</v>
+        <v>636180.6800000001</v>
       </c>
       <c r="L167">
-        <v>93989.58</v>
+        <v>636180.6800000001</v>
       </c>
     </row>
     <row r="168" spans="1:12">
       <c r="A168" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B168" t="s">
         <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D168" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E168" t="s">
-        <v>473</v>
+        <v>224</v>
       </c>
       <c r="F168" t="s">
-        <v>473</v>
+        <v>224</v>
       </c>
       <c r="I168" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J168">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K168">
-        <v>636180.6800000001</v>
+        <v>27987.95</v>
       </c>
       <c r="L168">
-        <v>636180.6800000001</v>
+        <v>83963.85000000001</v>
       </c>
     </row>
     <row r="169" spans="1:12">
@@ -7089,60 +7083,60 @@
         <v>173</v>
       </c>
       <c r="C169" t="s">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="D169" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E169" t="s">
-        <v>225</v>
+        <v>259</v>
       </c>
       <c r="F169" t="s">
-        <v>225</v>
+        <v>475</v>
       </c>
       <c r="I169" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J169">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K169">
-        <v>27987.95</v>
+        <v>274730.29</v>
       </c>
       <c r="L169">
-        <v>83963.85000000001</v>
+        <v>2747302.9</v>
       </c>
     </row>
     <row r="170" spans="1:12">
       <c r="A170" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B170" t="s">
         <v>174</v>
       </c>
       <c r="C170" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="D170" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E170" t="s">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="F170" t="s">
-        <v>477</v>
+        <v>224</v>
       </c>
       <c r="I170" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J170">
         <v>10</v>
       </c>
       <c r="K170">
-        <v>274730.29</v>
+        <v>5073.44</v>
       </c>
       <c r="L170">
-        <v>2747302.9</v>
+        <v>50734.4</v>
       </c>
     </row>
     <row r="171" spans="1:12">
@@ -7153,60 +7147,60 @@
         <v>175</v>
       </c>
       <c r="C171" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D171" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E171" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F171" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="I171" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J171">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K171">
-        <v>5073.44</v>
+        <v>271098.72</v>
       </c>
       <c r="L171">
-        <v>50734.4</v>
+        <v>1626592.32</v>
       </c>
     </row>
     <row r="172" spans="1:12">
       <c r="A172" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B172" t="s">
         <v>176</v>
       </c>
       <c r="C172" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D172" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E172" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F172" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I172" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J172">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K172">
-        <v>271098.72</v>
+        <v>21390.12</v>
       </c>
       <c r="L172">
-        <v>1626592.32</v>
+        <v>171120.96</v>
       </c>
     </row>
     <row r="173" spans="1:12">
@@ -7217,28 +7211,28 @@
         <v>177</v>
       </c>
       <c r="C173" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="D173" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E173" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="F173" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="I173" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J173">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K173">
-        <v>21390.12</v>
+        <v>325882.63</v>
       </c>
       <c r="L173">
-        <v>171120.96</v>
+        <v>325882.63</v>
       </c>
     </row>
     <row r="174" spans="1:12">
@@ -7249,28 +7243,28 @@
         <v>178</v>
       </c>
       <c r="C174" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="D174" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E174" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F174" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="I174" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K174">
-        <v>325882.63</v>
+        <v>66789.11</v>
       </c>
       <c r="L174">
-        <v>325882.63</v>
+        <v>133578.22</v>
       </c>
     </row>
     <row r="175" spans="1:12">
@@ -7281,28 +7275,28 @@
         <v>179</v>
       </c>
       <c r="C175" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D175" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E175" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F175" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I175" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J175">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K175">
-        <v>66789.11</v>
+        <v>78468.91</v>
       </c>
       <c r="L175">
-        <v>133578.22</v>
+        <v>235406.73</v>
       </c>
     </row>
     <row r="176" spans="1:12">
@@ -7313,28 +7307,28 @@
         <v>180</v>
       </c>
       <c r="C176" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D176" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E176" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="F176" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="I176" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J176">
         <v>3</v>
       </c>
       <c r="K176">
-        <v>78468.91</v>
+        <v>263646.09</v>
       </c>
       <c r="L176">
-        <v>235406.73</v>
+        <v>790938.27</v>
       </c>
     </row>
     <row r="177" spans="1:12">
@@ -7345,28 +7339,28 @@
         <v>181</v>
       </c>
       <c r="C177" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D177" t="s">
-        <v>431</v>
+        <v>333</v>
       </c>
       <c r="E177" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F177" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I177" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J177">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K177">
-        <v>263646.09</v>
+        <v>271387.84</v>
       </c>
       <c r="L177">
-        <v>790938.27</v>
+        <v>542775.6800000001</v>
       </c>
     </row>
     <row r="178" spans="1:12">
@@ -7377,92 +7371,92 @@
         <v>182</v>
       </c>
       <c r="C178" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D178" t="s">
-        <v>334</v>
+        <v>430</v>
       </c>
       <c r="E178" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F178" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I178" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J178">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K178">
-        <v>271387.84</v>
+        <v>73037.78999999999</v>
       </c>
       <c r="L178">
-        <v>542775.6800000001</v>
+        <v>219113.37</v>
       </c>
     </row>
     <row r="179" spans="1:12">
       <c r="A179" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B179" t="s">
         <v>183</v>
       </c>
       <c r="C179" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D179" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E179" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F179" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I179" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J179">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K179">
-        <v>73037.78999999999</v>
+        <v>7049.74</v>
       </c>
       <c r="L179">
-        <v>219113.37</v>
+        <v>98696.36</v>
       </c>
     </row>
     <row r="180" spans="1:12">
       <c r="A180" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B180" t="s">
         <v>184</v>
       </c>
       <c r="C180" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D180" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E180" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F180" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I180" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J180">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K180">
-        <v>7049.74</v>
+        <v>73190.35000000001</v>
       </c>
       <c r="L180">
-        <v>98696.36</v>
+        <v>805093.85</v>
       </c>
     </row>
     <row r="181" spans="1:12">
@@ -7473,28 +7467,28 @@
         <v>185</v>
       </c>
       <c r="C181" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="D181" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E181" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="F181" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="I181" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J181">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K181">
-        <v>73190.35000000001</v>
+        <v>128859.45</v>
       </c>
       <c r="L181">
-        <v>805093.85</v>
+        <v>257718.9</v>
       </c>
     </row>
     <row r="182" spans="1:12">
@@ -7505,28 +7499,28 @@
         <v>186</v>
       </c>
       <c r="C182" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D182" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E182" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F182" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="I182" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J182">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K182">
-        <v>128859.45</v>
+        <v>451021.21</v>
       </c>
       <c r="L182">
-        <v>257718.9</v>
+        <v>451021.21</v>
       </c>
     </row>
     <row r="183" spans="1:12">
@@ -7537,28 +7531,28 @@
         <v>187</v>
       </c>
       <c r="C183" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="D183" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E183" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="F183" t="s">
-        <v>241</v>
+        <v>474</v>
       </c>
       <c r="I183" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J183">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K183">
-        <v>451021.21</v>
+        <v>76547.52</v>
       </c>
       <c r="L183">
-        <v>451021.21</v>
+        <v>229642.56</v>
       </c>
     </row>
     <row r="184" spans="1:12">
@@ -7569,28 +7563,28 @@
         <v>188</v>
       </c>
       <c r="C184" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D184" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E184" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="F184" t="s">
-        <v>476</v>
+        <v>224</v>
       </c>
       <c r="I184" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J184">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K184">
-        <v>76547.52</v>
+        <v>116937.56</v>
       </c>
       <c r="L184">
-        <v>229642.56</v>
+        <v>116937.56</v>
       </c>
     </row>
     <row r="185" spans="1:12">
@@ -7601,92 +7595,92 @@
         <v>189</v>
       </c>
       <c r="C185" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D185" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E185" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F185" t="s">
-        <v>225</v>
+        <v>474</v>
       </c>
       <c r="I185" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J185">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K185">
-        <v>116937.56</v>
+        <v>98083.52</v>
       </c>
       <c r="L185">
-        <v>116937.56</v>
+        <v>686584.64</v>
       </c>
     </row>
     <row r="186" spans="1:12">
       <c r="A186" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B186" t="s">
         <v>190</v>
       </c>
       <c r="C186" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="D186" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E186" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="F186" t="s">
-        <v>476</v>
+        <v>246</v>
       </c>
       <c r="I186" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J186">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K186">
-        <v>98083.52</v>
+        <v>167744.87</v>
       </c>
       <c r="L186">
-        <v>686584.64</v>
+        <v>167744.87</v>
       </c>
     </row>
     <row r="187" spans="1:12">
       <c r="A187" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B187" t="s">
         <v>191</v>
       </c>
       <c r="C187" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="D187" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E187" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="F187" t="s">
-        <v>247</v>
+        <v>476</v>
       </c>
       <c r="I187" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J187">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K187">
-        <v>167744.87</v>
+        <v>23661.7</v>
       </c>
       <c r="L187">
-        <v>167744.87</v>
+        <v>141970.2</v>
       </c>
     </row>
     <row r="188" spans="1:12">
@@ -7697,28 +7691,28 @@
         <v>192</v>
       </c>
       <c r="C188" t="s">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="D188" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E188" t="s">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="F188" t="s">
-        <v>478</v>
+        <v>224</v>
       </c>
       <c r="I188" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J188">
         <v>6</v>
       </c>
       <c r="K188">
-        <v>23661.7</v>
+        <v>20116.83</v>
       </c>
       <c r="L188">
-        <v>141970.2</v>
+        <v>120700.98</v>
       </c>
     </row>
     <row r="189" spans="1:12">
@@ -7729,28 +7723,28 @@
         <v>193</v>
       </c>
       <c r="C189" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D189" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E189" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F189" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I189" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J189">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K189">
-        <v>20116.83</v>
+        <v>60010.35</v>
       </c>
       <c r="L189">
-        <v>120700.98</v>
+        <v>240041.4</v>
       </c>
     </row>
     <row r="190" spans="1:12">
@@ -7761,28 +7755,28 @@
         <v>194</v>
       </c>
       <c r="C190" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D190" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E190" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F190" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I190" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J190">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K190">
-        <v>60010.35</v>
+        <v>100496.28</v>
       </c>
       <c r="L190">
-        <v>240041.4</v>
+        <v>200992.56</v>
       </c>
     </row>
     <row r="191" spans="1:12">
@@ -7793,28 +7787,28 @@
         <v>195</v>
       </c>
       <c r="C191" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D191" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E191" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F191" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I191" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J191">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K191">
-        <v>100496.28</v>
+        <v>10684.18</v>
       </c>
       <c r="L191">
-        <v>200992.56</v>
+        <v>427367.2</v>
       </c>
     </row>
     <row r="192" spans="1:12">
@@ -7825,28 +7819,28 @@
         <v>196</v>
       </c>
       <c r="C192" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D192" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E192" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F192" t="s">
-        <v>232</v>
+        <v>474</v>
       </c>
       <c r="I192" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J192">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="K192">
-        <v>10684.18</v>
+        <v>128320.65</v>
       </c>
       <c r="L192">
-        <v>427367.2</v>
+        <v>128320.65</v>
       </c>
     </row>
     <row r="193" spans="1:12">
@@ -7857,28 +7851,28 @@
         <v>197</v>
       </c>
       <c r="C193" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D193" t="s">
-        <v>446</v>
+        <v>349</v>
       </c>
       <c r="E193" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F193" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I193" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J193">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K193">
-        <v>128320.65</v>
+        <v>156649.71</v>
       </c>
       <c r="L193">
-        <v>128320.65</v>
+        <v>939898.26</v>
       </c>
     </row>
     <row r="194" spans="1:12">
@@ -7889,28 +7883,28 @@
         <v>198</v>
       </c>
       <c r="C194" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D194" t="s">
-        <v>350</v>
+        <v>445</v>
       </c>
       <c r="E194" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F194" t="s">
-        <v>476</v>
+        <v>231</v>
       </c>
       <c r="I194" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J194">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K194">
-        <v>156649.71</v>
+        <v>92193.81</v>
       </c>
       <c r="L194">
-        <v>939898.26</v>
+        <v>184387.62</v>
       </c>
     </row>
     <row r="195" spans="1:12">
@@ -7921,220 +7915,220 @@
         <v>199</v>
       </c>
       <c r="C195" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D195" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E195" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="F195" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="I195" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J195">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K195">
-        <v>92193.81</v>
+        <v>99834.53</v>
       </c>
       <c r="L195">
-        <v>184387.62</v>
+        <v>1098179.83</v>
       </c>
     </row>
     <row r="196" spans="1:12">
       <c r="A196" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B196" t="s">
         <v>200</v>
       </c>
       <c r="C196" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="D196" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E196" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="F196" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="I196" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J196">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K196">
-        <v>99834.53</v>
+        <v>24129.88</v>
       </c>
       <c r="L196">
-        <v>1098179.83</v>
+        <v>144779.28</v>
       </c>
     </row>
     <row r="197" spans="1:12">
       <c r="A197" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B197" t="s">
         <v>201</v>
       </c>
       <c r="C197" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D197" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E197" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F197" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I197" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J197">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K197">
-        <v>24129.88</v>
+        <v>477767.5</v>
       </c>
       <c r="L197">
-        <v>144779.28</v>
+        <v>477767.5</v>
       </c>
     </row>
     <row r="198" spans="1:12">
       <c r="A198" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B198" t="s">
         <v>202</v>
       </c>
       <c r="C198" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="D198" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E198" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="F198" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="I198" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J198">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K198">
-        <v>477767.5</v>
+        <v>119118.65</v>
       </c>
       <c r="L198">
-        <v>477767.5</v>
+        <v>476474.6</v>
       </c>
     </row>
     <row r="199" spans="1:12">
       <c r="A199" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B199" t="s">
         <v>203</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="D199" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E199" t="s">
-        <v>264</v>
+        <v>224</v>
       </c>
       <c r="F199" t="s">
-        <v>264</v>
+        <v>224</v>
       </c>
       <c r="I199" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J199">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K199">
-        <v>119118.65</v>
+        <v>12254.05</v>
       </c>
       <c r="L199">
-        <v>476474.6</v>
+        <v>134794.55</v>
       </c>
     </row>
     <row r="200" spans="1:12">
       <c r="A200" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B200" t="s">
         <v>204</v>
       </c>
       <c r="C200" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D200" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E200" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F200" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="I200" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J200">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="K200">
-        <v>12254.05</v>
+        <v>2043.59</v>
       </c>
       <c r="L200">
-        <v>134794.55</v>
+        <v>198228.23</v>
       </c>
     </row>
     <row r="201" spans="1:12">
       <c r="A201" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B201" t="s">
         <v>205</v>
       </c>
       <c r="C201" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D201" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E201" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F201" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I201" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J201">
-        <v>97</v>
+        <v>2</v>
       </c>
       <c r="K201">
-        <v>2043.59</v>
+        <v>57019.29</v>
       </c>
       <c r="L201">
-        <v>198228.23</v>
+        <v>114038.58</v>
       </c>
     </row>
     <row r="202" spans="1:12">
@@ -8145,28 +8139,28 @@
         <v>206</v>
       </c>
       <c r="C202" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D202" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E202" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="F202" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="I202" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J202">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K202">
-        <v>57019.29</v>
+        <v>54790.74</v>
       </c>
       <c r="L202">
-        <v>114038.58</v>
+        <v>219162.96</v>
       </c>
     </row>
     <row r="203" spans="1:12">
@@ -8177,60 +8171,60 @@
         <v>207</v>
       </c>
       <c r="C203" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D203" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E203" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F203" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I203" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J203">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K203">
-        <v>54790.74</v>
+        <v>276872.24</v>
       </c>
       <c r="L203">
-        <v>219162.96</v>
+        <v>276872.24</v>
       </c>
     </row>
     <row r="204" spans="1:12">
       <c r="A204" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B204" t="s">
         <v>208</v>
       </c>
       <c r="C204" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D204" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E204" t="s">
-        <v>232</v>
+        <v>472</v>
       </c>
       <c r="F204" t="s">
-        <v>232</v>
+        <v>472</v>
       </c>
       <c r="I204" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J204">
         <v>1</v>
       </c>
       <c r="K204">
-        <v>276872.24</v>
+        <v>228580.22</v>
       </c>
       <c r="L204">
-        <v>276872.24</v>
+        <v>228580.22</v>
       </c>
     </row>
     <row r="205" spans="1:12">
@@ -8241,156 +8235,156 @@
         <v>209</v>
       </c>
       <c r="C205" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D205" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E205" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F205" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I205" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J205">
         <v>1</v>
       </c>
       <c r="K205">
-        <v>228580.22</v>
+        <v>588448.45</v>
       </c>
       <c r="L205">
-        <v>228580.22</v>
+        <v>588448.45</v>
       </c>
     </row>
     <row r="206" spans="1:12">
       <c r="A206" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B206" t="s">
         <v>210</v>
       </c>
       <c r="C206" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D206" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E206" t="s">
-        <v>473</v>
+        <v>224</v>
       </c>
       <c r="F206" t="s">
-        <v>473</v>
+        <v>224</v>
       </c>
       <c r="I206" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J206">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K206">
-        <v>588448.45</v>
+        <v>171904.24</v>
       </c>
       <c r="L206">
-        <v>588448.45</v>
+        <v>343808.48</v>
       </c>
     </row>
     <row r="207" spans="1:12">
       <c r="A207" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B207" t="s">
         <v>211</v>
       </c>
       <c r="C207" t="s">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="D207" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E207" t="s">
-        <v>225</v>
+        <v>263</v>
       </c>
       <c r="F207" t="s">
-        <v>225</v>
+        <v>263</v>
       </c>
       <c r="I207" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J207">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K207">
-        <v>171904.24</v>
+        <v>52120.37</v>
       </c>
       <c r="L207">
-        <v>343808.48</v>
+        <v>52120.37</v>
       </c>
     </row>
     <row r="208" spans="1:12">
       <c r="A208" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B208" t="s">
         <v>212</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="D208" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E208" t="s">
-        <v>264</v>
+        <v>224</v>
       </c>
       <c r="F208" t="s">
-        <v>264</v>
+        <v>224</v>
       </c>
       <c r="I208" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J208">
         <v>1</v>
       </c>
       <c r="K208">
-        <v>52120.37</v>
+        <v>907492.78</v>
       </c>
       <c r="L208">
-        <v>52120.37</v>
+        <v>907492.78</v>
       </c>
     </row>
     <row r="209" spans="1:12">
       <c r="A209" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B209" t="s">
         <v>213</v>
       </c>
       <c r="C209" t="s">
-        <v>225</v>
+        <v>260</v>
       </c>
       <c r="D209" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E209" t="s">
-        <v>225</v>
+        <v>472</v>
       </c>
       <c r="F209" t="s">
-        <v>225</v>
+        <v>472</v>
       </c>
       <c r="I209" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J209">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K209">
-        <v>907492.78</v>
+        <v>118001.73</v>
       </c>
       <c r="L209">
-        <v>907492.78</v>
+        <v>236003.46</v>
       </c>
     </row>
     <row r="210" spans="1:12">
@@ -8401,60 +8395,60 @@
         <v>214</v>
       </c>
       <c r="C210" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D210" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E210" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F210" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I210" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J210">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K210">
-        <v>118001.73</v>
+        <v>56470.99</v>
       </c>
       <c r="L210">
-        <v>236003.46</v>
+        <v>56470.99</v>
       </c>
     </row>
     <row r="211" spans="1:12">
       <c r="A211" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B211" t="s">
         <v>215</v>
       </c>
       <c r="C211" t="s">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="D211" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E211" t="s">
-        <v>473</v>
+        <v>231</v>
       </c>
       <c r="F211" t="s">
-        <v>473</v>
+        <v>231</v>
       </c>
       <c r="I211" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J211">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K211">
-        <v>56470.99</v>
+        <v>20316.27</v>
       </c>
       <c r="L211">
-        <v>56470.99</v>
+        <v>121897.62</v>
       </c>
     </row>
     <row r="212" spans="1:12">
@@ -8465,28 +8459,28 @@
         <v>216</v>
       </c>
       <c r="C212" t="s">
-        <v>232</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E212" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="F212" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="I212" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J212">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K212">
-        <v>20316.27</v>
+        <v>64719.29</v>
       </c>
       <c r="L212">
-        <v>121897.62</v>
+        <v>64719.29</v>
       </c>
     </row>
     <row r="213" spans="1:12">
@@ -8497,28 +8491,28 @@
         <v>217</v>
       </c>
       <c r="C213" t="s">
-        <v>262</v>
+        <v>224</v>
       </c>
       <c r="D213" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E213" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F213" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I213" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J213">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K213">
-        <v>64719.29</v>
+        <v>15431.69</v>
       </c>
       <c r="L213">
-        <v>64719.29</v>
+        <v>77158.45</v>
       </c>
     </row>
     <row r="214" spans="1:12">
@@ -8529,28 +8523,28 @@
         <v>218</v>
       </c>
       <c r="C214" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D214" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E214" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F214" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I214" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J214">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="K214">
-        <v>15431.69</v>
+        <v>2999.26</v>
       </c>
       <c r="L214">
-        <v>77158.45</v>
+        <v>68982.98</v>
       </c>
     </row>
     <row r="215" spans="1:12">
@@ -8561,60 +8555,60 @@
         <v>219</v>
       </c>
       <c r="C215" t="s">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="D215" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E215" t="s">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="F215" t="s">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="I215" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J215">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="K215">
-        <v>2999.26</v>
+        <v>40143.73</v>
       </c>
       <c r="L215">
-        <v>68982.98</v>
+        <v>160574.92</v>
       </c>
     </row>
     <row r="216" spans="1:12">
       <c r="A216" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B216" t="s">
         <v>220</v>
       </c>
       <c r="C216" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E216" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="F216" t="s">
-        <v>263</v>
+        <v>475</v>
       </c>
       <c r="I216" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J216">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K216">
-        <v>40143.73</v>
+        <v>259475.34</v>
       </c>
       <c r="L216">
-        <v>160574.92</v>
+        <v>259475.34</v>
       </c>
     </row>
     <row r="217" spans="1:12">
@@ -8625,28 +8619,28 @@
         <v>221</v>
       </c>
       <c r="C217" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D217" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E217" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F217" t="s">
-        <v>477</v>
+        <v>263</v>
       </c>
       <c r="I217" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J217">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K217">
-        <v>259475.34</v>
+        <v>112000</v>
       </c>
       <c r="L217">
-        <v>259475.34</v>
+        <v>224000</v>
       </c>
     </row>
     <row r="218" spans="1:12">
@@ -8660,7 +8654,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E218" t="s">
         <v>264</v>
@@ -8669,47 +8663,15 @@
         <v>264</v>
       </c>
       <c r="I218" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J218">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K218">
-        <v>112000</v>
+        <v>128205</v>
       </c>
       <c r="L218">
-        <v>224000</v>
-      </c>
-    </row>
-    <row r="219" spans="1:12">
-      <c r="A219" t="s">
-        <v>13</v>
-      </c>
-      <c r="B219" t="s">
-        <v>223</v>
-      </c>
-      <c r="C219" t="s">
-        <v>265</v>
-      </c>
-      <c r="D219" t="s">
-        <v>471</v>
-      </c>
-      <c r="E219" t="s">
-        <v>265</v>
-      </c>
-      <c r="F219" t="s">
-        <v>265</v>
-      </c>
-      <c r="I219" t="s">
-        <v>479</v>
-      </c>
-      <c r="J219">
-        <v>6</v>
-      </c>
-      <c r="K219">
-        <v>128205</v>
-      </c>
-      <c r="L219">
         <v>769230</v>
       </c>
     </row>

--- a/VALORIZADO FALTANTES.xlsx
+++ b/VALORIZADO FALTANTES.xlsx
@@ -295,7 +295,7 @@
     <t>68012/4089544CLE</t>
   </si>
   <si>
-    <t>690437C95/436005PAI</t>
+    <t>690437/436005 PAI</t>
   </si>
   <si>
     <t>87-5966KQC/3685966</t>
@@ -571,10 +571,10 @@
     <t>BRA11205X2728</t>
   </si>
   <si>
-    <t>C21900/3948095/226-4566 MAH</t>
-  </si>
-  <si>
-    <t>EK35181/3804276CLE</t>
+    <t>3948095/C21900 MAH</t>
+  </si>
+  <si>
+    <t>3804276/EK35181 CLE</t>
   </si>
   <si>
     <t>HM813843/10 MER/802613</t>
@@ -1465,13 +1465,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 30/11/2025 08:47:22</t>
+    <t>Período: 31/12/2025 08:45:38</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 26/11/2025 08:48:22</t>
+    <t>Fecha y hora de generación: 04/12/2025 08:46:40</t>
   </si>
 </sst>
 </file>

--- a/VALORIZADO FALTANTES.xlsx
+++ b/VALORIZADO FALTANTES.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1483" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="490">
   <si>
     <t>Categoría</t>
   </si>
@@ -175,6 +175,9 @@
     <t>17-16413/6430774</t>
   </si>
   <si>
+    <t>1821915/460046PAI</t>
+  </si>
+  <si>
     <t>1824647C1</t>
   </si>
   <si>
@@ -331,6 +334,9 @@
     <t>A6918</t>
   </si>
   <si>
+    <t>B0210756-0,75MAH/4893693</t>
+  </si>
+  <si>
     <t>B13299A6787</t>
   </si>
   <si>
@@ -928,6 +934,9 @@
     <t>CORBATIN FREIGHTLINER COLUMBIA</t>
   </si>
   <si>
+    <t>VOLANTE MOTOR ELECTRO DT466/530</t>
+  </si>
+  <si>
     <t>GUIA VALVULA ADMI Y ESCAPE DT466 MY  ELE</t>
   </si>
   <si>
@@ -1081,6 +1090,9 @@
     <t>VALVULA DOBLE BOTON GRIS 18 CAMBIOS</t>
   </si>
   <si>
+    <t>CASQ BIEL 0,75 P30 FRACTUR 4BT JGO8UND</t>
+  </si>
+  <si>
     <t>PORTA LEVA 7600 TRASERA VOLQUETA</t>
   </si>
   <si>
@@ -1465,13 +1477,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/12/2025 08:45:38</t>
+    <t>Período: 31/01/2026 07:42:42</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 04/12/2025 08:46:40</t>
+    <t>Fecha y hora de generación: 08/01/2026 07:43:14</t>
   </si>
 </sst>
 </file>
@@ -1885,28 +1897,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L218"/>
+  <dimension ref="A1:L220"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1922,7 +1934,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1938,12 +1950,12 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="I7" s="5" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -1995,19 +2007,19 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I10" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J10">
         <v>3</v>
@@ -2027,19 +2039,19 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D11" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I11" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -2059,19 +2071,19 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D12" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I12" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -2091,19 +2103,19 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E13" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="F13" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="I13" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -2123,19 +2135,19 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E14" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F14" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I14" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -2155,19 +2167,19 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D15" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E15" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F15" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I15" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -2187,19 +2199,19 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D16" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E16" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F16" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I16" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J16">
         <v>2</v>
@@ -2219,19 +2231,19 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D17" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E17" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F17" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I17" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2251,19 +2263,19 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D18" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E18" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F18" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I18" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2283,19 +2295,19 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D19" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E19" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F19" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I19" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -2315,19 +2327,19 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D20" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E20" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F20" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I20" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2347,19 +2359,19 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D21" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E21" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F21" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I21" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2379,19 +2391,19 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D22" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E22" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F22" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I22" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J22">
         <v>3</v>
@@ -2411,19 +2423,19 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D23" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E23" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F23" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I23" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J23">
         <v>2</v>
@@ -2443,19 +2455,19 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D24" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E24" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F24" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I24" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -2475,19 +2487,19 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D25" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E25" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F25" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I25" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J25">
         <v>2</v>
@@ -2507,19 +2519,19 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D26" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E26" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F26" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I26" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -2539,19 +2551,19 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D27" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E27" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F27" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I27" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J27">
         <v>3</v>
@@ -2571,19 +2583,19 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D28" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E28" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F28" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I28" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2603,19 +2615,19 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D29" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E29" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F29" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I29" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2635,19 +2647,19 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D30" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E30" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F30" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I30" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J30">
         <v>2</v>
@@ -2667,19 +2679,19 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D31" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E31" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F31" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I31" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J31">
         <v>2</v>
@@ -2699,19 +2711,19 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D32" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E32" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="F32" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I32" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J32">
         <v>12</v>
@@ -2731,19 +2743,19 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D33" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E33" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="F33" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I33" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J33">
         <v>6</v>
@@ -2763,19 +2775,19 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D34" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E34" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="F34" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I34" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J34">
         <v>6</v>
@@ -2795,19 +2807,19 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D35" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F35" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I35" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2827,19 +2839,19 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D36" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E36" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F36" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I36" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2859,19 +2871,19 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D37" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E37" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F37" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I37" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J37">
         <v>3</v>
@@ -2891,19 +2903,19 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D38" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E38" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F38" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="I38" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J38">
         <v>123</v>
@@ -2923,19 +2935,19 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D39" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E39" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F39" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I39" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J39">
         <v>4</v>
@@ -2955,19 +2967,19 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D40" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E40" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F40" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I40" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -2987,19 +2999,19 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D41" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E41" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F41" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I41" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -3019,19 +3031,19 @@
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D42" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E42" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="F42" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I42" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J42">
         <v>12</v>
@@ -3051,19 +3063,19 @@
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D43" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E43" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F43" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I43" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -3083,19 +3095,19 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D44" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E44" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="F44" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="I44" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J44">
         <v>2</v>
@@ -3115,19 +3127,19 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D45" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E45" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="F45" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="I45" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J45">
         <v>12</v>
@@ -3147,19 +3159,19 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D46" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E46" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F46" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I46" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -3179,19 +3191,19 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D47" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E47" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F47" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I47" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J47">
         <v>2</v>
@@ -3211,19 +3223,19 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D48" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E48" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F48" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I48" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J48">
         <v>4</v>
@@ -3243,28 +3255,28 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D49" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E49" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F49" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="I49" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J49">
         <v>1</v>
       </c>
       <c r="K49">
-        <v>57029.66</v>
+        <v>781011.86</v>
       </c>
       <c r="L49">
-        <v>57029.66</v>
+        <v>781011.86</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -3275,28 +3287,28 @@
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D50" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E50" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F50" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I50" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K50">
-        <v>124113.03</v>
+        <v>57029.66</v>
       </c>
       <c r="L50">
-        <v>620565.15</v>
+        <v>57029.66</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -3307,92 +3319,92 @@
         <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D51" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E51" t="s">
-        <v>470</v>
+        <v>237</v>
       </c>
       <c r="F51" t="s">
-        <v>470</v>
+        <v>237</v>
       </c>
       <c r="I51" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K51">
-        <v>143954.72</v>
+        <v>124113.03</v>
       </c>
       <c r="L51">
-        <v>143954.72</v>
+        <v>620565.15</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
         <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D52" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E52" t="s">
-        <v>239</v>
+        <v>474</v>
       </c>
       <c r="F52" t="s">
-        <v>239</v>
+        <v>474</v>
       </c>
       <c r="I52" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K52">
-        <v>374186</v>
+        <v>143954.72</v>
       </c>
       <c r="L52">
-        <v>1122558</v>
+        <v>143954.72</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B53" t="s">
         <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D53" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E53" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F53" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I53" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K53">
-        <v>451755.47</v>
+        <v>374186</v>
       </c>
       <c r="L53">
-        <v>903510.9399999999</v>
+        <v>1122558</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -3403,28 +3415,28 @@
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="D54" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E54" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="F54" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="I54" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K54">
-        <v>297477.98</v>
+        <v>451755.47</v>
       </c>
       <c r="L54">
-        <v>297477.98</v>
+        <v>903510.9399999999</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3435,28 +3447,28 @@
         <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="D55" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E55" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="F55" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="I55" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K55">
-        <v>116675.06</v>
+        <v>297477.98</v>
       </c>
       <c r="L55">
-        <v>350025.18</v>
+        <v>297477.98</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -3467,28 +3479,28 @@
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="D56" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E56" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="F56" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="I56" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K56">
-        <v>241521.59</v>
+        <v>116675.06</v>
       </c>
       <c r="L56">
-        <v>241521.59</v>
+        <v>350025.18</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -3499,28 +3511,28 @@
         <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D57" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E57" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F57" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I57" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K57">
-        <v>123123.72</v>
+        <v>241521.59</v>
       </c>
       <c r="L57">
-        <v>246247.44</v>
+        <v>241521.59</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3531,28 +3543,28 @@
         <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D58" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E58" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F58" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I58" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J58">
         <v>2</v>
       </c>
       <c r="K58">
-        <v>277740.62</v>
+        <v>123123.72</v>
       </c>
       <c r="L58">
-        <v>555481.24</v>
+        <v>246247.44</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3563,28 +3575,28 @@
         <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D59" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E59" t="s">
-        <v>471</v>
+        <v>226</v>
       </c>
       <c r="F59" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I59" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J59">
-        <v>206</v>
+        <v>2</v>
       </c>
       <c r="K59">
-        <v>10428.31</v>
+        <v>277740.62</v>
       </c>
       <c r="L59">
-        <v>2148231.86</v>
+        <v>555481.24</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3595,92 +3607,92 @@
         <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D60" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E60" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="F60" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I60" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J60">
-        <v>46</v>
+        <v>206</v>
       </c>
       <c r="K60">
-        <v>5719.65</v>
+        <v>10428.31</v>
       </c>
       <c r="L60">
-        <v>263103.9</v>
+        <v>2148231.86</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
         <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D61" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E61" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="F61" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I61" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J61">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="K61">
-        <v>12871.55</v>
+        <v>5719.65</v>
       </c>
       <c r="L61">
-        <v>77229.3</v>
+        <v>263103.9</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B62" t="s">
         <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="D62" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E62" t="s">
-        <v>244</v>
+        <v>475</v>
       </c>
       <c r="F62" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="I62" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J62">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="K62">
-        <v>11227.66</v>
+        <v>12871.55</v>
       </c>
       <c r="L62">
-        <v>718570.24</v>
+        <v>77229.3</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3691,92 +3703,92 @@
         <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D63" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E63" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F63" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I63" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J63">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="K63">
-        <v>74410.03</v>
+        <v>11227.66</v>
       </c>
       <c r="L63">
-        <v>223230.09</v>
+        <v>718570.24</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B64" t="s">
         <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="D64" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E64" t="s">
-        <v>472</v>
+        <v>246</v>
       </c>
       <c r="F64" t="s">
-        <v>472</v>
+        <v>242</v>
       </c>
       <c r="I64" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K64">
-        <v>52014.93</v>
+        <v>74410.03</v>
       </c>
       <c r="L64">
-        <v>104029.86</v>
+        <v>223230.09</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B65" t="s">
         <v>69</v>
       </c>
       <c r="C65" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D65" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E65" t="s">
-        <v>237</v>
+        <v>476</v>
       </c>
       <c r="F65" t="s">
-        <v>237</v>
+        <v>476</v>
       </c>
       <c r="I65" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J65">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K65">
-        <v>94380.39999999999</v>
+        <v>52014.93</v>
       </c>
       <c r="L65">
-        <v>1887608</v>
+        <v>104029.86</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3787,28 +3799,28 @@
         <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D66" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E66" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F66" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I66" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J66">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K66">
-        <v>1157466.59</v>
+        <v>94380.39999999999</v>
       </c>
       <c r="L66">
-        <v>5787332.95</v>
+        <v>1887608</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3819,28 +3831,28 @@
         <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D67" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E67" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F67" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I67" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J67">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K67">
-        <v>553925.89</v>
+        <v>1157466.59</v>
       </c>
       <c r="L67">
-        <v>553925.89</v>
+        <v>5787332.95</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3851,28 +3863,28 @@
         <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="D68" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E68" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="F68" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="I68" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J68">
         <v>1</v>
       </c>
       <c r="K68">
-        <v>456192.75</v>
+        <v>553925.89</v>
       </c>
       <c r="L68">
-        <v>456192.75</v>
+        <v>553925.89</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3883,92 +3895,92 @@
         <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D69" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E69" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F69" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I69" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J69">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K69">
-        <v>459216.59</v>
+        <v>456192.75</v>
       </c>
       <c r="L69">
-        <v>2296082.95</v>
+        <v>456192.75</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B70" t="s">
         <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="D70" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E70" t="s">
-        <v>473</v>
+        <v>233</v>
       </c>
       <c r="F70" t="s">
-        <v>473</v>
+        <v>233</v>
       </c>
       <c r="I70" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J70">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K70">
-        <v>107611.43</v>
+        <v>459216.59</v>
       </c>
       <c r="L70">
-        <v>215222.86</v>
+        <v>2296082.95</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B71" t="s">
         <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="D71" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E71" t="s">
-        <v>235</v>
+        <v>477</v>
       </c>
       <c r="F71" t="s">
-        <v>235</v>
+        <v>477</v>
       </c>
       <c r="I71" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K71">
-        <v>162784.49</v>
+        <v>107611.43</v>
       </c>
       <c r="L71">
-        <v>651137.96</v>
+        <v>215222.86</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3979,28 +3991,28 @@
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D72" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E72" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F72" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="I72" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K72">
-        <v>64596.41</v>
+        <v>162784.49</v>
       </c>
       <c r="L72">
-        <v>193789.23</v>
+        <v>651137.96</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -4011,28 +4023,28 @@
         <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="D73" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E73" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="F73" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="I73" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K73">
-        <v>520965.57</v>
+        <v>64596.41</v>
       </c>
       <c r="L73">
-        <v>2083862.28</v>
+        <v>193789.23</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -4043,28 +4055,28 @@
         <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D74" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E74" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F74" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="I74" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J74">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K74">
-        <v>234957.18</v>
+        <v>520965.57</v>
       </c>
       <c r="L74">
-        <v>234957.18</v>
+        <v>2083862.28</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -4075,60 +4087,60 @@
         <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D75" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E75" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F75" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I75" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J75">
         <v>1</v>
       </c>
       <c r="K75">
-        <v>561136.28</v>
+        <v>234957.18</v>
       </c>
       <c r="L75">
-        <v>561136.28</v>
+        <v>234957.18</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D76" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E76" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F76" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I76" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J76">
         <v>1</v>
       </c>
       <c r="K76">
-        <v>548933.98</v>
+        <v>561136.28</v>
       </c>
       <c r="L76">
-        <v>548933.98</v>
+        <v>561136.28</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -4139,28 +4151,28 @@
         <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D77" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E77" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F77" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I77" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K77">
-        <v>348438.94</v>
+        <v>548933.98</v>
       </c>
       <c r="L77">
-        <v>696877.88</v>
+        <v>548933.98</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -4171,28 +4183,28 @@
         <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D78" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E78" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F78" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I78" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K78">
-        <v>176616.64</v>
+        <v>348438.94</v>
       </c>
       <c r="L78">
-        <v>176616.64</v>
+        <v>696877.88</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -4203,60 +4215,60 @@
         <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D79" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E79" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F79" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I79" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K79">
-        <v>54474.6</v>
+        <v>176616.64</v>
       </c>
       <c r="L79">
-        <v>163423.8</v>
+        <v>176616.64</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B80" t="s">
         <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D80" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E80" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F80" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I80" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K80">
-        <v>289538.6</v>
+        <v>54474.6</v>
       </c>
       <c r="L80">
-        <v>289538.6</v>
+        <v>163423.8</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -4267,28 +4279,28 @@
         <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="D81" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E81" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F81" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="I81" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K81">
-        <v>60191.18</v>
+        <v>289538.6</v>
       </c>
       <c r="L81">
-        <v>120382.36</v>
+        <v>289538.6</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -4299,28 +4311,28 @@
         <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D82" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E82" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="F82" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="I82" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J82">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K82">
-        <v>106058.91</v>
+        <v>60191.18</v>
       </c>
       <c r="L82">
-        <v>530294.55</v>
+        <v>120382.36</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -4331,92 +4343,92 @@
         <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D83" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E83" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F83" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I83" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J83">
         <v>5</v>
       </c>
       <c r="K83">
-        <v>24077.89</v>
+        <v>106058.91</v>
       </c>
       <c r="L83">
-        <v>120389.45</v>
+        <v>530294.55</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B84" t="s">
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D84" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E84" t="s">
-        <v>472</v>
+        <v>238</v>
       </c>
       <c r="F84" t="s">
-        <v>472</v>
+        <v>238</v>
       </c>
       <c r="I84" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J84">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="K84">
-        <v>13504.82</v>
+        <v>24077.89</v>
       </c>
       <c r="L84">
-        <v>283601.22</v>
+        <v>120389.45</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B85" t="s">
         <v>89</v>
       </c>
       <c r="C85" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D85" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E85" t="s">
-        <v>242</v>
+        <v>476</v>
       </c>
       <c r="F85" t="s">
-        <v>242</v>
+        <v>476</v>
       </c>
       <c r="I85" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J85">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K85">
-        <v>244653.18</v>
+        <v>13504.82</v>
       </c>
       <c r="L85">
-        <v>244653.18</v>
+        <v>283601.22</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4427,60 +4439,60 @@
         <v>90</v>
       </c>
       <c r="C86" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D86" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E86" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F86" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I86" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J86">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K86">
-        <v>116579.52</v>
+        <v>244653.18</v>
       </c>
       <c r="L86">
-        <v>466318.08</v>
+        <v>244653.18</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
         <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D87" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E87" t="s">
-        <v>473</v>
+        <v>248</v>
       </c>
       <c r="F87" t="s">
-        <v>473</v>
+        <v>248</v>
       </c>
       <c r="I87" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J87">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K87">
-        <v>132950.29</v>
+        <v>116579.52</v>
       </c>
       <c r="L87">
-        <v>265900.58</v>
+        <v>466318.08</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4491,124 +4503,124 @@
         <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D88" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E88" t="s">
-        <v>244</v>
+        <v>477</v>
       </c>
       <c r="F88" t="s">
-        <v>240</v>
+        <v>477</v>
       </c>
       <c r="I88" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J88">
         <v>2</v>
       </c>
       <c r="K88">
-        <v>130565.76</v>
+        <v>132950.29</v>
       </c>
       <c r="L88">
-        <v>261131.52</v>
+        <v>265900.58</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B89" t="s">
         <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="D89" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E89" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="F89" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="I89" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J89">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K89">
-        <v>32532.84</v>
+        <v>130565.76</v>
       </c>
       <c r="L89">
-        <v>325328.4</v>
+        <v>261131.52</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B90" t="s">
         <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D90" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E90" t="s">
-        <v>471</v>
+        <v>238</v>
       </c>
       <c r="F90" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="I90" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J90">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K90">
-        <v>36184.1</v>
+        <v>32532.84</v>
       </c>
       <c r="L90">
-        <v>289472.8</v>
+        <v>325328.4</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B91" t="s">
         <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="D91" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E91" t="s">
-        <v>247</v>
+        <v>475</v>
       </c>
       <c r="F91" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="I91" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J91">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K91">
-        <v>202984.86</v>
+        <v>36184.1</v>
       </c>
       <c r="L91">
-        <v>202984.86</v>
+        <v>289472.8</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4619,60 +4631,60 @@
         <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D92" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E92" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F92" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I92" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K92">
-        <v>98967.53</v>
+        <v>202984.86</v>
       </c>
       <c r="L92">
-        <v>197935.06</v>
+        <v>202984.86</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B93" t="s">
         <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D93" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E93" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F93" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I93" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J93">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K93">
-        <v>140000</v>
+        <v>98967.53</v>
       </c>
       <c r="L93">
-        <v>560000</v>
+        <v>197935.06</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4683,28 +4695,28 @@
         <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D94" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E94" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F94" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I94" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J94">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K94">
-        <v>60000</v>
+        <v>140000</v>
       </c>
       <c r="L94">
-        <v>480000</v>
+        <v>560000</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4715,60 +4727,60 @@
         <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="D95" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E95" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="F95" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="I95" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J95">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K95">
-        <v>183395.81</v>
+        <v>60000</v>
       </c>
       <c r="L95">
-        <v>366791.62</v>
+        <v>480000</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B96" t="s">
         <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="D96" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E96" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="F96" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="I96" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K96">
-        <v>561283.11</v>
+        <v>183395.81</v>
       </c>
       <c r="L96">
-        <v>561283.11</v>
+        <v>366791.62</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4779,28 +4791,28 @@
         <v>101</v>
       </c>
       <c r="C97" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D97" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E97" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I97" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K97">
-        <v>400703.47</v>
+        <v>561283.11</v>
       </c>
       <c r="L97">
-        <v>801406.9399999999</v>
+        <v>561283.11</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4811,28 +4823,28 @@
         <v>102</v>
       </c>
       <c r="C98" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D98" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E98" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F98" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I98" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J98">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="K98">
-        <v>62347.32</v>
+        <v>400703.47</v>
       </c>
       <c r="L98">
-        <v>1309293.72</v>
+        <v>801406.9399999999</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4843,28 +4855,28 @@
         <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D99" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E99" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F99" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="I99" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J99">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K99">
-        <v>339984.3</v>
+        <v>62347.32</v>
       </c>
       <c r="L99">
-        <v>339984.3</v>
+        <v>1309293.72</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -4875,92 +4887,92 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D100" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E100" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F100" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I100" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J100">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K100">
-        <v>212047.99</v>
+        <v>339984.3</v>
       </c>
       <c r="L100">
-        <v>636143.97</v>
+        <v>339984.3</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B101" t="s">
         <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D101" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E101" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F101" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I101" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J101">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K101">
-        <v>116716.34</v>
+        <v>212047.99</v>
       </c>
       <c r="L101">
-        <v>116716.34</v>
+        <v>636143.97</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B102" t="s">
         <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D102" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E102" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F102" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I102" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K102">
-        <v>147576.31</v>
+        <v>79854.5</v>
       </c>
       <c r="L102">
-        <v>147576.31</v>
+        <v>159709</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -4971,92 +4983,92 @@
         <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D103" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E103" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="F103" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="I103" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K103">
-        <v>25956.31</v>
+        <v>116716.34</v>
       </c>
       <c r="L103">
-        <v>51912.62</v>
+        <v>116716.34</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B104" t="s">
         <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="D104" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E104" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="F104" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="I104" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K104">
-        <v>207223.89</v>
+        <v>147576.31</v>
       </c>
       <c r="L104">
-        <v>414447.78</v>
+        <v>147576.31</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B105" t="s">
         <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D105" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E105" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="F105" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="I105" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J105">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K105">
-        <v>52993.42</v>
+        <v>25956.31</v>
       </c>
       <c r="L105">
-        <v>688914.46</v>
+        <v>51912.62</v>
       </c>
     </row>
     <row r="106" spans="1:12">
@@ -5067,124 +5079,124 @@
         <v>110</v>
       </c>
       <c r="C106" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="D106" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E106" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="F106" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="I106" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K106">
-        <v>365807.37</v>
+        <v>207223.89</v>
       </c>
       <c r="L106">
-        <v>1097422.11</v>
+        <v>414447.78</v>
       </c>
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B107" t="s">
         <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="D107" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E107" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="F107" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="I107" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J107">
-        <v>276</v>
+        <v>13</v>
       </c>
       <c r="K107">
-        <v>910.4400000000001</v>
+        <v>52993.42</v>
       </c>
       <c r="L107">
-        <v>251281.44</v>
+        <v>688914.46</v>
       </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B108" t="s">
         <v>112</v>
       </c>
       <c r="C108" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="D108" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E108" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="F108" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="I108" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K108">
-        <v>61252.9</v>
+        <v>365807.37</v>
       </c>
       <c r="L108">
-        <v>61252.9</v>
+        <v>1097422.11</v>
       </c>
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B109" t="s">
         <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D109" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E109" t="s">
-        <v>471</v>
+        <v>252</v>
       </c>
       <c r="F109" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I109" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J109">
-        <v>144</v>
+        <v>276</v>
       </c>
       <c r="K109">
-        <v>12408.84</v>
+        <v>910.4400000000001</v>
       </c>
       <c r="L109">
-        <v>1786872.96</v>
+        <v>251281.44</v>
       </c>
     </row>
     <row r="110" spans="1:12">
@@ -5195,28 +5207,28 @@
         <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D110" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E110" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="F110" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="I110" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J110">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K110">
-        <v>82259.44</v>
+        <v>61252.9</v>
       </c>
       <c r="L110">
-        <v>822594.4</v>
+        <v>61252.9</v>
       </c>
     </row>
     <row r="111" spans="1:12">
@@ -5227,28 +5239,28 @@
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="D111" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E111" t="s">
-        <v>224</v>
+        <v>475</v>
       </c>
       <c r="F111" t="s">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="I111" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J111">
-        <v>5</v>
+        <v>144</v>
       </c>
       <c r="K111">
-        <v>43930.6</v>
+        <v>12408.84</v>
       </c>
       <c r="L111">
-        <v>219653</v>
+        <v>1786872.96</v>
       </c>
     </row>
     <row r="112" spans="1:12">
@@ -5259,28 +5271,28 @@
         <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="D112" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E112" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="F112" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="I112" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J112">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K112">
-        <v>78505.56</v>
+        <v>82259.44</v>
       </c>
       <c r="L112">
-        <v>78505.56</v>
+        <v>822594.4</v>
       </c>
     </row>
     <row r="113" spans="1:12">
@@ -5291,156 +5303,156 @@
         <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D113" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E113" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F113" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I113" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J113">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K113">
-        <v>253717.21</v>
+        <v>43930.6</v>
       </c>
       <c r="L113">
-        <v>507434.42</v>
+        <v>219653</v>
       </c>
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B114" t="s">
         <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="D114" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E114" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="F114" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="I114" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J114">
         <v>1</v>
       </c>
       <c r="K114">
-        <v>462132.13</v>
+        <v>78505.56</v>
       </c>
       <c r="L114">
-        <v>462132.13</v>
+        <v>78505.56</v>
       </c>
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B115" t="s">
         <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="D115" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E115" t="s">
-        <v>263</v>
+        <v>226</v>
       </c>
       <c r="F115" t="s">
-        <v>263</v>
+        <v>226</v>
       </c>
       <c r="I115" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K115">
-        <v>294400</v>
+        <v>253717.21</v>
       </c>
       <c r="L115">
-        <v>294400</v>
+        <v>507434.42</v>
       </c>
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B116" t="s">
         <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="D116" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E116" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="F116" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="I116" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K116">
-        <v>308720.23</v>
+        <v>462132.13</v>
       </c>
       <c r="L116">
-        <v>617440.46</v>
+        <v>462132.13</v>
       </c>
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B117" t="s">
         <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D117" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E117" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="F117" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="I117" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J117">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K117">
-        <v>130424.26</v>
+        <v>294400</v>
       </c>
       <c r="L117">
-        <v>521697.04</v>
+        <v>294400</v>
       </c>
     </row>
     <row r="118" spans="1:12">
@@ -5451,28 +5463,28 @@
         <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D118" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E118" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F118" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I118" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K118">
-        <v>142359.27</v>
+        <v>308720.23</v>
       </c>
       <c r="L118">
-        <v>142359.27</v>
+        <v>617440.46</v>
       </c>
     </row>
     <row r="119" spans="1:12">
@@ -5483,60 +5495,60 @@
         <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="D119" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E119" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="F119" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="I119" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J119">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K119">
-        <v>153331.85</v>
+        <v>130424.26</v>
       </c>
       <c r="L119">
-        <v>459995.55</v>
+        <v>521697.04</v>
       </c>
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B120" t="s">
         <v>124</v>
       </c>
       <c r="C120" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D120" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E120" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F120" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I120" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J120">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K120">
-        <v>151827.5</v>
+        <v>142359.27</v>
       </c>
       <c r="L120">
-        <v>759137.5</v>
+        <v>142359.27</v>
       </c>
     </row>
     <row r="121" spans="1:12">
@@ -5547,60 +5559,60 @@
         <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D121" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E121" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F121" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I121" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J121">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K121">
-        <v>126875.69</v>
+        <v>153331.85</v>
       </c>
       <c r="L121">
-        <v>126875.69</v>
+        <v>459995.55</v>
       </c>
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B122" t="s">
         <v>126</v>
       </c>
       <c r="C122" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D122" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E122" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F122" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I122" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J122">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K122">
-        <v>418397.52</v>
+        <v>151827.5</v>
       </c>
       <c r="L122">
-        <v>418397.52</v>
+        <v>759137.5</v>
       </c>
     </row>
     <row r="123" spans="1:12">
@@ -5611,28 +5623,28 @@
         <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="D123" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E123" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="F123" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="I123" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J123">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K123">
-        <v>60881.05</v>
+        <v>126875.69</v>
       </c>
       <c r="L123">
-        <v>730572.6</v>
+        <v>126875.69</v>
       </c>
     </row>
     <row r="124" spans="1:12">
@@ -5643,28 +5655,28 @@
         <v>128</v>
       </c>
       <c r="C124" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="D124" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E124" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="F124" t="s">
-        <v>474</v>
+        <v>238</v>
       </c>
       <c r="I124" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J124">
         <v>1</v>
       </c>
       <c r="K124">
-        <v>53403.02</v>
+        <v>418397.52</v>
       </c>
       <c r="L124">
-        <v>53403.02</v>
+        <v>418397.52</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -5675,28 +5687,28 @@
         <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D125" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E125" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F125" t="s">
-        <v>474</v>
+        <v>233</v>
       </c>
       <c r="I125" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J125">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K125">
-        <v>80962.22</v>
+        <v>60881.05</v>
       </c>
       <c r="L125">
-        <v>404811.1</v>
+        <v>730572.6</v>
       </c>
     </row>
     <row r="126" spans="1:12">
@@ -5707,28 +5719,28 @@
         <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D126" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E126" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F126" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="I126" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J126">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K126">
-        <v>30016.79</v>
+        <v>53403.02</v>
       </c>
       <c r="L126">
-        <v>90050.37</v>
+        <v>53403.02</v>
       </c>
     </row>
     <row r="127" spans="1:12">
@@ -5739,28 +5751,28 @@
         <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D127" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E127" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F127" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="I127" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J127">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K127">
-        <v>55960.12</v>
+        <v>80962.22</v>
       </c>
       <c r="L127">
-        <v>111920.24</v>
+        <v>404811.1</v>
       </c>
     </row>
     <row r="128" spans="1:12">
@@ -5771,28 +5783,28 @@
         <v>132</v>
       </c>
       <c r="C128" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D128" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E128" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F128" t="s">
-        <v>231</v>
+        <v>478</v>
       </c>
       <c r="I128" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J128">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K128">
-        <v>57770.2</v>
+        <v>30016.79</v>
       </c>
       <c r="L128">
-        <v>57770.2</v>
+        <v>90050.37</v>
       </c>
     </row>
     <row r="129" spans="1:12">
@@ -5803,92 +5815,92 @@
         <v>133</v>
       </c>
       <c r="C129" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D129" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E129" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F129" t="s">
-        <v>231</v>
+        <v>478</v>
       </c>
       <c r="I129" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J129">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K129">
-        <v>122224.03</v>
+        <v>55960.12</v>
       </c>
       <c r="L129">
-        <v>488896.12</v>
+        <v>111920.24</v>
       </c>
     </row>
     <row r="130" spans="1:12">
       <c r="A130" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B130" t="s">
         <v>134</v>
       </c>
       <c r="C130" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D130" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E130" t="s">
-        <v>472</v>
+        <v>233</v>
       </c>
       <c r="F130" t="s">
-        <v>472</v>
+        <v>233</v>
       </c>
       <c r="I130" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K130">
-        <v>345599.99</v>
+        <v>57770.2</v>
       </c>
       <c r="L130">
-        <v>691199.98</v>
+        <v>57770.2</v>
       </c>
     </row>
     <row r="131" spans="1:12">
       <c r="A131" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B131" t="s">
         <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D131" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E131" t="s">
-        <v>472</v>
+        <v>233</v>
       </c>
       <c r="F131" t="s">
-        <v>472</v>
+        <v>233</v>
       </c>
       <c r="I131" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J131">
         <v>4</v>
       </c>
       <c r="K131">
-        <v>406977.4</v>
+        <v>122224.03</v>
       </c>
       <c r="L131">
-        <v>1627909.6</v>
+        <v>488896.12</v>
       </c>
     </row>
     <row r="132" spans="1:12">
@@ -5899,92 +5911,92 @@
         <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D132" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E132" t="s">
-        <v>224</v>
+        <v>476</v>
       </c>
       <c r="F132" t="s">
-        <v>224</v>
+        <v>476</v>
       </c>
       <c r="I132" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K132">
-        <v>108921.66</v>
+        <v>345599.99</v>
       </c>
       <c r="L132">
-        <v>108921.66</v>
+        <v>691199.98</v>
       </c>
     </row>
     <row r="133" spans="1:12">
       <c r="A133" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B133" t="s">
         <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="D133" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E133" t="s">
-        <v>253</v>
+        <v>476</v>
       </c>
       <c r="F133" t="s">
-        <v>253</v>
+        <v>476</v>
       </c>
       <c r="I133" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J133">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K133">
-        <v>155407.11</v>
+        <v>406977.4</v>
       </c>
       <c r="L133">
-        <v>155407.11</v>
+        <v>1627909.6</v>
       </c>
     </row>
     <row r="134" spans="1:12">
       <c r="A134" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B134" t="s">
         <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="D134" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E134" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="F134" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="I134" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K134">
-        <v>302306.98</v>
+        <v>108921.66</v>
       </c>
       <c r="L134">
-        <v>604613.96</v>
+        <v>108921.66</v>
       </c>
     </row>
     <row r="135" spans="1:12">
@@ -5995,28 +6007,28 @@
         <v>139</v>
       </c>
       <c r="C135" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D135" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E135" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F135" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I135" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J135">
         <v>1</v>
       </c>
       <c r="K135">
-        <v>462946.56</v>
+        <v>155407.11</v>
       </c>
       <c r="L135">
-        <v>462946.56</v>
+        <v>155407.11</v>
       </c>
     </row>
     <row r="136" spans="1:12">
@@ -6027,28 +6039,28 @@
         <v>140</v>
       </c>
       <c r="C136" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D136" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E136" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F136" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I136" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K136">
-        <v>622170.75</v>
+        <v>302306.98</v>
       </c>
       <c r="L136">
-        <v>622170.75</v>
+        <v>604613.96</v>
       </c>
     </row>
     <row r="137" spans="1:12">
@@ -6059,28 +6071,28 @@
         <v>141</v>
       </c>
       <c r="C137" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="D137" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E137" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="F137" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="I137" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J137">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K137">
-        <v>7246.46</v>
+        <v>462946.56</v>
       </c>
       <c r="L137">
-        <v>65218.14</v>
+        <v>462946.56</v>
       </c>
     </row>
     <row r="138" spans="1:12">
@@ -6091,60 +6103,60 @@
         <v>142</v>
       </c>
       <c r="C138" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="D138" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E138" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="F138" t="s">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="I138" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J138">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K138">
-        <v>9200.629999999999</v>
+        <v>622170.75</v>
       </c>
       <c r="L138">
-        <v>202413.86</v>
+        <v>622170.75</v>
       </c>
     </row>
     <row r="139" spans="1:12">
       <c r="A139" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B139" t="s">
         <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D139" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E139" t="s">
-        <v>472</v>
+        <v>226</v>
       </c>
       <c r="F139" t="s">
-        <v>472</v>
+        <v>226</v>
       </c>
       <c r="I139" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J139">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K139">
-        <v>13906.96</v>
+        <v>7246.46</v>
       </c>
       <c r="L139">
-        <v>83441.75999999999</v>
+        <v>65218.14</v>
       </c>
     </row>
     <row r="140" spans="1:12">
@@ -6155,60 +6167,60 @@
         <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>255</v>
+        <v>226</v>
       </c>
       <c r="D140" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E140" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F140" t="s">
-        <v>255</v>
+        <v>226</v>
       </c>
       <c r="I140" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J140">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K140">
-        <v>67728.10000000001</v>
+        <v>9200.629999999999</v>
       </c>
       <c r="L140">
-        <v>677281</v>
+        <v>202413.86</v>
       </c>
     </row>
     <row r="141" spans="1:12">
       <c r="A141" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B141" t="s">
         <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D141" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E141" t="s">
-        <v>224</v>
+        <v>476</v>
       </c>
       <c r="F141" t="s">
-        <v>224</v>
+        <v>476</v>
       </c>
       <c r="I141" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J141">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K141">
-        <v>541166.88</v>
+        <v>13906.96</v>
       </c>
       <c r="L141">
-        <v>2164667.52</v>
+        <v>83441.75999999999</v>
       </c>
     </row>
     <row r="142" spans="1:12">
@@ -6219,60 +6231,60 @@
         <v>146</v>
       </c>
       <c r="C142" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="D142" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E142" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F142" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="I142" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J142">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K142">
-        <v>31630.01</v>
+        <v>67728.10000000001</v>
       </c>
       <c r="L142">
-        <v>63260.02</v>
+        <v>677281</v>
       </c>
     </row>
     <row r="143" spans="1:12">
       <c r="A143" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B143" t="s">
         <v>147</v>
       </c>
       <c r="C143" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="D143" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E143" t="s">
-        <v>263</v>
+        <v>226</v>
       </c>
       <c r="F143" t="s">
-        <v>263</v>
+        <v>226</v>
       </c>
       <c r="I143" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J143">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K143">
-        <v>107104.68</v>
+        <v>541166.88</v>
       </c>
       <c r="L143">
-        <v>214209.36</v>
+        <v>2164667.52</v>
       </c>
     </row>
     <row r="144" spans="1:12">
@@ -6283,92 +6295,92 @@
         <v>148</v>
       </c>
       <c r="C144" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D144" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E144" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F144" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="I144" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K144">
-        <v>221067.08</v>
+        <v>31630.01</v>
       </c>
       <c r="L144">
-        <v>221067.08</v>
+        <v>63260.02</v>
       </c>
     </row>
     <row r="145" spans="1:12">
       <c r="A145" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B145" t="s">
         <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>224</v>
+        <v>258</v>
       </c>
       <c r="D145" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E145" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="F145" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="I145" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K145">
-        <v>204405.71</v>
+        <v>107104.68</v>
       </c>
       <c r="L145">
-        <v>204405.71</v>
+        <v>214209.36</v>
       </c>
     </row>
     <row r="146" spans="1:12">
       <c r="A146" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B146" t="s">
         <v>150</v>
       </c>
       <c r="C146" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D146" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E146" t="s">
-        <v>472</v>
+        <v>226</v>
       </c>
       <c r="F146" t="s">
-        <v>472</v>
+        <v>226</v>
       </c>
       <c r="I146" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J146">
         <v>1</v>
       </c>
       <c r="K146">
-        <v>151612.17</v>
+        <v>221067.08</v>
       </c>
       <c r="L146">
-        <v>151612.17</v>
+        <v>221067.08</v>
       </c>
     </row>
     <row r="147" spans="1:12">
@@ -6379,60 +6391,60 @@
         <v>151</v>
       </c>
       <c r="C147" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D147" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E147" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F147" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I147" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J147">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K147">
-        <v>152565.53</v>
+        <v>204405.71</v>
       </c>
       <c r="L147">
-        <v>762827.65</v>
+        <v>204405.71</v>
       </c>
     </row>
     <row r="148" spans="1:12">
       <c r="A148" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B148" t="s">
         <v>152</v>
       </c>
       <c r="C148" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D148" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E148" t="s">
-        <v>224</v>
+        <v>476</v>
       </c>
       <c r="F148" t="s">
-        <v>224</v>
+        <v>476</v>
       </c>
       <c r="I148" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J148">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K148">
-        <v>648344.71</v>
+        <v>151612.17</v>
       </c>
       <c r="L148">
-        <v>1945034.13</v>
+        <v>151612.17</v>
       </c>
     </row>
     <row r="149" spans="1:12">
@@ -6443,28 +6455,28 @@
         <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D149" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E149" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F149" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I149" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J149">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K149">
-        <v>61274.69</v>
+        <v>152565.53</v>
       </c>
       <c r="L149">
-        <v>245098.76</v>
+        <v>762827.65</v>
       </c>
     </row>
     <row r="150" spans="1:12">
@@ -6475,60 +6487,60 @@
         <v>154</v>
       </c>
       <c r="C150" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="D150" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E150" t="s">
-        <v>470</v>
+        <v>226</v>
       </c>
       <c r="F150" t="s">
-        <v>470</v>
+        <v>226</v>
       </c>
       <c r="I150" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J150">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K150">
-        <v>134461.16</v>
+        <v>648344.71</v>
       </c>
       <c r="L150">
-        <v>134461.16</v>
+        <v>1945034.13</v>
       </c>
     </row>
     <row r="151" spans="1:12">
       <c r="A151" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B151" t="s">
         <v>155</v>
       </c>
       <c r="C151" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D151" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E151" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F151" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I151" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J151">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K151">
-        <v>150000</v>
+        <v>61274.69</v>
       </c>
       <c r="L151">
-        <v>150000</v>
+        <v>245098.76</v>
       </c>
     </row>
     <row r="152" spans="1:12">
@@ -6539,60 +6551,60 @@
         <v>156</v>
       </c>
       <c r="C152" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="D152" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E152" t="s">
-        <v>224</v>
+        <v>474</v>
       </c>
       <c r="F152" t="s">
-        <v>224</v>
+        <v>474</v>
       </c>
       <c r="I152" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J152">
         <v>1</v>
       </c>
       <c r="K152">
-        <v>437278.29</v>
+        <v>134461.16</v>
       </c>
       <c r="L152">
-        <v>437278.29</v>
+        <v>134461.16</v>
       </c>
     </row>
     <row r="153" spans="1:12">
       <c r="A153" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B153" t="s">
         <v>157</v>
       </c>
       <c r="C153" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D153" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E153" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F153" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="I153" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J153">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K153">
-        <v>68988.75999999999</v>
+        <v>150000</v>
       </c>
       <c r="L153">
-        <v>689887.6</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="154" spans="1:12">
@@ -6603,188 +6615,188 @@
         <v>158</v>
       </c>
       <c r="C154" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D154" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E154" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F154" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I154" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J154">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K154">
-        <v>321061.61</v>
+        <v>437278.29</v>
       </c>
       <c r="L154">
-        <v>642123.22</v>
+        <v>437278.29</v>
       </c>
     </row>
     <row r="155" spans="1:12">
       <c r="A155" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B155" t="s">
         <v>159</v>
       </c>
       <c r="C155" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D155" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E155" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F155" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I155" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J155">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K155">
-        <v>86292.41</v>
+        <v>68988.75999999999</v>
       </c>
       <c r="L155">
-        <v>86292.41</v>
+        <v>689887.6</v>
       </c>
     </row>
     <row r="156" spans="1:12">
       <c r="A156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B156" t="s">
         <v>160</v>
       </c>
       <c r="C156" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D156" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E156" t="s">
-        <v>472</v>
+        <v>226</v>
       </c>
       <c r="F156" t="s">
-        <v>472</v>
+        <v>226</v>
       </c>
       <c r="I156" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J156">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K156">
-        <v>275914.15</v>
+        <v>321061.61</v>
       </c>
       <c r="L156">
-        <v>827742.45</v>
+        <v>642123.22</v>
       </c>
     </row>
     <row r="157" spans="1:12">
       <c r="A157" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B157" t="s">
         <v>161</v>
       </c>
       <c r="C157" t="s">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="D157" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E157" t="s">
-        <v>473</v>
+        <v>233</v>
       </c>
       <c r="F157" t="s">
-        <v>473</v>
+        <v>233</v>
       </c>
       <c r="I157" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J157">
         <v>1</v>
       </c>
       <c r="K157">
-        <v>145438.64</v>
+        <v>86292.41</v>
       </c>
       <c r="L157">
-        <v>145438.64</v>
+        <v>86292.41</v>
       </c>
     </row>
     <row r="158" spans="1:12">
       <c r="A158" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B158" t="s">
         <v>162</v>
       </c>
       <c r="C158" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D158" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E158" t="s">
-        <v>231</v>
+        <v>476</v>
       </c>
       <c r="F158" t="s">
-        <v>231</v>
+        <v>476</v>
       </c>
       <c r="I158" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J158">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K158">
-        <v>124259.74</v>
+        <v>275914.15</v>
       </c>
       <c r="L158">
-        <v>1988155.84</v>
+        <v>827742.45</v>
       </c>
     </row>
     <row r="159" spans="1:12">
       <c r="A159" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B159" t="s">
         <v>163</v>
       </c>
       <c r="C159" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E159" t="s">
-        <v>244</v>
+        <v>477</v>
       </c>
       <c r="F159" t="s">
-        <v>244</v>
+        <v>477</v>
       </c>
       <c r="I159" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J159">
         <v>1</v>
       </c>
       <c r="K159">
-        <v>127385.01</v>
+        <v>145438.64</v>
       </c>
       <c r="L159">
-        <v>127385.01</v>
+        <v>145438.64</v>
       </c>
     </row>
     <row r="160" spans="1:12">
@@ -6795,28 +6807,28 @@
         <v>164</v>
       </c>
       <c r="C160" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D160" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E160" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F160" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="I160" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J160">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K160">
-        <v>409485.91</v>
+        <v>124259.74</v>
       </c>
       <c r="L160">
-        <v>818971.8199999999</v>
+        <v>1988155.84</v>
       </c>
     </row>
     <row r="161" spans="1:12">
@@ -6827,28 +6839,28 @@
         <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="D161" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E161" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="F161" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="I161" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J161">
         <v>1</v>
       </c>
       <c r="K161">
-        <v>411573.74</v>
+        <v>127385.01</v>
       </c>
       <c r="L161">
-        <v>411573.74</v>
+        <v>127385.01</v>
       </c>
     </row>
     <row r="162" spans="1:12">
@@ -6859,60 +6871,60 @@
         <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="D162" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E162" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="F162" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="I162" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J162">
         <v>2</v>
       </c>
       <c r="K162">
-        <v>177929.28</v>
+        <v>409485.91</v>
       </c>
       <c r="L162">
-        <v>355858.56</v>
+        <v>818971.8199999999</v>
       </c>
     </row>
     <row r="163" spans="1:12">
       <c r="A163" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B163" t="s">
         <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="D163" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E163" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F163" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="I163" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J163">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K163">
-        <v>386975.07</v>
+        <v>411573.74</v>
       </c>
       <c r="L163">
-        <v>773950.14</v>
+        <v>411573.74</v>
       </c>
     </row>
     <row r="164" spans="1:12">
@@ -6923,28 +6935,28 @@
         <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="D164" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E164" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="F164" t="s">
-        <v>474</v>
+        <v>238</v>
       </c>
       <c r="I164" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J164">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K164">
-        <v>66983.8</v>
+        <v>177929.28</v>
       </c>
       <c r="L164">
-        <v>267935.2</v>
+        <v>355858.56</v>
       </c>
     </row>
     <row r="165" spans="1:12">
@@ -6955,284 +6967,284 @@
         <v>169</v>
       </c>
       <c r="C165" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="D165" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E165" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="F165" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="I165" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J165">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K165">
-        <v>159709.51</v>
+        <v>386975.07</v>
       </c>
       <c r="L165">
-        <v>159709.51</v>
+        <v>773950.14</v>
       </c>
     </row>
     <row r="166" spans="1:12">
       <c r="A166" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B166" t="s">
         <v>170</v>
       </c>
       <c r="C166" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D166" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E166" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F166" t="s">
-        <v>224</v>
+        <v>478</v>
       </c>
       <c r="I166" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J166">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="K166">
-        <v>2473.41</v>
+        <v>66983.8</v>
       </c>
       <c r="L166">
-        <v>93989.58</v>
+        <v>267935.2</v>
       </c>
     </row>
     <row r="167" spans="1:12">
       <c r="A167" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B167" t="s">
         <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="D167" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E167" t="s">
-        <v>472</v>
+        <v>256</v>
       </c>
       <c r="F167" t="s">
-        <v>472</v>
+        <v>256</v>
       </c>
       <c r="I167" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J167">
         <v>1</v>
       </c>
       <c r="K167">
-        <v>636180.6800000001</v>
+        <v>159709.51</v>
       </c>
       <c r="L167">
-        <v>636180.6800000001</v>
+        <v>159709.51</v>
       </c>
     </row>
     <row r="168" spans="1:12">
       <c r="A168" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B168" t="s">
         <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D168" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E168" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F168" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I168" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J168">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="K168">
-        <v>27987.95</v>
+        <v>2473.41</v>
       </c>
       <c r="L168">
-        <v>83963.85000000001</v>
+        <v>93989.58</v>
       </c>
     </row>
     <row r="169" spans="1:12">
       <c r="A169" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B169" t="s">
         <v>173</v>
       </c>
       <c r="C169" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="D169" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E169" t="s">
-        <v>259</v>
+        <v>476</v>
       </c>
       <c r="F169" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I169" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J169">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K169">
-        <v>274730.29</v>
+        <v>636180.6800000001</v>
       </c>
       <c r="L169">
-        <v>2747302.9</v>
+        <v>636180.6800000001</v>
       </c>
     </row>
     <row r="170" spans="1:12">
       <c r="A170" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B170" t="s">
         <v>174</v>
       </c>
       <c r="C170" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D170" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E170" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F170" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I170" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J170">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K170">
-        <v>5073.44</v>
+        <v>27987.95</v>
       </c>
       <c r="L170">
-        <v>50734.4</v>
+        <v>83963.85000000001</v>
       </c>
     </row>
     <row r="171" spans="1:12">
       <c r="A171" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B171" t="s">
         <v>175</v>
       </c>
       <c r="C171" t="s">
-        <v>229</v>
+        <v>260</v>
       </c>
       <c r="D171" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E171" t="s">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="F171" t="s">
-        <v>229</v>
+        <v>479</v>
       </c>
       <c r="I171" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J171">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K171">
-        <v>271098.72</v>
+        <v>274730.29</v>
       </c>
       <c r="L171">
-        <v>1626592.32</v>
+        <v>2747302.9</v>
       </c>
     </row>
     <row r="172" spans="1:12">
       <c r="A172" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B172" t="s">
         <v>176</v>
       </c>
       <c r="C172" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D172" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E172" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F172" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I172" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J172">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K172">
-        <v>21390.12</v>
+        <v>5073.44</v>
       </c>
       <c r="L172">
-        <v>171120.96</v>
+        <v>50734.4</v>
       </c>
     </row>
     <row r="173" spans="1:12">
       <c r="A173" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B173" t="s">
         <v>177</v>
       </c>
       <c r="C173" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="D173" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E173" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="F173" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="I173" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J173">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K173">
-        <v>325882.63</v>
+        <v>271098.72</v>
       </c>
       <c r="L173">
-        <v>325882.63</v>
+        <v>1626592.32</v>
       </c>
     </row>
     <row r="174" spans="1:12">
@@ -7243,28 +7255,28 @@
         <v>178</v>
       </c>
       <c r="C174" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D174" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E174" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F174" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="I174" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J174">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K174">
-        <v>66789.11</v>
+        <v>21390.12</v>
       </c>
       <c r="L174">
-        <v>133578.22</v>
+        <v>171120.96</v>
       </c>
     </row>
     <row r="175" spans="1:12">
@@ -7275,28 +7287,28 @@
         <v>179</v>
       </c>
       <c r="C175" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="D175" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E175" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F175" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="I175" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J175">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K175">
-        <v>78468.91</v>
+        <v>325882.63</v>
       </c>
       <c r="L175">
-        <v>235406.73</v>
+        <v>325882.63</v>
       </c>
     </row>
     <row r="176" spans="1:12">
@@ -7307,28 +7319,28 @@
         <v>180</v>
       </c>
       <c r="C176" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D176" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E176" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F176" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I176" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J176">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K176">
-        <v>263646.09</v>
+        <v>66789.11</v>
       </c>
       <c r="L176">
-        <v>790938.27</v>
+        <v>133578.22</v>
       </c>
     </row>
     <row r="177" spans="1:12">
@@ -7339,28 +7351,28 @@
         <v>181</v>
       </c>
       <c r="C177" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D177" t="s">
-        <v>333</v>
+        <v>432</v>
       </c>
       <c r="E177" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F177" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="I177" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J177">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K177">
-        <v>271387.84</v>
+        <v>78468.91</v>
       </c>
       <c r="L177">
-        <v>542775.6800000001</v>
+        <v>235406.73</v>
       </c>
     </row>
     <row r="178" spans="1:12">
@@ -7371,60 +7383,60 @@
         <v>182</v>
       </c>
       <c r="C178" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D178" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E178" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F178" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I178" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J178">
         <v>3</v>
       </c>
       <c r="K178">
-        <v>73037.78999999999</v>
+        <v>263646.09</v>
       </c>
       <c r="L178">
-        <v>219113.37</v>
+        <v>790938.27</v>
       </c>
     </row>
     <row r="179" spans="1:12">
       <c r="A179" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B179" t="s">
         <v>183</v>
       </c>
       <c r="C179" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D179" t="s">
-        <v>431</v>
+        <v>336</v>
       </c>
       <c r="E179" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F179" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I179" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J179">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K179">
-        <v>7049.74</v>
+        <v>271387.84</v>
       </c>
       <c r="L179">
-        <v>98696.36</v>
+        <v>542775.6800000001</v>
       </c>
     </row>
     <row r="180" spans="1:12">
@@ -7435,60 +7447,60 @@
         <v>184</v>
       </c>
       <c r="C180" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D180" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E180" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F180" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I180" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J180">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K180">
-        <v>73190.35000000001</v>
+        <v>73037.78999999999</v>
       </c>
       <c r="L180">
-        <v>805093.85</v>
+        <v>219113.37</v>
       </c>
     </row>
     <row r="181" spans="1:12">
       <c r="A181" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B181" t="s">
         <v>185</v>
       </c>
       <c r="C181" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="D181" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E181" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="F181" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="I181" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J181">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K181">
-        <v>128859.45</v>
+        <v>7049.74</v>
       </c>
       <c r="L181">
-        <v>257718.9</v>
+        <v>98696.36</v>
       </c>
     </row>
     <row r="182" spans="1:12">
@@ -7499,28 +7511,28 @@
         <v>186</v>
       </c>
       <c r="C182" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D182" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E182" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="F182" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="I182" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J182">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K182">
-        <v>451021.21</v>
+        <v>73190.35000000001</v>
       </c>
       <c r="L182">
-        <v>451021.21</v>
+        <v>805093.85</v>
       </c>
     </row>
     <row r="183" spans="1:12">
@@ -7531,28 +7543,28 @@
         <v>187</v>
       </c>
       <c r="C183" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="D183" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E183" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="F183" t="s">
-        <v>474</v>
+        <v>246</v>
       </c>
       <c r="I183" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J183">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K183">
-        <v>76547.52</v>
+        <v>128859.45</v>
       </c>
       <c r="L183">
-        <v>229642.56</v>
+        <v>257718.9</v>
       </c>
     </row>
     <row r="184" spans="1:12">
@@ -7563,28 +7575,28 @@
         <v>188</v>
       </c>
       <c r="C184" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="D184" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E184" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="F184" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="I184" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J184">
         <v>1</v>
       </c>
       <c r="K184">
-        <v>116937.56</v>
+        <v>451021.21</v>
       </c>
       <c r="L184">
-        <v>116937.56</v>
+        <v>451021.21</v>
       </c>
     </row>
     <row r="185" spans="1:12">
@@ -7595,60 +7607,60 @@
         <v>189</v>
       </c>
       <c r="C185" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D185" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E185" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F185" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="I185" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J185">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K185">
-        <v>98083.52</v>
+        <v>76547.52</v>
       </c>
       <c r="L185">
-        <v>686584.64</v>
+        <v>229642.56</v>
       </c>
     </row>
     <row r="186" spans="1:12">
       <c r="A186" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B186" t="s">
         <v>190</v>
       </c>
       <c r="C186" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="D186" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E186" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="F186" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="I186" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J186">
         <v>1</v>
       </c>
       <c r="K186">
-        <v>167744.87</v>
+        <v>116937.56</v>
       </c>
       <c r="L186">
-        <v>167744.87</v>
+        <v>116937.56</v>
       </c>
     </row>
     <row r="187" spans="1:12">
@@ -7659,60 +7671,60 @@
         <v>191</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="D187" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E187" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="F187" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="I187" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J187">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K187">
-        <v>23661.7</v>
+        <v>98083.52</v>
       </c>
       <c r="L187">
-        <v>141970.2</v>
+        <v>686584.64</v>
       </c>
     </row>
     <row r="188" spans="1:12">
       <c r="A188" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B188" t="s">
         <v>192</v>
       </c>
       <c r="C188" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="D188" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E188" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="F188" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="I188" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J188">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K188">
-        <v>20116.83</v>
+        <v>167744.87</v>
       </c>
       <c r="L188">
-        <v>120700.98</v>
+        <v>167744.87</v>
       </c>
     </row>
     <row r="189" spans="1:12">
@@ -7723,28 +7735,28 @@
         <v>193</v>
       </c>
       <c r="C189" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E189" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="F189" t="s">
-        <v>231</v>
+        <v>480</v>
       </c>
       <c r="I189" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J189">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K189">
-        <v>60010.35</v>
+        <v>23661.7</v>
       </c>
       <c r="L189">
-        <v>240041.4</v>
+        <v>141970.2</v>
       </c>
     </row>
     <row r="190" spans="1:12">
@@ -7755,28 +7767,28 @@
         <v>194</v>
       </c>
       <c r="C190" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D190" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E190" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F190" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I190" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J190">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K190">
-        <v>100496.28</v>
+        <v>20116.83</v>
       </c>
       <c r="L190">
-        <v>200992.56</v>
+        <v>120700.98</v>
       </c>
     </row>
     <row r="191" spans="1:12">
@@ -7787,28 +7799,28 @@
         <v>195</v>
       </c>
       <c r="C191" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D191" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E191" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F191" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I191" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J191">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="K191">
-        <v>10684.18</v>
+        <v>60010.35</v>
       </c>
       <c r="L191">
-        <v>427367.2</v>
+        <v>240041.4</v>
       </c>
     </row>
     <row r="192" spans="1:12">
@@ -7819,28 +7831,28 @@
         <v>196</v>
       </c>
       <c r="C192" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D192" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E192" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F192" t="s">
-        <v>474</v>
+        <v>233</v>
       </c>
       <c r="I192" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J192">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K192">
-        <v>128320.65</v>
+        <v>100496.28</v>
       </c>
       <c r="L192">
-        <v>128320.65</v>
+        <v>200992.56</v>
       </c>
     </row>
     <row r="193" spans="1:12">
@@ -7851,28 +7863,28 @@
         <v>197</v>
       </c>
       <c r="C193" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D193" t="s">
-        <v>349</v>
+        <v>447</v>
       </c>
       <c r="E193" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F193" t="s">
-        <v>474</v>
+        <v>233</v>
       </c>
       <c r="I193" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J193">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="K193">
-        <v>156649.71</v>
+        <v>10684.18</v>
       </c>
       <c r="L193">
-        <v>939898.26</v>
+        <v>427367.2</v>
       </c>
     </row>
     <row r="194" spans="1:12">
@@ -7883,28 +7895,28 @@
         <v>198</v>
       </c>
       <c r="C194" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D194" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E194" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F194" t="s">
-        <v>231</v>
+        <v>478</v>
       </c>
       <c r="I194" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J194">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K194">
-        <v>92193.81</v>
+        <v>128320.65</v>
       </c>
       <c r="L194">
-        <v>184387.62</v>
+        <v>128320.65</v>
       </c>
     </row>
     <row r="195" spans="1:12">
@@ -7915,60 +7927,60 @@
         <v>199</v>
       </c>
       <c r="C195" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D195" t="s">
-        <v>446</v>
+        <v>352</v>
       </c>
       <c r="E195" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F195" t="s">
-        <v>224</v>
+        <v>478</v>
       </c>
       <c r="I195" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J195">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K195">
-        <v>99834.53</v>
+        <v>156649.71</v>
       </c>
       <c r="L195">
-        <v>1098179.83</v>
+        <v>939898.26</v>
       </c>
     </row>
     <row r="196" spans="1:12">
       <c r="A196" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B196" t="s">
         <v>200</v>
       </c>
       <c r="C196" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D196" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E196" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F196" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I196" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J196">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K196">
-        <v>24129.88</v>
+        <v>92193.81</v>
       </c>
       <c r="L196">
-        <v>144779.28</v>
+        <v>184387.62</v>
       </c>
     </row>
     <row r="197" spans="1:12">
@@ -7979,28 +7991,28 @@
         <v>201</v>
       </c>
       <c r="C197" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D197" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E197" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F197" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I197" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J197">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K197">
-        <v>477767.5</v>
+        <v>99834.53</v>
       </c>
       <c r="L197">
-        <v>477767.5</v>
+        <v>1098179.83</v>
       </c>
     </row>
     <row r="198" spans="1:12">
@@ -8011,28 +8023,28 @@
         <v>202</v>
       </c>
       <c r="C198" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="D198" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E198" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="F198" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="I198" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J198">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K198">
-        <v>119118.65</v>
+        <v>24129.88</v>
       </c>
       <c r="L198">
-        <v>476474.6</v>
+        <v>144779.28</v>
       </c>
     </row>
     <row r="199" spans="1:12">
@@ -8043,28 +8055,28 @@
         <v>203</v>
       </c>
       <c r="C199" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D199" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E199" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F199" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="I199" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J199">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K199">
-        <v>12254.05</v>
+        <v>477767.5</v>
       </c>
       <c r="L199">
-        <v>134794.55</v>
+        <v>477767.5</v>
       </c>
     </row>
     <row r="200" spans="1:12">
@@ -8075,28 +8087,28 @@
         <v>204</v>
       </c>
       <c r="C200" t="s">
-        <v>229</v>
+        <v>260</v>
       </c>
       <c r="D200" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E200" t="s">
-        <v>229</v>
+        <v>265</v>
       </c>
       <c r="F200" t="s">
-        <v>229</v>
+        <v>265</v>
       </c>
       <c r="I200" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J200">
-        <v>97</v>
+        <v>4</v>
       </c>
       <c r="K200">
-        <v>2043.59</v>
+        <v>119118.65</v>
       </c>
       <c r="L200">
-        <v>198228.23</v>
+        <v>476474.6</v>
       </c>
     </row>
     <row r="201" spans="1:12">
@@ -8107,60 +8119,60 @@
         <v>205</v>
       </c>
       <c r="C201" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D201" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E201" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F201" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I201" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J201">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K201">
-        <v>57019.29</v>
+        <v>12254.05</v>
       </c>
       <c r="L201">
-        <v>114038.58</v>
+        <v>134794.55</v>
       </c>
     </row>
     <row r="202" spans="1:12">
       <c r="A202" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B202" t="s">
         <v>206</v>
       </c>
       <c r="C202" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="D202" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E202" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="F202" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="I202" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J202">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="K202">
-        <v>54790.74</v>
+        <v>2043.59</v>
       </c>
       <c r="L202">
-        <v>219162.96</v>
+        <v>198228.23</v>
       </c>
     </row>
     <row r="203" spans="1:12">
@@ -8171,124 +8183,124 @@
         <v>207</v>
       </c>
       <c r="C203" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D203" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E203" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F203" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I203" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J203">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K203">
-        <v>276872.24</v>
+        <v>57019.29</v>
       </c>
       <c r="L203">
-        <v>276872.24</v>
+        <v>114038.58</v>
       </c>
     </row>
     <row r="204" spans="1:12">
       <c r="A204" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B204" t="s">
         <v>208</v>
       </c>
       <c r="C204" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D204" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E204" t="s">
-        <v>472</v>
+        <v>226</v>
       </c>
       <c r="F204" t="s">
-        <v>472</v>
+        <v>226</v>
       </c>
       <c r="I204" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J204">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K204">
-        <v>228580.22</v>
+        <v>54790.74</v>
       </c>
       <c r="L204">
-        <v>228580.22</v>
+        <v>219162.96</v>
       </c>
     </row>
     <row r="205" spans="1:12">
       <c r="A205" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B205" t="s">
         <v>209</v>
       </c>
       <c r="C205" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D205" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E205" t="s">
-        <v>472</v>
+        <v>233</v>
       </c>
       <c r="F205" t="s">
-        <v>472</v>
+        <v>233</v>
       </c>
       <c r="I205" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J205">
         <v>1</v>
       </c>
       <c r="K205">
-        <v>588448.45</v>
+        <v>276872.24</v>
       </c>
       <c r="L205">
-        <v>588448.45</v>
+        <v>276872.24</v>
       </c>
     </row>
     <row r="206" spans="1:12">
       <c r="A206" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B206" t="s">
         <v>210</v>
       </c>
       <c r="C206" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D206" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E206" t="s">
-        <v>224</v>
+        <v>476</v>
       </c>
       <c r="F206" t="s">
-        <v>224</v>
+        <v>476</v>
       </c>
       <c r="I206" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J206">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K206">
-        <v>171904.24</v>
+        <v>228580.22</v>
       </c>
       <c r="L206">
-        <v>343808.48</v>
+        <v>228580.22</v>
       </c>
     </row>
     <row r="207" spans="1:12">
@@ -8299,28 +8311,28 @@
         <v>211</v>
       </c>
       <c r="C207" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="D207" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E207" t="s">
-        <v>263</v>
+        <v>476</v>
       </c>
       <c r="F207" t="s">
-        <v>263</v>
+        <v>476</v>
       </c>
       <c r="I207" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J207">
         <v>1</v>
       </c>
       <c r="K207">
-        <v>52120.37</v>
+        <v>588448.45</v>
       </c>
       <c r="L207">
-        <v>52120.37</v>
+        <v>588448.45</v>
       </c>
     </row>
     <row r="208" spans="1:12">
@@ -8331,28 +8343,28 @@
         <v>212</v>
       </c>
       <c r="C208" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D208" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E208" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F208" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I208" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J208">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K208">
-        <v>907492.78</v>
+        <v>171904.24</v>
       </c>
       <c r="L208">
-        <v>907492.78</v>
+        <v>343808.48</v>
       </c>
     </row>
     <row r="209" spans="1:12">
@@ -8366,121 +8378,121 @@
         <v>260</v>
       </c>
       <c r="D209" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E209" t="s">
-        <v>472</v>
+        <v>265</v>
       </c>
       <c r="F209" t="s">
-        <v>472</v>
+        <v>265</v>
       </c>
       <c r="I209" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J209">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K209">
-        <v>118001.73</v>
+        <v>52120.37</v>
       </c>
       <c r="L209">
-        <v>236003.46</v>
+        <v>52120.37</v>
       </c>
     </row>
     <row r="210" spans="1:12">
       <c r="A210" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B210" t="s">
         <v>214</v>
       </c>
       <c r="C210" t="s">
-        <v>260</v>
+        <v>226</v>
       </c>
       <c r="D210" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E210" t="s">
-        <v>472</v>
+        <v>226</v>
       </c>
       <c r="F210" t="s">
-        <v>472</v>
+        <v>226</v>
       </c>
       <c r="I210" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J210">
         <v>1</v>
       </c>
       <c r="K210">
-        <v>56470.99</v>
+        <v>907492.78</v>
       </c>
       <c r="L210">
-        <v>56470.99</v>
+        <v>907492.78</v>
       </c>
     </row>
     <row r="211" spans="1:12">
       <c r="A211" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B211" t="s">
         <v>215</v>
       </c>
       <c r="C211" t="s">
-        <v>231</v>
+        <v>262</v>
       </c>
       <c r="D211" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E211" t="s">
-        <v>231</v>
+        <v>476</v>
       </c>
       <c r="F211" t="s">
-        <v>231</v>
+        <v>476</v>
       </c>
       <c r="I211" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J211">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K211">
-        <v>20316.27</v>
+        <v>118001.73</v>
       </c>
       <c r="L211">
-        <v>121897.62</v>
+        <v>236003.46</v>
       </c>
     </row>
     <row r="212" spans="1:12">
       <c r="A212" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B212" t="s">
         <v>216</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E212" t="s">
-        <v>224</v>
+        <v>476</v>
       </c>
       <c r="F212" t="s">
-        <v>224</v>
+        <v>476</v>
       </c>
       <c r="I212" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J212">
         <v>1</v>
       </c>
       <c r="K212">
-        <v>64719.29</v>
+        <v>56470.99</v>
       </c>
       <c r="L212">
-        <v>64719.29</v>
+        <v>56470.99</v>
       </c>
     </row>
     <row r="213" spans="1:12">
@@ -8491,28 +8503,28 @@
         <v>217</v>
       </c>
       <c r="C213" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="D213" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E213" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F213" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="I213" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J213">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K213">
-        <v>15431.69</v>
+        <v>20316.27</v>
       </c>
       <c r="L213">
-        <v>77158.45</v>
+        <v>121897.62</v>
       </c>
     </row>
     <row r="214" spans="1:12">
@@ -8523,28 +8535,28 @@
         <v>218</v>
       </c>
       <c r="C214" t="s">
-        <v>224</v>
+        <v>263</v>
       </c>
       <c r="D214" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E214" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F214" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I214" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J214">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K214">
-        <v>2999.26</v>
+        <v>64719.29</v>
       </c>
       <c r="L214">
-        <v>68982.98</v>
+        <v>64719.29</v>
       </c>
     </row>
     <row r="215" spans="1:12">
@@ -8555,92 +8567,92 @@
         <v>219</v>
       </c>
       <c r="C215" t="s">
-        <v>262</v>
+        <v>226</v>
       </c>
       <c r="D215" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E215" t="s">
-        <v>262</v>
+        <v>226</v>
       </c>
       <c r="F215" t="s">
-        <v>262</v>
+        <v>226</v>
       </c>
       <c r="I215" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J215">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K215">
-        <v>40143.73</v>
+        <v>15431.69</v>
       </c>
       <c r="L215">
-        <v>160574.92</v>
+        <v>77158.45</v>
       </c>
     </row>
     <row r="216" spans="1:12">
       <c r="A216" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B216" t="s">
         <v>220</v>
       </c>
       <c r="C216" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="D216" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E216" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="F216" t="s">
-        <v>475</v>
+        <v>226</v>
       </c>
       <c r="I216" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J216">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="K216">
-        <v>259475.34</v>
+        <v>2999.26</v>
       </c>
       <c r="L216">
-        <v>259475.34</v>
+        <v>68982.98</v>
       </c>
     </row>
     <row r="217" spans="1:12">
       <c r="A217" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B217" t="s">
         <v>221</v>
       </c>
       <c r="C217" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E217" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F217" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I217" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J217">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K217">
-        <v>112000</v>
+        <v>40143.73</v>
       </c>
       <c r="L217">
-        <v>224000</v>
+        <v>160574.92</v>
       </c>
     </row>
     <row r="218" spans="1:12">
@@ -8651,27 +8663,91 @@
         <v>222</v>
       </c>
       <c r="C218" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D218" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E218" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F218" t="s">
-        <v>264</v>
+        <v>479</v>
       </c>
       <c r="I218" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J218">
+        <v>1</v>
+      </c>
+      <c r="K218">
+        <v>259475.34</v>
+      </c>
+      <c r="L218">
+        <v>259475.34</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12">
+      <c r="A219" t="s">
+        <v>13</v>
+      </c>
+      <c r="B219" t="s">
+        <v>223</v>
+      </c>
+      <c r="C219" t="s">
+        <v>265</v>
+      </c>
+      <c r="D219" t="s">
+        <v>472</v>
+      </c>
+      <c r="E219" t="s">
+        <v>265</v>
+      </c>
+      <c r="F219" t="s">
+        <v>265</v>
+      </c>
+      <c r="I219" t="s">
+        <v>481</v>
+      </c>
+      <c r="J219">
+        <v>2</v>
+      </c>
+      <c r="K219">
+        <v>112000</v>
+      </c>
+      <c r="L219">
+        <v>224000</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12">
+      <c r="A220" t="s">
+        <v>13</v>
+      </c>
+      <c r="B220" t="s">
+        <v>224</v>
+      </c>
+      <c r="C220" t="s">
+        <v>266</v>
+      </c>
+      <c r="D220" t="s">
+        <v>473</v>
+      </c>
+      <c r="E220" t="s">
+        <v>266</v>
+      </c>
+      <c r="F220" t="s">
+        <v>266</v>
+      </c>
+      <c r="I220" t="s">
+        <v>481</v>
+      </c>
+      <c r="J220">
         <v>6</v>
       </c>
-      <c r="K218">
+      <c r="K220">
         <v>128205</v>
       </c>
-      <c r="L218">
+      <c r="L220">
         <v>769230</v>
       </c>
     </row>

--- a/VALORIZADO FALTANTES.xlsx
+++ b/VALORIZADO FALTANTES.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="498">
   <si>
     <t>Categoría</t>
   </si>
@@ -94,6 +94,9 @@
     <t>4301762</t>
   </si>
   <si>
+    <t>4302316</t>
+  </si>
+  <si>
     <t>4302411</t>
   </si>
   <si>
@@ -403,6 +406,9 @@
     <t>PAI8575-STD</t>
   </si>
   <si>
+    <t>R309324</t>
+  </si>
+  <si>
     <t>R824003</t>
   </si>
   <si>
@@ -691,6 +697,9 @@
     <t>2878168JGOX7</t>
   </si>
   <si>
+    <t>4306025/8879</t>
+  </si>
+  <si>
     <t>FIRESTONE</t>
   </si>
   <si>
@@ -802,6 +811,9 @@
     <t>WAP</t>
   </si>
   <si>
+    <t>NATIONAL</t>
+  </si>
+  <si>
     <t>FAG</t>
   </si>
   <si>
@@ -853,6 +865,9 @@
     <t>PIÑÓN 2DA CDIZO S-6305A</t>
   </si>
   <si>
+    <t>VARILLA  EJE CORREDIZO  FR/FRO TODAS</t>
+  </si>
+  <si>
     <t>PIÑÓN  1RA CDIZO 11210C</t>
   </si>
   <si>
@@ -1159,6 +1174,9 @@
     <t>CASQUETE BANCADA MACK 676 TIPO VIEJO</t>
   </si>
   <si>
+    <t>CORBATIN SUSPENSION 3 1/2 MERITOR</t>
+  </si>
+  <si>
     <t>RACHE FRENO MEC. 1-1/2"28E</t>
   </si>
   <si>
@@ -1438,6 +1456,9 @@
     <t>BUJES EJE DE LEVAS CUMMINS L10 - ISM (JUEGO X 7UND)</t>
   </si>
   <si>
+    <t>RODILLO TORRE MONO 125215 RT14613</t>
+  </si>
+  <si>
     <t>MT-OTROS</t>
   </si>
   <si>
@@ -1450,6 +1471,9 @@
     <t>AMORTIGUADORES</t>
   </si>
   <si>
+    <t>CVG</t>
+  </si>
+  <si>
     <t>MERITOR-RODAMIENTO-B</t>
   </si>
   <si>
@@ -1477,13 +1501,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/01/2026 07:42:42</t>
+    <t>Período: 31/01/2026 07:42:40</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 08/01/2026 07:43:14</t>
+    <t>Fecha y hora de generación: 09/01/2026 07:43:12</t>
   </si>
 </sst>
 </file>
@@ -1897,28 +1921,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L220"/>
+  <dimension ref="A1:L223"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1934,7 +1958,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1950,12 +1974,12 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="4" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="I7" s="5" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -2007,19 +2031,19 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D10" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E10" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F10" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I10" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J10">
         <v>3</v>
@@ -2039,19 +2063,19 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D11" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E11" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F11" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I11" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -2071,19 +2095,19 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E12" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F12" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I12" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -2103,19 +2127,19 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D13" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E13" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="F13" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="I13" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -2135,19 +2159,19 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D14" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E14" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F14" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I14" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -2167,19 +2191,19 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D15" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E15" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F15" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I15" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -2199,19 +2223,19 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D16" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E16" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F16" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="I16" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J16">
         <v>2</v>
@@ -2231,19 +2255,19 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D17" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E17" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F17" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="I17" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2263,19 +2287,19 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D18" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E18" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F18" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I18" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2295,19 +2319,19 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D19" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E19" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F19" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I19" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -2327,19 +2351,19 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D20" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E20" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F20" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I20" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2359,19 +2383,19 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D21" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E21" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F21" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I21" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2391,28 +2415,28 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D22" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E22" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F22" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I22" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K22">
-        <v>286220.53</v>
+        <v>8111.55</v>
       </c>
       <c r="L22">
-        <v>858661.59</v>
+        <v>8111.55</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2423,28 +2447,28 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D23" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E23" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F23" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I23" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23">
-        <v>355066.43</v>
+        <v>286220.53</v>
       </c>
       <c r="L23">
-        <v>710132.86</v>
+        <v>858661.59</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -2455,28 +2479,28 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D24" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E24" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F24" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I24" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J24">
         <v>2</v>
       </c>
       <c r="K24">
-        <v>309397.93</v>
+        <v>355066.43</v>
       </c>
       <c r="L24">
-        <v>618795.86</v>
+        <v>710132.86</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2487,28 +2511,28 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D25" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E25" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F25" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I25" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J25">
         <v>2</v>
       </c>
       <c r="K25">
-        <v>453521.87</v>
+        <v>309397.93</v>
       </c>
       <c r="L25">
-        <v>907043.74</v>
+        <v>618795.86</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2519,28 +2543,28 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D26" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E26" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F26" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I26" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J26">
         <v>2</v>
       </c>
       <c r="K26">
-        <v>264088.37</v>
+        <v>453521.87</v>
       </c>
       <c r="L26">
-        <v>528176.74</v>
+        <v>907043.74</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2551,92 +2575,92 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D27" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E27" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F27" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I27" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K27">
-        <v>294809.24</v>
+        <v>264088.37</v>
       </c>
       <c r="L27">
-        <v>884427.72</v>
+        <v>528176.74</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D28" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E28" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F28" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I28" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K28">
-        <v>324848.81</v>
+        <v>294809.24</v>
       </c>
       <c r="L28">
-        <v>324848.81</v>
+        <v>884427.72</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D29" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E29" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F29" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I29" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J29">
         <v>1</v>
       </c>
       <c r="K29">
-        <v>119219.24</v>
+        <v>324848.81</v>
       </c>
       <c r="L29">
-        <v>119219.24</v>
+        <v>324848.81</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2647,28 +2671,28 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D30" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E30" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F30" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I30" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>456594.41</v>
+        <v>119219.24</v>
       </c>
       <c r="L30">
-        <v>913188.8199999999</v>
+        <v>119219.24</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2679,28 +2703,28 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D31" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E31" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F31" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I31" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J31">
         <v>2</v>
       </c>
       <c r="K31">
-        <v>84932.64999999999</v>
+        <v>456594.41</v>
       </c>
       <c r="L31">
-        <v>169865.3</v>
+        <v>913188.8199999999</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2714,25 +2738,25 @@
         <v>229</v>
       </c>
       <c r="D32" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E32" t="s">
-        <v>475</v>
+        <v>229</v>
       </c>
       <c r="F32" t="s">
         <v>229</v>
       </c>
       <c r="I32" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J32">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K32">
-        <v>30580.36</v>
+        <v>84932.64999999999</v>
       </c>
       <c r="L32">
-        <v>366964.32</v>
+        <v>169865.3</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -2743,28 +2767,28 @@
         <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D33" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E33" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="F33" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I33" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J33">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K33">
-        <v>33351.89</v>
+        <v>30580.36</v>
       </c>
       <c r="L33">
-        <v>200111.34</v>
+        <v>366964.32</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2775,28 +2799,28 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D34" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E34" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="F34" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I34" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J34">
         <v>6</v>
       </c>
       <c r="K34">
-        <v>26185.2</v>
+        <v>33351.89</v>
       </c>
       <c r="L34">
-        <v>157111.2</v>
+        <v>200111.34</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2807,28 +2831,28 @@
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D35" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E35" t="s">
-        <v>231</v>
+        <v>482</v>
       </c>
       <c r="F35" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I35" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J35">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K35">
-        <v>132383.57</v>
+        <v>26185.2</v>
       </c>
       <c r="L35">
-        <v>132383.57</v>
+        <v>157111.2</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2839,28 +2863,28 @@
         <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D36" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E36" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F36" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="I36" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J36">
         <v>1</v>
       </c>
       <c r="K36">
-        <v>1666305.17</v>
+        <v>132383.57</v>
       </c>
       <c r="L36">
-        <v>1666305.17</v>
+        <v>132383.57</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2871,92 +2895,92 @@
         <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D37" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E37" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F37" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I37" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K37">
-        <v>1195074.95</v>
+        <v>1666305.17</v>
       </c>
       <c r="L37">
-        <v>3585224.85</v>
+        <v>1666305.17</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D38" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E38" t="s">
-        <v>476</v>
+        <v>234</v>
       </c>
       <c r="F38" t="s">
-        <v>476</v>
+        <v>234</v>
       </c>
       <c r="I38" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J38">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="K38">
-        <v>1578.02</v>
+        <v>1195074.95</v>
       </c>
       <c r="L38">
-        <v>194096.46</v>
+        <v>3585224.85</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D39" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E39" t="s">
-        <v>233</v>
+        <v>483</v>
       </c>
       <c r="F39" t="s">
-        <v>233</v>
+        <v>483</v>
       </c>
       <c r="I39" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J39">
-        <v>4</v>
+        <v>123</v>
       </c>
       <c r="K39">
-        <v>16186.82</v>
+        <v>1578.02</v>
       </c>
       <c r="L39">
-        <v>64747.28</v>
+        <v>194096.46</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2967,28 +2991,28 @@
         <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D40" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="E40" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F40" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I40" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K40">
-        <v>151783.14</v>
+        <v>16186.82</v>
       </c>
       <c r="L40">
-        <v>151783.14</v>
+        <v>64747.28</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2999,92 +3023,92 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D41" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E41" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F41" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I41" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J41">
         <v>1</v>
       </c>
       <c r="K41">
-        <v>133605.86</v>
+        <v>151783.14</v>
       </c>
       <c r="L41">
-        <v>133605.86</v>
+        <v>151783.14</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D42" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E42" t="s">
-        <v>475</v>
+        <v>237</v>
       </c>
       <c r="F42" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="I42" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J42">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K42">
-        <v>10090.39</v>
+        <v>133605.86</v>
       </c>
       <c r="L42">
-        <v>121084.68</v>
+        <v>133605.86</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B43" t="s">
         <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D43" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E43" t="s">
-        <v>239</v>
+        <v>482</v>
       </c>
       <c r="F43" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="I43" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J43">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K43">
-        <v>55214.31</v>
+        <v>10090.39</v>
       </c>
       <c r="L43">
-        <v>55214.31</v>
+        <v>121084.68</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -3095,28 +3119,28 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D44" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E44" t="s">
-        <v>474</v>
+        <v>242</v>
       </c>
       <c r="F44" t="s">
-        <v>474</v>
+        <v>242</v>
       </c>
       <c r="I44" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K44">
-        <v>273006.7</v>
+        <v>55214.31</v>
       </c>
       <c r="L44">
-        <v>546013.4</v>
+        <v>55214.31</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -3127,28 +3151,28 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D45" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E45" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="F45" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="I45" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J45">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K45">
-        <v>22300.22</v>
+        <v>273006.7</v>
       </c>
       <c r="L45">
-        <v>267602.64</v>
+        <v>546013.4</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -3159,28 +3183,28 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D46" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E46" t="s">
-        <v>237</v>
+        <v>481</v>
       </c>
       <c r="F46" t="s">
-        <v>237</v>
+        <v>481</v>
       </c>
       <c r="I46" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J46">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K46">
-        <v>69469.2</v>
+        <v>22300.22</v>
       </c>
       <c r="L46">
-        <v>69469.2</v>
+        <v>267602.64</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -3191,28 +3215,28 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D47" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E47" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F47" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I47" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K47">
-        <v>38542.45</v>
+        <v>69469.2</v>
       </c>
       <c r="L47">
-        <v>77084.89999999999</v>
+        <v>69469.2</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -3223,28 +3247,28 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D48" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E48" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F48" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I48" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K48">
-        <v>73169.58</v>
+        <v>38542.45</v>
       </c>
       <c r="L48">
-        <v>292678.32</v>
+        <v>77084.89999999999</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -3255,28 +3279,28 @@
         <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D49" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E49" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F49" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="I49" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K49">
-        <v>781011.86</v>
+        <v>73169.58</v>
       </c>
       <c r="L49">
-        <v>781011.86</v>
+        <v>292678.32</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -3287,28 +3311,28 @@
         <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D50" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E50" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F50" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="I50" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J50">
         <v>1</v>
       </c>
       <c r="K50">
-        <v>57029.66</v>
+        <v>781011.86</v>
       </c>
       <c r="L50">
-        <v>57029.66</v>
+        <v>781011.86</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -3319,28 +3343,28 @@
         <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D51" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E51" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F51" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="I51" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J51">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K51">
-        <v>124113.03</v>
+        <v>57029.66</v>
       </c>
       <c r="L51">
-        <v>620565.15</v>
+        <v>57029.66</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -3354,89 +3378,89 @@
         <v>240</v>
       </c>
       <c r="D52" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E52" t="s">
-        <v>474</v>
+        <v>240</v>
       </c>
       <c r="F52" t="s">
-        <v>474</v>
+        <v>240</v>
       </c>
       <c r="I52" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K52">
-        <v>143954.72</v>
+        <v>124113.03</v>
       </c>
       <c r="L52">
-        <v>143954.72</v>
+        <v>620565.15</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B53" t="s">
         <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D53" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E53" t="s">
-        <v>241</v>
+        <v>481</v>
       </c>
       <c r="F53" t="s">
-        <v>241</v>
+        <v>481</v>
       </c>
       <c r="I53" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K53">
-        <v>374186</v>
+        <v>143954.72</v>
       </c>
       <c r="L53">
-        <v>1122558</v>
+        <v>143954.72</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B54" t="s">
         <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D54" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E54" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F54" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="I54" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K54">
-        <v>451755.47</v>
+        <v>374186</v>
       </c>
       <c r="L54">
-        <v>903510.9399999999</v>
+        <v>1122558</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3447,28 +3471,28 @@
         <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="D55" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E55" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="F55" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="I55" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K55">
-        <v>297477.98</v>
+        <v>451755.47</v>
       </c>
       <c r="L55">
-        <v>297477.98</v>
+        <v>903510.9399999999</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -3479,28 +3503,28 @@
         <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D56" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E56" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="F56" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="I56" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K56">
-        <v>116675.06</v>
+        <v>297477.98</v>
       </c>
       <c r="L56">
-        <v>350025.18</v>
+        <v>297477.98</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -3511,28 +3535,28 @@
         <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="D57" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E57" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="F57" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="I57" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K57">
-        <v>241521.59</v>
+        <v>116675.06</v>
       </c>
       <c r="L57">
-        <v>241521.59</v>
+        <v>350025.18</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3543,28 +3567,28 @@
         <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D58" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E58" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F58" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I58" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K58">
-        <v>123123.72</v>
+        <v>241521.59</v>
       </c>
       <c r="L58">
-        <v>246247.44</v>
+        <v>241521.59</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3575,28 +3599,28 @@
         <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D59" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E59" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F59" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I59" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J59">
         <v>2</v>
       </c>
       <c r="K59">
-        <v>277740.62</v>
+        <v>123123.72</v>
       </c>
       <c r="L59">
-        <v>555481.24</v>
+        <v>246247.44</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3607,28 +3631,28 @@
         <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D60" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E60" t="s">
-        <v>475</v>
+        <v>229</v>
       </c>
       <c r="F60" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I60" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J60">
-        <v>206</v>
+        <v>2</v>
       </c>
       <c r="K60">
-        <v>10428.31</v>
+        <v>277740.62</v>
       </c>
       <c r="L60">
-        <v>2148231.86</v>
+        <v>555481.24</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3639,92 +3663,92 @@
         <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D61" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E61" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="F61" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I61" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J61">
-        <v>46</v>
+        <v>206</v>
       </c>
       <c r="K61">
-        <v>5719.65</v>
+        <v>10428.31</v>
       </c>
       <c r="L61">
-        <v>263103.9</v>
+        <v>2148231.86</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
         <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D62" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E62" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="F62" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I62" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J62">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="K62">
-        <v>12871.55</v>
+        <v>5719.65</v>
       </c>
       <c r="L62">
-        <v>77229.3</v>
+        <v>263103.9</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B63" t="s">
         <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="D63" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E63" t="s">
-        <v>246</v>
+        <v>482</v>
       </c>
       <c r="F63" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="I63" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J63">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="K63">
-        <v>11227.66</v>
+        <v>12871.55</v>
       </c>
       <c r="L63">
-        <v>718570.24</v>
+        <v>77229.3</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3735,92 +3759,92 @@
         <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D64" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E64" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F64" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="I64" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J64">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="K64">
-        <v>74410.03</v>
+        <v>11227.66</v>
       </c>
       <c r="L64">
-        <v>223230.09</v>
+        <v>718570.24</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B65" t="s">
         <v>69</v>
       </c>
       <c r="C65" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="D65" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E65" t="s">
-        <v>476</v>
+        <v>249</v>
       </c>
       <c r="F65" t="s">
-        <v>476</v>
+        <v>245</v>
       </c>
       <c r="I65" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K65">
-        <v>52014.93</v>
+        <v>74410.03</v>
       </c>
       <c r="L65">
-        <v>104029.86</v>
+        <v>223230.09</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B66" t="s">
         <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D66" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E66" t="s">
-        <v>239</v>
+        <v>483</v>
       </c>
       <c r="F66" t="s">
-        <v>239</v>
+        <v>483</v>
       </c>
       <c r="I66" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J66">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K66">
-        <v>94380.39999999999</v>
+        <v>52014.93</v>
       </c>
       <c r="L66">
-        <v>1887608</v>
+        <v>104029.86</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3831,28 +3855,28 @@
         <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D67" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E67" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F67" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I67" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J67">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K67">
-        <v>1157466.59</v>
+        <v>94380.39999999999</v>
       </c>
       <c r="L67">
-        <v>5787332.95</v>
+        <v>1887608</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3863,28 +3887,28 @@
         <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D68" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E68" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F68" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I68" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J68">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K68">
-        <v>553925.89</v>
+        <v>1157466.59</v>
       </c>
       <c r="L68">
-        <v>553925.89</v>
+        <v>5787332.95</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3895,28 +3919,28 @@
         <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="D69" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E69" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="F69" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="I69" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J69">
         <v>1</v>
       </c>
       <c r="K69">
-        <v>456192.75</v>
+        <v>553925.89</v>
       </c>
       <c r="L69">
-        <v>456192.75</v>
+        <v>553925.89</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3927,92 +3951,92 @@
         <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D70" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E70" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F70" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="I70" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J70">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K70">
-        <v>459216.59</v>
+        <v>456192.75</v>
       </c>
       <c r="L70">
-        <v>2296082.95</v>
+        <v>456192.75</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
         <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="D71" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E71" t="s">
-        <v>477</v>
+        <v>236</v>
       </c>
       <c r="F71" t="s">
-        <v>477</v>
+        <v>236</v>
       </c>
       <c r="I71" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J71">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K71">
-        <v>107611.43</v>
+        <v>459216.59</v>
       </c>
       <c r="L71">
-        <v>215222.86</v>
+        <v>2296082.95</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B72" t="s">
         <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D72" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E72" t="s">
-        <v>237</v>
+        <v>484</v>
       </c>
       <c r="F72" t="s">
-        <v>237</v>
+        <v>484</v>
       </c>
       <c r="I72" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J72">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K72">
-        <v>162784.49</v>
+        <v>107611.43</v>
       </c>
       <c r="L72">
-        <v>651137.96</v>
+        <v>215222.86</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -4023,28 +4047,28 @@
         <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D73" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E73" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="F73" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="I73" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K73">
-        <v>64596.41</v>
+        <v>162784.49</v>
       </c>
       <c r="L73">
-        <v>193789.23</v>
+        <v>651137.96</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -4055,28 +4079,28 @@
         <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="D74" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E74" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="F74" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="I74" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K74">
-        <v>520965.57</v>
+        <v>64596.41</v>
       </c>
       <c r="L74">
-        <v>2083862.28</v>
+        <v>193789.23</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -4087,28 +4111,28 @@
         <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D75" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E75" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F75" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="I75" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K75">
-        <v>234957.18</v>
+        <v>520965.57</v>
       </c>
       <c r="L75">
-        <v>234957.18</v>
+        <v>2083862.28</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -4119,60 +4143,60 @@
         <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D76" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E76" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F76" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I76" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J76">
         <v>1</v>
       </c>
       <c r="K76">
-        <v>561136.28</v>
+        <v>234957.18</v>
       </c>
       <c r="L76">
-        <v>561136.28</v>
+        <v>234957.18</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
         <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D77" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E77" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F77" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I77" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J77">
         <v>1</v>
       </c>
       <c r="K77">
-        <v>548933.98</v>
+        <v>561136.28</v>
       </c>
       <c r="L77">
-        <v>548933.98</v>
+        <v>561136.28</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -4183,28 +4207,28 @@
         <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D78" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E78" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F78" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I78" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K78">
-        <v>348438.94</v>
+        <v>548933.98</v>
       </c>
       <c r="L78">
-        <v>696877.88</v>
+        <v>548933.98</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -4215,28 +4239,28 @@
         <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D79" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E79" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F79" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I79" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K79">
-        <v>176616.64</v>
+        <v>348438.94</v>
       </c>
       <c r="L79">
-        <v>176616.64</v>
+        <v>696877.88</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -4247,60 +4271,60 @@
         <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D80" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E80" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F80" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I80" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K80">
-        <v>54474.6</v>
+        <v>176616.64</v>
       </c>
       <c r="L80">
-        <v>163423.8</v>
+        <v>176616.64</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B81" t="s">
         <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D81" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E81" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F81" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I81" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K81">
-        <v>289538.6</v>
+        <v>54474.6</v>
       </c>
       <c r="L81">
-        <v>289538.6</v>
+        <v>163423.8</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -4311,28 +4335,28 @@
         <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="D82" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E82" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="F82" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="I82" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K82">
-        <v>60191.18</v>
+        <v>289538.6</v>
       </c>
       <c r="L82">
-        <v>120382.36</v>
+        <v>289538.6</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -4343,28 +4367,28 @@
         <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="D83" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="E83" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="F83" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="I83" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J83">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K83">
-        <v>106058.91</v>
+        <v>60191.18</v>
       </c>
       <c r="L83">
-        <v>530294.55</v>
+        <v>120382.36</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -4375,92 +4399,92 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D84" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E84" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F84" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I84" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J84">
         <v>5</v>
       </c>
       <c r="K84">
-        <v>24077.89</v>
+        <v>106058.91</v>
       </c>
       <c r="L84">
-        <v>120389.45</v>
+        <v>530294.55</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B85" t="s">
         <v>89</v>
       </c>
       <c r="C85" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D85" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E85" t="s">
-        <v>476</v>
+        <v>241</v>
       </c>
       <c r="F85" t="s">
-        <v>476</v>
+        <v>241</v>
       </c>
       <c r="I85" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J85">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="K85">
-        <v>13504.82</v>
+        <v>24077.89</v>
       </c>
       <c r="L85">
-        <v>283601.22</v>
+        <v>120389.45</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B86" t="s">
         <v>90</v>
       </c>
       <c r="C86" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D86" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="E86" t="s">
-        <v>244</v>
+        <v>483</v>
       </c>
       <c r="F86" t="s">
-        <v>244</v>
+        <v>483</v>
       </c>
       <c r="I86" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J86">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K86">
-        <v>244653.18</v>
+        <v>13504.82</v>
       </c>
       <c r="L86">
-        <v>244653.18</v>
+        <v>283601.22</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -4471,60 +4495,60 @@
         <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D87" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E87" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F87" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I87" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J87">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K87">
-        <v>116579.52</v>
+        <v>244653.18</v>
       </c>
       <c r="L87">
-        <v>466318.08</v>
+        <v>244653.18</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
         <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="D88" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E88" t="s">
-        <v>477</v>
+        <v>251</v>
       </c>
       <c r="F88" t="s">
-        <v>477</v>
+        <v>251</v>
       </c>
       <c r="I88" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J88">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K88">
-        <v>132950.29</v>
+        <v>116579.52</v>
       </c>
       <c r="L88">
-        <v>265900.58</v>
+        <v>466318.08</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4535,124 +4559,124 @@
         <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D89" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E89" t="s">
-        <v>246</v>
+        <v>484</v>
       </c>
       <c r="F89" t="s">
-        <v>242</v>
+        <v>484</v>
       </c>
       <c r="I89" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J89">
         <v>2</v>
       </c>
       <c r="K89">
-        <v>130565.76</v>
+        <v>132950.29</v>
       </c>
       <c r="L89">
-        <v>261131.52</v>
+        <v>265900.58</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B90" t="s">
         <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D90" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E90" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="F90" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="I90" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J90">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K90">
-        <v>32532.84</v>
+        <v>130565.76</v>
       </c>
       <c r="L90">
-        <v>325328.4</v>
+        <v>261131.52</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B91" t="s">
         <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="D91" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E91" t="s">
-        <v>475</v>
+        <v>241</v>
       </c>
       <c r="F91" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="I91" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J91">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K91">
-        <v>36184.1</v>
+        <v>32532.84</v>
       </c>
       <c r="L91">
-        <v>289472.8</v>
+        <v>325328.4</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B92" t="s">
         <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="D92" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E92" t="s">
-        <v>249</v>
+        <v>482</v>
       </c>
       <c r="F92" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="I92" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J92">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K92">
-        <v>202984.86</v>
+        <v>36184.1</v>
       </c>
       <c r="L92">
-        <v>202984.86</v>
+        <v>289472.8</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4663,60 +4687,60 @@
         <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D93" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E93" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F93" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="I93" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K93">
-        <v>98967.53</v>
+        <v>202984.86</v>
       </c>
       <c r="L93">
-        <v>197935.06</v>
+        <v>202984.86</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B94" t="s">
         <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D94" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E94" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F94" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I94" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J94">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K94">
-        <v>140000</v>
+        <v>98967.53</v>
       </c>
       <c r="L94">
-        <v>560000</v>
+        <v>197935.06</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4727,28 +4751,28 @@
         <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D95" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E95" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F95" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="I95" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J95">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K95">
-        <v>60000</v>
+        <v>140000</v>
       </c>
       <c r="L95">
-        <v>480000</v>
+        <v>560000</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4759,60 +4783,60 @@
         <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="D96" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E96" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="F96" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="I96" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J96">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K96">
-        <v>183395.81</v>
+        <v>60000</v>
       </c>
       <c r="L96">
-        <v>366791.62</v>
+        <v>480000</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B97" t="s">
         <v>101</v>
       </c>
       <c r="C97" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="D97" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="E97" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F97" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="I97" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K97">
-        <v>561283.11</v>
+        <v>183395.81</v>
       </c>
       <c r="L97">
-        <v>561283.11</v>
+        <v>366791.62</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4826,7 +4850,7 @@
         <v>228</v>
       </c>
       <c r="D98" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="E98" t="s">
         <v>228</v>
@@ -4835,16 +4859,16 @@
         <v>228</v>
       </c>
       <c r="I98" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K98">
-        <v>400703.47</v>
+        <v>561283.11</v>
       </c>
       <c r="L98">
-        <v>801406.9399999999</v>
+        <v>561283.11</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4855,28 +4879,28 @@
         <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D99" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E99" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F99" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I99" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J99">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="K99">
-        <v>62347.32</v>
+        <v>400703.47</v>
       </c>
       <c r="L99">
-        <v>1309293.72</v>
+        <v>801406.9399999999</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -4887,28 +4911,28 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D100" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E100" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F100" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="I100" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J100">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K100">
-        <v>339984.3</v>
+        <v>62347.32</v>
       </c>
       <c r="L100">
-        <v>339984.3</v>
+        <v>1309293.72</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -4919,60 +4943,60 @@
         <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D101" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E101" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F101" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I101" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K101">
-        <v>212047.99</v>
+        <v>339984.3</v>
       </c>
       <c r="L101">
-        <v>636143.97</v>
+        <v>339984.3</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B102" t="s">
         <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="D102" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E102" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="F102" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="I102" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J102">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K102">
-        <v>79854.5</v>
+        <v>212047.99</v>
       </c>
       <c r="L102">
-        <v>159709</v>
+        <v>636143.97</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -4983,92 +5007,92 @@
         <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="D103" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E103" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="F103" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="I103" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K103">
-        <v>116716.34</v>
+        <v>79854.5</v>
       </c>
       <c r="L103">
-        <v>116716.34</v>
+        <v>159709</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B104" t="s">
         <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="D104" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="E104" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="F104" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="I104" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J104">
         <v>1</v>
       </c>
       <c r="K104">
-        <v>147576.31</v>
+        <v>116716.34</v>
       </c>
       <c r="L104">
-        <v>147576.31</v>
+        <v>116716.34</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B105" t="s">
         <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="D105" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E105" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="F105" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="I105" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K105">
-        <v>25956.31</v>
+        <v>147576.31</v>
       </c>
       <c r="L105">
-        <v>51912.62</v>
+        <v>147576.31</v>
       </c>
     </row>
     <row r="106" spans="1:12">
@@ -5079,92 +5103,92 @@
         <v>110</v>
       </c>
       <c r="C106" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D106" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E106" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="F106" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="I106" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J106">
         <v>2</v>
       </c>
       <c r="K106">
-        <v>207223.89</v>
+        <v>25956.31</v>
       </c>
       <c r="L106">
-        <v>414447.78</v>
+        <v>51912.62</v>
       </c>
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B107" t="s">
         <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D107" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E107" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F107" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I107" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J107">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K107">
-        <v>52993.42</v>
+        <v>207223.89</v>
       </c>
       <c r="L107">
-        <v>688914.46</v>
+        <v>414447.78</v>
       </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B108" t="s">
         <v>112</v>
       </c>
       <c r="C108" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="D108" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="E108" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F108" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="I108" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J108">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K108">
-        <v>365807.37</v>
+        <v>52993.42</v>
       </c>
       <c r="L108">
-        <v>1097422.11</v>
+        <v>688914.46</v>
       </c>
     </row>
     <row r="109" spans="1:12">
@@ -5175,60 +5199,60 @@
         <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="D109" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E109" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="F109" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="I109" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J109">
-        <v>276</v>
+        <v>3</v>
       </c>
       <c r="K109">
-        <v>910.4400000000001</v>
+        <v>365807.37</v>
       </c>
       <c r="L109">
-        <v>251281.44</v>
+        <v>1097422.11</v>
       </c>
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B110" t="s">
         <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D110" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E110" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F110" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="I110" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J110">
-        <v>1</v>
+        <v>276</v>
       </c>
       <c r="K110">
-        <v>61252.9</v>
+        <v>910.4400000000001</v>
       </c>
       <c r="L110">
-        <v>61252.9</v>
+        <v>251281.44</v>
       </c>
     </row>
     <row r="111" spans="1:12">
@@ -5239,28 +5263,28 @@
         <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D111" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E111" t="s">
-        <v>475</v>
+        <v>255</v>
       </c>
       <c r="F111" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="I111" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J111">
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="K111">
-        <v>12408.84</v>
+        <v>61252.9</v>
       </c>
       <c r="L111">
-        <v>1786872.96</v>
+        <v>61252.9</v>
       </c>
     </row>
     <row r="112" spans="1:12">
@@ -5271,28 +5295,28 @@
         <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="D112" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="E112" t="s">
-        <v>246</v>
+        <v>482</v>
       </c>
       <c r="F112" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="I112" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J112">
-        <v>10</v>
+        <v>144</v>
       </c>
       <c r="K112">
-        <v>82259.44</v>
+        <v>12408.84</v>
       </c>
       <c r="L112">
-        <v>822594.4</v>
+        <v>1786872.96</v>
       </c>
     </row>
     <row r="113" spans="1:12">
@@ -5303,28 +5327,28 @@
         <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="D113" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E113" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="F113" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="I113" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J113">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K113">
-        <v>43930.6</v>
+        <v>82259.44</v>
       </c>
       <c r="L113">
-        <v>219653</v>
+        <v>822594.4</v>
       </c>
     </row>
     <row r="114" spans="1:12">
@@ -5335,28 +5359,28 @@
         <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D114" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E114" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F114" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I114" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J114">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K114">
-        <v>78505.56</v>
+        <v>43930.6</v>
       </c>
       <c r="L114">
-        <v>78505.56</v>
+        <v>219653</v>
       </c>
     </row>
     <row r="115" spans="1:12">
@@ -5367,60 +5391,60 @@
         <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D115" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E115" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F115" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I115" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K115">
-        <v>253717.21</v>
+        <v>78505.56</v>
       </c>
       <c r="L115">
-        <v>507434.42</v>
+        <v>78505.56</v>
       </c>
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B116" t="s">
         <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="D116" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E116" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="F116" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="I116" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K116">
-        <v>462132.13</v>
+        <v>253717.21</v>
       </c>
       <c r="L116">
-        <v>462132.13</v>
+        <v>507434.42</v>
       </c>
     </row>
     <row r="117" spans="1:12">
@@ -5431,60 +5455,60 @@
         <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D117" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E117" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="F117" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="I117" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J117">
         <v>1</v>
       </c>
       <c r="K117">
-        <v>294400</v>
+        <v>462132.13</v>
       </c>
       <c r="L117">
-        <v>294400</v>
+        <v>462132.13</v>
       </c>
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B118" t="s">
         <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="D118" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E118" t="s">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="F118" t="s">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="I118" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K118">
-        <v>308720.23</v>
+        <v>294400</v>
       </c>
       <c r="L118">
-        <v>617440.46</v>
+        <v>294400</v>
       </c>
     </row>
     <row r="119" spans="1:12">
@@ -5495,28 +5519,28 @@
         <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D119" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E119" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F119" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="I119" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J119">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K119">
-        <v>130424.26</v>
+        <v>308720.23</v>
       </c>
       <c r="L119">
-        <v>521697.04</v>
+        <v>617440.46</v>
       </c>
     </row>
     <row r="120" spans="1:12">
@@ -5527,28 +5551,28 @@
         <v>124</v>
       </c>
       <c r="C120" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="D120" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E120" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="F120" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="I120" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J120">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K120">
-        <v>142359.27</v>
+        <v>130424.26</v>
       </c>
       <c r="L120">
-        <v>142359.27</v>
+        <v>521697.04</v>
       </c>
     </row>
     <row r="121" spans="1:12">
@@ -5559,92 +5583,92 @@
         <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D121" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E121" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F121" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I121" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J121">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K121">
-        <v>153331.85</v>
+        <v>142359.27</v>
       </c>
       <c r="L121">
-        <v>459995.55</v>
+        <v>142359.27</v>
       </c>
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B122" t="s">
         <v>126</v>
       </c>
       <c r="C122" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D122" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E122" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F122" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I122" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J122">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K122">
-        <v>151827.5</v>
+        <v>153331.85</v>
       </c>
       <c r="L122">
-        <v>759137.5</v>
+        <v>459995.55</v>
       </c>
     </row>
     <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B123" t="s">
         <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D123" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E123" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F123" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I123" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J123">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K123">
-        <v>126875.69</v>
+        <v>151827.5</v>
       </c>
       <c r="L123">
-        <v>126875.69</v>
+        <v>759137.5</v>
       </c>
     </row>
     <row r="124" spans="1:12">
@@ -5655,28 +5679,28 @@
         <v>128</v>
       </c>
       <c r="C124" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D124" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E124" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F124" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I124" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J124">
         <v>1</v>
       </c>
       <c r="K124">
-        <v>418397.52</v>
+        <v>126875.69</v>
       </c>
       <c r="L124">
-        <v>418397.52</v>
+        <v>126875.69</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -5687,28 +5711,28 @@
         <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="D125" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E125" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="F125" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="I125" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J125">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K125">
-        <v>60881.05</v>
+        <v>418397.52</v>
       </c>
       <c r="L125">
-        <v>730572.6</v>
+        <v>418397.52</v>
       </c>
     </row>
     <row r="126" spans="1:12">
@@ -5719,28 +5743,28 @@
         <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D126" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E126" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F126" t="s">
-        <v>478</v>
+        <v>236</v>
       </c>
       <c r="I126" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K126">
-        <v>53403.02</v>
+        <v>128234.89</v>
       </c>
       <c r="L126">
-        <v>53403.02</v>
+        <v>256469.78</v>
       </c>
     </row>
     <row r="127" spans="1:12">
@@ -5751,28 +5775,28 @@
         <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D127" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E127" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F127" t="s">
-        <v>478</v>
+        <v>236</v>
       </c>
       <c r="I127" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J127">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K127">
-        <v>80962.22</v>
+        <v>60881.05</v>
       </c>
       <c r="L127">
-        <v>404811.1</v>
+        <v>730572.6</v>
       </c>
     </row>
     <row r="128" spans="1:12">
@@ -5783,28 +5807,28 @@
         <v>132</v>
       </c>
       <c r="C128" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D128" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="E128" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F128" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="I128" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J128">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K128">
-        <v>30016.79</v>
+        <v>53403.02</v>
       </c>
       <c r="L128">
-        <v>90050.37</v>
+        <v>53403.02</v>
       </c>
     </row>
     <row r="129" spans="1:12">
@@ -5815,28 +5839,28 @@
         <v>133</v>
       </c>
       <c r="C129" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D129" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E129" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F129" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="I129" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J129">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K129">
-        <v>55960.12</v>
+        <v>80962.22</v>
       </c>
       <c r="L129">
-        <v>111920.24</v>
+        <v>404811.1</v>
       </c>
     </row>
     <row r="130" spans="1:12">
@@ -5847,28 +5871,28 @@
         <v>134</v>
       </c>
       <c r="C130" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D130" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E130" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F130" t="s">
-        <v>233</v>
+        <v>486</v>
       </c>
       <c r="I130" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J130">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K130">
-        <v>57770.2</v>
+        <v>30016.79</v>
       </c>
       <c r="L130">
-        <v>57770.2</v>
+        <v>90050.37</v>
       </c>
     </row>
     <row r="131" spans="1:12">
@@ -5879,92 +5903,92 @@
         <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D131" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E131" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F131" t="s">
-        <v>233</v>
+        <v>486</v>
       </c>
       <c r="I131" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J131">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K131">
-        <v>122224.03</v>
+        <v>55960.12</v>
       </c>
       <c r="L131">
-        <v>488896.12</v>
+        <v>111920.24</v>
       </c>
     </row>
     <row r="132" spans="1:12">
       <c r="A132" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B132" t="s">
         <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D132" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E132" t="s">
-        <v>476</v>
+        <v>236</v>
       </c>
       <c r="F132" t="s">
-        <v>476</v>
+        <v>236</v>
       </c>
       <c r="I132" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K132">
-        <v>345599.99</v>
+        <v>57770.2</v>
       </c>
       <c r="L132">
-        <v>691199.98</v>
+        <v>57770.2</v>
       </c>
     </row>
     <row r="133" spans="1:12">
       <c r="A133" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B133" t="s">
         <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D133" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="E133" t="s">
-        <v>476</v>
+        <v>236</v>
       </c>
       <c r="F133" t="s">
-        <v>476</v>
+        <v>236</v>
       </c>
       <c r="I133" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J133">
         <v>4</v>
       </c>
       <c r="K133">
-        <v>406977.4</v>
+        <v>122224.03</v>
       </c>
       <c r="L133">
-        <v>1627909.6</v>
+        <v>488896.12</v>
       </c>
     </row>
     <row r="134" spans="1:12">
@@ -5975,92 +5999,92 @@
         <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="D134" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E134" t="s">
-        <v>226</v>
+        <v>483</v>
       </c>
       <c r="F134" t="s">
-        <v>226</v>
+        <v>483</v>
       </c>
       <c r="I134" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K134">
-        <v>108921.66</v>
+        <v>345599.99</v>
       </c>
       <c r="L134">
-        <v>108921.66</v>
+        <v>691199.98</v>
       </c>
     </row>
     <row r="135" spans="1:12">
       <c r="A135" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B135" t="s">
         <v>139</v>
       </c>
       <c r="C135" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="D135" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E135" t="s">
-        <v>255</v>
+        <v>483</v>
       </c>
       <c r="F135" t="s">
-        <v>255</v>
+        <v>483</v>
       </c>
       <c r="I135" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J135">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K135">
-        <v>155407.11</v>
+        <v>406977.4</v>
       </c>
       <c r="L135">
-        <v>155407.11</v>
+        <v>1627909.6</v>
       </c>
     </row>
     <row r="136" spans="1:12">
       <c r="A136" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B136" t="s">
         <v>140</v>
       </c>
       <c r="C136" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="D136" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="E136" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="F136" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="I136" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K136">
-        <v>302306.98</v>
+        <v>108921.66</v>
       </c>
       <c r="L136">
-        <v>604613.96</v>
+        <v>108921.66</v>
       </c>
     </row>
     <row r="137" spans="1:12">
@@ -6071,28 +6095,28 @@
         <v>141</v>
       </c>
       <c r="C137" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D137" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E137" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F137" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I137" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J137">
         <v>1</v>
       </c>
       <c r="K137">
-        <v>462946.56</v>
+        <v>155407.11</v>
       </c>
       <c r="L137">
-        <v>462946.56</v>
+        <v>155407.11</v>
       </c>
     </row>
     <row r="138" spans="1:12">
@@ -6103,28 +6127,28 @@
         <v>142</v>
       </c>
       <c r="C138" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D138" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E138" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F138" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="I138" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K138">
-        <v>622170.75</v>
+        <v>302306.98</v>
       </c>
       <c r="L138">
-        <v>622170.75</v>
+        <v>604613.96</v>
       </c>
     </row>
     <row r="139" spans="1:12">
@@ -6135,28 +6159,28 @@
         <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>226</v>
+        <v>259</v>
       </c>
       <c r="D139" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="E139" t="s">
-        <v>226</v>
+        <v>259</v>
       </c>
       <c r="F139" t="s">
-        <v>226</v>
+        <v>259</v>
       </c>
       <c r="I139" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J139">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K139">
-        <v>7246.46</v>
+        <v>462946.56</v>
       </c>
       <c r="L139">
-        <v>65218.14</v>
+        <v>462946.56</v>
       </c>
     </row>
     <row r="140" spans="1:12">
@@ -6167,60 +6191,60 @@
         <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>226</v>
+        <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E140" t="s">
-        <v>226</v>
+        <v>259</v>
       </c>
       <c r="F140" t="s">
-        <v>226</v>
+        <v>259</v>
       </c>
       <c r="I140" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J140">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K140">
-        <v>9200.629999999999</v>
+        <v>622170.75</v>
       </c>
       <c r="L140">
-        <v>202413.86</v>
+        <v>622170.75</v>
       </c>
     </row>
     <row r="141" spans="1:12">
       <c r="A141" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B141" t="s">
         <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D141" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E141" t="s">
-        <v>476</v>
+        <v>229</v>
       </c>
       <c r="F141" t="s">
-        <v>476</v>
+        <v>229</v>
       </c>
       <c r="I141" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J141">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K141">
-        <v>13906.96</v>
+        <v>7246.46</v>
       </c>
       <c r="L141">
-        <v>83441.75999999999</v>
+        <v>65218.14</v>
       </c>
     </row>
     <row r="142" spans="1:12">
@@ -6231,60 +6255,60 @@
         <v>146</v>
       </c>
       <c r="C142" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="D142" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E142" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F142" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="I142" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J142">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K142">
-        <v>67728.10000000001</v>
+        <v>9200.629999999999</v>
       </c>
       <c r="L142">
-        <v>677281</v>
+        <v>202413.86</v>
       </c>
     </row>
     <row r="143" spans="1:12">
       <c r="A143" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B143" t="s">
         <v>147</v>
       </c>
       <c r="C143" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="D143" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E143" t="s">
-        <v>226</v>
+        <v>483</v>
       </c>
       <c r="F143" t="s">
-        <v>226</v>
+        <v>483</v>
       </c>
       <c r="I143" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J143">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K143">
-        <v>541166.88</v>
+        <v>13906.96</v>
       </c>
       <c r="L143">
-        <v>2164667.52</v>
+        <v>83441.75999999999</v>
       </c>
     </row>
     <row r="144" spans="1:12">
@@ -6295,60 +6319,60 @@
         <v>148</v>
       </c>
       <c r="C144" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E144" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F144" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="I144" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J144">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K144">
-        <v>31630.01</v>
+        <v>67728.10000000001</v>
       </c>
       <c r="L144">
-        <v>63260.02</v>
+        <v>677281</v>
       </c>
     </row>
     <row r="145" spans="1:12">
       <c r="A145" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B145" t="s">
         <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>258</v>
+        <v>229</v>
       </c>
       <c r="D145" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E145" t="s">
-        <v>265</v>
+        <v>229</v>
       </c>
       <c r="F145" t="s">
-        <v>265</v>
+        <v>229</v>
       </c>
       <c r="I145" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J145">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K145">
-        <v>107104.68</v>
+        <v>541166.88</v>
       </c>
       <c r="L145">
-        <v>214209.36</v>
+        <v>2164667.52</v>
       </c>
     </row>
     <row r="146" spans="1:12">
@@ -6359,92 +6383,92 @@
         <v>150</v>
       </c>
       <c r="C146" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D146" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E146" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F146" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="I146" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K146">
-        <v>221067.08</v>
+        <v>31630.01</v>
       </c>
       <c r="L146">
-        <v>221067.08</v>
+        <v>63260.02</v>
       </c>
     </row>
     <row r="147" spans="1:12">
       <c r="A147" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B147" t="s">
         <v>151</v>
       </c>
       <c r="C147" t="s">
-        <v>226</v>
+        <v>261</v>
       </c>
       <c r="D147" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E147" t="s">
-        <v>226</v>
+        <v>269</v>
       </c>
       <c r="F147" t="s">
-        <v>226</v>
+        <v>269</v>
       </c>
       <c r="I147" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K147">
-        <v>204405.71</v>
+        <v>107104.68</v>
       </c>
       <c r="L147">
-        <v>204405.71</v>
+        <v>214209.36</v>
       </c>
     </row>
     <row r="148" spans="1:12">
       <c r="A148" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B148" t="s">
         <v>152</v>
       </c>
       <c r="C148" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D148" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E148" t="s">
-        <v>476</v>
+        <v>229</v>
       </c>
       <c r="F148" t="s">
-        <v>476</v>
+        <v>229</v>
       </c>
       <c r="I148" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J148">
         <v>1</v>
       </c>
       <c r="K148">
-        <v>151612.17</v>
+        <v>221067.08</v>
       </c>
       <c r="L148">
-        <v>151612.17</v>
+        <v>221067.08</v>
       </c>
     </row>
     <row r="149" spans="1:12">
@@ -6455,60 +6479,60 @@
         <v>153</v>
       </c>
       <c r="C149" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D149" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E149" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F149" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I149" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J149">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K149">
-        <v>152565.53</v>
+        <v>204405.71</v>
       </c>
       <c r="L149">
-        <v>762827.65</v>
+        <v>204405.71</v>
       </c>
     </row>
     <row r="150" spans="1:12">
       <c r="A150" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B150" t="s">
         <v>154</v>
       </c>
       <c r="C150" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="D150" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E150" t="s">
-        <v>226</v>
+        <v>483</v>
       </c>
       <c r="F150" t="s">
-        <v>226</v>
+        <v>483</v>
       </c>
       <c r="I150" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J150">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K150">
-        <v>648344.71</v>
+        <v>151612.17</v>
       </c>
       <c r="L150">
-        <v>1945034.13</v>
+        <v>151612.17</v>
       </c>
     </row>
     <row r="151" spans="1:12">
@@ -6519,28 +6543,28 @@
         <v>155</v>
       </c>
       <c r="C151" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D151" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E151" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F151" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="I151" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J151">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K151">
-        <v>61274.69</v>
+        <v>152565.53</v>
       </c>
       <c r="L151">
-        <v>245098.76</v>
+        <v>762827.65</v>
       </c>
     </row>
     <row r="152" spans="1:12">
@@ -6551,60 +6575,60 @@
         <v>156</v>
       </c>
       <c r="C152" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D152" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E152" t="s">
-        <v>474</v>
+        <v>229</v>
       </c>
       <c r="F152" t="s">
-        <v>474</v>
+        <v>229</v>
       </c>
       <c r="I152" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J152">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K152">
-        <v>134461.16</v>
+        <v>648344.71</v>
       </c>
       <c r="L152">
-        <v>134461.16</v>
+        <v>1945034.13</v>
       </c>
     </row>
     <row r="153" spans="1:12">
       <c r="A153" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B153" t="s">
         <v>157</v>
       </c>
       <c r="C153" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D153" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="E153" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F153" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="I153" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J153">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K153">
-        <v>150000</v>
+        <v>61274.69</v>
       </c>
       <c r="L153">
-        <v>150000</v>
+        <v>245098.76</v>
       </c>
     </row>
     <row r="154" spans="1:12">
@@ -6615,60 +6639,60 @@
         <v>158</v>
       </c>
       <c r="C154" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="D154" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E154" t="s">
-        <v>226</v>
+        <v>481</v>
       </c>
       <c r="F154" t="s">
-        <v>226</v>
+        <v>481</v>
       </c>
       <c r="I154" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J154">
         <v>1</v>
       </c>
       <c r="K154">
-        <v>437278.29</v>
+        <v>134461.16</v>
       </c>
       <c r="L154">
-        <v>437278.29</v>
+        <v>134461.16</v>
       </c>
     </row>
     <row r="155" spans="1:12">
       <c r="A155" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B155" t="s">
         <v>159</v>
       </c>
       <c r="C155" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D155" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E155" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F155" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="I155" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J155">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K155">
-        <v>68988.75999999999</v>
+        <v>150000</v>
       </c>
       <c r="L155">
-        <v>689887.6</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="156" spans="1:12">
@@ -6679,188 +6703,188 @@
         <v>160</v>
       </c>
       <c r="C156" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D156" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="E156" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F156" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I156" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J156">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K156">
-        <v>321061.61</v>
+        <v>437278.29</v>
       </c>
       <c r="L156">
-        <v>642123.22</v>
+        <v>437278.29</v>
       </c>
     </row>
     <row r="157" spans="1:12">
       <c r="A157" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B157" t="s">
         <v>161</v>
       </c>
       <c r="C157" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D157" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E157" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F157" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="I157" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J157">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K157">
-        <v>86292.41</v>
+        <v>68988.75999999999</v>
       </c>
       <c r="L157">
-        <v>86292.41</v>
+        <v>689887.6</v>
       </c>
     </row>
     <row r="158" spans="1:12">
       <c r="A158" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B158" t="s">
         <v>162</v>
       </c>
       <c r="C158" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D158" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E158" t="s">
-        <v>476</v>
+        <v>229</v>
       </c>
       <c r="F158" t="s">
-        <v>476</v>
+        <v>229</v>
       </c>
       <c r="I158" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J158">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K158">
-        <v>275914.15</v>
+        <v>321061.61</v>
       </c>
       <c r="L158">
-        <v>827742.45</v>
+        <v>642123.22</v>
       </c>
     </row>
     <row r="159" spans="1:12">
       <c r="A159" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B159" t="s">
         <v>163</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="D159" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E159" t="s">
-        <v>477</v>
+        <v>236</v>
       </c>
       <c r="F159" t="s">
-        <v>477</v>
+        <v>236</v>
       </c>
       <c r="I159" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J159">
         <v>1</v>
       </c>
       <c r="K159">
-        <v>145438.64</v>
+        <v>86292.41</v>
       </c>
       <c r="L159">
-        <v>145438.64</v>
+        <v>86292.41</v>
       </c>
     </row>
     <row r="160" spans="1:12">
       <c r="A160" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B160" t="s">
         <v>164</v>
       </c>
       <c r="C160" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D160" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E160" t="s">
-        <v>233</v>
+        <v>483</v>
       </c>
       <c r="F160" t="s">
-        <v>233</v>
+        <v>483</v>
       </c>
       <c r="I160" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J160">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="K160">
-        <v>124259.74</v>
+        <v>275914.15</v>
       </c>
       <c r="L160">
-        <v>1988155.84</v>
+        <v>827742.45</v>
       </c>
     </row>
     <row r="161" spans="1:12">
       <c r="A161" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B161" t="s">
         <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="D161" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="E161" t="s">
-        <v>246</v>
+        <v>484</v>
       </c>
       <c r="F161" t="s">
-        <v>246</v>
+        <v>484</v>
       </c>
       <c r="I161" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J161">
         <v>1</v>
       </c>
       <c r="K161">
-        <v>127385.01</v>
+        <v>145438.64</v>
       </c>
       <c r="L161">
-        <v>127385.01</v>
+        <v>145438.64</v>
       </c>
     </row>
     <row r="162" spans="1:12">
@@ -6871,28 +6895,28 @@
         <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D162" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E162" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F162" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="I162" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J162">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K162">
-        <v>409485.91</v>
+        <v>124259.74</v>
       </c>
       <c r="L162">
-        <v>818971.8199999999</v>
+        <v>1988155.84</v>
       </c>
     </row>
     <row r="163" spans="1:12">
@@ -6903,28 +6927,28 @@
         <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="D163" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E163" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="F163" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="I163" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J163">
         <v>1</v>
       </c>
       <c r="K163">
-        <v>411573.74</v>
+        <v>127385.01</v>
       </c>
       <c r="L163">
-        <v>411573.74</v>
+        <v>127385.01</v>
       </c>
     </row>
     <row r="164" spans="1:12">
@@ -6935,60 +6959,60 @@
         <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="D164" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E164" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="F164" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="I164" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J164">
         <v>2</v>
       </c>
       <c r="K164">
-        <v>177929.28</v>
+        <v>409485.91</v>
       </c>
       <c r="L164">
-        <v>355858.56</v>
+        <v>818971.8199999999</v>
       </c>
     </row>
     <row r="165" spans="1:12">
       <c r="A165" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B165" t="s">
         <v>169</v>
       </c>
       <c r="C165" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="D165" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E165" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="F165" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="I165" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J165">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K165">
-        <v>386975.07</v>
+        <v>411573.74</v>
       </c>
       <c r="L165">
-        <v>773950.14</v>
+        <v>411573.74</v>
       </c>
     </row>
     <row r="166" spans="1:12">
@@ -6999,28 +7023,28 @@
         <v>170</v>
       </c>
       <c r="C166" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="D166" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E166" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="F166" t="s">
-        <v>478</v>
+        <v>241</v>
       </c>
       <c r="I166" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J166">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K166">
-        <v>66983.8</v>
+        <v>177929.28</v>
       </c>
       <c r="L166">
-        <v>267935.2</v>
+        <v>355858.56</v>
       </c>
     </row>
     <row r="167" spans="1:12">
@@ -7031,284 +7055,284 @@
         <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="D167" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E167" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="F167" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="I167" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J167">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K167">
-        <v>159709.51</v>
+        <v>386975.07</v>
       </c>
       <c r="L167">
-        <v>159709.51</v>
+        <v>773950.14</v>
       </c>
     </row>
     <row r="168" spans="1:12">
       <c r="A168" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B168" t="s">
         <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D168" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E168" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F168" t="s">
-        <v>226</v>
+        <v>486</v>
       </c>
       <c r="I168" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J168">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="K168">
-        <v>2473.41</v>
+        <v>66983.8</v>
       </c>
       <c r="L168">
-        <v>93989.58</v>
+        <v>267935.2</v>
       </c>
     </row>
     <row r="169" spans="1:12">
       <c r="A169" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B169" t="s">
         <v>173</v>
       </c>
       <c r="C169" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E169" t="s">
-        <v>476</v>
+        <v>259</v>
       </c>
       <c r="F169" t="s">
-        <v>476</v>
+        <v>259</v>
       </c>
       <c r="I169" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J169">
         <v>1</v>
       </c>
       <c r="K169">
-        <v>636180.6800000001</v>
+        <v>159709.51</v>
       </c>
       <c r="L169">
-        <v>636180.6800000001</v>
+        <v>159709.51</v>
       </c>
     </row>
     <row r="170" spans="1:12">
       <c r="A170" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B170" t="s">
         <v>174</v>
       </c>
       <c r="C170" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D170" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E170" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F170" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I170" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J170">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="K170">
-        <v>27987.95</v>
+        <v>2473.41</v>
       </c>
       <c r="L170">
-        <v>83963.85000000001</v>
+        <v>93989.58</v>
       </c>
     </row>
     <row r="171" spans="1:12">
       <c r="A171" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B171" t="s">
         <v>175</v>
       </c>
       <c r="C171" t="s">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="D171" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="E171" t="s">
-        <v>261</v>
+        <v>483</v>
       </c>
       <c r="F171" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="I171" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J171">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K171">
-        <v>274730.29</v>
+        <v>636180.6800000001</v>
       </c>
       <c r="L171">
-        <v>2747302.9</v>
+        <v>636180.6800000001</v>
       </c>
     </row>
     <row r="172" spans="1:12">
       <c r="A172" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B172" t="s">
         <v>176</v>
       </c>
       <c r="C172" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D172" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="E172" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F172" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I172" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J172">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K172">
-        <v>5073.44</v>
+        <v>27987.95</v>
       </c>
       <c r="L172">
-        <v>50734.4</v>
+        <v>83963.85000000001</v>
       </c>
     </row>
     <row r="173" spans="1:12">
       <c r="A173" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B173" t="s">
         <v>177</v>
       </c>
       <c r="C173" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="D173" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="E173" t="s">
-        <v>231</v>
+        <v>264</v>
       </c>
       <c r="F173" t="s">
-        <v>231</v>
+        <v>487</v>
       </c>
       <c r="I173" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J173">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K173">
-        <v>271098.72</v>
+        <v>274730.29</v>
       </c>
       <c r="L173">
-        <v>1626592.32</v>
+        <v>2747302.9</v>
       </c>
     </row>
     <row r="174" spans="1:12">
       <c r="A174" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B174" t="s">
         <v>178</v>
       </c>
       <c r="C174" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D174" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E174" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F174" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="I174" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J174">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K174">
-        <v>21390.12</v>
+        <v>5073.44</v>
       </c>
       <c r="L174">
-        <v>171120.96</v>
+        <v>50734.4</v>
       </c>
     </row>
     <row r="175" spans="1:12">
       <c r="A175" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B175" t="s">
         <v>179</v>
       </c>
       <c r="C175" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="D175" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E175" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F175" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="I175" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J175">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K175">
-        <v>325882.63</v>
+        <v>271098.72</v>
       </c>
       <c r="L175">
-        <v>325882.63</v>
+        <v>1626592.32</v>
       </c>
     </row>
     <row r="176" spans="1:12">
@@ -7319,28 +7343,28 @@
         <v>180</v>
       </c>
       <c r="C176" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D176" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="E176" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F176" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="I176" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J176">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K176">
-        <v>66789.11</v>
+        <v>21390.12</v>
       </c>
       <c r="L176">
-        <v>133578.22</v>
+        <v>171120.96</v>
       </c>
     </row>
     <row r="177" spans="1:12">
@@ -7351,28 +7375,28 @@
         <v>181</v>
       </c>
       <c r="C177" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="D177" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E177" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F177" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="I177" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J177">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K177">
-        <v>78468.91</v>
+        <v>325882.63</v>
       </c>
       <c r="L177">
-        <v>235406.73</v>
+        <v>325882.63</v>
       </c>
     </row>
     <row r="178" spans="1:12">
@@ -7383,28 +7407,28 @@
         <v>182</v>
       </c>
       <c r="C178" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D178" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E178" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F178" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I178" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J178">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K178">
-        <v>263646.09</v>
+        <v>66789.11</v>
       </c>
       <c r="L178">
-        <v>790938.27</v>
+        <v>133578.22</v>
       </c>
     </row>
     <row r="179" spans="1:12">
@@ -7415,28 +7439,28 @@
         <v>183</v>
       </c>
       <c r="C179" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D179" t="s">
-        <v>336</v>
+        <v>438</v>
       </c>
       <c r="E179" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F179" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="I179" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J179">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K179">
-        <v>271387.84</v>
+        <v>78468.91</v>
       </c>
       <c r="L179">
-        <v>542775.6800000001</v>
+        <v>235406.73</v>
       </c>
     </row>
     <row r="180" spans="1:12">
@@ -7447,60 +7471,60 @@
         <v>184</v>
       </c>
       <c r="C180" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D180" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="E180" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F180" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="I180" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J180">
         <v>3</v>
       </c>
       <c r="K180">
-        <v>73037.78999999999</v>
+        <v>263646.09</v>
       </c>
       <c r="L180">
-        <v>219113.37</v>
+        <v>790938.27</v>
       </c>
     </row>
     <row r="181" spans="1:12">
       <c r="A181" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B181" t="s">
         <v>185</v>
       </c>
       <c r="C181" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D181" t="s">
-        <v>435</v>
+        <v>341</v>
       </c>
       <c r="E181" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F181" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="I181" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J181">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K181">
-        <v>7049.74</v>
+        <v>271387.84</v>
       </c>
       <c r="L181">
-        <v>98696.36</v>
+        <v>542775.6800000001</v>
       </c>
     </row>
     <row r="182" spans="1:12">
@@ -7511,60 +7535,60 @@
         <v>186</v>
       </c>
       <c r="C182" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D182" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E182" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F182" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="I182" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J182">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K182">
-        <v>73190.35000000001</v>
+        <v>73037.78999999999</v>
       </c>
       <c r="L182">
-        <v>805093.85</v>
+        <v>219113.37</v>
       </c>
     </row>
     <row r="183" spans="1:12">
       <c r="A183" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B183" t="s">
         <v>187</v>
       </c>
       <c r="C183" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="D183" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E183" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="F183" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="I183" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J183">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K183">
-        <v>128859.45</v>
+        <v>7049.74</v>
       </c>
       <c r="L183">
-        <v>257718.9</v>
+        <v>98696.36</v>
       </c>
     </row>
     <row r="184" spans="1:12">
@@ -7575,28 +7599,28 @@
         <v>188</v>
       </c>
       <c r="C184" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D184" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E184" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="F184" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="I184" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J184">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K184">
-        <v>451021.21</v>
+        <v>73190.35000000001</v>
       </c>
       <c r="L184">
-        <v>451021.21</v>
+        <v>805093.85</v>
       </c>
     </row>
     <row r="185" spans="1:12">
@@ -7607,28 +7631,28 @@
         <v>189</v>
       </c>
       <c r="C185" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="D185" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E185" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="F185" t="s">
-        <v>478</v>
+        <v>249</v>
       </c>
       <c r="I185" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J185">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K185">
-        <v>76547.52</v>
+        <v>128859.45</v>
       </c>
       <c r="L185">
-        <v>229642.56</v>
+        <v>257718.9</v>
       </c>
     </row>
     <row r="186" spans="1:12">
@@ -7639,28 +7663,28 @@
         <v>190</v>
       </c>
       <c r="C186" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="D186" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E186" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="F186" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="I186" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J186">
         <v>1</v>
       </c>
       <c r="K186">
-        <v>116937.56</v>
+        <v>451021.21</v>
       </c>
       <c r="L186">
-        <v>116937.56</v>
+        <v>451021.21</v>
       </c>
     </row>
     <row r="187" spans="1:12">
@@ -7671,60 +7695,60 @@
         <v>191</v>
       </c>
       <c r="C187" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D187" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E187" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F187" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="I187" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J187">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K187">
-        <v>98083.52</v>
+        <v>76547.52</v>
       </c>
       <c r="L187">
-        <v>686584.64</v>
+        <v>229642.56</v>
       </c>
     </row>
     <row r="188" spans="1:12">
       <c r="A188" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B188" t="s">
         <v>192</v>
       </c>
       <c r="C188" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="D188" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E188" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="F188" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="I188" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J188">
         <v>1</v>
       </c>
       <c r="K188">
-        <v>167744.87</v>
+        <v>116937.56</v>
       </c>
       <c r="L188">
-        <v>167744.87</v>
+        <v>116937.56</v>
       </c>
     </row>
     <row r="189" spans="1:12">
@@ -7735,60 +7759,60 @@
         <v>193</v>
       </c>
       <c r="C189" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="D189" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E189" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="F189" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="I189" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J189">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K189">
-        <v>23661.7</v>
+        <v>98083.52</v>
       </c>
       <c r="L189">
-        <v>141970.2</v>
+        <v>686584.64</v>
       </c>
     </row>
     <row r="190" spans="1:12">
       <c r="A190" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B190" t="s">
         <v>194</v>
       </c>
       <c r="C190" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D190" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E190" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="F190" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="I190" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J190">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K190">
-        <v>20116.83</v>
+        <v>167744.87</v>
       </c>
       <c r="L190">
-        <v>120700.98</v>
+        <v>167744.87</v>
       </c>
     </row>
     <row r="191" spans="1:12">
@@ -7799,28 +7823,28 @@
         <v>195</v>
       </c>
       <c r="C191" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="D191" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E191" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="F191" t="s">
-        <v>233</v>
+        <v>488</v>
       </c>
       <c r="I191" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J191">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K191">
-        <v>60010.35</v>
+        <v>23661.7</v>
       </c>
       <c r="L191">
-        <v>240041.4</v>
+        <v>141970.2</v>
       </c>
     </row>
     <row r="192" spans="1:12">
@@ -7831,28 +7855,28 @@
         <v>196</v>
       </c>
       <c r="C192" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D192" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E192" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F192" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="I192" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J192">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K192">
-        <v>100496.28</v>
+        <v>20116.83</v>
       </c>
       <c r="L192">
-        <v>200992.56</v>
+        <v>120700.98</v>
       </c>
     </row>
     <row r="193" spans="1:12">
@@ -7863,28 +7887,28 @@
         <v>197</v>
       </c>
       <c r="C193" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D193" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="E193" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F193" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="I193" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J193">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="K193">
-        <v>10684.18</v>
+        <v>60010.35</v>
       </c>
       <c r="L193">
-        <v>427367.2</v>
+        <v>240041.4</v>
       </c>
     </row>
     <row r="194" spans="1:12">
@@ -7895,28 +7919,28 @@
         <v>198</v>
       </c>
       <c r="C194" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D194" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E194" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F194" t="s">
-        <v>478</v>
+        <v>236</v>
       </c>
       <c r="I194" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J194">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K194">
-        <v>128320.65</v>
+        <v>100496.28</v>
       </c>
       <c r="L194">
-        <v>128320.65</v>
+        <v>200992.56</v>
       </c>
     </row>
     <row r="195" spans="1:12">
@@ -7927,28 +7951,28 @@
         <v>199</v>
       </c>
       <c r="C195" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D195" t="s">
-        <v>352</v>
+        <v>453</v>
       </c>
       <c r="E195" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F195" t="s">
-        <v>478</v>
+        <v>236</v>
       </c>
       <c r="I195" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J195">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="K195">
-        <v>156649.71</v>
+        <v>10684.18</v>
       </c>
       <c r="L195">
-        <v>939898.26</v>
+        <v>427367.2</v>
       </c>
     </row>
     <row r="196" spans="1:12">
@@ -7959,28 +7983,28 @@
         <v>200</v>
       </c>
       <c r="C196" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D196" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="E196" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F196" t="s">
-        <v>233</v>
+        <v>486</v>
       </c>
       <c r="I196" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J196">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K196">
-        <v>92193.81</v>
+        <v>128320.65</v>
       </c>
       <c r="L196">
-        <v>184387.62</v>
+        <v>128320.65</v>
       </c>
     </row>
     <row r="197" spans="1:12">
@@ -7991,60 +8015,60 @@
         <v>201</v>
       </c>
       <c r="C197" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D197" t="s">
-        <v>450</v>
+        <v>357</v>
       </c>
       <c r="E197" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F197" t="s">
-        <v>226</v>
+        <v>486</v>
       </c>
       <c r="I197" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J197">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K197">
-        <v>99834.53</v>
+        <v>156649.71</v>
       </c>
       <c r="L197">
-        <v>1098179.83</v>
+        <v>939898.26</v>
       </c>
     </row>
     <row r="198" spans="1:12">
       <c r="A198" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B198" t="s">
         <v>202</v>
       </c>
       <c r="C198" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D198" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="E198" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F198" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I198" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J198">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K198">
-        <v>24129.88</v>
+        <v>92193.81</v>
       </c>
       <c r="L198">
-        <v>144779.28</v>
+        <v>184387.62</v>
       </c>
     </row>
     <row r="199" spans="1:12">
@@ -8055,28 +8079,28 @@
         <v>203</v>
       </c>
       <c r="C199" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D199" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="E199" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F199" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="I199" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J199">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K199">
-        <v>477767.5</v>
+        <v>99834.53</v>
       </c>
       <c r="L199">
-        <v>477767.5</v>
+        <v>1098179.83</v>
       </c>
     </row>
     <row r="200" spans="1:12">
@@ -8087,28 +8111,28 @@
         <v>204</v>
       </c>
       <c r="C200" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D200" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E200" t="s">
-        <v>265</v>
+        <v>485</v>
       </c>
       <c r="F200" t="s">
-        <v>265</v>
+        <v>485</v>
       </c>
       <c r="I200" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J200">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K200">
-        <v>119118.65</v>
+        <v>24129.88</v>
       </c>
       <c r="L200">
-        <v>476474.6</v>
+        <v>144779.28</v>
       </c>
     </row>
     <row r="201" spans="1:12">
@@ -8119,28 +8143,28 @@
         <v>205</v>
       </c>
       <c r="C201" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D201" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E201" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F201" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="I201" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J201">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K201">
-        <v>12254.05</v>
+        <v>477767.5</v>
       </c>
       <c r="L201">
-        <v>134794.55</v>
+        <v>477767.5</v>
       </c>
     </row>
     <row r="202" spans="1:12">
@@ -8151,28 +8175,28 @@
         <v>206</v>
       </c>
       <c r="C202" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="D202" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E202" t="s">
-        <v>231</v>
+        <v>269</v>
       </c>
       <c r="F202" t="s">
-        <v>231</v>
+        <v>269</v>
       </c>
       <c r="I202" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J202">
-        <v>97</v>
+        <v>4</v>
       </c>
       <c r="K202">
-        <v>2043.59</v>
+        <v>119118.65</v>
       </c>
       <c r="L202">
-        <v>198228.23</v>
+        <v>476474.6</v>
       </c>
     </row>
     <row r="203" spans="1:12">
@@ -8183,60 +8207,60 @@
         <v>207</v>
       </c>
       <c r="C203" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D203" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E203" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F203" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="I203" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J203">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K203">
-        <v>57019.29</v>
+        <v>12254.05</v>
       </c>
       <c r="L203">
-        <v>114038.58</v>
+        <v>134794.55</v>
       </c>
     </row>
     <row r="204" spans="1:12">
       <c r="A204" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B204" t="s">
         <v>208</v>
       </c>
       <c r="C204" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D204" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E204" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F204" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="I204" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J204">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="K204">
-        <v>54790.74</v>
+        <v>2043.59</v>
       </c>
       <c r="L204">
-        <v>219162.96</v>
+        <v>198228.23</v>
       </c>
     </row>
     <row r="205" spans="1:12">
@@ -8247,124 +8271,124 @@
         <v>209</v>
       </c>
       <c r="C205" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D205" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="E205" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F205" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="I205" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J205">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K205">
-        <v>276872.24</v>
+        <v>57019.29</v>
       </c>
       <c r="L205">
-        <v>276872.24</v>
+        <v>114038.58</v>
       </c>
     </row>
     <row r="206" spans="1:12">
       <c r="A206" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B206" t="s">
         <v>210</v>
       </c>
       <c r="C206" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D206" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E206" t="s">
-        <v>476</v>
+        <v>229</v>
       </c>
       <c r="F206" t="s">
-        <v>476</v>
+        <v>229</v>
       </c>
       <c r="I206" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J206">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K206">
-        <v>228580.22</v>
+        <v>54790.74</v>
       </c>
       <c r="L206">
-        <v>228580.22</v>
+        <v>219162.96</v>
       </c>
     </row>
     <row r="207" spans="1:12">
       <c r="A207" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B207" t="s">
         <v>211</v>
       </c>
       <c r="C207" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D207" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="E207" t="s">
-        <v>476</v>
+        <v>236</v>
       </c>
       <c r="F207" t="s">
-        <v>476</v>
+        <v>236</v>
       </c>
       <c r="I207" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J207">
         <v>1</v>
       </c>
       <c r="K207">
-        <v>588448.45</v>
+        <v>276872.24</v>
       </c>
       <c r="L207">
-        <v>588448.45</v>
+        <v>276872.24</v>
       </c>
     </row>
     <row r="208" spans="1:12">
       <c r="A208" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B208" t="s">
         <v>212</v>
       </c>
       <c r="C208" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="D208" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E208" t="s">
-        <v>226</v>
+        <v>483</v>
       </c>
       <c r="F208" t="s">
-        <v>226</v>
+        <v>483</v>
       </c>
       <c r="I208" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J208">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K208">
-        <v>171904.24</v>
+        <v>228580.22</v>
       </c>
       <c r="L208">
-        <v>343808.48</v>
+        <v>228580.22</v>
       </c>
     </row>
     <row r="209" spans="1:12">
@@ -8375,28 +8399,28 @@
         <v>213</v>
       </c>
       <c r="C209" t="s">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="D209" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="E209" t="s">
-        <v>265</v>
+        <v>483</v>
       </c>
       <c r="F209" t="s">
-        <v>265</v>
+        <v>483</v>
       </c>
       <c r="I209" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J209">
         <v>1</v>
       </c>
       <c r="K209">
-        <v>52120.37</v>
+        <v>588448.45</v>
       </c>
       <c r="L209">
-        <v>52120.37</v>
+        <v>588448.45</v>
       </c>
     </row>
     <row r="210" spans="1:12">
@@ -8407,28 +8431,28 @@
         <v>214</v>
       </c>
       <c r="C210" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D210" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="E210" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F210" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I210" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J210">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K210">
-        <v>907492.78</v>
+        <v>171904.24</v>
       </c>
       <c r="L210">
-        <v>907492.78</v>
+        <v>343808.48</v>
       </c>
     </row>
     <row r="211" spans="1:12">
@@ -8439,124 +8463,124 @@
         <v>215</v>
       </c>
       <c r="C211" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D211" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E211" t="s">
-        <v>476</v>
+        <v>269</v>
       </c>
       <c r="F211" t="s">
-        <v>476</v>
+        <v>269</v>
       </c>
       <c r="I211" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J211">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K211">
-        <v>118001.73</v>
+        <v>52120.37</v>
       </c>
       <c r="L211">
-        <v>236003.46</v>
+        <v>52120.37</v>
       </c>
     </row>
     <row r="212" spans="1:12">
       <c r="A212" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B212" t="s">
         <v>216</v>
       </c>
       <c r="C212" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
       <c r="D212" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="E212" t="s">
-        <v>476</v>
+        <v>229</v>
       </c>
       <c r="F212" t="s">
-        <v>476</v>
+        <v>229</v>
       </c>
       <c r="I212" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J212">
         <v>1</v>
       </c>
       <c r="K212">
-        <v>56470.99</v>
+        <v>907492.78</v>
       </c>
       <c r="L212">
-        <v>56470.99</v>
+        <v>907492.78</v>
       </c>
     </row>
     <row r="213" spans="1:12">
       <c r="A213" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B213" t="s">
         <v>217</v>
       </c>
       <c r="C213" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="D213" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E213" t="s">
-        <v>233</v>
+        <v>483</v>
       </c>
       <c r="F213" t="s">
-        <v>233</v>
+        <v>483</v>
       </c>
       <c r="I213" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J213">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K213">
-        <v>20316.27</v>
+        <v>118001.73</v>
       </c>
       <c r="L213">
-        <v>121897.62</v>
+        <v>236003.46</v>
       </c>
     </row>
     <row r="214" spans="1:12">
       <c r="A214" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B214" t="s">
         <v>218</v>
       </c>
       <c r="C214" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D214" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="E214" t="s">
-        <v>226</v>
+        <v>483</v>
       </c>
       <c r="F214" t="s">
-        <v>226</v>
+        <v>483</v>
       </c>
       <c r="I214" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J214">
         <v>1</v>
       </c>
       <c r="K214">
-        <v>64719.29</v>
+        <v>56470.99</v>
       </c>
       <c r="L214">
-        <v>64719.29</v>
+        <v>56470.99</v>
       </c>
     </row>
     <row r="215" spans="1:12">
@@ -8567,28 +8591,28 @@
         <v>219</v>
       </c>
       <c r="C215" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D215" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="E215" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F215" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="I215" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J215">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K215">
-        <v>15431.69</v>
+        <v>20316.27</v>
       </c>
       <c r="L215">
-        <v>77158.45</v>
+        <v>121897.62</v>
       </c>
     </row>
     <row r="216" spans="1:12">
@@ -8599,28 +8623,28 @@
         <v>220</v>
       </c>
       <c r="C216" t="s">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="D216" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="E216" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F216" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I216" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J216">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K216">
-        <v>2999.26</v>
+        <v>64719.29</v>
       </c>
       <c r="L216">
-        <v>68982.98</v>
+        <v>64719.29</v>
       </c>
     </row>
     <row r="217" spans="1:12">
@@ -8631,92 +8655,92 @@
         <v>221</v>
       </c>
       <c r="C217" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="D217" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E217" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="F217" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="I217" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J217">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K217">
-        <v>40143.73</v>
+        <v>15431.69</v>
       </c>
       <c r="L217">
-        <v>160574.92</v>
+        <v>77158.45</v>
       </c>
     </row>
     <row r="218" spans="1:12">
       <c r="A218" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B218" t="s">
         <v>222</v>
       </c>
       <c r="C218" t="s">
-        <v>261</v>
+        <v>229</v>
       </c>
       <c r="D218" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="E218" t="s">
-        <v>261</v>
+        <v>229</v>
       </c>
       <c r="F218" t="s">
-        <v>479</v>
+        <v>229</v>
       </c>
       <c r="I218" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J218">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="K218">
-        <v>259475.34</v>
+        <v>2999.26</v>
       </c>
       <c r="L218">
-        <v>259475.34</v>
+        <v>68982.98</v>
       </c>
     </row>
     <row r="219" spans="1:12">
       <c r="A219" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B219" t="s">
         <v>223</v>
       </c>
       <c r="C219" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D219" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E219" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F219" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I219" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J219">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K219">
-        <v>112000</v>
+        <v>40143.73</v>
       </c>
       <c r="L219">
-        <v>224000</v>
+        <v>160574.92</v>
       </c>
     </row>
     <row r="220" spans="1:12">
@@ -8727,28 +8751,124 @@
         <v>224</v>
       </c>
       <c r="C220" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="E220" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F220" t="s">
-        <v>266</v>
+        <v>487</v>
       </c>
       <c r="I220" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="J220">
+        <v>1</v>
+      </c>
+      <c r="K220">
+        <v>259475.34</v>
+      </c>
+      <c r="L220">
+        <v>259475.34</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12">
+      <c r="A221" t="s">
+        <v>13</v>
+      </c>
+      <c r="B221" t="s">
+        <v>225</v>
+      </c>
+      <c r="C221" t="s">
+        <v>269</v>
+      </c>
+      <c r="D221" t="s">
+        <v>478</v>
+      </c>
+      <c r="E221" t="s">
+        <v>269</v>
+      </c>
+      <c r="F221" t="s">
+        <v>269</v>
+      </c>
+      <c r="I221" t="s">
+        <v>489</v>
+      </c>
+      <c r="J221">
+        <v>2</v>
+      </c>
+      <c r="K221">
+        <v>112000</v>
+      </c>
+      <c r="L221">
+        <v>224000</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12">
+      <c r="A222" t="s">
+        <v>13</v>
+      </c>
+      <c r="B222" t="s">
+        <v>226</v>
+      </c>
+      <c r="C222" t="s">
+        <v>270</v>
+      </c>
+      <c r="D222" t="s">
+        <v>479</v>
+      </c>
+      <c r="E222" t="s">
+        <v>270</v>
+      </c>
+      <c r="F222" t="s">
+        <v>270</v>
+      </c>
+      <c r="I222" t="s">
+        <v>489</v>
+      </c>
+      <c r="J222">
         <v>6</v>
       </c>
-      <c r="K220">
+      <c r="K222">
         <v>128205</v>
       </c>
-      <c r="L220">
+      <c r="L222">
         <v>769230</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12">
+      <c r="A223" t="s">
+        <v>12</v>
+      </c>
+      <c r="B223" t="s">
+        <v>227</v>
+      </c>
+      <c r="C223" t="s">
+        <v>229</v>
+      </c>
+      <c r="D223" t="s">
+        <v>480</v>
+      </c>
+      <c r="E223" t="s">
+        <v>229</v>
+      </c>
+      <c r="F223" t="s">
+        <v>229</v>
+      </c>
+      <c r="I223" t="s">
+        <v>489</v>
+      </c>
+      <c r="J223">
+        <v>2</v>
+      </c>
+      <c r="K223">
+        <v>64638.73</v>
+      </c>
+      <c r="L223">
+        <v>129277.46</v>
       </c>
     </row>
   </sheetData>

--- a/VALORIZADO FALTANTES.xlsx
+++ b/VALORIZADO FALTANTES.xlsx
@@ -1501,13 +1501,13 @@
     <t>Valorizado</t>
   </si>
   <si>
-    <t>Período: 31/01/2026 07:42:40</t>
+    <t>Período: 31/01/2026 08:56:04</t>
   </si>
   <si>
     <t>COLGAAP</t>
   </si>
   <si>
-    <t>Fecha y hora de generación: 09/01/2026 07:43:12</t>
+    <t>Fecha y hora de generación: 19/01/2026 08:56:22</t>
   </si>
 </sst>
 </file>
